--- a/content/xls/DB_01.01.2026_NP.xlsx
+++ b/content/xls/DB_01.01.2026_NP.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Python\InfPanel\content\xls\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Python\InfPanel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44C4C654-90BC-4E16-88DD-D1255B2A4C3B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F3157E9-B3A1-4FBD-A1CF-CD361A72361F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-111" yWindow="-111" windowWidth="31729" windowHeight="17342" xr2:uid="{CD9FBE00-C105-441E-AC9D-D16C82556AEE}"/>
   </bookViews>
@@ -3151,7 +3151,7 @@
         <v>846</v>
       </c>
       <c r="D2" s="3">
-        <f t="shared" ref="D2:D65" si="0">100%-F2</f>
+        <f>100%-F2</f>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E2" s="4">
@@ -3193,7 +3193,7 @@
         <v>100</v>
       </c>
       <c r="D3" s="3">
-        <f t="shared" si="0"/>
+        <f>100%-F3</f>
         <v>0.30000000000000004</v>
       </c>
       <c r="E3" s="4">
@@ -3235,7 +3235,7 @@
         <v>497</v>
       </c>
       <c r="D4" s="3">
-        <f t="shared" si="0"/>
+        <f>100%-F4</f>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="E4" s="4">
@@ -3277,7 +3277,7 @@
         <v>160</v>
       </c>
       <c r="D5" s="3">
-        <f t="shared" si="0"/>
+        <f>100%-F5</f>
         <v>0.18000000000000005</v>
       </c>
       <c r="E5" s="4">
@@ -3319,7 +3319,7 @@
         <v>591</v>
       </c>
       <c r="D6" s="3">
-        <f t="shared" si="0"/>
+        <f>100%-F6</f>
         <v>0</v>
       </c>
       <c r="E6" s="4">
@@ -3361,7 +3361,7 @@
         <v>346</v>
       </c>
       <c r="D7" s="3">
-        <f t="shared" si="0"/>
+        <f>100%-F7</f>
         <v>0.30000000000000004</v>
       </c>
       <c r="E7" s="4">
@@ -3403,7 +3403,7 @@
         <v>295</v>
       </c>
       <c r="D8" s="3">
-        <f t="shared" si="0"/>
+        <f>100%-F8</f>
         <v>0.44999999999999996</v>
       </c>
       <c r="E8" s="4">
@@ -3445,7 +3445,7 @@
         <v>791</v>
       </c>
       <c r="D9" s="3">
-        <f t="shared" si="0"/>
+        <f>100%-F9</f>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="E9" s="4">
@@ -3487,7 +3487,7 @@
         <v>419</v>
       </c>
       <c r="D10" s="3">
-        <f t="shared" si="0"/>
+        <f>100%-F10</f>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E10" s="4">
@@ -3529,7 +3529,7 @@
         <v>213</v>
       </c>
       <c r="D11" s="3">
-        <f t="shared" si="0"/>
+        <f>100%-F11</f>
         <v>0.37</v>
       </c>
       <c r="E11" s="4">
@@ -3571,7 +3571,7 @@
         <v>146</v>
       </c>
       <c r="D12" s="3">
-        <f t="shared" si="0"/>
+        <f>100%-F12</f>
         <v>0.44999999999999996</v>
       </c>
       <c r="E12" s="4">
@@ -3613,7 +3613,7 @@
         <v>477</v>
       </c>
       <c r="D13" s="3">
-        <f t="shared" si="0"/>
+        <f>100%-F13</f>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="E13" s="4">
@@ -3652,10 +3652,10 @@
         <v>15</v>
       </c>
       <c r="C14" s="2">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D14" s="3">
-        <f t="shared" si="0"/>
+        <f>100%-F14</f>
         <v>0.37</v>
       </c>
       <c r="E14" s="4">
@@ -3697,7 +3697,7 @@
         <v>576</v>
       </c>
       <c r="D15" s="3">
-        <f t="shared" si="0"/>
+        <f>100%-F15</f>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E15" s="4">
@@ -3739,7 +3739,7 @@
         <v>553</v>
       </c>
       <c r="D16" s="3">
-        <f t="shared" si="0"/>
+        <f>100%-F16</f>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E16" s="4">
@@ -3781,7 +3781,7 @@
         <v>182</v>
       </c>
       <c r="D17" s="3">
-        <f t="shared" si="0"/>
+        <f>100%-F17</f>
         <v>0.30000000000000004</v>
       </c>
       <c r="E17" s="4">
@@ -3823,7 +3823,7 @@
         <v>101</v>
       </c>
       <c r="D18" s="3">
-        <f t="shared" si="0"/>
+        <f>100%-F18</f>
         <v>0.30000000000000004</v>
       </c>
       <c r="E18" s="4">
@@ -3865,7 +3865,7 @@
         <v>345</v>
       </c>
       <c r="D19" s="3">
-        <f t="shared" si="0"/>
+        <f>100%-F19</f>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E19" s="4">
@@ -3907,7 +3907,7 @@
         <v>270</v>
       </c>
       <c r="D20" s="3">
-        <f t="shared" si="0"/>
+        <f>100%-F20</f>
         <v>0.22999999999999998</v>
       </c>
       <c r="E20" s="4">
@@ -3949,7 +3949,7 @@
         <v>143</v>
       </c>
       <c r="D21" s="3">
-        <f t="shared" si="0"/>
+        <f>100%-F21</f>
         <v>0.30000000000000004</v>
       </c>
       <c r="E21" s="4">
@@ -3991,7 +3991,7 @@
         <v>141</v>
       </c>
       <c r="D22" s="3">
-        <f t="shared" si="0"/>
+        <f>100%-F22</f>
         <v>0.30000000000000004</v>
       </c>
       <c r="E22" s="4">
@@ -4033,7 +4033,7 @@
         <v>142</v>
       </c>
       <c r="D23" s="3">
-        <f t="shared" si="0"/>
+        <f>100%-F23</f>
         <v>0.22999999999999998</v>
       </c>
       <c r="E23" s="4">
@@ -4075,7 +4075,7 @@
         <v>5482</v>
       </c>
       <c r="D24" s="3">
-        <f t="shared" si="0"/>
+        <f>100%-F24</f>
         <v>0</v>
       </c>
       <c r="E24" s="4">
@@ -4117,7 +4117,7 @@
         <v>323</v>
       </c>
       <c r="D25" s="3">
-        <f t="shared" si="0"/>
+        <f>100%-F25</f>
         <v>0.30000000000000004</v>
       </c>
       <c r="E25" s="4">
@@ -4159,7 +4159,7 @@
         <v>109</v>
       </c>
       <c r="D26" s="3">
-        <f t="shared" si="0"/>
+        <f>100%-F26</f>
         <v>0.37</v>
       </c>
       <c r="E26" s="4">
@@ -4201,7 +4201,7 @@
         <v>484</v>
       </c>
       <c r="D27" s="3">
-        <f t="shared" si="0"/>
+        <f>100%-F27</f>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E27" s="4">
@@ -4243,7 +4243,7 @@
         <v>123</v>
       </c>
       <c r="D28" s="3">
-        <f t="shared" si="0"/>
+        <f>100%-F28</f>
         <v>0.30000000000000004</v>
       </c>
       <c r="E28" s="4">
@@ -4285,7 +4285,7 @@
         <v>474</v>
       </c>
       <c r="D29" s="3">
-        <f t="shared" si="0"/>
+        <f>100%-F29</f>
         <v>0.22999999999999998</v>
       </c>
       <c r="E29" s="4">
@@ -4327,7 +4327,7 @@
         <v>124</v>
       </c>
       <c r="D30" s="3">
-        <f t="shared" si="0"/>
+        <f>100%-F30</f>
         <v>0.22999999999999998</v>
       </c>
       <c r="E30" s="4">
@@ -4369,7 +4369,7 @@
         <v>482</v>
       </c>
       <c r="D31" s="3">
-        <f t="shared" si="0"/>
+        <f>100%-F31</f>
         <v>0.15000000000000002</v>
       </c>
       <c r="E31" s="4">
@@ -4411,7 +4411,7 @@
         <v>499</v>
       </c>
       <c r="D32" s="3">
-        <f t="shared" si="0"/>
+        <f>100%-F32</f>
         <v>0.18000000000000005</v>
       </c>
       <c r="E32" s="4">
@@ -4453,7 +4453,7 @@
         <v>144</v>
       </c>
       <c r="D33" s="3">
-        <f t="shared" si="0"/>
+        <f>100%-F33</f>
         <v>0.38</v>
       </c>
       <c r="E33" s="4">
@@ -4495,7 +4495,7 @@
         <v>419</v>
       </c>
       <c r="D34" s="3">
-        <f t="shared" si="0"/>
+        <f>100%-F34</f>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="E34" s="4">
@@ -4537,7 +4537,7 @@
         <v>676</v>
       </c>
       <c r="D35" s="3">
-        <f t="shared" si="0"/>
+        <f>100%-F35</f>
         <v>0</v>
       </c>
       <c r="E35" s="4">
@@ -4579,7 +4579,7 @@
         <v>152</v>
       </c>
       <c r="D36" s="3">
-        <f t="shared" si="0"/>
+        <f>100%-F36</f>
         <v>0.38</v>
       </c>
       <c r="E36" s="4">
@@ -4621,7 +4621,7 @@
         <v>108</v>
       </c>
       <c r="D37" s="3">
-        <f t="shared" si="0"/>
+        <f>100%-F37</f>
         <v>0.8</v>
       </c>
       <c r="E37" s="4">
@@ -4663,7 +4663,7 @@
         <v>633</v>
       </c>
       <c r="D38" s="3">
-        <f t="shared" si="0"/>
+        <f>100%-F38</f>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="E38" s="4">
@@ -4705,7 +4705,7 @@
         <v>213</v>
       </c>
       <c r="D39" s="3">
-        <f t="shared" si="0"/>
+        <f>100%-F39</f>
         <v>0.38</v>
       </c>
       <c r="E39" s="4">
@@ -4747,7 +4747,7 @@
         <v>524</v>
       </c>
       <c r="D40" s="3">
-        <f t="shared" si="0"/>
+        <f>100%-F40</f>
         <v>0</v>
       </c>
       <c r="E40" s="4">
@@ -4789,7 +4789,7 @@
         <v>103</v>
       </c>
       <c r="D41" s="3">
-        <f t="shared" si="0"/>
+        <f>100%-F41</f>
         <v>0.44999999999999996</v>
       </c>
       <c r="E41" s="4">
@@ -4831,7 +4831,7 @@
         <v>196</v>
       </c>
       <c r="D42" s="3">
-        <f t="shared" si="0"/>
+        <f>100%-F42</f>
         <v>0.44999999999999996</v>
       </c>
       <c r="E42" s="4">
@@ -4873,7 +4873,7 @@
         <v>211</v>
       </c>
       <c r="D43" s="3">
-        <f t="shared" si="0"/>
+        <f>100%-F43</f>
         <v>0.44999999999999996</v>
       </c>
       <c r="E43" s="4">
@@ -4915,7 +4915,7 @@
         <v>367</v>
       </c>
       <c r="D44" s="3">
-        <f t="shared" si="0"/>
+        <f>100%-F44</f>
         <v>0.38</v>
       </c>
       <c r="E44" s="4">
@@ -4957,7 +4957,7 @@
         <v>822</v>
       </c>
       <c r="D45" s="3">
-        <f t="shared" si="0"/>
+        <f>100%-F45</f>
         <v>0</v>
       </c>
       <c r="E45" s="4">
@@ -4999,7 +4999,7 @@
         <v>271</v>
       </c>
       <c r="D46" s="3">
-        <f t="shared" si="0"/>
+        <f>100%-F46</f>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E46" s="4">
@@ -5041,7 +5041,7 @@
         <v>116</v>
       </c>
       <c r="D47" s="3">
-        <f t="shared" si="0"/>
+        <f>100%-F47</f>
         <v>0.22999999999999998</v>
       </c>
       <c r="E47" s="4">
@@ -5083,7 +5083,7 @@
         <v>480</v>
       </c>
       <c r="D48" s="3">
-        <f t="shared" si="0"/>
+        <f>100%-F48</f>
         <v>0</v>
       </c>
       <c r="E48" s="4">
@@ -5125,7 +5125,7 @@
         <v>176</v>
       </c>
       <c r="D49" s="3">
-        <f t="shared" si="0"/>
+        <f>100%-F49</f>
         <v>0.44999999999999996</v>
       </c>
       <c r="E49" s="4">
@@ -5167,7 +5167,7 @@
         <v>351</v>
       </c>
       <c r="D50" s="3">
-        <f t="shared" si="0"/>
+        <f>100%-F50</f>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E50" s="4">
@@ -5209,7 +5209,7 @@
         <v>106</v>
       </c>
       <c r="D51" s="3">
-        <f t="shared" si="0"/>
+        <f>100%-F51</f>
         <v>0.65</v>
       </c>
       <c r="E51" s="4">
@@ -5251,7 +5251,7 @@
         <v>294</v>
       </c>
       <c r="D52" s="3">
-        <f t="shared" si="0"/>
+        <f>100%-F52</f>
         <v>0.44999999999999996</v>
       </c>
       <c r="E52" s="4">
@@ -5293,7 +5293,7 @@
         <v>272</v>
       </c>
       <c r="D53" s="3">
-        <f t="shared" si="0"/>
+        <f>100%-F53</f>
         <v>0.22999999999999998</v>
       </c>
       <c r="E53" s="4">
@@ -5335,7 +5335,7 @@
         <v>413</v>
       </c>
       <c r="D54" s="3">
-        <f t="shared" si="0"/>
+        <f>100%-F54</f>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="E54" s="4">
@@ -5377,7 +5377,7 @@
         <v>166</v>
       </c>
       <c r="D55" s="3">
-        <f t="shared" si="0"/>
+        <f>100%-F55</f>
         <v>0.38</v>
       </c>
       <c r="E55" s="4">
@@ -5419,7 +5419,7 @@
         <v>150</v>
       </c>
       <c r="D56" s="3">
-        <f t="shared" si="0"/>
+        <f>100%-F56</f>
         <v>0.44999999999999996</v>
       </c>
       <c r="E56" s="4">
@@ -5461,7 +5461,7 @@
         <v>563</v>
       </c>
       <c r="D57" s="3">
-        <f t="shared" si="0"/>
+        <f>100%-F57</f>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E57" s="4">
@@ -5503,7 +5503,7 @@
         <v>314</v>
       </c>
       <c r="D58" s="3">
-        <f t="shared" si="0"/>
+        <f>100%-F58</f>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E58" s="4">
@@ -5545,7 +5545,7 @@
         <v>355</v>
       </c>
       <c r="D59" s="3">
-        <f t="shared" si="0"/>
+        <f>100%-F59</f>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="E59" s="4">
@@ -5587,7 +5587,7 @@
         <v>267</v>
       </c>
       <c r="D60" s="3">
-        <f t="shared" si="0"/>
+        <f>100%-F60</f>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E60" s="4">
@@ -5629,7 +5629,7 @@
         <v>611</v>
       </c>
       <c r="D61" s="3">
-        <f t="shared" si="0"/>
+        <f>100%-F61</f>
         <v>0</v>
       </c>
       <c r="E61" s="4">
@@ -5671,7 +5671,7 @@
         <v>178</v>
       </c>
       <c r="D62" s="3">
-        <f t="shared" si="0"/>
+        <f>100%-F62</f>
         <v>0.44999999999999996</v>
       </c>
       <c r="E62" s="4">
@@ -5713,7 +5713,7 @@
         <v>233</v>
       </c>
       <c r="D63" s="3">
-        <f t="shared" si="0"/>
+        <f>100%-F63</f>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E63" s="4">
@@ -5755,7 +5755,7 @@
         <v>712</v>
       </c>
       <c r="D64" s="3">
-        <f t="shared" si="0"/>
+        <f>100%-F64</f>
         <v>0.32999999999999996</v>
       </c>
       <c r="E64" s="4">
@@ -5797,7 +5797,7 @@
         <v>695</v>
       </c>
       <c r="D65" s="3">
-        <f t="shared" si="0"/>
+        <f>100%-F65</f>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E65" s="4">
@@ -5839,7 +5839,7 @@
         <v>434</v>
       </c>
       <c r="D66" s="3">
-        <f t="shared" ref="D66:D129" si="1">100%-F66</f>
+        <f>100%-F66</f>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E66" s="4">
@@ -5881,7 +5881,7 @@
         <v>371</v>
       </c>
       <c r="D67" s="3">
-        <f t="shared" si="1"/>
+        <f>100%-F67</f>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E67" s="4">
@@ -5923,7 +5923,7 @@
         <v>365</v>
       </c>
       <c r="D68" s="3">
-        <f t="shared" si="1"/>
+        <f>100%-F68</f>
         <v>0.15000000000000002</v>
       </c>
       <c r="E68" s="4">
@@ -5965,7 +5965,7 @@
         <v>221</v>
       </c>
       <c r="D69" s="3">
-        <f t="shared" si="1"/>
+        <f>100%-F69</f>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E69" s="4">
@@ -6007,7 +6007,7 @@
         <v>122</v>
       </c>
       <c r="D70" s="3">
-        <f t="shared" si="1"/>
+        <f>100%-F70</f>
         <v>0.37</v>
       </c>
       <c r="E70" s="4">
@@ -6049,7 +6049,7 @@
         <v>387</v>
       </c>
       <c r="D71" s="3">
-        <f t="shared" si="1"/>
+        <f>100%-F71</f>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E71" s="4">
@@ -6091,7 +6091,7 @@
         <v>232</v>
       </c>
       <c r="D72" s="3">
-        <f t="shared" si="1"/>
+        <f>100%-F72</f>
         <v>0.15000000000000002</v>
       </c>
       <c r="E72" s="4">
@@ -6133,7 +6133,7 @@
         <v>279</v>
       </c>
       <c r="D73" s="3">
-        <f t="shared" si="1"/>
+        <f>100%-F73</f>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E73" s="4">
@@ -6175,7 +6175,7 @@
         <v>157</v>
       </c>
       <c r="D74" s="3">
-        <f t="shared" si="1"/>
+        <f>100%-F74</f>
         <v>0.30000000000000004</v>
       </c>
       <c r="E74" s="4">
@@ -6217,7 +6217,7 @@
         <v>291</v>
       </c>
       <c r="D75" s="3">
-        <f t="shared" si="1"/>
+        <f>100%-F75</f>
         <v>0.38</v>
       </c>
       <c r="E75" s="4">
@@ -6259,7 +6259,7 @@
         <v>524</v>
       </c>
       <c r="D76" s="3">
-        <f t="shared" si="1"/>
+        <f>100%-F76</f>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E76" s="4">
@@ -6301,7 +6301,7 @@
         <v>218</v>
       </c>
       <c r="D77" s="3">
-        <f t="shared" si="1"/>
+        <f>100%-F77</f>
         <v>0.30000000000000004</v>
       </c>
       <c r="E77" s="4">
@@ -6343,7 +6343,7 @@
         <v>706</v>
       </c>
       <c r="D78" s="3">
-        <f t="shared" si="1"/>
+        <f>100%-F78</f>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E78" s="4">
@@ -6385,7 +6385,7 @@
         <v>230</v>
       </c>
       <c r="D79" s="3">
-        <f t="shared" si="1"/>
+        <f>100%-F79</f>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E79" s="4">
@@ -6427,7 +6427,7 @@
         <v>344</v>
       </c>
       <c r="D80" s="3">
-        <f t="shared" si="1"/>
+        <f>100%-F80</f>
         <v>0.18000000000000005</v>
       </c>
       <c r="E80" s="4">
@@ -6469,7 +6469,7 @@
         <v>179</v>
       </c>
       <c r="D81" s="3">
-        <f t="shared" si="1"/>
+        <f>100%-F81</f>
         <v>0.30000000000000004</v>
       </c>
       <c r="E81" s="4">
@@ -6511,7 +6511,7 @@
         <v>565</v>
       </c>
       <c r="D82" s="3">
-        <f t="shared" si="1"/>
+        <f>100%-F82</f>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="E82" s="4">
@@ -6553,7 +6553,7 @@
         <v>230</v>
       </c>
       <c r="D83" s="3">
-        <f t="shared" si="1"/>
+        <f>100%-F83</f>
         <v>0.25</v>
       </c>
       <c r="E83" s="4">
@@ -6595,7 +6595,7 @@
         <v>495</v>
       </c>
       <c r="D84" s="3">
-        <f t="shared" si="1"/>
+        <f>100%-F84</f>
         <v>0.18000000000000005</v>
       </c>
       <c r="E84" s="4">
@@ -6637,7 +6637,7 @@
         <v>465</v>
       </c>
       <c r="D85" s="3">
-        <f t="shared" si="1"/>
+        <f>100%-F85</f>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E85" s="4">
@@ -6679,7 +6679,7 @@
         <v>409</v>
       </c>
       <c r="D86" s="3">
-        <f t="shared" si="1"/>
+        <f>100%-F86</f>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E86" s="4">
@@ -6721,7 +6721,7 @@
         <v>217</v>
       </c>
       <c r="D87" s="3">
-        <f t="shared" si="1"/>
+        <f>100%-F87</f>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="E87" s="4">
@@ -6763,7 +6763,7 @@
         <v>122</v>
       </c>
       <c r="D88" s="3">
-        <f t="shared" si="1"/>
+        <f>100%-F88</f>
         <v>0.17000000000000004</v>
       </c>
       <c r="E88" s="4">
@@ -6805,7 +6805,7 @@
         <v>466</v>
       </c>
       <c r="D89" s="3">
-        <f t="shared" si="1"/>
+        <f>100%-F89</f>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="E89" s="4">
@@ -6847,7 +6847,7 @@
         <v>202</v>
       </c>
       <c r="D90" s="3">
-        <f t="shared" si="1"/>
+        <f>100%-F90</f>
         <v>0.32999999999999996</v>
       </c>
       <c r="E90" s="4">
@@ -6889,7 +6889,7 @@
         <v>278</v>
       </c>
       <c r="D91" s="3">
-        <f t="shared" si="1"/>
+        <f>100%-F91</f>
         <v>0.15000000000000002</v>
       </c>
       <c r="E91" s="4">
@@ -6931,7 +6931,7 @@
         <v>207</v>
       </c>
       <c r="D92" s="3">
-        <f t="shared" si="1"/>
+        <f>100%-F92</f>
         <v>0.22999999999999998</v>
       </c>
       <c r="E92" s="4">
@@ -6973,7 +6973,7 @@
         <v>125</v>
       </c>
       <c r="D93" s="3">
-        <f t="shared" si="1"/>
+        <f>100%-F93</f>
         <v>0.30000000000000004</v>
       </c>
       <c r="E93" s="4">
@@ -7015,7 +7015,7 @@
         <v>904</v>
       </c>
       <c r="D94" s="3">
-        <f t="shared" si="1"/>
+        <f>100%-F94</f>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="E94" s="4">
@@ -7057,7 +7057,7 @@
         <v>548</v>
       </c>
       <c r="D95" s="3">
-        <f t="shared" si="1"/>
+        <f>100%-F95</f>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E95" s="4">
@@ -7099,7 +7099,7 @@
         <v>265</v>
       </c>
       <c r="D96" s="3">
-        <f t="shared" si="1"/>
+        <f>100%-F96</f>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E96" s="4">
@@ -7141,7 +7141,7 @@
         <v>457</v>
       </c>
       <c r="D97" s="3">
-        <f t="shared" si="1"/>
+        <f>100%-F97</f>
         <v>0</v>
       </c>
       <c r="E97" s="4">
@@ -7183,7 +7183,7 @@
         <v>177</v>
       </c>
       <c r="D98" s="3">
-        <f t="shared" si="1"/>
+        <f>100%-F98</f>
         <v>0.22999999999999998</v>
       </c>
       <c r="E98" s="4">
@@ -7225,7 +7225,7 @@
         <v>447</v>
       </c>
       <c r="D99" s="3">
-        <f t="shared" si="1"/>
+        <f>100%-F99</f>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E99" s="4">
@@ -7267,7 +7267,7 @@
         <v>347</v>
       </c>
       <c r="D100" s="3">
-        <f t="shared" si="1"/>
+        <f>100%-F100</f>
         <v>0.32999999999999996</v>
       </c>
       <c r="E100" s="4">
@@ -7309,7 +7309,7 @@
         <v>194</v>
       </c>
       <c r="D101" s="3">
-        <f t="shared" si="1"/>
+        <f>100%-F101</f>
         <v>0.22999999999999998</v>
       </c>
       <c r="E101" s="4">
@@ -7351,7 +7351,7 @@
         <v>189</v>
       </c>
       <c r="D102" s="3">
-        <f t="shared" si="1"/>
+        <f>100%-F102</f>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E102" s="4">
@@ -7393,7 +7393,7 @@
         <v>970</v>
       </c>
       <c r="D103" s="3">
-        <f t="shared" si="1"/>
+        <f>100%-F103</f>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="E103" s="4">
@@ -7435,7 +7435,7 @@
         <v>243</v>
       </c>
       <c r="D104" s="3">
-        <f t="shared" si="1"/>
+        <f>100%-F104</f>
         <v>0.17000000000000004</v>
       </c>
       <c r="E104" s="4">
@@ -7477,7 +7477,7 @@
         <v>478</v>
       </c>
       <c r="D105" s="3">
-        <f t="shared" si="1"/>
+        <f>100%-F105</f>
         <v>0.38</v>
       </c>
       <c r="E105" s="4">
@@ -7519,7 +7519,7 @@
         <v>134</v>
       </c>
       <c r="D106" s="3">
-        <f t="shared" si="1"/>
+        <f>100%-F106</f>
         <v>0.30000000000000004</v>
       </c>
       <c r="E106" s="4">
@@ -7561,7 +7561,7 @@
         <v>160</v>
       </c>
       <c r="D107" s="3">
-        <f t="shared" si="1"/>
+        <f>100%-F107</f>
         <v>0.38</v>
       </c>
       <c r="E107" s="4">
@@ -7603,7 +7603,7 @@
         <v>248</v>
       </c>
       <c r="D108" s="3">
-        <f t="shared" si="1"/>
+        <f>100%-F108</f>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E108" s="4">
@@ -7645,7 +7645,7 @@
         <v>360</v>
       </c>
       <c r="D109" s="3">
-        <f t="shared" si="1"/>
+        <f>100%-F109</f>
         <v>0.38</v>
       </c>
       <c r="E109" s="4">
@@ -7687,7 +7687,7 @@
         <v>147</v>
       </c>
       <c r="D110" s="3">
-        <f t="shared" si="1"/>
+        <f>100%-F110</f>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="E110" s="4">
@@ -7729,7 +7729,7 @@
         <v>655</v>
       </c>
       <c r="D111" s="3">
-        <f t="shared" si="1"/>
+        <f>100%-F111</f>
         <v>0</v>
       </c>
       <c r="E111" s="4">
@@ -7771,7 +7771,7 @@
         <v>6090</v>
       </c>
       <c r="D112" s="3">
-        <f t="shared" si="1"/>
+        <f>100%-F112</f>
         <v>0</v>
       </c>
       <c r="E112" s="4">
@@ -7813,7 +7813,7 @@
         <v>461</v>
       </c>
       <c r="D113" s="3">
-        <f t="shared" si="1"/>
+        <f>100%-F113</f>
         <v>0.15000000000000002</v>
       </c>
       <c r="E113" s="4">
@@ -7855,7 +7855,7 @@
         <v>113</v>
       </c>
       <c r="D114" s="3">
-        <f t="shared" si="1"/>
+        <f>100%-F114</f>
         <v>0.18999999999999995</v>
       </c>
       <c r="E114" s="4">
@@ -7897,7 +7897,7 @@
         <v>830</v>
       </c>
       <c r="D115" s="3">
-        <f t="shared" si="1"/>
+        <f>100%-F115</f>
         <v>0.15000000000000002</v>
       </c>
       <c r="E115" s="4">
@@ -7939,7 +7939,7 @@
         <v>514</v>
       </c>
       <c r="D116" s="3">
-        <f t="shared" si="1"/>
+        <f>100%-F116</f>
         <v>0</v>
       </c>
       <c r="E116" s="4">
@@ -7981,7 +7981,7 @@
         <v>606</v>
       </c>
       <c r="D117" s="3">
-        <f t="shared" si="1"/>
+        <f>100%-F117</f>
         <v>0.15000000000000002</v>
       </c>
       <c r="E117" s="4">
@@ -8023,7 +8023,7 @@
         <v>554</v>
       </c>
       <c r="D118" s="3">
-        <f t="shared" si="1"/>
+        <f>100%-F118</f>
         <v>0</v>
       </c>
       <c r="E118" s="4">
@@ -8065,7 +8065,7 @@
         <v>142</v>
       </c>
       <c r="D119" s="3">
-        <f t="shared" si="1"/>
+        <f>100%-F119</f>
         <v>0.5</v>
       </c>
       <c r="E119" s="4">
@@ -8107,7 +8107,7 @@
         <v>227</v>
       </c>
       <c r="D120" s="3">
-        <f t="shared" si="1"/>
+        <f>100%-F120</f>
         <v>0.15000000000000002</v>
       </c>
       <c r="E120" s="4">
@@ -8149,7 +8149,7 @@
         <v>797</v>
       </c>
       <c r="D121" s="3">
-        <f t="shared" si="1"/>
+        <f>100%-F121</f>
         <v>0</v>
       </c>
       <c r="E121" s="4">
@@ -8191,7 +8191,7 @@
         <v>395</v>
       </c>
       <c r="D122" s="3">
-        <f t="shared" si="1"/>
+        <f>100%-F122</f>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="E122" s="4">
@@ -8233,7 +8233,7 @@
         <v>656</v>
       </c>
       <c r="D123" s="3">
-        <f t="shared" si="1"/>
+        <f>100%-F123</f>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="E123" s="4">
@@ -8275,7 +8275,7 @@
         <v>143</v>
       </c>
       <c r="D124" s="3">
-        <f t="shared" si="1"/>
+        <f>100%-F124</f>
         <v>0.35</v>
       </c>
       <c r="E124" s="4">
@@ -8317,7 +8317,7 @@
         <v>162</v>
       </c>
       <c r="D125" s="3">
-        <f t="shared" si="1"/>
+        <f>100%-F125</f>
         <v>0.15000000000000002</v>
       </c>
       <c r="E125" s="4">
@@ -8359,7 +8359,7 @@
         <v>6155</v>
       </c>
       <c r="D126" s="3">
-        <f t="shared" si="1"/>
+        <f>100%-F126</f>
         <v>0</v>
       </c>
       <c r="E126" s="4">
@@ -8401,7 +8401,7 @@
         <v>309</v>
       </c>
       <c r="D127" s="3">
-        <f t="shared" si="1"/>
+        <f>100%-F127</f>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="E127" s="4">
@@ -8443,7 +8443,7 @@
         <v>510</v>
       </c>
       <c r="D128" s="3">
-        <f t="shared" si="1"/>
+        <f>100%-F128</f>
         <v>0.15000000000000002</v>
       </c>
       <c r="E128" s="4">
@@ -8485,7 +8485,7 @@
         <v>671</v>
       </c>
       <c r="D129" s="3">
-        <f t="shared" si="1"/>
+        <f>100%-F129</f>
         <v>0</v>
       </c>
       <c r="E129" s="4">
@@ -8527,7 +8527,7 @@
         <v>113</v>
       </c>
       <c r="D130" s="3">
-        <f t="shared" ref="D130:D193" si="2">100%-F130</f>
+        <f>100%-F130</f>
         <v>0.30000000000000004</v>
       </c>
       <c r="E130" s="4">
@@ -8569,7 +8569,7 @@
         <v>682</v>
       </c>
       <c r="D131" s="3">
-        <f t="shared" si="2"/>
+        <f>100%-F131</f>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E131" s="4">
@@ -8611,7 +8611,7 @@
         <v>239</v>
       </c>
       <c r="D132" s="3">
-        <f t="shared" si="2"/>
+        <f>100%-F132</f>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E132" s="4">
@@ -8653,7 +8653,7 @@
         <v>562</v>
       </c>
       <c r="D133" s="3">
-        <f t="shared" si="2"/>
+        <f>100%-F133</f>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E133" s="4">
@@ -8695,7 +8695,7 @@
         <v>107</v>
       </c>
       <c r="D134" s="3">
-        <f t="shared" si="2"/>
+        <f>100%-F134</f>
         <v>0.15000000000000002</v>
       </c>
       <c r="E134" s="4">
@@ -8737,7 +8737,7 @@
         <v>253</v>
       </c>
       <c r="D135" s="3">
-        <f t="shared" si="2"/>
+        <f>100%-F135</f>
         <v>0.22999999999999998</v>
       </c>
       <c r="E135" s="4">
@@ -8779,7 +8779,7 @@
         <v>107</v>
       </c>
       <c r="D136" s="3">
-        <f t="shared" si="2"/>
+        <f>100%-F136</f>
         <v>0.44999999999999996</v>
       </c>
       <c r="E136" s="4">
@@ -8821,7 +8821,7 @@
         <v>277</v>
       </c>
       <c r="D137" s="3">
-        <f t="shared" si="2"/>
+        <f>100%-F137</f>
         <v>0.38</v>
       </c>
       <c r="E137" s="4">
@@ -8863,7 +8863,7 @@
         <v>375</v>
       </c>
       <c r="D138" s="3">
-        <f t="shared" si="2"/>
+        <f>100%-F138</f>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="E138" s="4">
@@ -8905,7 +8905,7 @@
         <v>131</v>
       </c>
       <c r="D139" s="3">
-        <f t="shared" si="2"/>
+        <f>100%-F139</f>
         <v>0.15000000000000002</v>
       </c>
       <c r="E139" s="4">
@@ -8947,7 +8947,7 @@
         <v>632</v>
       </c>
       <c r="D140" s="3">
-        <f t="shared" si="2"/>
+        <f>100%-F140</f>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E140" s="4">
@@ -8989,7 +8989,7 @@
         <v>615</v>
       </c>
       <c r="D141" s="3">
-        <f t="shared" si="2"/>
+        <f>100%-F141</f>
         <v>0</v>
       </c>
       <c r="E141" s="4">
@@ -9031,7 +9031,7 @@
         <v>4961</v>
       </c>
       <c r="D142" s="3">
-        <f t="shared" si="2"/>
+        <f>100%-F142</f>
         <v>0</v>
       </c>
       <c r="E142" s="4">
@@ -9073,7 +9073,7 @@
         <v>501</v>
       </c>
       <c r="D143" s="3">
-        <f t="shared" si="2"/>
+        <f>100%-F143</f>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E143" s="4">
@@ -9115,7 +9115,7 @@
         <v>584</v>
       </c>
       <c r="D144" s="3">
-        <f t="shared" si="2"/>
+        <f>100%-F144</f>
         <v>0</v>
       </c>
       <c r="E144" s="4">
@@ -9157,7 +9157,7 @@
         <v>663</v>
       </c>
       <c r="D145" s="3">
-        <f t="shared" si="2"/>
+        <f>100%-F145</f>
         <v>0</v>
       </c>
       <c r="E145" s="4">
@@ -9199,7 +9199,7 @@
         <v>303</v>
       </c>
       <c r="D146" s="3">
-        <f t="shared" si="2"/>
+        <f>100%-F146</f>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="E146" s="4">
@@ -9241,7 +9241,7 @@
         <v>170</v>
       </c>
       <c r="D147" s="3">
-        <f t="shared" si="2"/>
+        <f>100%-F147</f>
         <v>0.30000000000000004</v>
       </c>
       <c r="E147" s="4">
@@ -9283,7 +9283,7 @@
         <v>130</v>
       </c>
       <c r="D148" s="3">
-        <f t="shared" si="2"/>
+        <f>100%-F148</f>
         <v>0.22999999999999998</v>
       </c>
       <c r="E148" s="4">
@@ -9325,7 +9325,7 @@
         <v>619</v>
       </c>
       <c r="D149" s="3">
-        <f t="shared" si="2"/>
+        <f>100%-F149</f>
         <v>0.22999999999999998</v>
       </c>
       <c r="E149" s="4">
@@ -9367,7 +9367,7 @@
         <v>1049</v>
       </c>
       <c r="D150" s="3">
-        <f t="shared" si="2"/>
+        <f>100%-F150</f>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E150" s="4">
@@ -9409,7 +9409,7 @@
         <v>677</v>
       </c>
       <c r="D151" s="3">
-        <f t="shared" si="2"/>
+        <f>100%-F151</f>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E151" s="4">
@@ -9451,7 +9451,7 @@
         <v>169</v>
       </c>
       <c r="D152" s="3">
-        <f t="shared" si="2"/>
+        <f>100%-F152</f>
         <v>0.30000000000000004</v>
       </c>
       <c r="E152" s="4">
@@ -9493,7 +9493,7 @@
         <v>516</v>
       </c>
       <c r="D153" s="3">
-        <f t="shared" si="2"/>
+        <f>100%-F153</f>
         <v>0.22999999999999998</v>
       </c>
       <c r="E153" s="4">
@@ -9535,7 +9535,7 @@
         <v>406</v>
       </c>
       <c r="D154" s="3">
-        <f t="shared" si="2"/>
+        <f>100%-F154</f>
         <v>0.22999999999999998</v>
       </c>
       <c r="E154" s="4">
@@ -9577,7 +9577,7 @@
         <v>382</v>
       </c>
       <c r="D155" s="3">
-        <f t="shared" si="2"/>
+        <f>100%-F155</f>
         <v>0.22999999999999998</v>
       </c>
       <c r="E155" s="4">
@@ -9619,7 +9619,7 @@
         <v>2043.0000000000002</v>
       </c>
       <c r="D156" s="3">
-        <f t="shared" si="2"/>
+        <f>100%-F156</f>
         <v>0</v>
       </c>
       <c r="E156" s="4">
@@ -9661,7 +9661,7 @@
         <v>223</v>
       </c>
       <c r="D157" s="3">
-        <f t="shared" si="2"/>
+        <f>100%-F157</f>
         <v>0.38</v>
       </c>
       <c r="E157" s="4">
@@ -9703,7 +9703,7 @@
         <v>424</v>
       </c>
       <c r="D158" s="3">
-        <f t="shared" si="2"/>
+        <f>100%-F158</f>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E158" s="4">
@@ -9745,7 +9745,7 @@
         <v>315</v>
       </c>
       <c r="D159" s="3">
-        <f t="shared" si="2"/>
+        <f>100%-F159</f>
         <v>0.22999999999999998</v>
       </c>
       <c r="E159" s="4">
@@ -9787,7 +9787,7 @@
         <v>150</v>
       </c>
       <c r="D160" s="3">
-        <f t="shared" si="2"/>
+        <f>100%-F160</f>
         <v>0.37</v>
       </c>
       <c r="E160" s="4">
@@ -9829,7 +9829,7 @@
         <v>1341</v>
       </c>
       <c r="D161" s="3">
-        <f t="shared" si="2"/>
+        <f>100%-F161</f>
         <v>0</v>
       </c>
       <c r="E161" s="4">
@@ -9871,7 +9871,7 @@
         <v>266</v>
       </c>
       <c r="D162" s="3">
-        <f t="shared" si="2"/>
+        <f>100%-F162</f>
         <v>0.30000000000000004</v>
       </c>
       <c r="E162" s="4">
@@ -9913,7 +9913,7 @@
         <v>364</v>
       </c>
       <c r="D163" s="3">
-        <f t="shared" si="2"/>
+        <f>100%-F163</f>
         <v>0.22999999999999998</v>
       </c>
       <c r="E163" s="4">
@@ -9955,7 +9955,7 @@
         <v>176</v>
       </c>
       <c r="D164" s="3">
-        <f t="shared" si="2"/>
+        <f>100%-F164</f>
         <v>0.37</v>
       </c>
       <c r="E164" s="4">
@@ -9997,7 +9997,7 @@
         <v>1774</v>
       </c>
       <c r="D165" s="3">
-        <f t="shared" si="2"/>
+        <f>100%-F165</f>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E165" s="4">
@@ -10039,7 +10039,7 @@
         <v>115</v>
       </c>
       <c r="D166" s="3">
-        <f t="shared" si="2"/>
+        <f>100%-F166</f>
         <v>0.37</v>
       </c>
       <c r="E166" s="4">
@@ -10081,7 +10081,7 @@
         <v>162</v>
       </c>
       <c r="D167" s="3">
-        <f t="shared" si="2"/>
+        <f>100%-F167</f>
         <v>0.37</v>
       </c>
       <c r="E167" s="4">
@@ -10123,7 +10123,7 @@
         <v>215</v>
       </c>
       <c r="D168" s="3">
-        <f t="shared" si="2"/>
+        <f>100%-F168</f>
         <v>0.22999999999999998</v>
       </c>
       <c r="E168" s="4">
@@ -10165,7 +10165,7 @@
         <v>715</v>
       </c>
       <c r="D169" s="3">
-        <f t="shared" si="2"/>
+        <f>100%-F169</f>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E169" s="4">
@@ -10207,7 +10207,7 @@
         <v>249</v>
       </c>
       <c r="D170" s="3">
-        <f t="shared" si="2"/>
+        <f>100%-F170</f>
         <v>0.28000000000000003</v>
       </c>
       <c r="E170" s="4">
@@ -10249,7 +10249,7 @@
         <v>610</v>
       </c>
       <c r="D171" s="3">
-        <f t="shared" si="2"/>
+        <f>100%-F171</f>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E171" s="4">
@@ -10291,7 +10291,7 @@
         <v>507</v>
       </c>
       <c r="D172" s="3">
-        <f t="shared" si="2"/>
+        <f>100%-F172</f>
         <v>0.15000000000000002</v>
       </c>
       <c r="E172" s="4">
@@ -10333,7 +10333,7 @@
         <v>3356</v>
       </c>
       <c r="D173" s="3">
-        <f t="shared" si="2"/>
+        <f>100%-F173</f>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E173" s="4">
@@ -10375,7 +10375,7 @@
         <v>1772</v>
       </c>
       <c r="D174" s="3">
-        <f t="shared" si="2"/>
+        <f>100%-F174</f>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E174" s="4">
@@ -10417,7 +10417,7 @@
         <v>150</v>
       </c>
       <c r="D175" s="3">
-        <f t="shared" si="2"/>
+        <f>100%-F175</f>
         <v>0.8</v>
       </c>
       <c r="E175" s="4">
@@ -10459,7 +10459,7 @@
         <v>249</v>
       </c>
       <c r="D176" s="3">
-        <f t="shared" si="2"/>
+        <f>100%-F176</f>
         <v>0.38</v>
       </c>
       <c r="E176" s="4">
@@ -10501,7 +10501,7 @@
         <v>489</v>
       </c>
       <c r="D177" s="3">
-        <f t="shared" si="2"/>
+        <f>100%-F177</f>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E177" s="4">
@@ -10543,7 +10543,7 @@
         <v>955</v>
       </c>
       <c r="D178" s="3">
-        <f t="shared" si="2"/>
+        <f>100%-F178</f>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E178" s="4">
@@ -10585,7 +10585,7 @@
         <v>663</v>
       </c>
       <c r="D179" s="3">
-        <f t="shared" si="2"/>
+        <f>100%-F179</f>
         <v>0.22999999999999998</v>
       </c>
       <c r="E179" s="4">
@@ -10627,7 +10627,7 @@
         <v>821</v>
       </c>
       <c r="D180" s="3">
-        <f t="shared" si="2"/>
+        <f>100%-F180</f>
         <v>0.22999999999999998</v>
       </c>
       <c r="E180" s="4">
@@ -10669,7 +10669,7 @@
         <v>1561</v>
       </c>
       <c r="D181" s="3">
-        <f t="shared" si="2"/>
+        <f>100%-F181</f>
         <v>0.15000000000000002</v>
       </c>
       <c r="E181" s="4">
@@ -10711,7 +10711,7 @@
         <v>107</v>
       </c>
       <c r="D182" s="3">
-        <f t="shared" si="2"/>
+        <f>100%-F182</f>
         <v>0.44999999999999996</v>
       </c>
       <c r="E182" s="4">
@@ -10753,7 +10753,7 @@
         <v>147</v>
       </c>
       <c r="D183" s="3">
-        <f t="shared" si="2"/>
+        <f>100%-F183</f>
         <v>0.38</v>
       </c>
       <c r="E183" s="4">
@@ -10795,7 +10795,7 @@
         <v>197</v>
       </c>
       <c r="D184" s="3">
-        <f t="shared" si="2"/>
+        <f>100%-F184</f>
         <v>0.44999999999999996</v>
       </c>
       <c r="E184" s="4">
@@ -10837,7 +10837,7 @@
         <v>1173</v>
       </c>
       <c r="D185" s="3">
-        <f t="shared" si="2"/>
+        <f>100%-F185</f>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E185" s="4">
@@ -10879,7 +10879,7 @@
         <v>2657</v>
       </c>
       <c r="D186" s="3">
-        <f t="shared" si="2"/>
+        <f>100%-F186</f>
         <v>0</v>
       </c>
       <c r="E186" s="4">
@@ -10921,7 +10921,7 @@
         <v>323</v>
       </c>
       <c r="D187" s="3">
-        <f t="shared" si="2"/>
+        <f>100%-F187</f>
         <v>0.15000000000000002</v>
       </c>
       <c r="E187" s="4">
@@ -10963,7 +10963,7 @@
         <v>676</v>
       </c>
       <c r="D188" s="3">
-        <f t="shared" si="2"/>
+        <f>100%-F188</f>
         <v>0.22999999999999998</v>
       </c>
       <c r="E188" s="4">
@@ -11005,7 +11005,7 @@
         <v>4695</v>
       </c>
       <c r="D189" s="3">
-        <f t="shared" si="2"/>
+        <f>100%-F189</f>
         <v>0</v>
       </c>
       <c r="E189" s="4">
@@ -11047,7 +11047,7 @@
         <v>623</v>
       </c>
       <c r="D190" s="3">
-        <f t="shared" si="2"/>
+        <f>100%-F190</f>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E190" s="4">
@@ -11089,7 +11089,7 @@
         <v>754</v>
       </c>
       <c r="D191" s="3">
-        <f t="shared" si="2"/>
+        <f>100%-F191</f>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="E191" s="4">
@@ -11131,7 +11131,7 @@
         <v>503</v>
       </c>
       <c r="D192" s="3">
-        <f t="shared" si="2"/>
+        <f>100%-F192</f>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="E192" s="4">
@@ -11173,7 +11173,7 @@
         <v>188</v>
       </c>
       <c r="D193" s="3">
-        <f t="shared" si="2"/>
+        <f>100%-F193</f>
         <v>0.44999999999999996</v>
       </c>
       <c r="E193" s="4">
@@ -11215,7 +11215,7 @@
         <v>149</v>
       </c>
       <c r="D194" s="3">
-        <f t="shared" ref="D194:D257" si="3">100%-F194</f>
+        <f>100%-F194</f>
         <v>0.44999999999999996</v>
       </c>
       <c r="E194" s="4">
@@ -11257,7 +11257,7 @@
         <v>571</v>
       </c>
       <c r="D195" s="3">
-        <f t="shared" si="3"/>
+        <f>100%-F195</f>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E195" s="4">
@@ -11299,7 +11299,7 @@
         <v>989</v>
       </c>
       <c r="D196" s="3">
-        <f t="shared" si="3"/>
+        <f>100%-F196</f>
         <v>0.15000000000000002</v>
       </c>
       <c r="E196" s="4">
@@ -11341,7 +11341,7 @@
         <v>214</v>
       </c>
       <c r="D197" s="3">
-        <f t="shared" si="3"/>
+        <f>100%-F197</f>
         <v>0.36</v>
       </c>
       <c r="E197" s="4">
@@ -11383,7 +11383,7 @@
         <v>147</v>
       </c>
       <c r="D198" s="3">
-        <f t="shared" si="3"/>
+        <f>100%-F198</f>
         <v>0.26</v>
       </c>
       <c r="E198" s="4">
@@ -11425,7 +11425,7 @@
         <v>227</v>
       </c>
       <c r="D199" s="3">
-        <f t="shared" si="3"/>
+        <f>100%-F199</f>
         <v>0.30000000000000004</v>
       </c>
       <c r="E199" s="4">
@@ -11467,7 +11467,7 @@
         <v>957</v>
       </c>
       <c r="D200" s="3">
-        <f t="shared" si="3"/>
+        <f>100%-F200</f>
         <v>0</v>
       </c>
       <c r="E200" s="4">
@@ -11509,7 +11509,7 @@
         <v>1130</v>
       </c>
       <c r="D201" s="3">
-        <f t="shared" si="3"/>
+        <f>100%-F201</f>
         <v>0</v>
       </c>
       <c r="E201" s="4">
@@ -11551,7 +11551,7 @@
         <v>17779</v>
       </c>
       <c r="D202" s="3">
-        <f t="shared" si="3"/>
+        <f>100%-F202</f>
         <v>0</v>
       </c>
       <c r="E202" s="4">
@@ -11593,7 +11593,7 @@
         <v>409</v>
       </c>
       <c r="D203" s="3">
-        <f t="shared" si="3"/>
+        <f>100%-F203</f>
         <v>0.30000000000000004</v>
       </c>
       <c r="E203" s="4">
@@ -11635,7 +11635,7 @@
         <v>109</v>
       </c>
       <c r="D204" s="3">
-        <f t="shared" si="3"/>
+        <f>100%-F204</f>
         <v>0.37</v>
       </c>
       <c r="E204" s="4">
@@ -11677,7 +11677,7 @@
         <v>523</v>
       </c>
       <c r="D205" s="3">
-        <f t="shared" si="3"/>
+        <f>100%-F205</f>
         <v>0</v>
       </c>
       <c r="E205" s="4">
@@ -11719,7 +11719,7 @@
         <v>648</v>
       </c>
       <c r="D206" s="3">
-        <f t="shared" si="3"/>
+        <f>100%-F206</f>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="E206" s="4">
@@ -11761,7 +11761,7 @@
         <v>903</v>
       </c>
       <c r="D207" s="3">
-        <f t="shared" si="3"/>
+        <f>100%-F207</f>
         <v>0</v>
       </c>
       <c r="E207" s="4">
@@ -11803,7 +11803,7 @@
         <v>630</v>
       </c>
       <c r="D208" s="3">
-        <f t="shared" si="3"/>
+        <f>100%-F208</f>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="E208" s="4">
@@ -11845,7 +11845,7 @@
         <v>801</v>
       </c>
       <c r="D209" s="3">
-        <f t="shared" si="3"/>
+        <f>100%-F209</f>
         <v>0</v>
       </c>
       <c r="E209" s="4">
@@ -11887,7 +11887,7 @@
         <v>401</v>
       </c>
       <c r="D210" s="3">
-        <f t="shared" si="3"/>
+        <f>100%-F210</f>
         <v>0.22999999999999998</v>
       </c>
       <c r="E210" s="4">
@@ -11929,7 +11929,7 @@
         <v>246</v>
       </c>
       <c r="D211" s="3">
-        <f t="shared" si="3"/>
+        <f>100%-F211</f>
         <v>0.31999999999999995</v>
       </c>
       <c r="E211" s="4">
@@ -11971,7 +11971,7 @@
         <v>374</v>
       </c>
       <c r="D212" s="3">
-        <f t="shared" si="3"/>
+        <f>100%-F212</f>
         <v>0.30000000000000004</v>
       </c>
       <c r="E212" s="4">
@@ -12013,7 +12013,7 @@
         <v>621</v>
       </c>
       <c r="D213" s="3">
-        <f t="shared" si="3"/>
+        <f>100%-F213</f>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="E213" s="4">
@@ -12055,7 +12055,7 @@
         <v>204</v>
       </c>
       <c r="D214" s="3">
-        <f t="shared" si="3"/>
+        <f>100%-F214</f>
         <v>0.31999999999999995</v>
       </c>
       <c r="E214" s="4">
@@ -12097,7 +12097,7 @@
         <v>614</v>
       </c>
       <c r="D215" s="3">
-        <f t="shared" si="3"/>
+        <f>100%-F215</f>
         <v>0.22999999999999998</v>
       </c>
       <c r="E215" s="4">
@@ -12139,7 +12139,7 @@
         <v>814</v>
       </c>
       <c r="D216" s="3">
-        <f t="shared" si="3"/>
+        <f>100%-F216</f>
         <v>0</v>
       </c>
       <c r="E216" s="4">
@@ -12181,7 +12181,7 @@
         <v>205</v>
       </c>
       <c r="D217" s="3">
-        <f t="shared" si="3"/>
+        <f>100%-F217</f>
         <v>0.30000000000000004</v>
       </c>
       <c r="E217" s="4">
@@ -12223,7 +12223,7 @@
         <v>119</v>
       </c>
       <c r="D218" s="3">
-        <f t="shared" si="3"/>
+        <f>100%-F218</f>
         <v>0.20999999999999996</v>
       </c>
       <c r="E218" s="4">
@@ -12265,7 +12265,7 @@
         <v>122</v>
       </c>
       <c r="D219" s="3">
-        <f t="shared" si="3"/>
+        <f>100%-F219</f>
         <v>0.30000000000000004</v>
       </c>
       <c r="E219" s="4">
@@ -12307,7 +12307,7 @@
         <v>477</v>
       </c>
       <c r="D220" s="3">
-        <f t="shared" si="3"/>
+        <f>100%-F220</f>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E220" s="4">
@@ -12349,7 +12349,7 @@
         <v>503</v>
       </c>
       <c r="D221" s="3">
-        <f t="shared" si="3"/>
+        <f>100%-F221</f>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="E221" s="4">
@@ -12391,7 +12391,7 @@
         <v>125</v>
       </c>
       <c r="D222" s="3">
-        <f t="shared" si="3"/>
+        <f>100%-F222</f>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E222" s="4">
@@ -12433,7 +12433,7 @@
         <v>262</v>
       </c>
       <c r="D223" s="3">
-        <f t="shared" si="3"/>
+        <f>100%-F223</f>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E223" s="4">
@@ -12475,7 +12475,7 @@
         <v>184</v>
       </c>
       <c r="D224" s="3">
-        <f t="shared" si="3"/>
+        <f>100%-F224</f>
         <v>0.37</v>
       </c>
       <c r="E224" s="4">
@@ -12517,7 +12517,7 @@
         <v>439</v>
       </c>
       <c r="D225" s="3">
-        <f t="shared" si="3"/>
+        <f>100%-F225</f>
         <v>0.30000000000000004</v>
       </c>
       <c r="E225" s="4">
@@ -12559,7 +12559,7 @@
         <v>173</v>
       </c>
       <c r="D226" s="3">
-        <f t="shared" si="3"/>
+        <f>100%-F226</f>
         <v>0.22999999999999998</v>
       </c>
       <c r="E226" s="4">
@@ -12601,7 +12601,7 @@
         <v>528</v>
       </c>
       <c r="D227" s="3">
-        <f t="shared" si="3"/>
+        <f>100%-F227</f>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="E227" s="4">
@@ -12643,7 +12643,7 @@
         <v>189</v>
       </c>
       <c r="D228" s="3">
-        <f t="shared" si="3"/>
+        <f>100%-F228</f>
         <v>0.22999999999999998</v>
       </c>
       <c r="E228" s="4">
@@ -12685,7 +12685,7 @@
         <v>494</v>
       </c>
       <c r="D229" s="3">
-        <f t="shared" si="3"/>
+        <f>100%-F229</f>
         <v>0</v>
       </c>
       <c r="E229" s="4">
@@ -12727,7 +12727,7 @@
         <v>112</v>
       </c>
       <c r="D230" s="3">
-        <f t="shared" si="3"/>
+        <f>100%-F230</f>
         <v>0.44999999999999996</v>
       </c>
       <c r="E230" s="4">
@@ -12769,7 +12769,7 @@
         <v>700</v>
       </c>
       <c r="D231" s="3">
-        <f t="shared" si="3"/>
+        <f>100%-F231</f>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="E231" s="4">
@@ -12811,7 +12811,7 @@
         <v>630</v>
       </c>
       <c r="D232" s="3">
-        <f t="shared" si="3"/>
+        <f>100%-F232</f>
         <v>0</v>
       </c>
       <c r="E232" s="4">
@@ -12853,7 +12853,7 @@
         <v>274</v>
       </c>
       <c r="D233" s="3">
-        <f t="shared" si="3"/>
+        <f>100%-F233</f>
         <v>0.22999999999999998</v>
       </c>
       <c r="E233" s="4">
@@ -12895,7 +12895,7 @@
         <v>102</v>
       </c>
       <c r="D234" s="3">
-        <f t="shared" si="3"/>
+        <f>100%-F234</f>
         <v>0.65</v>
       </c>
       <c r="E234" s="4">
@@ -12937,7 +12937,7 @@
         <v>390</v>
       </c>
       <c r="D235" s="3">
-        <f t="shared" si="3"/>
+        <f>100%-F235</f>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E235" s="4">
@@ -12979,7 +12979,7 @@
         <v>238</v>
       </c>
       <c r="D236" s="3">
-        <f t="shared" si="3"/>
+        <f>100%-F236</f>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E236" s="4">
@@ -13021,7 +13021,7 @@
         <v>314</v>
       </c>
       <c r="D237" s="3">
-        <f t="shared" si="3"/>
+        <f>100%-F237</f>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="E237" s="4">
@@ -13063,7 +13063,7 @@
         <v>218</v>
       </c>
       <c r="D238" s="3">
-        <f t="shared" si="3"/>
+        <f>100%-F238</f>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E238" s="4">
@@ -13105,7 +13105,7 @@
         <v>232</v>
       </c>
       <c r="D239" s="3">
-        <f t="shared" si="3"/>
+        <f>100%-F239</f>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E239" s="4">
@@ -13147,7 +13147,7 @@
         <v>111</v>
       </c>
       <c r="D240" s="3">
-        <f t="shared" si="3"/>
+        <f>100%-F240</f>
         <v>0.38</v>
       </c>
       <c r="E240" s="4">
@@ -13189,7 +13189,7 @@
         <v>104</v>
       </c>
       <c r="D241" s="3">
-        <f t="shared" si="3"/>
+        <f>100%-F241</f>
         <v>0.38</v>
       </c>
       <c r="E241" s="4">
@@ -13231,7 +13231,7 @@
         <v>852</v>
       </c>
       <c r="D242" s="3">
-        <f t="shared" si="3"/>
+        <f>100%-F242</f>
         <v>0</v>
       </c>
       <c r="E242" s="4">
@@ -13273,7 +13273,7 @@
         <v>152</v>
       </c>
       <c r="D243" s="3">
-        <f t="shared" si="3"/>
+        <f>100%-F243</f>
         <v>0.22999999999999998</v>
       </c>
       <c r="E243" s="4">
@@ -13315,7 +13315,7 @@
         <v>679</v>
       </c>
       <c r="D244" s="3">
-        <f t="shared" si="3"/>
+        <f>100%-F244</f>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="E244" s="4">
@@ -13357,7 +13357,7 @@
         <v>145</v>
       </c>
       <c r="D245" s="3">
-        <f t="shared" si="3"/>
+        <f>100%-F245</f>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E245" s="4">
@@ -13399,7 +13399,7 @@
         <v>278</v>
       </c>
       <c r="D246" s="3">
-        <f t="shared" si="3"/>
+        <f>100%-F246</f>
         <v>0.32999999999999996</v>
       </c>
       <c r="E246" s="4">
@@ -13441,7 +13441,7 @@
         <v>224</v>
       </c>
       <c r="D247" s="3">
-        <f t="shared" si="3"/>
+        <f>100%-F247</f>
         <v>0.22999999999999998</v>
       </c>
       <c r="E247" s="4">
@@ -13483,7 +13483,7 @@
         <v>115</v>
       </c>
       <c r="D248" s="3">
-        <f t="shared" si="3"/>
+        <f>100%-F248</f>
         <v>0.22999999999999998</v>
       </c>
       <c r="E248" s="4">
@@ -13525,7 +13525,7 @@
         <v>992</v>
       </c>
       <c r="D249" s="3">
-        <f t="shared" si="3"/>
+        <f>100%-F249</f>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="E249" s="4">
@@ -13567,7 +13567,7 @@
         <v>189</v>
       </c>
       <c r="D250" s="3">
-        <f t="shared" si="3"/>
+        <f>100%-F250</f>
         <v>0.38</v>
       </c>
       <c r="E250" s="4">
@@ -13609,7 +13609,7 @@
         <v>217</v>
       </c>
       <c r="D251" s="3">
-        <f t="shared" si="3"/>
+        <f>100%-F251</f>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="E251" s="4">
@@ -13651,7 +13651,7 @@
         <v>231</v>
       </c>
       <c r="D252" s="3">
-        <f t="shared" si="3"/>
+        <f>100%-F252</f>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="E252" s="4">
@@ -13693,7 +13693,7 @@
         <v>259</v>
       </c>
       <c r="D253" s="3">
-        <f t="shared" si="3"/>
+        <f>100%-F253</f>
         <v>0.22999999999999998</v>
       </c>
       <c r="E253" s="4">
@@ -13735,7 +13735,7 @@
         <v>891</v>
       </c>
       <c r="D254" s="3">
-        <f t="shared" si="3"/>
+        <f>100%-F254</f>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="E254" s="4">
@@ -13777,7 +13777,7 @@
         <v>152</v>
       </c>
       <c r="D255" s="3">
-        <f t="shared" si="3"/>
+        <f>100%-F255</f>
         <v>0.37</v>
       </c>
       <c r="E255" s="4">
@@ -13819,7 +13819,7 @@
         <v>403</v>
       </c>
       <c r="D256" s="3">
-        <f t="shared" si="3"/>
+        <f>100%-F256</f>
         <v>0.22999999999999998</v>
       </c>
       <c r="E256" s="4">
@@ -13861,7 +13861,7 @@
         <v>2082</v>
       </c>
       <c r="D257" s="3">
-        <f t="shared" si="3"/>
+        <f>100%-F257</f>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="E257" s="4">
@@ -13903,7 +13903,7 @@
         <v>232</v>
       </c>
       <c r="D258" s="3">
-        <f t="shared" ref="D258:D321" si="4">100%-F258</f>
+        <f>100%-F258</f>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E258" s="4">
@@ -13945,7 +13945,7 @@
         <v>430</v>
       </c>
       <c r="D259" s="3">
-        <f t="shared" si="4"/>
+        <f>100%-F259</f>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E259" s="4">
@@ -13987,7 +13987,7 @@
         <v>128</v>
       </c>
       <c r="D260" s="3">
-        <f t="shared" si="4"/>
+        <f>100%-F260</f>
         <v>0.17000000000000004</v>
       </c>
       <c r="E260" s="4">
@@ -14029,7 +14029,7 @@
         <v>112</v>
       </c>
       <c r="D261" s="3">
-        <f t="shared" si="4"/>
+        <f>100%-F261</f>
         <v>0.37</v>
       </c>
       <c r="E261" s="4">
@@ -14071,7 +14071,7 @@
         <v>498</v>
       </c>
       <c r="D262" s="3">
-        <f t="shared" si="4"/>
+        <f>100%-F262</f>
         <v>0</v>
       </c>
       <c r="E262" s="4">
@@ -14113,7 +14113,7 @@
         <v>512</v>
       </c>
       <c r="D263" s="3">
-        <f t="shared" si="4"/>
+        <f>100%-F263</f>
         <v>0.22999999999999998</v>
       </c>
       <c r="E263" s="4">
@@ -14155,7 +14155,7 @@
         <v>1228</v>
       </c>
       <c r="D264" s="3">
-        <f t="shared" si="4"/>
+        <f>100%-F264</f>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="E264" s="4">
@@ -14197,7 +14197,7 @@
         <v>255</v>
       </c>
       <c r="D265" s="3">
-        <f t="shared" si="4"/>
+        <f>100%-F265</f>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E265" s="4">
@@ -14239,7 +14239,7 @@
         <v>102</v>
       </c>
       <c r="D266" s="3">
-        <f t="shared" si="4"/>
+        <f>100%-F266</f>
         <v>0.15000000000000002</v>
       </c>
       <c r="E266" s="4">
@@ -14281,7 +14281,7 @@
         <v>487</v>
       </c>
       <c r="D267" s="3">
-        <f t="shared" si="4"/>
+        <f>100%-F267</f>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E267" s="4">
@@ -14323,7 +14323,7 @@
         <v>226</v>
       </c>
       <c r="D268" s="3">
-        <f t="shared" si="4"/>
+        <f>100%-F268</f>
         <v>0.32999999999999996</v>
       </c>
       <c r="E268" s="4">
@@ -14365,7 +14365,7 @@
         <v>682</v>
       </c>
       <c r="D269" s="3">
-        <f t="shared" si="4"/>
+        <f>100%-F269</f>
         <v>0</v>
       </c>
       <c r="E269" s="4">
@@ -14407,7 +14407,7 @@
         <v>111</v>
       </c>
       <c r="D270" s="3">
-        <f t="shared" si="4"/>
+        <f>100%-F270</f>
         <v>0.31999999999999995</v>
       </c>
       <c r="E270" s="4">
@@ -14449,7 +14449,7 @@
         <v>543</v>
       </c>
       <c r="D271" s="3">
-        <f t="shared" si="4"/>
+        <f>100%-F271</f>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="E271" s="4">
@@ -14491,7 +14491,7 @@
         <v>1048</v>
       </c>
       <c r="D272" s="3">
-        <f t="shared" si="4"/>
+        <f>100%-F272</f>
         <v>0</v>
       </c>
       <c r="E272" s="4">
@@ -14533,7 +14533,7 @@
         <v>210</v>
       </c>
       <c r="D273" s="3">
-        <f t="shared" si="4"/>
+        <f>100%-F273</f>
         <v>0.22999999999999998</v>
       </c>
       <c r="E273" s="4">
@@ -14575,7 +14575,7 @@
         <v>297</v>
       </c>
       <c r="D274" s="3">
-        <f t="shared" si="4"/>
+        <f>100%-F274</f>
         <v>0.22999999999999998</v>
       </c>
       <c r="E274" s="4">
@@ -14617,7 +14617,7 @@
         <v>730</v>
       </c>
       <c r="D275" s="3">
-        <f t="shared" si="4"/>
+        <f>100%-F275</f>
         <v>0.22999999999999998</v>
       </c>
       <c r="E275" s="4">
@@ -14659,7 +14659,7 @@
         <v>12585</v>
       </c>
       <c r="D276" s="3">
-        <f t="shared" si="4"/>
+        <f>100%-F276</f>
         <v>0</v>
       </c>
       <c r="E276" s="4">
@@ -14701,7 +14701,7 @@
         <v>165</v>
       </c>
       <c r="D277" s="3">
-        <f t="shared" si="4"/>
+        <f>100%-F277</f>
         <v>0.22999999999999998</v>
       </c>
       <c r="E277" s="4">
@@ -14743,7 +14743,7 @@
         <v>208</v>
       </c>
       <c r="D278" s="3">
-        <f t="shared" si="4"/>
+        <f>100%-F278</f>
         <v>0.30000000000000004</v>
       </c>
       <c r="E278" s="4">
@@ -14785,7 +14785,7 @@
         <v>805</v>
       </c>
       <c r="D279" s="3">
-        <f t="shared" si="4"/>
+        <f>100%-F279</f>
         <v>0</v>
       </c>
       <c r="E279" s="4">
@@ -14827,7 +14827,7 @@
         <v>629</v>
       </c>
       <c r="D280" s="3">
-        <f t="shared" si="4"/>
+        <f>100%-F280</f>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="E280" s="4">
@@ -14869,7 +14869,7 @@
         <v>812</v>
       </c>
       <c r="D281" s="3">
-        <f t="shared" si="4"/>
+        <f>100%-F281</f>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E281" s="4">
@@ -14911,7 +14911,7 @@
         <v>210</v>
       </c>
       <c r="D282" s="3">
-        <f t="shared" si="4"/>
+        <f>100%-F282</f>
         <v>0.22999999999999998</v>
       </c>
       <c r="E282" s="4">
@@ -14953,7 +14953,7 @@
         <v>208</v>
       </c>
       <c r="D283" s="3">
-        <f t="shared" si="4"/>
+        <f>100%-F283</f>
         <v>0.30000000000000004</v>
       </c>
       <c r="E283" s="4">
@@ -14995,7 +14995,7 @@
         <v>146</v>
       </c>
       <c r="D284" s="3">
-        <f t="shared" si="4"/>
+        <f>100%-F284</f>
         <v>0.37</v>
       </c>
       <c r="E284" s="4">
@@ -15037,7 +15037,7 @@
         <v>761</v>
       </c>
       <c r="D285" s="3">
-        <f t="shared" si="4"/>
+        <f>100%-F285</f>
         <v>0</v>
       </c>
       <c r="E285" s="5">
@@ -15079,7 +15079,7 @@
         <v>584</v>
       </c>
       <c r="D286" s="3">
-        <f t="shared" si="4"/>
+        <f>100%-F286</f>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E286" s="4">
@@ -15121,7 +15121,7 @@
         <v>118</v>
       </c>
       <c r="D287" s="3">
-        <f t="shared" si="4"/>
+        <f>100%-F287</f>
         <v>0.30000000000000004</v>
       </c>
       <c r="E287" s="4">
@@ -15163,7 +15163,7 @@
         <v>596</v>
       </c>
       <c r="D288" s="3">
-        <f t="shared" si="4"/>
+        <f>100%-F288</f>
         <v>0.30000000000000004</v>
       </c>
       <c r="E288" s="4">
@@ -15205,7 +15205,7 @@
         <v>302</v>
       </c>
       <c r="D289" s="3">
-        <f t="shared" si="4"/>
+        <f>100%-F289</f>
         <v>0.22999999999999998</v>
       </c>
       <c r="E289" s="4">
@@ -15247,7 +15247,7 @@
         <v>204</v>
       </c>
       <c r="D290" s="3">
-        <f t="shared" si="4"/>
+        <f>100%-F290</f>
         <v>0.30000000000000004</v>
       </c>
       <c r="E290" s="4">
@@ -15289,7 +15289,7 @@
         <v>337</v>
       </c>
       <c r="D291" s="3">
-        <f t="shared" si="4"/>
+        <f>100%-F291</f>
         <v>0.15000000000000002</v>
       </c>
       <c r="E291" s="4">
@@ -15331,7 +15331,7 @@
         <v>474</v>
       </c>
       <c r="D292" s="3">
-        <f t="shared" si="4"/>
+        <f>100%-F292</f>
         <v>0.13</v>
       </c>
       <c r="E292" s="4">
@@ -15373,7 +15373,7 @@
         <v>584</v>
       </c>
       <c r="D293" s="3">
-        <f t="shared" si="4"/>
+        <f>100%-F293</f>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E293" s="4">
@@ -15415,7 +15415,7 @@
         <v>254</v>
       </c>
       <c r="D294" s="3">
-        <f t="shared" si="4"/>
+        <f>100%-F294</f>
         <v>0.22999999999999998</v>
       </c>
       <c r="E294" s="4">
@@ -15457,7 +15457,7 @@
         <v>230</v>
       </c>
       <c r="D295" s="3">
-        <f t="shared" si="4"/>
+        <f>100%-F295</f>
         <v>0.30000000000000004</v>
       </c>
       <c r="E295" s="4">
@@ -15499,7 +15499,7 @@
         <v>358</v>
       </c>
       <c r="D296" s="3">
-        <f t="shared" si="4"/>
+        <f>100%-F296</f>
         <v>0.28000000000000003</v>
       </c>
       <c r="E296" s="4">
@@ -15542,7 +15542,7 @@
         <v>5961</v>
       </c>
       <c r="D297" s="3">
-        <f t="shared" si="4"/>
+        <f>100%-F297</f>
         <v>0</v>
       </c>
       <c r="E297" s="4">
@@ -15584,7 +15584,7 @@
         <v>125</v>
       </c>
       <c r="D298" s="3">
-        <f t="shared" si="4"/>
+        <f>100%-F298</f>
         <v>0.37</v>
       </c>
       <c r="E298" s="4">
@@ -15626,7 +15626,7 @@
         <v>1189</v>
       </c>
       <c r="D299" s="3">
-        <f t="shared" si="4"/>
+        <f>100%-F299</f>
         <v>0.25</v>
       </c>
       <c r="E299" s="4">
@@ -15668,7 +15668,7 @@
         <v>120</v>
       </c>
       <c r="D300" s="3">
-        <f t="shared" si="4"/>
+        <f>100%-F300</f>
         <v>0.44999999999999996</v>
       </c>
       <c r="E300" s="4">
@@ -15710,7 +15710,7 @@
         <v>560</v>
       </c>
       <c r="D301" s="3">
-        <f t="shared" si="4"/>
+        <f>100%-F301</f>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E301" s="4">
@@ -15753,7 +15753,7 @@
         <v>1210</v>
       </c>
       <c r="D302" s="3">
-        <f t="shared" si="4"/>
+        <f>100%-F302</f>
         <v>0</v>
       </c>
       <c r="E302" s="4">
@@ -15795,7 +15795,7 @@
         <v>101</v>
       </c>
       <c r="D303" s="3">
-        <f t="shared" si="4"/>
+        <f>100%-F303</f>
         <v>0.44999999999999996</v>
       </c>
       <c r="E303" s="4">
@@ -15837,7 +15837,7 @@
         <v>1082</v>
       </c>
       <c r="D304" s="3">
-        <f t="shared" si="4"/>
+        <f>100%-F304</f>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E304" s="4">
@@ -15880,7 +15880,7 @@
         <v>246</v>
       </c>
       <c r="D305" s="3">
-        <f t="shared" si="4"/>
+        <f>100%-F305</f>
         <v>0.22999999999999998</v>
       </c>
       <c r="E305" s="4">
@@ -15923,7 +15923,7 @@
         <v>557</v>
       </c>
       <c r="D306" s="3">
-        <f t="shared" si="4"/>
+        <f>100%-F306</f>
         <v>0.32999999999999996</v>
       </c>
       <c r="E306" s="4">
@@ -15965,7 +15965,7 @@
         <v>177</v>
       </c>
       <c r="D307" s="3">
-        <f t="shared" si="4"/>
+        <f>100%-F307</f>
         <v>0.72</v>
       </c>
       <c r="E307" s="4">
@@ -16007,7 +16007,7 @@
         <v>1276</v>
       </c>
       <c r="D308" s="3">
-        <f t="shared" si="4"/>
+        <f>100%-F308</f>
         <v>0</v>
       </c>
       <c r="E308" s="4">
@@ -16049,7 +16049,7 @@
         <v>397</v>
       </c>
       <c r="D309" s="3">
-        <f t="shared" si="4"/>
+        <f>100%-F309</f>
         <v>0.22999999999999998</v>
       </c>
       <c r="E309" s="4">
@@ -16091,7 +16091,7 @@
         <v>285</v>
       </c>
       <c r="D310" s="3">
-        <f t="shared" si="4"/>
+        <f>100%-F310</f>
         <v>0.37</v>
       </c>
       <c r="E310" s="4">
@@ -16133,7 +16133,7 @@
         <v>952</v>
       </c>
       <c r="D311" s="3">
-        <f t="shared" si="4"/>
+        <f>100%-F311</f>
         <v>0</v>
       </c>
       <c r="E311" s="4">
@@ -16175,7 +16175,7 @@
         <v>5078</v>
       </c>
       <c r="D312" s="3">
-        <f t="shared" si="4"/>
+        <f>100%-F312</f>
         <v>0</v>
       </c>
       <c r="E312" s="4">
@@ -16217,7 +16217,7 @@
         <v>17053</v>
       </c>
       <c r="D313" s="3">
-        <f t="shared" si="4"/>
+        <f>100%-F313</f>
         <v>0</v>
       </c>
       <c r="E313" s="5">
@@ -16259,7 +16259,7 @@
         <v>373</v>
       </c>
       <c r="D314" s="3">
-        <f t="shared" si="4"/>
+        <f>100%-F314</f>
         <v>0.30000000000000004</v>
       </c>
       <c r="E314" s="4">
@@ -16301,7 +16301,7 @@
         <v>859</v>
       </c>
       <c r="D315" s="3">
-        <f t="shared" si="4"/>
+        <f>100%-F315</f>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E315" s="4">
@@ -16343,7 +16343,7 @@
         <v>365</v>
       </c>
       <c r="D316" s="3">
-        <f t="shared" si="4"/>
+        <f>100%-F316</f>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E316" s="4">
@@ -16385,7 +16385,7 @@
         <v>496</v>
       </c>
       <c r="D317" s="3">
-        <f t="shared" si="4"/>
+        <f>100%-F317</f>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E317" s="4">
@@ -16427,7 +16427,7 @@
         <v>1631</v>
       </c>
       <c r="D318" s="3">
-        <f t="shared" si="4"/>
+        <f>100%-F318</f>
         <v>0</v>
       </c>
       <c r="E318" s="4">
@@ -16469,7 +16469,7 @@
         <v>955</v>
       </c>
       <c r="D319" s="3">
-        <f t="shared" si="4"/>
+        <f>100%-F319</f>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E319" s="4">
@@ -16511,7 +16511,7 @@
         <v>923</v>
       </c>
       <c r="D320" s="3">
-        <f t="shared" si="4"/>
+        <f>100%-F320</f>
         <v>0.22999999999999998</v>
       </c>
       <c r="E320" s="4">
@@ -16553,7 +16553,7 @@
         <v>3670</v>
       </c>
       <c r="D321" s="3">
-        <f t="shared" si="4"/>
+        <f>100%-F321</f>
         <v>0</v>
       </c>
       <c r="E321" s="4">
@@ -16595,7 +16595,7 @@
         <v>222</v>
       </c>
       <c r="D322" s="3">
-        <f t="shared" ref="D322:D385" si="5">100%-F322</f>
+        <f>100%-F322</f>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E322" s="4">
@@ -16637,7 +16637,7 @@
         <v>890</v>
       </c>
       <c r="D323" s="3">
-        <f t="shared" si="5"/>
+        <f>100%-F323</f>
         <v>0</v>
       </c>
       <c r="E323" s="4">
@@ -16679,7 +16679,7 @@
         <v>265</v>
       </c>
       <c r="D324" s="3">
-        <f t="shared" si="5"/>
+        <f>100%-F324</f>
         <v>0.25</v>
       </c>
       <c r="E324" s="4">
@@ -16721,7 +16721,7 @@
         <v>875</v>
       </c>
       <c r="D325" s="3">
-        <f t="shared" si="5"/>
+        <f>100%-F325</f>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="E325" s="4">
@@ -16763,7 +16763,7 @@
         <v>446</v>
       </c>
       <c r="D326" s="3">
-        <f t="shared" si="5"/>
+        <f>100%-F326</f>
         <v>0.38</v>
       </c>
       <c r="E326" s="4">
@@ -16806,7 +16806,7 @@
         <v>111</v>
       </c>
       <c r="D327" s="3">
-        <f t="shared" si="5"/>
+        <f>100%-F327</f>
         <v>0.37</v>
       </c>
       <c r="E327" s="4">
@@ -16848,7 +16848,7 @@
         <v>585</v>
       </c>
       <c r="D328" s="3">
-        <f t="shared" si="5"/>
+        <f>100%-F328</f>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="E328" s="4">
@@ -16890,7 +16890,7 @@
         <v>801</v>
       </c>
       <c r="D329" s="3">
-        <f t="shared" si="5"/>
+        <f>100%-F329</f>
         <v>0</v>
       </c>
       <c r="E329" s="4">
@@ -16932,7 +16932,7 @@
         <v>191</v>
       </c>
       <c r="D330" s="3">
-        <f t="shared" si="5"/>
+        <f>100%-F330</f>
         <v>0.30000000000000004</v>
       </c>
       <c r="E330" s="4">
@@ -16975,7 +16975,7 @@
         <v>2820</v>
       </c>
       <c r="D331" s="3">
-        <f t="shared" si="5"/>
+        <f>100%-F331</f>
         <v>0</v>
       </c>
       <c r="E331" s="4">
@@ -17017,7 +17017,7 @@
         <v>805</v>
       </c>
       <c r="D332" s="3">
-        <f t="shared" si="5"/>
+        <f>100%-F332</f>
         <v>0</v>
       </c>
       <c r="E332" s="4">
@@ -17059,7 +17059,7 @@
         <v>147</v>
       </c>
       <c r="D333" s="3">
-        <f t="shared" si="5"/>
+        <f>100%-F333</f>
         <v>0.8</v>
       </c>
       <c r="E333" s="4">
@@ -17101,7 +17101,7 @@
         <v>227</v>
       </c>
       <c r="D334" s="3">
-        <f t="shared" si="5"/>
+        <f>100%-F334</f>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E334" s="4">
@@ -17144,7 +17144,7 @@
         <v>580</v>
       </c>
       <c r="D335" s="3">
-        <f t="shared" si="5"/>
+        <f>100%-F335</f>
         <v>0</v>
       </c>
       <c r="E335" s="4">
@@ -17186,7 +17186,7 @@
         <v>924</v>
       </c>
       <c r="D336" s="3">
-        <f t="shared" si="5"/>
+        <f>100%-F336</f>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E336" s="4">
@@ -17229,7 +17229,7 @@
         <v>492</v>
       </c>
       <c r="D337" s="3">
-        <f t="shared" si="5"/>
+        <f>100%-F337</f>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E337" s="4">
@@ -17271,7 +17271,7 @@
         <v>880</v>
       </c>
       <c r="D338" s="3">
-        <f t="shared" si="5"/>
+        <f>100%-F338</f>
         <v>0</v>
       </c>
       <c r="E338" s="4">
@@ -17313,7 +17313,7 @@
         <v>272</v>
       </c>
       <c r="D339" s="3">
-        <f t="shared" si="5"/>
+        <f>100%-F339</f>
         <v>0.30000000000000004</v>
       </c>
       <c r="E339" s="4">
@@ -17355,7 +17355,7 @@
         <v>915</v>
       </c>
       <c r="D340" s="3">
-        <f t="shared" si="5"/>
+        <f>100%-F340</f>
         <v>0</v>
       </c>
       <c r="E340" s="4">
@@ -17397,7 +17397,7 @@
         <v>413</v>
       </c>
       <c r="D341" s="3">
-        <f t="shared" si="5"/>
+        <f>100%-F341</f>
         <v>0.30000000000000004</v>
       </c>
       <c r="E341" s="4">
@@ -17440,7 +17440,7 @@
         <v>683</v>
       </c>
       <c r="D342" s="3">
-        <f t="shared" si="5"/>
+        <f>100%-F342</f>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="E342" s="4">
@@ -17482,7 +17482,7 @@
         <v>767</v>
       </c>
       <c r="D343" s="3">
-        <f t="shared" si="5"/>
+        <f>100%-F343</f>
         <v>0.38</v>
       </c>
       <c r="E343" s="4">
@@ -17524,7 +17524,7 @@
         <v>323</v>
       </c>
       <c r="D344" s="3">
-        <f t="shared" si="5"/>
+        <f>100%-F344</f>
         <v>0.22999999999999998</v>
       </c>
       <c r="E344" s="4">
@@ -17566,7 +17566,7 @@
         <v>942</v>
       </c>
       <c r="D345" s="3">
-        <f t="shared" si="5"/>
+        <f>100%-F345</f>
         <v>0</v>
       </c>
       <c r="E345" s="4">
@@ -17608,7 +17608,7 @@
         <v>297</v>
       </c>
       <c r="D346" s="3">
-        <f t="shared" si="5"/>
+        <f>100%-F346</f>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E346" s="4">
@@ -17651,7 +17651,7 @@
         <v>461</v>
       </c>
       <c r="D347" s="3">
-        <f t="shared" si="5"/>
+        <f>100%-F347</f>
         <v>0.22999999999999998</v>
       </c>
       <c r="E347" s="4">
@@ -17693,7 +17693,7 @@
         <v>588</v>
       </c>
       <c r="D348" s="3">
-        <f t="shared" si="5"/>
+        <f>100%-F348</f>
         <v>0.22999999999999998</v>
       </c>
       <c r="E348" s="4">
@@ -17736,7 +17736,7 @@
         <v>370</v>
       </c>
       <c r="D349" s="3">
-        <f t="shared" si="5"/>
+        <f>100%-F349</f>
         <v>0.30000000000000004</v>
       </c>
       <c r="E349" s="4">
@@ -17779,7 +17779,7 @@
         <v>510</v>
       </c>
       <c r="D350" s="3">
-        <f t="shared" si="5"/>
+        <f>100%-F350</f>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="E350" s="4">
@@ -17821,7 +17821,7 @@
         <v>220</v>
       </c>
       <c r="D351" s="3">
-        <f t="shared" si="5"/>
+        <f>100%-F351</f>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E351" s="4">
@@ -17863,7 +17863,7 @@
         <v>627</v>
       </c>
       <c r="D352" s="3">
-        <f t="shared" si="5"/>
+        <f>100%-F352</f>
         <v>0</v>
       </c>
       <c r="E352" s="4">
@@ -17905,7 +17905,7 @@
         <v>276</v>
       </c>
       <c r="D353" s="3">
-        <f t="shared" si="5"/>
+        <f>100%-F353</f>
         <v>0.30000000000000004</v>
       </c>
       <c r="E353" s="4">
@@ -17947,7 +17947,7 @@
         <v>1483</v>
       </c>
       <c r="D354" s="3">
-        <f t="shared" si="5"/>
+        <f>100%-F354</f>
         <v>0</v>
       </c>
       <c r="E354" s="4">
@@ -17989,7 +17989,7 @@
         <v>504</v>
       </c>
       <c r="D355" s="3">
-        <f t="shared" si="5"/>
+        <f>100%-F355</f>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E355" s="4">
@@ -18032,7 +18032,7 @@
         <v>8955</v>
       </c>
       <c r="D356" s="3">
-        <f t="shared" si="5"/>
+        <f>100%-F356</f>
         <v>0</v>
       </c>
       <c r="E356" s="4">
@@ -18074,7 +18074,7 @@
         <v>360</v>
       </c>
       <c r="D357" s="3">
-        <f t="shared" si="5"/>
+        <f>100%-F357</f>
         <v>0.30000000000000004</v>
       </c>
       <c r="E357" s="4">
@@ -18116,7 +18116,7 @@
         <v>105</v>
       </c>
       <c r="D358" s="3">
-        <f t="shared" si="5"/>
+        <f>100%-F358</f>
         <v>0.73</v>
       </c>
       <c r="E358" s="4">
@@ -18158,7 +18158,7 @@
         <v>1012</v>
       </c>
       <c r="D359" s="3">
-        <f t="shared" si="5"/>
+        <f>100%-F359</f>
         <v>0</v>
       </c>
       <c r="E359" s="5">
@@ -18200,7 +18200,7 @@
         <v>139</v>
       </c>
       <c r="D360" s="3">
-        <f t="shared" si="5"/>
+        <f>100%-F360</f>
         <v>0.8</v>
       </c>
       <c r="E360" s="6">
@@ -18243,7 +18243,7 @@
         <v>776</v>
       </c>
       <c r="D361" s="3">
-        <f t="shared" si="5"/>
+        <f>100%-F361</f>
         <v>0</v>
       </c>
       <c r="E361" s="6">
@@ -18285,7 +18285,7 @@
         <v>217</v>
       </c>
       <c r="D362" s="3">
-        <f t="shared" si="5"/>
+        <f>100%-F362</f>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E362" s="6">
@@ -18327,7 +18327,7 @@
         <v>215</v>
       </c>
       <c r="D363" s="3">
-        <f t="shared" si="5"/>
+        <f>100%-F363</f>
         <v>0.32999999999999996</v>
       </c>
       <c r="E363" s="6">
@@ -18369,7 +18369,7 @@
         <v>274</v>
       </c>
       <c r="D364" s="3">
-        <f t="shared" si="5"/>
+        <f>100%-F364</f>
         <v>0.22999999999999998</v>
       </c>
       <c r="E364" s="6">
@@ -18411,7 +18411,7 @@
         <v>146</v>
       </c>
       <c r="D365" s="3">
-        <f t="shared" si="5"/>
+        <f>100%-F365</f>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E365" s="6">
@@ -18453,7 +18453,7 @@
         <v>1711</v>
       </c>
       <c r="D366" s="3">
-        <f t="shared" si="5"/>
+        <f>100%-F366</f>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E366" s="6">
@@ -18495,7 +18495,7 @@
         <v>357</v>
       </c>
       <c r="D367" s="3">
-        <f t="shared" si="5"/>
+        <f>100%-F367</f>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="E367" s="6">
@@ -18537,7 +18537,7 @@
         <v>122</v>
       </c>
       <c r="D368" s="3">
-        <f t="shared" si="5"/>
+        <f>100%-F368</f>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E368" s="6">
@@ -18579,7 +18579,7 @@
         <v>199</v>
       </c>
       <c r="D369" s="3">
-        <f t="shared" si="5"/>
+        <f>100%-F369</f>
         <v>0.30000000000000004</v>
       </c>
       <c r="E369" s="6">
@@ -18621,7 +18621,7 @@
         <v>162</v>
       </c>
       <c r="D370" s="3">
-        <f t="shared" si="5"/>
+        <f>100%-F370</f>
         <v>0.15000000000000002</v>
       </c>
       <c r="E370" s="6">
@@ -18663,7 +18663,7 @@
         <v>138</v>
       </c>
       <c r="D371" s="3">
-        <f t="shared" si="5"/>
+        <f>100%-F371</f>
         <v>0.8</v>
       </c>
       <c r="E371" s="6">
@@ -18705,7 +18705,7 @@
         <v>387</v>
       </c>
       <c r="D372" s="3">
-        <f t="shared" si="5"/>
+        <f>100%-F372</f>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="E372" s="4">
@@ -18748,7 +18748,7 @@
         <v>365</v>
       </c>
       <c r="D373" s="3">
-        <f t="shared" si="5"/>
+        <f>100%-F373</f>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="E373" s="4">
@@ -18790,7 +18790,7 @@
         <v>244</v>
       </c>
       <c r="D374" s="3">
-        <f t="shared" si="5"/>
+        <f>100%-F374</f>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E374" s="4">
@@ -18832,7 +18832,7 @@
         <v>514</v>
       </c>
       <c r="D375" s="3">
-        <f t="shared" si="5"/>
+        <f>100%-F375</f>
         <v>0</v>
       </c>
       <c r="E375" s="4">
@@ -18874,7 +18874,7 @@
         <v>421</v>
       </c>
       <c r="D376" s="3">
-        <f t="shared" si="5"/>
+        <f>100%-F376</f>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="E376" s="4">
@@ -18916,7 +18916,7 @@
         <v>520</v>
       </c>
       <c r="D377" s="3">
-        <f t="shared" si="5"/>
+        <f>100%-F377</f>
         <v>0</v>
       </c>
       <c r="E377" s="4">
@@ -18958,7 +18958,7 @@
         <v>164</v>
       </c>
       <c r="D378" s="3">
-        <f t="shared" si="5"/>
+        <f>100%-F378</f>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E378" s="4">
@@ -19001,7 +19001,7 @@
         <v>290</v>
       </c>
       <c r="D379" s="3">
-        <f t="shared" si="5"/>
+        <f>100%-F379</f>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E379" s="4">
@@ -19043,7 +19043,7 @@
         <v>252</v>
       </c>
       <c r="D380" s="3">
-        <f t="shared" si="5"/>
+        <f>100%-F380</f>
         <v>0.38</v>
       </c>
       <c r="E380" s="4">
@@ -19086,7 +19086,7 @@
         <v>451</v>
       </c>
       <c r="D381" s="3">
-        <f t="shared" si="5"/>
+        <f>100%-F381</f>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="E381" s="4">
@@ -19128,7 +19128,7 @@
         <v>207</v>
       </c>
       <c r="D382" s="3">
-        <f t="shared" si="5"/>
+        <f>100%-F382</f>
         <v>0.17000000000000004</v>
       </c>
       <c r="E382" s="4">
@@ -19170,7 +19170,7 @@
         <v>1457</v>
       </c>
       <c r="D383" s="3">
-        <f t="shared" si="5"/>
+        <f>100%-F383</f>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E383" s="4">
@@ -19212,7 +19212,7 @@
         <v>174</v>
       </c>
       <c r="D384" s="3">
-        <f t="shared" si="5"/>
+        <f>100%-F384</f>
         <v>0.44999999999999996</v>
       </c>
       <c r="E384" s="4">
@@ -19254,7 +19254,7 @@
         <v>571</v>
       </c>
       <c r="D385" s="3">
-        <f t="shared" si="5"/>
+        <f>100%-F385</f>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E385" s="4">
@@ -19296,7 +19296,7 @@
         <v>253</v>
       </c>
       <c r="D386" s="3">
-        <f t="shared" ref="D386:D449" si="6">100%-F386</f>
+        <f>100%-F386</f>
         <v>0.38</v>
       </c>
       <c r="E386" s="4">
@@ -19338,7 +19338,7 @@
         <v>147</v>
       </c>
       <c r="D387" s="3">
-        <f t="shared" si="6"/>
+        <f>100%-F387</f>
         <v>0.19999999999999996</v>
       </c>
       <c r="E387" s="4">
@@ -19380,7 +19380,7 @@
         <v>306</v>
       </c>
       <c r="D388" s="3">
-        <f t="shared" si="6"/>
+        <f>100%-F388</f>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E388" s="4">
@@ -19422,7 +19422,7 @@
         <v>575</v>
       </c>
       <c r="D389" s="3">
-        <f t="shared" si="6"/>
+        <f>100%-F389</f>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="E389" s="4">
@@ -19464,7 +19464,7 @@
         <v>235</v>
       </c>
       <c r="D390" s="3">
-        <f t="shared" si="6"/>
+        <f>100%-F390</f>
         <v>0.25</v>
       </c>
       <c r="E390" s="4">
@@ -19506,7 +19506,7 @@
         <v>631</v>
       </c>
       <c r="D391" s="3">
-        <f t="shared" si="6"/>
+        <f>100%-F391</f>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="E391" s="4">
@@ -19548,7 +19548,7 @@
         <v>431</v>
       </c>
       <c r="D392" s="3">
-        <f t="shared" si="6"/>
+        <f>100%-F392</f>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="E392" s="4">
@@ -19590,7 +19590,7 @@
         <v>526</v>
       </c>
       <c r="D393" s="3">
-        <f t="shared" si="6"/>
+        <f>100%-F393</f>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="E393" s="4">
@@ -19632,7 +19632,7 @@
         <v>201</v>
       </c>
       <c r="D394" s="3">
-        <f t="shared" si="6"/>
+        <f>100%-F394</f>
         <v>0.38</v>
       </c>
       <c r="E394" s="4">
@@ -19674,7 +19674,7 @@
         <v>354</v>
       </c>
       <c r="D395" s="3">
-        <f t="shared" si="6"/>
+        <f>100%-F395</f>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="E395" s="4">
@@ -19716,7 +19716,7 @@
         <v>270</v>
       </c>
       <c r="D396" s="3">
-        <f t="shared" si="6"/>
+        <f>100%-F396</f>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E396" s="4">
@@ -19758,7 +19758,7 @@
         <v>571</v>
       </c>
       <c r="D397" s="3">
-        <f t="shared" si="6"/>
+        <f>100%-F397</f>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="E397" s="4">
@@ -19800,7 +19800,7 @@
         <v>106</v>
       </c>
       <c r="D398" s="3">
-        <f t="shared" si="6"/>
+        <f>100%-F398</f>
         <v>0.37</v>
       </c>
       <c r="E398" s="4">
@@ -19842,7 +19842,7 @@
         <v>372</v>
       </c>
       <c r="D399" s="3">
-        <f t="shared" si="6"/>
+        <f>100%-F399</f>
         <v>0.12</v>
       </c>
       <c r="E399" s="4">
@@ -19884,7 +19884,7 @@
         <v>182</v>
       </c>
       <c r="D400" s="3">
-        <f t="shared" si="6"/>
+        <f>100%-F400</f>
         <v>0.30000000000000004</v>
       </c>
       <c r="E400" s="4">
@@ -19926,7 +19926,7 @@
         <v>501</v>
       </c>
       <c r="D401" s="3">
-        <f t="shared" si="6"/>
+        <f>100%-F401</f>
         <v>0</v>
       </c>
       <c r="E401" s="4">
@@ -19968,7 +19968,7 @@
         <v>486</v>
       </c>
       <c r="D402" s="3">
-        <f t="shared" si="6"/>
+        <f>100%-F402</f>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="E402" s="4">
@@ -20010,7 +20010,7 @@
         <v>517</v>
       </c>
       <c r="D403" s="3">
-        <f t="shared" si="6"/>
+        <f>100%-F403</f>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E403" s="4">
@@ -20052,7 +20052,7 @@
         <v>252</v>
       </c>
       <c r="D404" s="3">
-        <f t="shared" si="6"/>
+        <f>100%-F404</f>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="E404" s="4">
@@ -20094,7 +20094,7 @@
         <v>310</v>
       </c>
       <c r="D405" s="3">
-        <f t="shared" si="6"/>
+        <f>100%-F405</f>
         <v>0.15000000000000002</v>
       </c>
       <c r="E405" s="4">
@@ -20136,7 +20136,7 @@
         <v>339</v>
       </c>
       <c r="D406" s="3">
-        <f t="shared" si="6"/>
+        <f>100%-F406</f>
         <v>0.17000000000000004</v>
       </c>
       <c r="E406" s="4">
@@ -20178,7 +20178,7 @@
         <v>178</v>
       </c>
       <c r="D407" s="3">
-        <f t="shared" si="6"/>
+        <f>100%-F407</f>
         <v>0.38</v>
       </c>
       <c r="E407" s="4">
@@ -20220,7 +20220,7 @@
         <v>173</v>
       </c>
       <c r="D408" s="3">
-        <f t="shared" si="6"/>
+        <f>100%-F408</f>
         <v>0.12</v>
       </c>
       <c r="E408" s="4">
@@ -20262,7 +20262,7 @@
         <v>515</v>
       </c>
       <c r="D409" s="3">
-        <f t="shared" si="6"/>
+        <f>100%-F409</f>
         <v>0.15000000000000002</v>
       </c>
       <c r="E409" s="4">
@@ -20304,7 +20304,7 @@
         <v>169</v>
       </c>
       <c r="D410" s="3">
-        <f t="shared" si="6"/>
+        <f>100%-F410</f>
         <v>0.4</v>
       </c>
       <c r="E410" s="4">
@@ -20346,7 +20346,7 @@
         <v>401</v>
       </c>
       <c r="D411" s="3">
-        <f t="shared" si="6"/>
+        <f>100%-F411</f>
         <v>0</v>
       </c>
       <c r="E411" s="4">
@@ -20388,7 +20388,7 @@
         <v>267</v>
       </c>
       <c r="D412" s="3">
-        <f t="shared" si="6"/>
+        <f>100%-F412</f>
         <v>0.12</v>
       </c>
       <c r="E412" s="4">
@@ -20430,7 +20430,7 @@
         <v>153</v>
       </c>
       <c r="D413" s="3">
-        <f t="shared" si="6"/>
+        <f>100%-F413</f>
         <v>0.17000000000000004</v>
       </c>
       <c r="E413" s="4">
@@ -20472,7 +20472,7 @@
         <v>125</v>
       </c>
       <c r="D414" s="3">
-        <f t="shared" si="6"/>
+        <f>100%-F414</f>
         <v>0.17000000000000004</v>
       </c>
       <c r="E414" s="4">
@@ -20514,7 +20514,7 @@
         <v>295</v>
       </c>
       <c r="D415" s="3">
-        <f t="shared" si="6"/>
+        <f>100%-F415</f>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="E415" s="4">
@@ -20556,7 +20556,7 @@
         <v>224</v>
       </c>
       <c r="D416" s="3">
-        <f t="shared" si="6"/>
+        <f>100%-F416</f>
         <v>0.12</v>
       </c>
       <c r="E416" s="4">
@@ -20598,7 +20598,7 @@
         <v>152</v>
       </c>
       <c r="D417" s="3">
-        <f t="shared" si="6"/>
+        <f>100%-F417</f>
         <v>0.44999999999999996</v>
       </c>
       <c r="E417" s="4">
@@ -20640,7 +20640,7 @@
         <v>193</v>
       </c>
       <c r="D418" s="3">
-        <f t="shared" si="6"/>
+        <f>100%-F418</f>
         <v>0.12</v>
       </c>
       <c r="E418" s="4">
@@ -20682,7 +20682,7 @@
         <v>4974</v>
       </c>
       <c r="D419" s="3">
-        <f t="shared" si="6"/>
+        <f>100%-F419</f>
         <v>0</v>
       </c>
       <c r="E419" s="4">
@@ -20724,7 +20724,7 @@
         <v>194</v>
       </c>
       <c r="D420" s="3">
-        <f t="shared" si="6"/>
+        <f>100%-F420</f>
         <v>0.4</v>
       </c>
       <c r="E420" s="4">
@@ -20766,7 +20766,7 @@
         <v>103</v>
       </c>
       <c r="D421" s="3">
-        <f t="shared" si="6"/>
+        <f>100%-F421</f>
         <v>0.17000000000000004</v>
       </c>
       <c r="E421" s="4">
@@ -20808,7 +20808,7 @@
         <v>210</v>
       </c>
       <c r="D422" s="3">
-        <f t="shared" si="6"/>
+        <f>100%-F422</f>
         <v>0.17000000000000004</v>
       </c>
       <c r="E422" s="4">
@@ -20850,7 +20850,7 @@
         <v>204</v>
       </c>
       <c r="D423" s="3">
-        <f t="shared" si="6"/>
+        <f>100%-F423</f>
         <v>0.15000000000000002</v>
       </c>
       <c r="E423" s="4">
@@ -20892,7 +20892,7 @@
         <v>220</v>
       </c>
       <c r="D424" s="3">
-        <f t="shared" si="6"/>
+        <f>100%-F424</f>
         <v>0.12</v>
       </c>
       <c r="E424" s="4">
@@ -20934,7 +20934,7 @@
         <v>252</v>
       </c>
       <c r="D425" s="3">
-        <f t="shared" si="6"/>
+        <f>100%-F425</f>
         <v>0.4</v>
       </c>
       <c r="E425" s="4">
@@ -20976,7 +20976,7 @@
         <v>140</v>
       </c>
       <c r="D426" s="3">
-        <f t="shared" si="6"/>
+        <f>100%-F426</f>
         <v>0.44999999999999996</v>
       </c>
       <c r="E426" s="4">
@@ -21018,7 +21018,7 @@
         <v>104</v>
       </c>
       <c r="D427" s="3">
-        <f t="shared" si="6"/>
+        <f>100%-F427</f>
         <v>0.44999999999999996</v>
       </c>
       <c r="E427" s="4">
@@ -21060,7 +21060,7 @@
         <v>262</v>
       </c>
       <c r="D428" s="3">
-        <f t="shared" si="6"/>
+        <f>100%-F428</f>
         <v>0.38</v>
       </c>
       <c r="E428" s="4">
@@ -21102,7 +21102,7 @@
         <v>120</v>
       </c>
       <c r="D429" s="3">
-        <f t="shared" si="6"/>
+        <f>100%-F429</f>
         <v>0.31999999999999995</v>
       </c>
       <c r="E429" s="4">
@@ -21144,7 +21144,7 @@
         <v>363</v>
       </c>
       <c r="D430" s="3">
-        <f t="shared" si="6"/>
+        <f>100%-F430</f>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="E430" s="4">
@@ -21186,7 +21186,7 @@
         <v>107</v>
       </c>
       <c r="D431" s="3">
-        <f t="shared" si="6"/>
+        <f>100%-F431</f>
         <v>0.8</v>
       </c>
       <c r="E431" s="4">
@@ -21228,7 +21228,7 @@
         <v>519</v>
       </c>
       <c r="D432" s="3">
-        <f t="shared" si="6"/>
+        <f>100%-F432</f>
         <v>0.18000000000000005</v>
       </c>
       <c r="E432" s="4">
@@ -21270,7 +21270,7 @@
         <v>194</v>
       </c>
       <c r="D433" s="3">
-        <f t="shared" si="6"/>
+        <f>100%-F433</f>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E433" s="4">
@@ -21312,7 +21312,7 @@
         <v>334</v>
       </c>
       <c r="D434" s="3">
-        <f t="shared" si="6"/>
+        <f>100%-F434</f>
         <v>0.18000000000000005</v>
       </c>
       <c r="E434" s="4">
@@ -21354,7 +21354,7 @@
         <v>144</v>
       </c>
       <c r="D435" s="3">
-        <f t="shared" si="6"/>
+        <f>100%-F435</f>
         <v>0.15000000000000002</v>
       </c>
       <c r="E435" s="4">
@@ -21396,7 +21396,7 @@
         <v>131</v>
       </c>
       <c r="D436" s="3">
-        <f t="shared" si="6"/>
+        <f>100%-F436</f>
         <v>0.30000000000000004</v>
       </c>
       <c r="E436" s="4">
@@ -21438,7 +21438,7 @@
         <v>138</v>
       </c>
       <c r="D437" s="3">
-        <f t="shared" si="6"/>
+        <f>100%-F437</f>
         <v>0.22999999999999998</v>
       </c>
       <c r="E437" s="4">
@@ -21480,7 +21480,7 @@
         <v>406</v>
       </c>
       <c r="D438" s="3">
-        <f t="shared" si="6"/>
+        <f>100%-F438</f>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E438" s="4">
@@ -21523,7 +21523,7 @@
         <v>481</v>
       </c>
       <c r="D439" s="3">
-        <f t="shared" si="6"/>
+        <f>100%-F439</f>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E439" s="4">
@@ -21565,7 +21565,7 @@
         <v>459</v>
       </c>
       <c r="D440" s="3">
-        <f t="shared" si="6"/>
+        <f>100%-F440</f>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E440" s="4">
@@ -21607,7 +21607,7 @@
         <v>126</v>
       </c>
       <c r="D441" s="3">
-        <f t="shared" si="6"/>
+        <f>100%-F441</f>
         <v>0.37</v>
       </c>
       <c r="E441" s="4">
@@ -21649,7 +21649,7 @@
         <v>1793</v>
       </c>
       <c r="D442" s="3">
-        <f t="shared" si="6"/>
+        <f>100%-F442</f>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E442" s="4">
@@ -21691,7 +21691,7 @@
         <v>490</v>
       </c>
       <c r="D443" s="3">
-        <f t="shared" si="6"/>
+        <f>100%-F443</f>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E443" s="4">
@@ -21733,7 +21733,7 @@
         <v>156</v>
       </c>
       <c r="D444" s="3">
-        <f t="shared" si="6"/>
+        <f>100%-F444</f>
         <v>0.37</v>
       </c>
       <c r="E444" s="4">
@@ -21775,7 +21775,7 @@
         <v>129</v>
       </c>
       <c r="D445" s="3">
-        <f t="shared" si="6"/>
+        <f>100%-F445</f>
         <v>0.37</v>
       </c>
       <c r="E445" s="4">
@@ -21817,7 +21817,7 @@
         <v>757</v>
       </c>
       <c r="D446" s="3">
-        <f t="shared" si="6"/>
+        <f>100%-F446</f>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E446" s="4">
@@ -21860,11 +21860,11 @@
         <v>579</v>
       </c>
       <c r="D447" s="3">
-        <f t="shared" si="6"/>
+        <f>100%-F447</f>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E447" s="4">
-        <f t="shared" ref="E447:E448" si="7">I447*2%</f>
+        <f t="shared" ref="E447:E448" si="0">I447*2%</f>
         <v>0.02</v>
       </c>
       <c r="F447" s="4">
@@ -21903,11 +21903,11 @@
         <v>623</v>
       </c>
       <c r="D448" s="3">
-        <f t="shared" si="6"/>
+        <f>100%-F448</f>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E448" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="0"/>
         <v>0.02</v>
       </c>
       <c r="F448" s="4">
@@ -21946,7 +21946,7 @@
         <v>163</v>
       </c>
       <c r="D449" s="3">
-        <f t="shared" si="6"/>
+        <f>100%-F449</f>
         <v>0.17000000000000004</v>
       </c>
       <c r="E449" s="4">
@@ -21988,7 +21988,7 @@
         <v>166</v>
       </c>
       <c r="D450" s="3">
-        <f t="shared" ref="D450:D513" si="8">100%-F450</f>
+        <f>100%-F450</f>
         <v>0.22999999999999998</v>
       </c>
       <c r="E450" s="4">
@@ -22030,7 +22030,7 @@
         <v>654</v>
       </c>
       <c r="D451" s="3">
-        <f t="shared" si="8"/>
+        <f>100%-F451</f>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="E451" s="4">
@@ -22072,7 +22072,7 @@
         <v>510</v>
       </c>
       <c r="D452" s="3">
-        <f t="shared" si="8"/>
+        <f>100%-F452</f>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E452" s="4">
@@ -22114,7 +22114,7 @@
         <v>525</v>
       </c>
       <c r="D453" s="3">
-        <f t="shared" si="8"/>
+        <f>100%-F453</f>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E453" s="4">
@@ -22156,7 +22156,7 @@
         <v>539</v>
       </c>
       <c r="D454" s="3">
-        <f t="shared" si="8"/>
+        <f>100%-F454</f>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E454" s="4">
@@ -22199,7 +22199,7 @@
         <v>410</v>
       </c>
       <c r="D455" s="3">
-        <f t="shared" si="8"/>
+        <f>100%-F455</f>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E455" s="4">
@@ -22241,7 +22241,7 @@
         <v>13147</v>
       </c>
       <c r="D456" s="3">
-        <f t="shared" si="8"/>
+        <f>100%-F456</f>
         <v>0</v>
       </c>
       <c r="E456" s="4">
@@ -22283,7 +22283,7 @@
         <v>338</v>
       </c>
       <c r="D457" s="3">
-        <f t="shared" si="8"/>
+        <f>100%-F457</f>
         <v>0.25</v>
       </c>
       <c r="E457" s="4">
@@ -22325,7 +22325,7 @@
         <v>786</v>
       </c>
       <c r="D458" s="3">
-        <f t="shared" si="8"/>
+        <f>100%-F458</f>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E458" s="4">
@@ -22367,7 +22367,7 @@
         <v>120</v>
       </c>
       <c r="D459" s="3">
-        <f t="shared" si="8"/>
+        <f>100%-F459</f>
         <v>0.31999999999999995</v>
       </c>
       <c r="E459" s="4">
@@ -22409,7 +22409,7 @@
         <v>103</v>
       </c>
       <c r="D460" s="3">
-        <f t="shared" si="8"/>
+        <f>100%-F460</f>
         <v>0.30000000000000004</v>
       </c>
       <c r="E460" s="4">
@@ -22451,7 +22451,7 @@
         <v>2406</v>
       </c>
       <c r="D461" s="3">
-        <f t="shared" si="8"/>
+        <f>100%-F461</f>
         <v>0</v>
       </c>
       <c r="E461" s="4">
@@ -22493,7 +22493,7 @@
         <v>217</v>
       </c>
       <c r="D462" s="3">
-        <f t="shared" si="8"/>
+        <f>100%-F462</f>
         <v>0.30000000000000004</v>
       </c>
       <c r="E462" s="4">
@@ -22535,7 +22535,7 @@
         <v>715</v>
       </c>
       <c r="D463" s="3">
-        <f t="shared" si="8"/>
+        <f>100%-F463</f>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E463" s="4">
@@ -22577,7 +22577,7 @@
         <v>213</v>
       </c>
       <c r="D464" s="3">
-        <f t="shared" si="8"/>
+        <f>100%-F464</f>
         <v>0.18999999999999995</v>
       </c>
       <c r="E464" s="4">
@@ -22619,7 +22619,7 @@
         <v>497</v>
       </c>
       <c r="D465" s="3">
-        <f t="shared" si="8"/>
+        <f>100%-F465</f>
         <v>0.22999999999999998</v>
       </c>
       <c r="E465" s="4">
@@ -22661,7 +22661,7 @@
         <v>408</v>
       </c>
       <c r="D466" s="3">
-        <f t="shared" si="8"/>
+        <f>100%-F466</f>
         <v>0.22999999999999998</v>
       </c>
       <c r="E466" s="4">
@@ -22703,7 +22703,7 @@
         <v>5696</v>
       </c>
       <c r="D467" s="3">
-        <f t="shared" si="8"/>
+        <f>100%-F467</f>
         <v>0</v>
       </c>
       <c r="E467" s="4">
@@ -22745,7 +22745,7 @@
         <v>222</v>
       </c>
       <c r="D468" s="3">
-        <f t="shared" si="8"/>
+        <f>100%-F468</f>
         <v>0.25</v>
       </c>
       <c r="E468" s="4">
@@ -22787,7 +22787,7 @@
         <v>175</v>
       </c>
       <c r="D469" s="3">
-        <f t="shared" si="8"/>
+        <f>100%-F469</f>
         <v>0.22999999999999998</v>
       </c>
       <c r="E469" s="4">
@@ -22829,7 +22829,7 @@
         <v>776</v>
       </c>
       <c r="D470" s="3">
-        <f t="shared" si="8"/>
+        <f>100%-F470</f>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E470" s="4">
@@ -22871,7 +22871,7 @@
         <v>418</v>
       </c>
       <c r="D471" s="3">
-        <f t="shared" si="8"/>
+        <f>100%-F471</f>
         <v>0.22999999999999998</v>
       </c>
       <c r="E471" s="4">
@@ -22913,7 +22913,7 @@
         <v>201</v>
       </c>
       <c r="D472" s="3">
-        <f t="shared" si="8"/>
+        <f>100%-F472</f>
         <v>0.10999999999999999</v>
       </c>
       <c r="E472" s="4">
@@ -22955,7 +22955,7 @@
         <v>773</v>
       </c>
       <c r="D473" s="3">
-        <f t="shared" si="8"/>
+        <f>100%-F473</f>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E473" s="4">
@@ -22997,7 +22997,7 @@
         <v>175</v>
       </c>
       <c r="D474" s="3">
-        <f t="shared" si="8"/>
+        <f>100%-F474</f>
         <v>0.25</v>
       </c>
       <c r="E474" s="4">
@@ -23039,7 +23039,7 @@
         <v>135</v>
       </c>
       <c r="D475" s="3">
-        <f t="shared" si="8"/>
+        <f>100%-F475</f>
         <v>0.4</v>
       </c>
       <c r="E475" s="4">
@@ -23081,7 +23081,7 @@
         <v>352</v>
       </c>
       <c r="D476" s="3">
-        <f t="shared" si="8"/>
+        <f>100%-F476</f>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E476" s="4">
@@ -23123,7 +23123,7 @@
         <v>405</v>
       </c>
       <c r="D477" s="3">
-        <f t="shared" si="8"/>
+        <f>100%-F477</f>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E477" s="4">
@@ -23165,7 +23165,7 @@
         <v>986</v>
       </c>
       <c r="D478" s="3">
-        <f t="shared" si="8"/>
+        <f>100%-F478</f>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E478" s="4">
@@ -23207,7 +23207,7 @@
         <v>454</v>
       </c>
       <c r="D479" s="3">
-        <f t="shared" si="8"/>
+        <f>100%-F479</f>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E479" s="4">
@@ -23249,7 +23249,7 @@
         <v>133</v>
       </c>
       <c r="D480" s="3">
-        <f t="shared" si="8"/>
+        <f>100%-F480</f>
         <v>0.65</v>
       </c>
       <c r="E480" s="4">
@@ -23291,7 +23291,7 @@
         <v>857</v>
       </c>
       <c r="D481" s="3">
-        <f t="shared" si="8"/>
+        <f>100%-F481</f>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="E481" s="4">
@@ -23333,7 +23333,7 @@
         <v>238</v>
       </c>
       <c r="D482" s="3">
-        <f t="shared" si="8"/>
+        <f>100%-F482</f>
         <v>0.30000000000000004</v>
       </c>
       <c r="E482" s="4">
@@ -23375,7 +23375,7 @@
         <v>307</v>
       </c>
       <c r="D483" s="3">
-        <f t="shared" si="8"/>
+        <f>100%-F483</f>
         <v>0.22999999999999998</v>
       </c>
       <c r="E483" s="4">
@@ -23417,7 +23417,7 @@
         <v>7448</v>
       </c>
       <c r="D484" s="3">
-        <f t="shared" si="8"/>
+        <f>100%-F484</f>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E484" s="4">
@@ -23459,7 +23459,7 @@
         <v>159</v>
       </c>
       <c r="D485" s="3">
-        <f t="shared" si="8"/>
+        <f>100%-F485</f>
         <v>0.28000000000000003</v>
       </c>
       <c r="E485" s="4">
@@ -23501,7 +23501,7 @@
         <v>453</v>
       </c>
       <c r="D486" s="3">
-        <f t="shared" si="8"/>
+        <f>100%-F486</f>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E486" s="4">
@@ -23543,7 +23543,7 @@
         <v>437</v>
       </c>
       <c r="D487" s="3">
-        <f t="shared" si="8"/>
+        <f>100%-F487</f>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E487" s="4">
@@ -23585,7 +23585,7 @@
         <v>4178</v>
       </c>
       <c r="D488" s="3">
-        <f t="shared" si="8"/>
+        <f>100%-F488</f>
         <v>0</v>
       </c>
       <c r="E488" s="4">
@@ -23627,7 +23627,7 @@
         <v>9691</v>
       </c>
       <c r="D489" s="3">
-        <f t="shared" si="8"/>
+        <f>100%-F489</f>
         <v>0</v>
       </c>
       <c r="E489" s="4">
@@ -23669,7 +23669,7 @@
         <v>355</v>
       </c>
       <c r="D490" s="3">
-        <f t="shared" si="8"/>
+        <f>100%-F490</f>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E490" s="4">
@@ -23711,7 +23711,7 @@
         <v>504</v>
       </c>
       <c r="D491" s="3">
-        <f t="shared" si="8"/>
+        <f>100%-F491</f>
         <v>0.25</v>
       </c>
       <c r="E491" s="4">
@@ -23753,7 +23753,7 @@
         <v>273</v>
       </c>
       <c r="D492" s="3">
-        <f t="shared" si="8"/>
+        <f>100%-F492</f>
         <v>0.30000000000000004</v>
       </c>
       <c r="E492" s="4">
@@ -23795,7 +23795,7 @@
         <v>666</v>
       </c>
       <c r="D493" s="3">
-        <f t="shared" si="8"/>
+        <f>100%-F493</f>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E493" s="4">
@@ -23837,7 +23837,7 @@
         <v>3482</v>
       </c>
       <c r="D494" s="3">
-        <f t="shared" si="8"/>
+        <f>100%-F494</f>
         <v>0</v>
       </c>
       <c r="E494" s="4">
@@ -23879,7 +23879,7 @@
         <v>2213</v>
       </c>
       <c r="D495" s="3">
-        <f t="shared" si="8"/>
+        <f>100%-F495</f>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E495" s="4">
@@ -23921,7 +23921,7 @@
         <v>233</v>
       </c>
       <c r="D496" s="3">
-        <f t="shared" si="8"/>
+        <f>100%-F496</f>
         <v>0.30000000000000004</v>
       </c>
       <c r="E496" s="4">
@@ -23963,7 +23963,7 @@
         <v>312</v>
       </c>
       <c r="D497" s="3">
-        <f t="shared" si="8"/>
+        <f>100%-F497</f>
         <v>0.30000000000000004</v>
       </c>
       <c r="E497" s="4">
@@ -24005,7 +24005,7 @@
         <v>687</v>
       </c>
       <c r="D498" s="3">
-        <f t="shared" si="8"/>
+        <f>100%-F498</f>
         <v>0.15000000000000002</v>
       </c>
       <c r="E498" s="4">
@@ -24047,7 +24047,7 @@
         <v>9242</v>
       </c>
       <c r="D499" s="3">
-        <f t="shared" si="8"/>
+        <f>100%-F499</f>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E499" s="4">
@@ -24089,7 +24089,7 @@
         <v>862</v>
       </c>
       <c r="D500" s="3">
-        <f t="shared" si="8"/>
+        <f>100%-F500</f>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="E500" s="4">
@@ -24131,7 +24131,7 @@
         <v>439</v>
       </c>
       <c r="D501" s="3">
-        <f t="shared" si="8"/>
+        <f>100%-F501</f>
         <v>0.37</v>
       </c>
       <c r="E501" s="4">
@@ -24173,7 +24173,7 @@
         <v>4599</v>
       </c>
       <c r="D502" s="3">
-        <f t="shared" si="8"/>
+        <f>100%-F502</f>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E502" s="4">
@@ -24215,7 +24215,7 @@
         <v>586</v>
       </c>
       <c r="D503" s="3">
-        <f t="shared" si="8"/>
+        <f>100%-F503</f>
         <v>0.25</v>
       </c>
       <c r="E503" s="4">
@@ -24257,7 +24257,7 @@
         <v>354</v>
       </c>
       <c r="D504" s="3">
-        <f t="shared" si="8"/>
+        <f>100%-F504</f>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E504" s="4">
@@ -24299,7 +24299,7 @@
         <v>3589</v>
       </c>
       <c r="D505" s="3">
-        <f t="shared" si="8"/>
+        <f>100%-F505</f>
         <v>0</v>
       </c>
       <c r="E505" s="4">
@@ -24341,7 +24341,7 @@
         <v>653</v>
       </c>
       <c r="D506" s="3">
-        <f t="shared" si="8"/>
+        <f>100%-F506</f>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E506" s="4">
@@ -24383,7 +24383,7 @@
         <v>4220</v>
       </c>
       <c r="D507" s="3">
-        <f t="shared" si="8"/>
+        <f>100%-F507</f>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="E507" s="4">
@@ -24425,7 +24425,7 @@
         <v>270</v>
       </c>
       <c r="D508" s="3">
-        <f t="shared" si="8"/>
+        <f>100%-F508</f>
         <v>0.19999999999999996</v>
       </c>
       <c r="E508" s="4">
@@ -24467,7 +24467,7 @@
         <v>1516</v>
       </c>
       <c r="D509" s="3">
-        <f t="shared" si="8"/>
+        <f>100%-F509</f>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E509" s="4">
@@ -24509,7 +24509,7 @@
         <v>1000.9999999999999</v>
       </c>
       <c r="D510" s="3">
-        <f t="shared" si="8"/>
+        <f>100%-F510</f>
         <v>0.15000000000000002</v>
       </c>
       <c r="E510" s="4">
@@ -24551,7 +24551,7 @@
         <v>6949</v>
       </c>
       <c r="D511" s="3">
-        <f t="shared" si="8"/>
+        <f>100%-F511</f>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E511" s="4">
@@ -24593,7 +24593,7 @@
         <v>2625</v>
       </c>
       <c r="D512" s="3">
-        <f t="shared" si="8"/>
+        <f>100%-F512</f>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E512" s="4">
@@ -24635,7 +24635,7 @@
         <v>3346</v>
       </c>
       <c r="D513" s="3">
-        <f t="shared" si="8"/>
+        <f>100%-F513</f>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="E513" s="4">
@@ -24677,7 +24677,7 @@
         <v>1242</v>
       </c>
       <c r="D514" s="3">
-        <f t="shared" ref="D514:D577" si="9">100%-F514</f>
+        <f>100%-F514</f>
         <v>0.30000000000000004</v>
       </c>
       <c r="E514" s="4">
@@ -24719,7 +24719,7 @@
         <v>3480</v>
       </c>
       <c r="D515" s="3">
-        <f t="shared" si="9"/>
+        <f>100%-F515</f>
         <v>0</v>
       </c>
       <c r="E515" s="4">
@@ -24761,7 +24761,7 @@
         <v>1684</v>
       </c>
       <c r="D516" s="3">
-        <f t="shared" si="9"/>
+        <f>100%-F516</f>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E516" s="4">
@@ -24803,7 +24803,7 @@
         <v>6232</v>
       </c>
       <c r="D517" s="3">
-        <f t="shared" si="9"/>
+        <f>100%-F517</f>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E517" s="4">
@@ -24845,7 +24845,7 @@
         <v>2191</v>
       </c>
       <c r="D518" s="3">
-        <f t="shared" si="9"/>
+        <f>100%-F518</f>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E518" s="4">
@@ -24887,7 +24887,7 @@
         <v>1282</v>
       </c>
       <c r="D519" s="3">
-        <f t="shared" si="9"/>
+        <f>100%-F519</f>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E519" s="4">
@@ -24929,7 +24929,7 @@
         <v>177</v>
       </c>
       <c r="D520" s="3">
-        <f t="shared" si="9"/>
+        <f>100%-F520</f>
         <v>0.26</v>
       </c>
       <c r="E520" s="4">
@@ -24971,7 +24971,7 @@
         <v>5656</v>
       </c>
       <c r="D521" s="3">
-        <f t="shared" si="9"/>
+        <f>100%-F521</f>
         <v>0</v>
       </c>
       <c r="E521" s="4">
@@ -25013,7 +25013,7 @@
         <v>339</v>
       </c>
       <c r="D522" s="3">
-        <f t="shared" si="9"/>
+        <f>100%-F522</f>
         <v>0.30000000000000004</v>
       </c>
       <c r="E522" s="4">
@@ -25055,7 +25055,7 @@
         <v>1246</v>
       </c>
       <c r="D523" s="3">
-        <f t="shared" si="9"/>
+        <f>100%-F523</f>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="E523" s="4">
@@ -25097,7 +25097,7 @@
         <v>2000</v>
       </c>
       <c r="D524" s="3">
-        <f t="shared" si="9"/>
+        <f>100%-F524</f>
         <v>6.0000000000000053E-2</v>
       </c>
       <c r="E524" s="4">
@@ -25139,7 +25139,7 @@
         <v>276</v>
       </c>
       <c r="D525" s="3">
-        <f t="shared" si="9"/>
+        <f>100%-F525</f>
         <v>0.44999999999999996</v>
       </c>
       <c r="E525" s="4">
@@ -25181,7 +25181,7 @@
         <v>1126</v>
       </c>
       <c r="D526" s="3">
-        <f t="shared" si="9"/>
+        <f>100%-F526</f>
         <v>0.28000000000000003</v>
       </c>
       <c r="E526" s="4">
@@ -25223,7 +25223,7 @@
         <v>3690</v>
       </c>
       <c r="D527" s="3">
-        <f t="shared" si="9"/>
+        <f>100%-F527</f>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E527" s="4">
@@ -25265,7 +25265,7 @@
         <v>11874</v>
       </c>
       <c r="D528" s="3">
-        <f t="shared" si="9"/>
+        <f>100%-F528</f>
         <v>0</v>
       </c>
       <c r="E528" s="4">
@@ -25307,7 +25307,7 @@
         <v>6545</v>
       </c>
       <c r="D529" s="3">
-        <f t="shared" si="9"/>
+        <f>100%-F529</f>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E529" s="4">
@@ -25349,7 +25349,7 @@
         <v>284</v>
       </c>
       <c r="D530" s="3">
-        <f t="shared" si="9"/>
+        <f>100%-F530</f>
         <v>0.30000000000000004</v>
       </c>
       <c r="E530" s="4">
@@ -25391,7 +25391,7 @@
         <v>1989</v>
       </c>
       <c r="D531" s="3">
-        <f t="shared" si="9"/>
+        <f>100%-F531</f>
         <v>8.9999999999999969E-2</v>
       </c>
       <c r="E531" s="4">
@@ -25433,7 +25433,7 @@
         <v>2454</v>
       </c>
       <c r="D532" s="3">
-        <f t="shared" si="9"/>
+        <f>100%-F532</f>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E532" s="4">
@@ -25475,7 +25475,7 @@
         <v>206</v>
       </c>
       <c r="D533" s="3">
-        <f t="shared" si="9"/>
+        <f>100%-F533</f>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E533" s="4">
@@ -25517,7 +25517,7 @@
         <v>679</v>
       </c>
       <c r="D534" s="3">
-        <f t="shared" si="9"/>
+        <f>100%-F534</f>
         <v>0.26</v>
       </c>
       <c r="E534" s="4">
@@ -25559,7 +25559,7 @@
         <v>339</v>
       </c>
       <c r="D535" s="3">
-        <f t="shared" si="9"/>
+        <f>100%-F535</f>
         <v>0.37</v>
       </c>
       <c r="E535" s="4">
@@ -25601,7 +25601,7 @@
         <v>8324</v>
       </c>
       <c r="D536" s="3">
-        <f t="shared" si="9"/>
+        <f>100%-F536</f>
         <v>0</v>
       </c>
       <c r="E536" s="4">
@@ -25643,7 +25643,7 @@
         <v>614</v>
       </c>
       <c r="D537" s="3">
-        <f t="shared" si="9"/>
+        <f>100%-F537</f>
         <v>0.30000000000000004</v>
       </c>
       <c r="E537" s="4">
@@ -25685,7 +25685,7 @@
         <v>174</v>
       </c>
       <c r="D538" s="3">
-        <f t="shared" si="9"/>
+        <f>100%-F538</f>
         <v>0.37</v>
       </c>
       <c r="E538" s="4">
@@ -25727,7 +25727,7 @@
         <v>2402</v>
       </c>
       <c r="D539" s="3">
-        <f t="shared" si="9"/>
+        <f>100%-F539</f>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="E539" s="4">
@@ -25769,7 +25769,7 @@
         <v>400</v>
       </c>
       <c r="D540" s="3">
-        <f t="shared" si="9"/>
+        <f>100%-F540</f>
         <v>0.30000000000000004</v>
       </c>
       <c r="E540" s="4">
@@ -25811,7 +25811,7 @@
         <v>384</v>
       </c>
       <c r="D541" s="3">
-        <f t="shared" si="9"/>
+        <f>100%-F541</f>
         <v>0.22999999999999998</v>
       </c>
       <c r="E541" s="4">
@@ -25853,7 +25853,7 @@
         <v>153</v>
       </c>
       <c r="D542" s="3">
-        <f t="shared" si="9"/>
+        <f>100%-F542</f>
         <v>0.30000000000000004</v>
       </c>
       <c r="E542" s="4">
@@ -25895,7 +25895,7 @@
         <v>1541</v>
       </c>
       <c r="D543" s="3">
-        <f t="shared" si="9"/>
+        <f>100%-F543</f>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E543" s="4">
@@ -25937,7 +25937,7 @@
         <v>1456</v>
       </c>
       <c r="D544" s="3">
-        <f t="shared" si="9"/>
+        <f>100%-F544</f>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="E544" s="4">
@@ -25979,7 +25979,7 @@
         <v>627</v>
       </c>
       <c r="D545" s="3">
-        <f t="shared" si="9"/>
+        <f>100%-F545</f>
         <v>0.22999999999999998</v>
       </c>
       <c r="E545" s="4">
@@ -26021,7 +26021,7 @@
         <v>864</v>
       </c>
       <c r="D546" s="3">
-        <f t="shared" si="9"/>
+        <f>100%-F546</f>
         <v>0.22999999999999998</v>
       </c>
       <c r="E546" s="4">
@@ -26063,7 +26063,7 @@
         <v>999</v>
       </c>
       <c r="D547" s="3">
-        <f t="shared" si="9"/>
+        <f>100%-F547</f>
         <v>0.15000000000000002</v>
       </c>
       <c r="E547" s="4">
@@ -26105,7 +26105,7 @@
         <v>1422</v>
       </c>
       <c r="D548" s="3">
-        <f t="shared" si="9"/>
+        <f>100%-F548</f>
         <v>0.22999999999999998</v>
       </c>
       <c r="E548" s="4">
@@ -26147,7 +26147,7 @@
         <v>2518</v>
       </c>
       <c r="D549" s="3">
-        <f t="shared" si="9"/>
+        <f>100%-F549</f>
         <v>0</v>
       </c>
       <c r="E549" s="4">
@@ -26189,7 +26189,7 @@
         <v>5547</v>
       </c>
       <c r="D550" s="3">
-        <f t="shared" si="9"/>
+        <f>100%-F550</f>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E550" s="4">
@@ -26231,7 +26231,7 @@
         <v>29086</v>
       </c>
       <c r="D551" s="3">
-        <f t="shared" si="9"/>
+        <f>100%-F551</f>
         <v>0</v>
       </c>
       <c r="E551" s="4">
@@ -26273,7 +26273,7 @@
         <v>453</v>
       </c>
       <c r="D552" s="3">
-        <f t="shared" si="9"/>
+        <f>100%-F552</f>
         <v>0.31999999999999995</v>
       </c>
       <c r="E552" s="4">
@@ -26315,7 +26315,7 @@
         <v>571</v>
       </c>
       <c r="D553" s="3">
-        <f t="shared" si="9"/>
+        <f>100%-F553</f>
         <v>0</v>
       </c>
       <c r="E553" s="4">
@@ -26357,7 +26357,7 @@
         <v>631</v>
       </c>
       <c r="D554" s="3">
-        <f t="shared" si="9"/>
+        <f>100%-F554</f>
         <v>0</v>
       </c>
       <c r="E554" s="4">
@@ -26399,7 +26399,7 @@
         <v>107</v>
       </c>
       <c r="D555" s="3">
-        <f t="shared" si="9"/>
+        <f>100%-F555</f>
         <v>0.37</v>
       </c>
       <c r="E555" s="4">
@@ -26441,7 +26441,7 @@
         <v>127</v>
       </c>
       <c r="D556" s="3">
-        <f t="shared" si="9"/>
+        <f>100%-F556</f>
         <v>0.30000000000000004</v>
       </c>
       <c r="E556" s="4">
@@ -26483,7 +26483,7 @@
         <v>244</v>
       </c>
       <c r="D557" s="3">
-        <f t="shared" si="9"/>
+        <f>100%-F557</f>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E557" s="4">
@@ -26525,7 +26525,7 @@
         <v>385</v>
       </c>
       <c r="D558" s="3">
-        <f t="shared" si="9"/>
+        <f>100%-F558</f>
         <v>0.22999999999999998</v>
       </c>
       <c r="E558" s="4">
@@ -26567,7 +26567,7 @@
         <v>735</v>
       </c>
       <c r="D559" s="3">
-        <f t="shared" si="9"/>
+        <f>100%-F559</f>
         <v>0</v>
       </c>
       <c r="E559" s="4">
@@ -26609,7 +26609,7 @@
         <v>126</v>
       </c>
       <c r="D560" s="3">
-        <f t="shared" si="9"/>
+        <f>100%-F560</f>
         <v>0.15000000000000002</v>
       </c>
       <c r="E560" s="4">
@@ -26651,7 +26651,7 @@
         <v>168</v>
       </c>
       <c r="D561" s="3">
-        <f t="shared" si="9"/>
+        <f>100%-F561</f>
         <v>0.30000000000000004</v>
       </c>
       <c r="E561" s="4">
@@ -26693,7 +26693,7 @@
         <v>638</v>
       </c>
       <c r="D562" s="3">
-        <f t="shared" si="9"/>
+        <f>100%-F562</f>
         <v>0</v>
       </c>
       <c r="E562" s="4">
@@ -26735,7 +26735,7 @@
         <v>637</v>
       </c>
       <c r="D563" s="3">
-        <f t="shared" si="9"/>
+        <f>100%-F563</f>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="E563" s="4">
@@ -26777,7 +26777,7 @@
         <v>1266</v>
       </c>
       <c r="D564" s="3">
-        <f t="shared" si="9"/>
+        <f>100%-F564</f>
         <v>0</v>
       </c>
       <c r="E564" s="4">
@@ -26819,7 +26819,7 @@
         <v>1372</v>
       </c>
       <c r="D565" s="3">
-        <f t="shared" si="9"/>
+        <f>100%-F565</f>
         <v>0</v>
       </c>
       <c r="E565" s="4">
@@ -26861,7 +26861,7 @@
         <v>1033</v>
       </c>
       <c r="D566" s="3">
-        <f t="shared" si="9"/>
+        <f>100%-F566</f>
         <v>0</v>
       </c>
       <c r="E566" s="4">
@@ -26903,7 +26903,7 @@
         <v>954</v>
       </c>
       <c r="D567" s="3">
-        <f t="shared" si="9"/>
+        <f>100%-F567</f>
         <v>0</v>
       </c>
       <c r="E567" s="4">
@@ -26945,7 +26945,7 @@
         <v>243</v>
       </c>
       <c r="D568" s="3">
-        <f t="shared" si="9"/>
+        <f>100%-F568</f>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E568" s="4">
@@ -26987,7 +26987,7 @@
         <v>104</v>
       </c>
       <c r="D569" s="3">
-        <f t="shared" si="9"/>
+        <f>100%-F569</f>
         <v>0.36</v>
       </c>
       <c r="E569" s="4">
@@ -27029,7 +27029,7 @@
         <v>978</v>
       </c>
       <c r="D570" s="3">
-        <f t="shared" si="9"/>
+        <f>100%-F570</f>
         <v>0</v>
       </c>
       <c r="E570" s="4">
@@ -27071,7 +27071,7 @@
         <v>1431</v>
       </c>
       <c r="D571" s="3">
-        <f t="shared" si="9"/>
+        <f>100%-F571</f>
         <v>0</v>
       </c>
       <c r="E571" s="4">
@@ -27113,7 +27113,7 @@
         <v>140</v>
       </c>
       <c r="D572" s="3">
-        <f t="shared" si="9"/>
+        <f>100%-F572</f>
         <v>0.30000000000000004</v>
       </c>
       <c r="E572" s="4">
@@ -27155,7 +27155,7 @@
         <v>639</v>
       </c>
       <c r="D573" s="3">
-        <f t="shared" si="9"/>
+        <f>100%-F573</f>
         <v>0</v>
       </c>
       <c r="E573" s="4">
@@ -27197,7 +27197,7 @@
         <v>1550</v>
       </c>
       <c r="D574" s="3">
-        <f t="shared" si="9"/>
+        <f>100%-F574</f>
         <v>0</v>
       </c>
       <c r="E574" s="4">
@@ -27239,7 +27239,7 @@
         <v>115</v>
       </c>
       <c r="D575" s="3">
-        <f t="shared" si="9"/>
+        <f>100%-F575</f>
         <v>0.38</v>
       </c>
       <c r="E575" s="4">
@@ -27281,7 +27281,7 @@
         <v>506</v>
       </c>
       <c r="D576" s="3">
-        <f t="shared" si="9"/>
+        <f>100%-F576</f>
         <v>0</v>
       </c>
       <c r="E576" s="4">
@@ -27323,7 +27323,7 @@
         <v>217</v>
       </c>
       <c r="D577" s="3">
-        <f t="shared" si="9"/>
+        <f>100%-F577</f>
         <v>0.37</v>
       </c>
       <c r="E577" s="4">
@@ -27365,7 +27365,7 @@
         <v>340</v>
       </c>
       <c r="D578" s="3">
-        <f t="shared" ref="D578:D641" si="10">100%-F578</f>
+        <f>100%-F578</f>
         <v>0.20999999999999996</v>
       </c>
       <c r="E578" s="4">
@@ -27407,7 +27407,7 @@
         <v>2940</v>
       </c>
       <c r="D579" s="3">
-        <f t="shared" si="10"/>
+        <f>100%-F579</f>
         <v>0</v>
       </c>
       <c r="E579" s="4">
@@ -27449,7 +27449,7 @@
         <v>661</v>
       </c>
       <c r="D580" s="3">
-        <f t="shared" si="10"/>
+        <f>100%-F580</f>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="E580" s="4">
@@ -27491,7 +27491,7 @@
         <v>217</v>
       </c>
       <c r="D581" s="3">
-        <f t="shared" si="10"/>
+        <f>100%-F581</f>
         <v>0.30000000000000004</v>
       </c>
       <c r="E581" s="4">
@@ -27533,7 +27533,7 @@
         <v>581</v>
       </c>
       <c r="D582" s="3">
-        <f t="shared" si="10"/>
+        <f>100%-F582</f>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="E582" s="4">
@@ -27575,7 +27575,7 @@
         <v>1278</v>
       </c>
       <c r="D583" s="3">
-        <f t="shared" si="10"/>
+        <f>100%-F583</f>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E583" s="4">
@@ -27617,7 +27617,7 @@
         <v>2691</v>
       </c>
       <c r="D584" s="3">
-        <f t="shared" si="10"/>
+        <f>100%-F584</f>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E584" s="4">
@@ -27659,7 +27659,7 @@
         <v>9455</v>
       </c>
       <c r="D585" s="3">
-        <f t="shared" si="10"/>
+        <f>100%-F585</f>
         <v>0</v>
       </c>
       <c r="E585" s="4">
@@ -27701,7 +27701,7 @@
         <v>20862</v>
       </c>
       <c r="D586" s="9">
-        <f t="shared" si="10"/>
+        <f>100%-F586</f>
         <v>0</v>
       </c>
       <c r="E586" s="10">
@@ -27744,7 +27744,7 @@
         <v>190</v>
       </c>
       <c r="D587" s="3">
-        <f t="shared" si="10"/>
+        <f>100%-F587</f>
         <v>0.17000000000000004</v>
       </c>
       <c r="E587" s="4">
@@ -27786,7 +27786,7 @@
         <v>209</v>
       </c>
       <c r="D588" s="3">
-        <f t="shared" si="10"/>
+        <f>100%-F588</f>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E588" s="4">
@@ -27828,7 +27828,7 @@
         <v>216</v>
       </c>
       <c r="D589" s="3">
-        <f t="shared" si="10"/>
+        <f>100%-F589</f>
         <v>0.22999999999999998</v>
       </c>
       <c r="E589" s="4">
@@ -27870,7 +27870,7 @@
         <v>143</v>
       </c>
       <c r="D590" s="3">
-        <f t="shared" si="10"/>
+        <f>100%-F590</f>
         <v>0.15000000000000002</v>
       </c>
       <c r="E590" s="4">
@@ -27912,7 +27912,7 @@
         <v>4700</v>
       </c>
       <c r="D591" s="3">
-        <f t="shared" si="10"/>
+        <f>100%-F591</f>
         <v>0</v>
       </c>
       <c r="E591" s="4">
@@ -27954,7 +27954,7 @@
         <v>165</v>
       </c>
       <c r="D592" s="3">
-        <f t="shared" si="10"/>
+        <f>100%-F592</f>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E592" s="4">
@@ -27996,7 +27996,7 @@
         <v>146</v>
       </c>
       <c r="D593" s="3">
-        <f t="shared" si="10"/>
+        <f>100%-F593</f>
         <v>0.17000000000000004</v>
       </c>
       <c r="E593" s="4">
@@ -28038,7 +28038,7 @@
         <v>249</v>
       </c>
       <c r="D594" s="3">
-        <f t="shared" si="10"/>
+        <f>100%-F594</f>
         <v>0.25</v>
       </c>
       <c r="E594" s="4">
@@ -28080,7 +28080,7 @@
         <v>128</v>
       </c>
       <c r="D595" s="3">
-        <f t="shared" si="10"/>
+        <f>100%-F595</f>
         <v>0.65</v>
       </c>
       <c r="E595" s="4">
@@ -28122,7 +28122,7 @@
         <v>236</v>
       </c>
       <c r="D596" s="3">
-        <f t="shared" si="10"/>
+        <f>100%-F596</f>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="E596" s="4">
@@ -28164,7 +28164,7 @@
         <v>380</v>
       </c>
       <c r="D597" s="3">
-        <f t="shared" si="10"/>
+        <f>100%-F597</f>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="E597" s="4">
@@ -28206,7 +28206,7 @@
         <v>269</v>
       </c>
       <c r="D598" s="3">
-        <f t="shared" si="10"/>
+        <f>100%-F598</f>
         <v>0</v>
       </c>
       <c r="E598" s="4">
@@ -28248,7 +28248,7 @@
         <v>227</v>
       </c>
       <c r="D599" s="3">
-        <f t="shared" si="10"/>
+        <f>100%-F599</f>
         <v>0.32999999999999996</v>
       </c>
       <c r="E599" s="4">
@@ -28290,7 +28290,7 @@
         <v>175</v>
       </c>
       <c r="D600" s="3">
-        <f t="shared" si="10"/>
+        <f>100%-F600</f>
         <v>0.30000000000000004</v>
       </c>
       <c r="E600" s="4">
@@ -28332,7 +28332,7 @@
         <v>364</v>
       </c>
       <c r="D601" s="3">
-        <f t="shared" si="10"/>
+        <f>100%-F601</f>
         <v>0.15000000000000002</v>
       </c>
       <c r="E601" s="4">
@@ -28374,7 +28374,7 @@
         <v>1341</v>
       </c>
       <c r="D602" s="3">
-        <f t="shared" si="10"/>
+        <f>100%-F602</f>
         <v>0</v>
       </c>
       <c r="E602" s="4">
@@ -28416,7 +28416,7 @@
         <v>197</v>
       </c>
       <c r="D603" s="3">
-        <f t="shared" si="10"/>
+        <f>100%-F603</f>
         <v>0.37</v>
       </c>
       <c r="E603" s="4">
@@ -28458,7 +28458,7 @@
         <v>722</v>
       </c>
       <c r="D604" s="3">
-        <f t="shared" si="10"/>
+        <f>100%-F604</f>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E604" s="4">
@@ -28500,7 +28500,7 @@
         <v>244</v>
       </c>
       <c r="D605" s="3">
-        <f t="shared" si="10"/>
+        <f>100%-F605</f>
         <v>0.30000000000000004</v>
       </c>
       <c r="E605" s="4">
@@ -28542,7 +28542,7 @@
         <v>965</v>
       </c>
       <c r="D606" s="3">
-        <f t="shared" si="10"/>
+        <f>100%-F606</f>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="E606" s="4">
@@ -28584,7 +28584,7 @@
         <v>913</v>
       </c>
       <c r="D607" s="3">
-        <f t="shared" si="10"/>
+        <f>100%-F607</f>
         <v>0</v>
       </c>
       <c r="E607" s="4">
@@ -28626,7 +28626,7 @@
         <v>310</v>
       </c>
       <c r="D608" s="3">
-        <f t="shared" si="10"/>
+        <f>100%-F608</f>
         <v>0.22999999999999998</v>
       </c>
       <c r="E608" s="4">
@@ -28668,7 +28668,7 @@
         <v>622</v>
       </c>
       <c r="D609" s="3">
-        <f t="shared" si="10"/>
+        <f>100%-F609</f>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E609" s="4">
@@ -28710,7 +28710,7 @@
         <v>369</v>
       </c>
       <c r="D610" s="3">
-        <f t="shared" si="10"/>
+        <f>100%-F610</f>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E610" s="4">
@@ -28752,7 +28752,7 @@
         <v>152</v>
       </c>
       <c r="D611" s="3">
-        <f t="shared" si="10"/>
+        <f>100%-F611</f>
         <v>0.38</v>
       </c>
       <c r="E611" s="4">
@@ -28794,7 +28794,7 @@
         <v>539</v>
       </c>
       <c r="D612" s="3">
-        <f t="shared" si="10"/>
+        <f>100%-F612</f>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E612" s="4">
@@ -28836,7 +28836,7 @@
         <v>413</v>
       </c>
       <c r="D613" s="3">
-        <f t="shared" si="10"/>
+        <f>100%-F613</f>
         <v>0.30000000000000004</v>
       </c>
       <c r="E613" s="4">
@@ -28878,7 +28878,7 @@
         <v>875</v>
       </c>
       <c r="D614" s="3">
-        <f t="shared" si="10"/>
+        <f>100%-F614</f>
         <v>0</v>
       </c>
       <c r="E614" s="4">
@@ -28920,7 +28920,7 @@
         <v>120</v>
       </c>
       <c r="D615" s="3">
-        <f t="shared" si="10"/>
+        <f>100%-F615</f>
         <v>0.44999999999999996</v>
       </c>
       <c r="E615" s="4">
@@ -28962,7 +28962,7 @@
         <v>243</v>
       </c>
       <c r="D616" s="3">
-        <f t="shared" si="10"/>
+        <f>100%-F616</f>
         <v>0.38</v>
       </c>
       <c r="E616" s="4">
@@ -29004,7 +29004,7 @@
         <v>647</v>
       </c>
       <c r="D617" s="3">
-        <f t="shared" si="10"/>
+        <f>100%-F617</f>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E617" s="4">
@@ -29046,7 +29046,7 @@
         <v>1213</v>
       </c>
       <c r="D618" s="3">
-        <f t="shared" si="10"/>
+        <f>100%-F618</f>
         <v>0</v>
       </c>
       <c r="E618" s="4">
@@ -29088,7 +29088,7 @@
         <v>782</v>
       </c>
       <c r="D619" s="3">
-        <f t="shared" si="10"/>
+        <f>100%-F619</f>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="E619" s="4">
@@ -29130,7 +29130,7 @@
         <v>246</v>
       </c>
       <c r="D620" s="3">
-        <f t="shared" si="10"/>
+        <f>100%-F620</f>
         <v>0.22999999999999998</v>
       </c>
       <c r="E620" s="4">
@@ -29172,7 +29172,7 @@
         <v>958</v>
       </c>
       <c r="D621" s="3">
-        <f t="shared" si="10"/>
+        <f>100%-F621</f>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="E621" s="4">
@@ -29214,7 +29214,7 @@
         <v>179</v>
       </c>
       <c r="D622" s="3">
-        <f t="shared" si="10"/>
+        <f>100%-F622</f>
         <v>0.37</v>
       </c>
       <c r="E622" s="4">
@@ -29256,7 +29256,7 @@
         <v>1769</v>
       </c>
       <c r="D623" s="3">
-        <f t="shared" si="10"/>
+        <f>100%-F623</f>
         <v>0</v>
       </c>
       <c r="E623" s="4">
@@ -29298,7 +29298,7 @@
         <v>178</v>
       </c>
       <c r="D624" s="3">
-        <f t="shared" si="10"/>
+        <f>100%-F624</f>
         <v>0.37</v>
       </c>
       <c r="E624" s="4">
@@ -29340,7 +29340,7 @@
         <v>1114</v>
       </c>
       <c r="D625" s="3">
-        <f t="shared" si="10"/>
+        <f>100%-F625</f>
         <v>0</v>
       </c>
       <c r="E625" s="4">
@@ -29382,7 +29382,7 @@
         <v>193</v>
       </c>
       <c r="D626" s="3">
-        <f t="shared" si="10"/>
+        <f>100%-F626</f>
         <v>0.30000000000000004</v>
       </c>
       <c r="E626" s="4">
@@ -29424,7 +29424,7 @@
         <v>15482</v>
       </c>
       <c r="D627" s="3">
-        <f t="shared" si="10"/>
+        <f>100%-F627</f>
         <v>0</v>
       </c>
       <c r="E627" s="4">
@@ -29466,7 +29466,7 @@
         <v>170</v>
       </c>
       <c r="D628" s="3">
-        <f t="shared" si="10"/>
+        <f>100%-F628</f>
         <v>0.72</v>
       </c>
       <c r="E628" s="4">
@@ -29508,7 +29508,7 @@
         <v>295</v>
       </c>
       <c r="D629" s="3">
-        <f t="shared" si="10"/>
+        <f>100%-F629</f>
         <v>0.38</v>
       </c>
       <c r="E629" s="4">
@@ -29550,7 +29550,7 @@
         <v>547</v>
       </c>
       <c r="D630" s="3">
-        <f t="shared" si="10"/>
+        <f>100%-F630</f>
         <v>0</v>
       </c>
       <c r="E630" s="4">
@@ -29592,7 +29592,7 @@
         <v>168</v>
       </c>
       <c r="D631" s="3">
-        <f t="shared" si="10"/>
+        <f>100%-F631</f>
         <v>0.38</v>
       </c>
       <c r="E631" s="4">
@@ -29634,7 +29634,7 @@
         <v>154</v>
       </c>
       <c r="D632" s="3">
-        <f t="shared" si="10"/>
+        <f>100%-F632</f>
         <v>0.73</v>
       </c>
       <c r="E632" s="4">
@@ -29676,7 +29676,7 @@
         <v>828</v>
       </c>
       <c r="D633" s="3">
-        <f t="shared" si="10"/>
+        <f>100%-F633</f>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="E633" s="4">
@@ -29718,7 +29718,7 @@
         <v>117</v>
       </c>
       <c r="D634" s="3">
-        <f t="shared" si="10"/>
+        <f>100%-F634</f>
         <v>0.44999999999999996</v>
       </c>
       <c r="E634" s="4">
@@ -29760,7 +29760,7 @@
         <v>278</v>
       </c>
       <c r="D635" s="3">
-        <f t="shared" si="10"/>
+        <f>100%-F635</f>
         <v>0.22999999999999998</v>
       </c>
       <c r="E635" s="4">
@@ -29802,7 +29802,7 @@
         <v>129</v>
       </c>
       <c r="D636" s="3">
-        <f t="shared" si="10"/>
+        <f>100%-F636</f>
         <v>0.37</v>
       </c>
       <c r="E636" s="4">
@@ -29845,7 +29845,7 @@
         <v>270</v>
       </c>
       <c r="D637" s="3">
-        <f t="shared" si="10"/>
+        <f>100%-F637</f>
         <v>0.22999999999999998</v>
       </c>
       <c r="E637" s="4">
@@ -29887,7 +29887,7 @@
         <v>197</v>
       </c>
       <c r="D638" s="3">
-        <f t="shared" si="10"/>
+        <f>100%-F638</f>
         <v>0.38</v>
       </c>
       <c r="E638" s="4">
@@ -29929,7 +29929,7 @@
         <v>105</v>
       </c>
       <c r="D639" s="3">
-        <f t="shared" si="10"/>
+        <f>100%-F639</f>
         <v>0.65</v>
       </c>
       <c r="E639" s="4">
@@ -29971,7 +29971,7 @@
         <v>243</v>
       </c>
       <c r="D640" s="3">
-        <f t="shared" si="10"/>
+        <f>100%-F640</f>
         <v>0.30000000000000004</v>
       </c>
       <c r="E640" s="4">
@@ -30014,7 +30014,7 @@
         <v>617</v>
       </c>
       <c r="D641" s="3">
-        <f t="shared" si="10"/>
+        <f>100%-F641</f>
         <v>0.22999999999999998</v>
       </c>
       <c r="E641" s="4">
@@ -30056,7 +30056,7 @@
         <v>780</v>
       </c>
       <c r="D642" s="3">
-        <f t="shared" ref="D642:D705" si="11">100%-F642</f>
+        <f>100%-F642</f>
         <v>0</v>
       </c>
       <c r="E642" s="4">
@@ -30098,7 +30098,7 @@
         <v>656</v>
       </c>
       <c r="D643" s="3">
-        <f t="shared" si="11"/>
+        <f>100%-F643</f>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="E643" s="4">
@@ -30140,7 +30140,7 @@
         <v>162</v>
       </c>
       <c r="D644" s="3">
-        <f t="shared" si="11"/>
+        <f>100%-F644</f>
         <v>0.38</v>
       </c>
       <c r="E644" s="4">
@@ -30182,7 +30182,7 @@
         <v>380</v>
       </c>
       <c r="D645" s="3">
-        <f t="shared" si="11"/>
+        <f>100%-F645</f>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E645" s="4">
@@ -30225,7 +30225,7 @@
         <v>536</v>
       </c>
       <c r="D646" s="3">
-        <f t="shared" si="11"/>
+        <f>100%-F646</f>
         <v>0.38</v>
       </c>
       <c r="E646" s="4">
@@ -30268,7 +30268,7 @@
         <v>419</v>
       </c>
       <c r="D647" s="3">
-        <f t="shared" si="11"/>
+        <f>100%-F647</f>
         <v>0.38</v>
       </c>
       <c r="E647" s="4">
@@ -30311,7 +30311,7 @@
         <v>102</v>
       </c>
       <c r="D648" s="3">
-        <f t="shared" si="11"/>
+        <f>100%-F648</f>
         <v>0.65</v>
       </c>
       <c r="E648" s="4">
@@ -30353,7 +30353,7 @@
         <v>127</v>
       </c>
       <c r="D649" s="3">
-        <f t="shared" si="11"/>
+        <f>100%-F649</f>
         <v>0.44999999999999996</v>
       </c>
       <c r="E649" s="4">
@@ -30395,7 +30395,7 @@
         <v>440</v>
       </c>
       <c r="D650" s="3">
-        <f t="shared" si="11"/>
+        <f>100%-F650</f>
         <v>0.38</v>
       </c>
       <c r="E650" s="4">
@@ -30438,11 +30438,11 @@
         <v>260</v>
       </c>
       <c r="D651" s="3">
-        <f t="shared" si="11"/>
+        <f>100%-F651</f>
         <v>0.38</v>
       </c>
       <c r="E651" s="4">
-        <f t="shared" ref="E651:E652" si="12">I651*4%</f>
+        <f t="shared" ref="E651:E652" si="1">I651*4%</f>
         <v>0.04</v>
       </c>
       <c r="F651" s="4">
@@ -30481,11 +30481,11 @@
         <v>455</v>
       </c>
       <c r="D652" s="3">
-        <f t="shared" si="11"/>
+        <f>100%-F652</f>
         <v>0.38</v>
       </c>
       <c r="E652" s="4">
-        <f t="shared" si="12"/>
+        <f t="shared" si="1"/>
         <v>0.04</v>
       </c>
       <c r="F652" s="4">
@@ -30524,7 +30524,7 @@
         <v>352</v>
       </c>
       <c r="D653" s="3">
-        <f t="shared" si="11"/>
+        <f>100%-F653</f>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E653" s="4">
@@ -30567,7 +30567,7 @@
         <v>133</v>
       </c>
       <c r="D654" s="3">
-        <f t="shared" si="11"/>
+        <f>100%-F654</f>
         <v>0.73</v>
       </c>
       <c r="E654" s="4">
@@ -30609,7 +30609,7 @@
         <v>387</v>
       </c>
       <c r="D655" s="3">
-        <f t="shared" si="11"/>
+        <f>100%-F655</f>
         <v>0.22999999999999998</v>
       </c>
       <c r="E655" s="4">
@@ -30651,7 +30651,7 @@
         <v>682</v>
       </c>
       <c r="D656" s="3">
-        <f t="shared" si="11"/>
+        <f>100%-F656</f>
         <v>0.18000000000000005</v>
       </c>
       <c r="E656" s="4">
@@ -30693,7 +30693,7 @@
         <v>546</v>
       </c>
       <c r="D657" s="3">
-        <f t="shared" si="11"/>
+        <f>100%-F657</f>
         <v>0</v>
       </c>
       <c r="E657" s="4">
@@ -30735,7 +30735,7 @@
         <v>447</v>
       </c>
       <c r="D658" s="3">
-        <f t="shared" si="11"/>
+        <f>100%-F658</f>
         <v>0</v>
       </c>
       <c r="E658" s="4">
@@ -30777,7 +30777,7 @@
         <v>403</v>
       </c>
       <c r="D659" s="3">
-        <f t="shared" si="11"/>
+        <f>100%-F659</f>
         <v>0</v>
       </c>
       <c r="E659" s="4">
@@ -30819,7 +30819,7 @@
         <v>132</v>
       </c>
       <c r="D660" s="3">
-        <f t="shared" si="11"/>
+        <f>100%-F660</f>
         <v>0.8</v>
       </c>
       <c r="E660" s="4">
@@ -30861,7 +30861,7 @@
         <v>802</v>
       </c>
       <c r="D661" s="3">
-        <f t="shared" si="11"/>
+        <f>100%-F661</f>
         <v>0</v>
       </c>
       <c r="E661" s="4">
@@ -30903,7 +30903,7 @@
         <v>177</v>
       </c>
       <c r="D662" s="3">
-        <f t="shared" si="11"/>
+        <f>100%-F662</f>
         <v>0.44999999999999996</v>
       </c>
       <c r="E662" s="4">
@@ -30946,7 +30946,7 @@
         <v>1387</v>
       </c>
       <c r="D663" s="3">
-        <f t="shared" si="11"/>
+        <f>100%-F663</f>
         <v>0</v>
       </c>
       <c r="E663" s="4">
@@ -30988,7 +30988,7 @@
         <v>515</v>
       </c>
       <c r="D664" s="3">
-        <f t="shared" si="11"/>
+        <f>100%-F664</f>
         <v>0.25</v>
       </c>
       <c r="E664" s="4">
@@ -31030,7 +31030,7 @@
         <v>450</v>
       </c>
       <c r="D665" s="3">
-        <f t="shared" si="11"/>
+        <f>100%-F665</f>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="E665" s="4">
@@ -31072,7 +31072,7 @@
         <v>633</v>
       </c>
       <c r="D666" s="3">
-        <f t="shared" si="11"/>
+        <f>100%-F666</f>
         <v>0</v>
       </c>
       <c r="E666" s="4">
@@ -31114,7 +31114,7 @@
         <v>178</v>
       </c>
       <c r="D667" s="3">
-        <f t="shared" si="11"/>
+        <f>100%-F667</f>
         <v>0.22999999999999998</v>
       </c>
       <c r="E667" s="4">
@@ -31156,7 +31156,7 @@
         <v>162</v>
       </c>
       <c r="D668" s="3">
-        <f t="shared" si="11"/>
+        <f>100%-F668</f>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E668" s="4">
@@ -31198,7 +31198,7 @@
         <v>594</v>
       </c>
       <c r="D669" s="3">
-        <f t="shared" si="11"/>
+        <f>100%-F669</f>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E669" s="4">
@@ -31240,7 +31240,7 @@
         <v>549</v>
       </c>
       <c r="D670" s="3">
-        <f t="shared" si="11"/>
+        <f>100%-F670</f>
         <v>0.38</v>
       </c>
       <c r="E670" s="4">
@@ -31282,7 +31282,7 @@
         <v>1116</v>
       </c>
       <c r="D671" s="3">
-        <f t="shared" si="11"/>
+        <f>100%-F671</f>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E671" s="4">
@@ -31324,7 +31324,7 @@
         <v>294</v>
       </c>
       <c r="D672" s="3">
-        <f t="shared" si="11"/>
+        <f>100%-F672</f>
         <v>0.30000000000000004</v>
       </c>
       <c r="E672" s="4">
@@ -31366,7 +31366,7 @@
         <v>987</v>
       </c>
       <c r="D673" s="3">
-        <f t="shared" si="11"/>
+        <f>100%-F673</f>
         <v>0.30000000000000004</v>
       </c>
       <c r="E673" s="4">
@@ -31408,7 +31408,7 @@
         <v>137</v>
       </c>
       <c r="D674" s="3">
-        <f t="shared" si="11"/>
+        <f>100%-F674</f>
         <v>0.30000000000000004</v>
       </c>
       <c r="E674" s="4">
@@ -31450,7 +31450,7 @@
         <v>256</v>
       </c>
       <c r="D675" s="3">
-        <f t="shared" si="11"/>
+        <f>100%-F675</f>
         <v>0.26</v>
       </c>
       <c r="E675" s="4">
@@ -31492,7 +31492,7 @@
         <v>371</v>
       </c>
       <c r="D676" s="3">
-        <f t="shared" si="11"/>
+        <f>100%-F676</f>
         <v>0.25</v>
       </c>
       <c r="E676" s="4">
@@ -31534,7 +31534,7 @@
         <v>543</v>
       </c>
       <c r="D677" s="3">
-        <f t="shared" si="11"/>
+        <f>100%-F677</f>
         <v>0.28000000000000003</v>
       </c>
       <c r="E677" s="4">
@@ -31576,7 +31576,7 @@
         <v>546</v>
       </c>
       <c r="D678" s="3">
-        <f t="shared" si="11"/>
+        <f>100%-F678</f>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E678" s="4">
@@ -31618,7 +31618,7 @@
         <v>416</v>
       </c>
       <c r="D679" s="3">
-        <f t="shared" si="11"/>
+        <f>100%-F679</f>
         <v>0</v>
       </c>
       <c r="E679" s="4">
@@ -31660,7 +31660,7 @@
         <v>886</v>
       </c>
       <c r="D680" s="3">
-        <f t="shared" si="11"/>
+        <f>100%-F680</f>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E680" s="4">
@@ -31702,7 +31702,7 @@
         <v>388</v>
       </c>
       <c r="D681" s="3">
-        <f t="shared" si="11"/>
+        <f>100%-F681</f>
         <v>0.18000000000000005</v>
       </c>
       <c r="E681" s="4">
@@ -31744,7 +31744,7 @@
         <v>574</v>
       </c>
       <c r="D682" s="3">
-        <f t="shared" si="11"/>
+        <f>100%-F682</f>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E682" s="4">
@@ -31786,7 +31786,7 @@
         <v>102</v>
       </c>
       <c r="D683" s="3">
-        <f t="shared" si="11"/>
+        <f>100%-F683</f>
         <v>0.22999999999999998</v>
       </c>
       <c r="E683" s="4">
@@ -31828,7 +31828,7 @@
         <v>131</v>
       </c>
       <c r="D684" s="3">
-        <f t="shared" si="11"/>
+        <f>100%-F684</f>
         <v>0.30000000000000004</v>
       </c>
       <c r="E684" s="4">
@@ -31870,7 +31870,7 @@
         <v>183</v>
       </c>
       <c r="D685" s="3">
-        <f t="shared" si="11"/>
+        <f>100%-F685</f>
         <v>0.38</v>
       </c>
       <c r="E685" s="4">
@@ -31912,7 +31912,7 @@
         <v>458</v>
       </c>
       <c r="D686" s="3">
-        <f t="shared" si="11"/>
+        <f>100%-F686</f>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E686" s="4">
@@ -31954,7 +31954,7 @@
         <v>429</v>
       </c>
       <c r="D687" s="3">
-        <f t="shared" si="11"/>
+        <f>100%-F687</f>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="E687" s="4">
@@ -31996,7 +31996,7 @@
         <v>248</v>
       </c>
       <c r="D688" s="3">
-        <f t="shared" si="11"/>
+        <f>100%-F688</f>
         <v>0.38</v>
       </c>
       <c r="E688" s="4">
@@ -32038,7 +32038,7 @@
         <v>678</v>
       </c>
       <c r="D689" s="3">
-        <f t="shared" si="11"/>
+        <f>100%-F689</f>
         <v>0</v>
       </c>
       <c r="E689" s="4">
@@ -32080,7 +32080,7 @@
         <v>846</v>
       </c>
       <c r="D690" s="3">
-        <f t="shared" si="11"/>
+        <f>100%-F690</f>
         <v>0.32999999999999996</v>
       </c>
       <c r="E690" s="4">
@@ -32122,7 +32122,7 @@
         <v>189</v>
       </c>
       <c r="D691" s="3">
-        <f t="shared" si="11"/>
+        <f>100%-F691</f>
         <v>0.38</v>
       </c>
       <c r="E691" s="4">
@@ -32164,7 +32164,7 @@
         <v>130</v>
       </c>
       <c r="D692" s="3">
-        <f t="shared" si="11"/>
+        <f>100%-F692</f>
         <v>0.71</v>
       </c>
       <c r="E692" s="4">
@@ -32206,7 +32206,7 @@
         <v>105</v>
       </c>
       <c r="D693" s="3">
-        <f t="shared" si="11"/>
+        <f>100%-F693</f>
         <v>0.38</v>
       </c>
       <c r="E693" s="4">
@@ -32248,7 +32248,7 @@
         <v>249</v>
       </c>
       <c r="D694" s="3">
-        <f t="shared" si="11"/>
+        <f>100%-F694</f>
         <v>0.30000000000000004</v>
       </c>
       <c r="E694" s="4">
@@ -32290,7 +32290,7 @@
         <v>993</v>
       </c>
       <c r="D695" s="3">
-        <f t="shared" si="11"/>
+        <f>100%-F695</f>
         <v>0</v>
       </c>
       <c r="E695" s="4">
@@ -32332,7 +32332,7 @@
         <v>584</v>
       </c>
       <c r="D696" s="3">
-        <f t="shared" si="11"/>
+        <f>100%-F696</f>
         <v>0</v>
       </c>
       <c r="E696" s="4">
@@ -32374,7 +32374,7 @@
         <v>142</v>
       </c>
       <c r="D697" s="3">
-        <f t="shared" si="11"/>
+        <f>100%-F697</f>
         <v>0.20999999999999996</v>
       </c>
       <c r="E697" s="4">
@@ -32416,7 +32416,7 @@
         <v>114</v>
       </c>
       <c r="D698" s="3">
-        <f t="shared" si="11"/>
+        <f>100%-F698</f>
         <v>0.22999999999999998</v>
       </c>
       <c r="E698" s="4">
@@ -32458,7 +32458,7 @@
         <v>118</v>
       </c>
       <c r="D699" s="3">
-        <f t="shared" si="11"/>
+        <f>100%-F699</f>
         <v>0.37</v>
       </c>
       <c r="E699" s="4">
@@ -32500,7 +32500,7 @@
         <v>386</v>
       </c>
       <c r="D700" s="3">
-        <f t="shared" si="11"/>
+        <f>100%-F700</f>
         <v>0.18000000000000005</v>
       </c>
       <c r="E700" s="4">
@@ -32542,7 +32542,7 @@
         <v>188</v>
       </c>
       <c r="D701" s="3">
-        <f t="shared" si="11"/>
+        <f>100%-F701</f>
         <v>0.38</v>
       </c>
       <c r="E701" s="4">
@@ -32584,7 +32584,7 @@
         <v>153</v>
       </c>
       <c r="D702" s="3">
-        <f t="shared" si="11"/>
+        <f>100%-F702</f>
         <v>0.38</v>
       </c>
       <c r="E702" s="4">
@@ -32626,7 +32626,7 @@
         <v>109</v>
       </c>
       <c r="D703" s="3">
-        <f t="shared" si="11"/>
+        <f>100%-F703</f>
         <v>0.30000000000000004</v>
       </c>
       <c r="E703" s="4">
@@ -32668,7 +32668,7 @@
         <v>600</v>
       </c>
       <c r="D704" s="3">
-        <f t="shared" si="11"/>
+        <f>100%-F704</f>
         <v>0</v>
       </c>
       <c r="E704" s="4">
@@ -32710,7 +32710,7 @@
         <v>218</v>
       </c>
       <c r="D705" s="3">
-        <f t="shared" si="11"/>
+        <f>100%-F705</f>
         <v>0.22999999999999998</v>
       </c>
       <c r="E705" s="4">
@@ -32752,7 +32752,7 @@
         <v>109</v>
       </c>
       <c r="D706" s="3">
-        <f t="shared" ref="D706:D769" si="13">100%-F706</f>
+        <f>100%-F706</f>
         <v>0.44999999999999996</v>
       </c>
       <c r="E706" s="4">
@@ -32794,7 +32794,7 @@
         <v>649</v>
       </c>
       <c r="D707" s="3">
-        <f t="shared" si="13"/>
+        <f>100%-F707</f>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E707" s="4">
@@ -32836,7 +32836,7 @@
         <v>418</v>
       </c>
       <c r="D708" s="3">
-        <f t="shared" si="13"/>
+        <f>100%-F708</f>
         <v>0.18000000000000005</v>
       </c>
       <c r="E708" s="4">
@@ -32878,7 +32878,7 @@
         <v>228</v>
       </c>
       <c r="D709" s="3">
-        <f t="shared" si="13"/>
+        <f>100%-F709</f>
         <v>0.30000000000000004</v>
       </c>
       <c r="E709" s="4">
@@ -32920,7 +32920,7 @@
         <v>326</v>
       </c>
       <c r="D710" s="3">
-        <f t="shared" si="13"/>
+        <f>100%-F710</f>
         <v>0.30000000000000004</v>
       </c>
       <c r="E710" s="4">
@@ -32962,7 +32962,7 @@
         <v>593</v>
       </c>
       <c r="D711" s="3">
-        <f t="shared" si="13"/>
+        <f>100%-F711</f>
         <v>0</v>
       </c>
       <c r="E711" s="4">
@@ -33004,7 +33004,7 @@
         <v>130</v>
       </c>
       <c r="D712" s="3">
-        <f t="shared" si="13"/>
+        <f>100%-F712</f>
         <v>0.45999999999999996</v>
       </c>
       <c r="E712" s="4">
@@ -33046,7 +33046,7 @@
         <v>608</v>
       </c>
       <c r="D713" s="3">
-        <f t="shared" si="13"/>
+        <f>100%-F713</f>
         <v>0.30000000000000004</v>
       </c>
       <c r="E713" s="4">
@@ -33088,7 +33088,7 @@
         <v>145</v>
       </c>
       <c r="D714" s="3">
-        <f t="shared" si="13"/>
+        <f>100%-F714</f>
         <v>0.65</v>
       </c>
       <c r="E714" s="4">
@@ -33130,7 +33130,7 @@
         <v>113</v>
       </c>
       <c r="D715" s="3">
-        <f t="shared" si="13"/>
+        <f>100%-F715</f>
         <v>0.5</v>
       </c>
       <c r="E715" s="4">
@@ -33172,7 +33172,7 @@
         <v>130</v>
       </c>
       <c r="D716" s="3">
-        <f t="shared" si="13"/>
+        <f>100%-F716</f>
         <v>0.26</v>
       </c>
       <c r="E716" s="4">
@@ -33214,7 +33214,7 @@
         <v>886</v>
       </c>
       <c r="D717" s="3">
-        <f t="shared" si="13"/>
+        <f>100%-F717</f>
         <v>0</v>
       </c>
       <c r="E717" s="4">
@@ -33256,7 +33256,7 @@
         <v>681</v>
       </c>
       <c r="D718" s="3">
-        <f t="shared" si="13"/>
+        <f>100%-F718</f>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E718" s="4">
@@ -33298,7 +33298,7 @@
         <v>169</v>
       </c>
       <c r="D719" s="3">
-        <f t="shared" si="13"/>
+        <f>100%-F719</f>
         <v>0.22999999999999998</v>
       </c>
       <c r="E719" s="4">
@@ -33340,7 +33340,7 @@
         <v>110</v>
       </c>
       <c r="D720" s="3">
-        <f t="shared" si="13"/>
+        <f>100%-F720</f>
         <v>0.28000000000000003</v>
       </c>
       <c r="E720" s="4">
@@ -33382,7 +33382,7 @@
         <v>8967</v>
       </c>
       <c r="D721" s="3">
-        <f t="shared" si="13"/>
+        <f>100%-F721</f>
         <v>0</v>
       </c>
       <c r="E721" s="4">
@@ -33424,7 +33424,7 @@
         <v>216</v>
       </c>
       <c r="D722" s="3">
-        <f t="shared" si="13"/>
+        <f>100%-F722</f>
         <v>0.32999999999999996</v>
       </c>
       <c r="E722" s="4">
@@ -33466,7 +33466,7 @@
         <v>5047</v>
       </c>
       <c r="D723" s="3">
-        <f t="shared" si="13"/>
+        <f>100%-F723</f>
         <v>0</v>
       </c>
       <c r="E723" s="4">
@@ -33508,7 +33508,7 @@
         <v>157</v>
       </c>
       <c r="D724" s="3">
-        <f t="shared" si="13"/>
+        <f>100%-F724</f>
         <v>0.25</v>
       </c>
       <c r="E724" s="4">
@@ -33550,7 +33550,7 @@
         <v>147</v>
       </c>
       <c r="D725" s="3">
-        <f t="shared" si="13"/>
+        <f>100%-F725</f>
         <v>0.30000000000000004</v>
       </c>
       <c r="E725" s="4">
@@ -33592,7 +33592,7 @@
         <v>1524</v>
       </c>
       <c r="D726" s="3">
-        <f t="shared" si="13"/>
+        <f>100%-F726</f>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="E726" s="4">
@@ -33634,7 +33634,7 @@
         <v>138</v>
       </c>
       <c r="D727" s="3">
-        <f t="shared" si="13"/>
+        <f>100%-F727</f>
         <v>0.32999999999999996</v>
       </c>
       <c r="E727" s="4">
@@ -33676,7 +33676,7 @@
         <v>285</v>
       </c>
       <c r="D728" s="3">
-        <f t="shared" si="13"/>
+        <f>100%-F728</f>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E728" s="4">
@@ -33718,7 +33718,7 @@
         <v>281</v>
       </c>
       <c r="D729" s="3">
-        <f t="shared" si="13"/>
+        <f>100%-F729</f>
         <v>0.21999999999999997</v>
       </c>
       <c r="E729" s="4">
@@ -33760,7 +33760,7 @@
         <v>648</v>
       </c>
       <c r="D730" s="3">
-        <f t="shared" si="13"/>
+        <f>100%-F730</f>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="E730" s="4">
@@ -33802,7 +33802,7 @@
         <v>232</v>
       </c>
       <c r="D731" s="3">
-        <f t="shared" si="13"/>
+        <f>100%-F731</f>
         <v>0.15000000000000002</v>
       </c>
       <c r="E731" s="4">
@@ -33844,7 +33844,7 @@
         <v>221</v>
       </c>
       <c r="D732" s="3">
-        <f t="shared" si="13"/>
+        <f>100%-F732</f>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E732" s="4">
@@ -33886,7 +33886,7 @@
         <v>942</v>
       </c>
       <c r="D733" s="3">
-        <f t="shared" si="13"/>
+        <f>100%-F733</f>
         <v>0</v>
       </c>
       <c r="E733" s="4">
@@ -33928,7 +33928,7 @@
         <v>174</v>
       </c>
       <c r="D734" s="3">
-        <f t="shared" si="13"/>
+        <f>100%-F734</f>
         <v>0.15000000000000002</v>
       </c>
       <c r="E734" s="4">
@@ -33970,7 +33970,7 @@
         <v>213</v>
       </c>
       <c r="D735" s="3">
-        <f t="shared" si="13"/>
+        <f>100%-F735</f>
         <v>0.15000000000000002</v>
       </c>
       <c r="E735" s="4">
@@ -34012,7 +34012,7 @@
         <v>239</v>
       </c>
       <c r="D736" s="3">
-        <f t="shared" si="13"/>
+        <f>100%-F736</f>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="E736" s="4">
@@ -34054,7 +34054,7 @@
         <v>252</v>
       </c>
       <c r="D737" s="3">
-        <f t="shared" si="13"/>
+        <f>100%-F737</f>
         <v>0.17000000000000004</v>
       </c>
       <c r="E737" s="4">
@@ -34096,7 +34096,7 @@
         <v>415</v>
       </c>
       <c r="D738" s="3">
-        <f t="shared" si="13"/>
+        <f>100%-F738</f>
         <v>0.38</v>
       </c>
       <c r="E738" s="4">
@@ -34138,7 +34138,7 @@
         <v>601</v>
       </c>
       <c r="D739" s="3">
-        <f t="shared" si="13"/>
+        <f>100%-F739</f>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="E739" s="4">
@@ -34180,7 +34180,7 @@
         <v>118</v>
       </c>
       <c r="D740" s="3">
-        <f t="shared" si="13"/>
+        <f>100%-F740</f>
         <v>0.5</v>
       </c>
       <c r="E740" s="4">
@@ -34222,7 +34222,7 @@
         <v>635</v>
       </c>
       <c r="D741" s="3">
-        <f t="shared" si="13"/>
+        <f>100%-F741</f>
         <v>0.15000000000000002</v>
       </c>
       <c r="E741" s="4">
@@ -34264,7 +34264,7 @@
         <v>356</v>
       </c>
       <c r="D742" s="3">
-        <f t="shared" si="13"/>
+        <f>100%-F742</f>
         <v>0.22999999999999998</v>
       </c>
       <c r="E742" s="4">
@@ -34306,7 +34306,7 @@
         <v>4054.0000000000005</v>
       </c>
       <c r="D743" s="3">
-        <f t="shared" si="13"/>
+        <f>100%-F743</f>
         <v>0</v>
       </c>
       <c r="E743" s="4">
@@ -34348,7 +34348,7 @@
         <v>187</v>
       </c>
       <c r="D744" s="3">
-        <f t="shared" si="13"/>
+        <f>100%-F744</f>
         <v>0.53</v>
       </c>
       <c r="E744" s="4">
@@ -34390,7 +34390,7 @@
         <v>300</v>
       </c>
       <c r="D745" s="3">
-        <f t="shared" si="13"/>
+        <f>100%-F745</f>
         <v>0.43000000000000005</v>
       </c>
       <c r="E745" s="4">
@@ -34432,7 +34432,7 @@
         <v>317</v>
       </c>
       <c r="D746" s="3">
-        <f t="shared" si="13"/>
+        <f>100%-F746</f>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="E746" s="4">
@@ -34474,7 +34474,7 @@
         <v>191</v>
       </c>
       <c r="D747" s="3">
-        <f t="shared" si="13"/>
+        <f>100%-F747</f>
         <v>0.15000000000000002</v>
       </c>
       <c r="E747" s="4">
@@ -34516,7 +34516,7 @@
         <v>291</v>
       </c>
       <c r="D748" s="3">
-        <f t="shared" si="13"/>
+        <f>100%-F748</f>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="E748" s="4">
@@ -34558,7 +34558,7 @@
         <v>172</v>
       </c>
       <c r="D749" s="3">
-        <f t="shared" si="13"/>
+        <f>100%-F749</f>
         <v>0.65</v>
       </c>
       <c r="E749" s="4">
@@ -34600,7 +34600,7 @@
         <v>399</v>
       </c>
       <c r="D750" s="3">
-        <f t="shared" si="13"/>
+        <f>100%-F750</f>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="E750" s="4">
@@ -34642,7 +34642,7 @@
         <v>398</v>
       </c>
       <c r="D751" s="3">
-        <f t="shared" si="13"/>
+        <f>100%-F751</f>
         <v>0.28000000000000003</v>
       </c>
       <c r="E751" s="4">
@@ -34684,7 +34684,7 @@
         <v>139</v>
       </c>
       <c r="D752" s="3">
-        <f t="shared" si="13"/>
+        <f>100%-F752</f>
         <v>0.5</v>
       </c>
       <c r="E752" s="4">
@@ -34726,7 +34726,7 @@
         <v>305</v>
       </c>
       <c r="D753" s="3">
-        <f t="shared" si="13"/>
+        <f>100%-F753</f>
         <v>0.38</v>
       </c>
       <c r="E753" s="4">
@@ -34768,7 +34768,7 @@
         <v>575</v>
       </c>
       <c r="D754" s="3">
-        <f t="shared" si="13"/>
+        <f>100%-F754</f>
         <v>0</v>
       </c>
       <c r="E754" s="4">
@@ -34810,7 +34810,7 @@
         <v>763</v>
       </c>
       <c r="D755" s="3">
-        <f t="shared" si="13"/>
+        <f>100%-F755</f>
         <v>0</v>
       </c>
       <c r="E755" s="4">
@@ -34852,7 +34852,7 @@
         <v>120</v>
       </c>
       <c r="D756" s="3">
-        <f t="shared" si="13"/>
+        <f>100%-F756</f>
         <v>0.17000000000000004</v>
       </c>
       <c r="E756" s="4">
@@ -34894,7 +34894,7 @@
         <v>205</v>
       </c>
       <c r="D757" s="3">
-        <f t="shared" si="13"/>
+        <f>100%-F757</f>
         <v>0.22999999999999998</v>
       </c>
       <c r="E757" s="4">
@@ -34936,7 +34936,7 @@
         <v>338</v>
       </c>
       <c r="D758" s="3">
-        <f t="shared" si="13"/>
+        <f>100%-F758</f>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E758" s="4">
@@ -34978,7 +34978,7 @@
         <v>360</v>
       </c>
       <c r="D759" s="3">
-        <f t="shared" si="13"/>
+        <f>100%-F759</f>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="E759" s="4">
@@ -35020,7 +35020,7 @@
         <v>329</v>
       </c>
       <c r="D760" s="3">
-        <f t="shared" si="13"/>
+        <f>100%-F760</f>
         <v>0.30000000000000004</v>
       </c>
       <c r="E760" s="4">
@@ -35062,7 +35062,7 @@
         <v>265</v>
       </c>
       <c r="D761" s="3">
-        <f t="shared" si="13"/>
+        <f>100%-F761</f>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E761" s="4">
@@ -35104,7 +35104,7 @@
         <v>491</v>
       </c>
       <c r="D762" s="3">
-        <f t="shared" si="13"/>
+        <f>100%-F762</f>
         <v>0</v>
       </c>
       <c r="E762" s="4">
@@ -35146,7 +35146,7 @@
         <v>102</v>
       </c>
       <c r="D763" s="3">
-        <f t="shared" si="13"/>
+        <f>100%-F763</f>
         <v>0.37</v>
       </c>
       <c r="E763" s="4">
@@ -35188,7 +35188,7 @@
         <v>252</v>
       </c>
       <c r="D764" s="3">
-        <f t="shared" si="13"/>
+        <f>100%-F764</f>
         <v>0.30000000000000004</v>
       </c>
       <c r="E764" s="4">
@@ -35230,7 +35230,7 @@
         <v>124</v>
       </c>
       <c r="D765" s="3">
-        <f t="shared" si="13"/>
+        <f>100%-F765</f>
         <v>0.44999999999999996</v>
       </c>
       <c r="E765" s="4">
@@ -35272,7 +35272,7 @@
         <v>328</v>
       </c>
       <c r="D766" s="3">
-        <f t="shared" si="13"/>
+        <f>100%-F766</f>
         <v>0.30000000000000004</v>
       </c>
       <c r="E766" s="4">
@@ -35314,7 +35314,7 @@
         <v>644</v>
       </c>
       <c r="D767" s="3">
-        <f t="shared" si="13"/>
+        <f>100%-F767</f>
         <v>0</v>
       </c>
       <c r="E767" s="4">
@@ -35356,7 +35356,7 @@
         <v>336</v>
       </c>
       <c r="D768" s="3">
-        <f t="shared" si="13"/>
+        <f>100%-F768</f>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E768" s="4">
@@ -35398,7 +35398,7 @@
         <v>158</v>
       </c>
       <c r="D769" s="3">
-        <f t="shared" si="13"/>
+        <f>100%-F769</f>
         <v>0.30000000000000004</v>
       </c>
       <c r="E769" s="4">
@@ -35440,7 +35440,7 @@
         <v>171</v>
       </c>
       <c r="D770" s="3">
-        <f t="shared" ref="D770:D833" si="14">100%-F770</f>
+        <f>100%-F770</f>
         <v>0.15000000000000002</v>
       </c>
       <c r="E770" s="4">
@@ -35482,7 +35482,7 @@
         <v>358</v>
       </c>
       <c r="D771" s="3">
-        <f t="shared" si="14"/>
+        <f>100%-F771</f>
         <v>0.12</v>
       </c>
       <c r="E771" s="4">
@@ -35524,7 +35524,7 @@
         <v>322</v>
       </c>
       <c r="D772" s="3">
-        <f t="shared" si="14"/>
+        <f>100%-F772</f>
         <v>0.22999999999999998</v>
       </c>
       <c r="E772" s="4">
@@ -35566,7 +35566,7 @@
         <v>146</v>
       </c>
       <c r="D773" s="3">
-        <f t="shared" si="14"/>
+        <f>100%-F773</f>
         <v>0.30000000000000004</v>
       </c>
       <c r="E773" s="4">
@@ -35608,7 +35608,7 @@
         <v>1372</v>
       </c>
       <c r="D774" s="3">
-        <f t="shared" si="14"/>
+        <f>100%-F774</f>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="E774" s="4">
@@ -35650,7 +35650,7 @@
         <v>360</v>
       </c>
       <c r="D775" s="3">
-        <f t="shared" si="14"/>
+        <f>100%-F775</f>
         <v>0.15000000000000002</v>
       </c>
       <c r="E775" s="4">
@@ -35692,7 +35692,7 @@
         <v>158</v>
       </c>
       <c r="D776" s="3">
-        <f t="shared" si="14"/>
+        <f>100%-F776</f>
         <v>0.18999999999999995</v>
       </c>
       <c r="E776" s="4">
@@ -35734,7 +35734,7 @@
         <v>518</v>
       </c>
       <c r="D777" s="3">
-        <f t="shared" si="14"/>
+        <f>100%-F777</f>
         <v>0</v>
       </c>
       <c r="E777" s="4">
@@ -35776,7 +35776,7 @@
         <v>279</v>
       </c>
       <c r="D778" s="3">
-        <f t="shared" si="14"/>
+        <f>100%-F778</f>
         <v>0.28000000000000003</v>
       </c>
       <c r="E778" s="4">
@@ -35818,7 +35818,7 @@
         <v>345</v>
       </c>
       <c r="D779" s="3">
-        <f t="shared" si="14"/>
+        <f>100%-F779</f>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="E779" s="4">
@@ -35860,7 +35860,7 @@
         <v>105</v>
       </c>
       <c r="D780" s="3">
-        <f t="shared" si="14"/>
+        <f>100%-F780</f>
         <v>0.44999999999999996</v>
       </c>
       <c r="E780" s="4">
@@ -35902,7 +35902,7 @@
         <v>297</v>
       </c>
       <c r="D781" s="3">
-        <f t="shared" si="14"/>
+        <f>100%-F781</f>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E781" s="4">
@@ -35944,7 +35944,7 @@
         <v>342</v>
       </c>
       <c r="D782" s="3">
-        <f t="shared" si="14"/>
+        <f>100%-F782</f>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E782" s="4">
@@ -35986,7 +35986,7 @@
         <v>153</v>
       </c>
       <c r="D783" s="3">
-        <f t="shared" si="14"/>
+        <f>100%-F783</f>
         <v>0.22999999999999998</v>
       </c>
       <c r="E783" s="4">
@@ -36028,7 +36028,7 @@
         <v>216</v>
       </c>
       <c r="D784" s="3">
-        <f t="shared" si="14"/>
+        <f>100%-F784</f>
         <v>0.22999999999999998</v>
       </c>
       <c r="E784" s="4">
@@ -36070,7 +36070,7 @@
         <v>147</v>
       </c>
       <c r="D785" s="3">
-        <f t="shared" si="14"/>
+        <f>100%-F785</f>
         <v>0.30000000000000004</v>
       </c>
       <c r="E785" s="4">
@@ -36112,7 +36112,7 @@
         <v>471</v>
       </c>
       <c r="D786" s="3">
-        <f t="shared" si="14"/>
+        <f>100%-F786</f>
         <v>0</v>
       </c>
       <c r="E786" s="4">
@@ -36154,7 +36154,7 @@
         <v>107</v>
       </c>
       <c r="D787" s="3">
-        <f t="shared" si="14"/>
+        <f>100%-F787</f>
         <v>0.30000000000000004</v>
       </c>
       <c r="E787" s="4">
@@ -36196,7 +36196,7 @@
         <v>164</v>
       </c>
       <c r="D788" s="3">
-        <f t="shared" si="14"/>
+        <f>100%-F788</f>
         <v>0.38</v>
       </c>
       <c r="E788" s="4">
@@ -36238,7 +36238,7 @@
         <v>467</v>
       </c>
       <c r="D789" s="3">
-        <f t="shared" si="14"/>
+        <f>100%-F789</f>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="E789" s="4">
@@ -36280,7 +36280,7 @@
         <v>198</v>
       </c>
       <c r="D790" s="3">
-        <f t="shared" si="14"/>
+        <f>100%-F790</f>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E790" s="4">
@@ -36322,7 +36322,7 @@
         <v>220</v>
       </c>
       <c r="D791" s="3">
-        <f t="shared" si="14"/>
+        <f>100%-F791</f>
         <v>0.30000000000000004</v>
       </c>
       <c r="E791" s="4">
@@ -36364,7 +36364,7 @@
         <v>131</v>
       </c>
       <c r="D792" s="3">
-        <f t="shared" si="14"/>
+        <f>100%-F792</f>
         <v>0.15000000000000002</v>
       </c>
       <c r="E792" s="4">
@@ -36406,7 +36406,7 @@
         <v>708</v>
       </c>
       <c r="D793" s="3">
-        <f t="shared" si="14"/>
+        <f>100%-F793</f>
         <v>0</v>
       </c>
       <c r="E793" s="4">
@@ -36448,7 +36448,7 @@
         <v>117</v>
       </c>
       <c r="D794" s="3">
-        <f t="shared" si="14"/>
+        <f>100%-F794</f>
         <v>0.30000000000000004</v>
       </c>
       <c r="E794" s="4">
@@ -36490,7 +36490,7 @@
         <v>406</v>
       </c>
       <c r="D795" s="3">
-        <f t="shared" si="14"/>
+        <f>100%-F795</f>
         <v>0.30000000000000004</v>
       </c>
       <c r="E795" s="4">
@@ -36532,7 +36532,7 @@
         <v>8000</v>
       </c>
       <c r="D796" s="3">
-        <f t="shared" si="14"/>
+        <f>100%-F796</f>
         <v>0</v>
       </c>
       <c r="E796" s="4">
@@ -36574,7 +36574,7 @@
         <v>205</v>
       </c>
       <c r="D797" s="3">
-        <f t="shared" si="14"/>
+        <f>100%-F797</f>
         <v>0.30000000000000004</v>
       </c>
       <c r="E797" s="4">
@@ -36616,7 +36616,7 @@
         <v>1010</v>
       </c>
       <c r="D798" s="3">
-        <f t="shared" si="14"/>
+        <f>100%-F798</f>
         <v>0</v>
       </c>
       <c r="E798" s="4">
@@ -36658,7 +36658,7 @@
         <v>607</v>
       </c>
       <c r="D799" s="3">
-        <f t="shared" si="14"/>
+        <f>100%-F799</f>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="E799" s="4">
@@ -36700,7 +36700,7 @@
         <v>212</v>
       </c>
       <c r="D800" s="3">
-        <f t="shared" si="14"/>
+        <f>100%-F800</f>
         <v>0.30000000000000004</v>
       </c>
       <c r="E800" s="4">
@@ -36742,7 +36742,7 @@
         <v>292</v>
       </c>
       <c r="D801" s="3">
-        <f t="shared" si="14"/>
+        <f>100%-F801</f>
         <v>0.22999999999999998</v>
       </c>
       <c r="E801" s="4">
@@ -36784,7 +36784,7 @@
         <v>688</v>
       </c>
       <c r="D802" s="3">
-        <f t="shared" si="14"/>
+        <f>100%-F802</f>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E802" s="4">
@@ -36826,7 +36826,7 @@
         <v>140</v>
       </c>
       <c r="D803" s="3">
-        <f t="shared" si="14"/>
+        <f>100%-F803</f>
         <v>0.72</v>
       </c>
       <c r="E803" s="4">
@@ -36868,7 +36868,7 @@
         <v>127</v>
       </c>
       <c r="D804" s="3">
-        <f t="shared" si="14"/>
+        <f>100%-F804</f>
         <v>0.37</v>
       </c>
       <c r="E804" s="4">
@@ -36910,7 +36910,7 @@
         <v>277</v>
       </c>
       <c r="D805" s="3">
-        <f t="shared" si="14"/>
+        <f>100%-F805</f>
         <v>0.30000000000000004</v>
       </c>
       <c r="E805" s="4">
@@ -36952,7 +36952,7 @@
         <v>862</v>
       </c>
       <c r="D806" s="3">
-        <f t="shared" si="14"/>
+        <f>100%-F806</f>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E806" s="4">
@@ -36994,7 +36994,7 @@
         <v>1402</v>
       </c>
       <c r="D807" s="3">
-        <f t="shared" si="14"/>
+        <f>100%-F807</f>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E807" s="4">
@@ -37036,7 +37036,7 @@
         <v>720</v>
       </c>
       <c r="D808" s="3">
-        <f t="shared" si="14"/>
+        <f>100%-F808</f>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E808" s="4">
@@ -37078,7 +37078,7 @@
         <v>608</v>
       </c>
       <c r="D809" s="3">
-        <f t="shared" si="14"/>
+        <f>100%-F809</f>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E809" s="4">
@@ -37120,7 +37120,7 @@
         <v>241</v>
       </c>
       <c r="D810" s="3">
-        <f t="shared" si="14"/>
+        <f>100%-F810</f>
         <v>0.58000000000000007</v>
       </c>
       <c r="E810" s="4">
@@ -37162,7 +37162,7 @@
         <v>186</v>
       </c>
       <c r="D811" s="3">
-        <f t="shared" si="14"/>
+        <f>100%-F811</f>
         <v>0.30000000000000004</v>
       </c>
       <c r="E811" s="4">
@@ -37204,7 +37204,7 @@
         <v>202</v>
       </c>
       <c r="D812" s="3">
-        <f t="shared" si="14"/>
+        <f>100%-F812</f>
         <v>0.30000000000000004</v>
       </c>
       <c r="E812" s="4">
@@ -37246,7 +37246,7 @@
         <v>1116</v>
       </c>
       <c r="D813" s="3">
-        <f t="shared" si="14"/>
+        <f>100%-F813</f>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E813" s="4">
@@ -37288,7 +37288,7 @@
         <v>215</v>
       </c>
       <c r="D814" s="3">
-        <f t="shared" si="14"/>
+        <f>100%-F814</f>
         <v>0.37</v>
       </c>
       <c r="E814" s="4">
@@ -37330,7 +37330,7 @@
         <v>599</v>
       </c>
       <c r="D815" s="3">
-        <f t="shared" si="14"/>
+        <f>100%-F815</f>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E815" s="4">
@@ -37372,7 +37372,7 @@
         <v>1008.9999999999999</v>
       </c>
       <c r="D816" s="3">
-        <f t="shared" si="14"/>
+        <f>100%-F816</f>
         <v>0</v>
       </c>
       <c r="E816" s="4">
@@ -37414,7 +37414,7 @@
         <v>172</v>
       </c>
       <c r="D817" s="3">
-        <f t="shared" si="14"/>
+        <f>100%-F817</f>
         <v>0.30000000000000004</v>
       </c>
       <c r="E817" s="4">
@@ -37456,7 +37456,7 @@
         <v>138</v>
       </c>
       <c r="D818" s="3">
-        <f t="shared" si="14"/>
+        <f>100%-F818</f>
         <v>0.30000000000000004</v>
       </c>
       <c r="E818" s="4">
@@ -37498,7 +37498,7 @@
         <v>561</v>
       </c>
       <c r="D819" s="3">
-        <f t="shared" si="14"/>
+        <f>100%-F819</f>
         <v>0.18000000000000005</v>
       </c>
       <c r="E819" s="4">
@@ -37540,7 +37540,7 @@
         <v>144</v>
       </c>
       <c r="D820" s="3">
-        <f t="shared" si="14"/>
+        <f>100%-F820</f>
         <v>0.30000000000000004</v>
       </c>
       <c r="E820" s="4">
@@ -37582,7 +37582,7 @@
         <v>1180</v>
       </c>
       <c r="D821" s="3">
-        <f t="shared" si="14"/>
+        <f>100%-F821</f>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E821" s="4">
@@ -37624,7 +37624,7 @@
         <v>417</v>
       </c>
       <c r="D822" s="3">
-        <f t="shared" si="14"/>
+        <f>100%-F822</f>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E822" s="4">
@@ -37666,7 +37666,7 @@
         <v>127</v>
       </c>
       <c r="D823" s="3">
-        <f t="shared" si="14"/>
+        <f>100%-F823</f>
         <v>0.22999999999999998</v>
       </c>
       <c r="E823" s="4">
@@ -37708,7 +37708,7 @@
         <v>144</v>
       </c>
       <c r="D824" s="3">
-        <f t="shared" si="14"/>
+        <f>100%-F824</f>
         <v>0.30000000000000004</v>
       </c>
       <c r="E824" s="4">
@@ -37750,7 +37750,7 @@
         <v>1109</v>
       </c>
       <c r="D825" s="3">
-        <f t="shared" si="14"/>
+        <f>100%-F825</f>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E825" s="4">
@@ -37792,7 +37792,7 @@
         <v>1495</v>
       </c>
       <c r="D826" s="3">
-        <f t="shared" si="14"/>
+        <f>100%-F826</f>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E826" s="4">
@@ -37834,7 +37834,7 @@
         <v>701</v>
       </c>
       <c r="D827" s="3">
-        <f t="shared" si="14"/>
+        <f>100%-F827</f>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E827" s="4">
@@ -37876,7 +37876,7 @@
         <v>332</v>
       </c>
       <c r="D828" s="3">
-        <f t="shared" si="14"/>
+        <f>100%-F828</f>
         <v>0.30000000000000004</v>
       </c>
       <c r="E828" s="4">
@@ -37918,7 +37918,7 @@
         <v>352</v>
       </c>
       <c r="D829" s="3">
-        <f t="shared" si="14"/>
+        <f>100%-F829</f>
         <v>0.30000000000000004</v>
       </c>
       <c r="E829" s="4">
@@ -37960,7 +37960,7 @@
         <v>174</v>
       </c>
       <c r="D830" s="3">
-        <f t="shared" si="14"/>
+        <f>100%-F830</f>
         <v>0.65</v>
       </c>
       <c r="E830" s="4">
@@ -38002,7 +38002,7 @@
         <v>2041</v>
       </c>
       <c r="D831" s="3">
-        <f t="shared" si="14"/>
+        <f>100%-F831</f>
         <v>0</v>
       </c>
       <c r="E831" s="4">
@@ -38044,7 +38044,7 @@
         <v>371</v>
       </c>
       <c r="D832" s="3">
-        <f t="shared" si="14"/>
+        <f>100%-F832</f>
         <v>0.15000000000000002</v>
       </c>
       <c r="E832" s="4">
@@ -38086,7 +38086,7 @@
         <v>101</v>
       </c>
       <c r="D833" s="3">
-        <f t="shared" si="14"/>
+        <f>100%-F833</f>
         <v>0.37</v>
       </c>
       <c r="E833" s="4">
@@ -38128,7 +38128,7 @@
         <v>4657</v>
       </c>
       <c r="D834" s="3">
-        <f t="shared" ref="D834:D877" si="15">100%-F834</f>
+        <f>100%-F834</f>
         <v>0</v>
       </c>
       <c r="E834" s="4">
@@ -38170,7 +38170,7 @@
         <v>4163</v>
       </c>
       <c r="D835" s="3">
-        <f t="shared" si="15"/>
+        <f>100%-F835</f>
         <v>0</v>
       </c>
       <c r="E835" s="4">
@@ -38212,7 +38212,7 @@
         <v>554</v>
       </c>
       <c r="D836" s="3">
-        <f t="shared" si="15"/>
+        <f>100%-F836</f>
         <v>0</v>
       </c>
       <c r="E836" s="4">
@@ -38254,7 +38254,7 @@
         <v>301</v>
       </c>
       <c r="D837" s="3">
-        <f t="shared" si="15"/>
+        <f>100%-F837</f>
         <v>0.32999999999999996</v>
       </c>
       <c r="E837" s="4">
@@ -38296,7 +38296,7 @@
         <v>136</v>
       </c>
       <c r="D838" s="3">
-        <f t="shared" si="15"/>
+        <f>100%-F838</f>
         <v>0.30000000000000004</v>
       </c>
       <c r="E838" s="4">
@@ -38338,7 +38338,7 @@
         <v>144</v>
       </c>
       <c r="D839" s="3">
-        <f t="shared" si="15"/>
+        <f>100%-F839</f>
         <v>0.72</v>
       </c>
       <c r="E839" s="4">
@@ -38380,7 +38380,7 @@
         <v>1056</v>
       </c>
       <c r="D840" s="3">
-        <f t="shared" si="15"/>
+        <f>100%-F840</f>
         <v>0</v>
       </c>
       <c r="E840" s="4">
@@ -38422,7 +38422,7 @@
         <v>412</v>
       </c>
       <c r="D841" s="3">
-        <f t="shared" si="15"/>
+        <f>100%-F841</f>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="E841" s="4">
@@ -38464,7 +38464,7 @@
         <v>301</v>
       </c>
       <c r="D842" s="3">
-        <f t="shared" si="15"/>
+        <f>100%-F842</f>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="E842" s="4">
@@ -38506,7 +38506,7 @@
         <v>372</v>
       </c>
       <c r="D843" s="3">
-        <f t="shared" si="15"/>
+        <f>100%-F843</f>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="E843" s="4">
@@ -38548,7 +38548,7 @@
         <v>109</v>
       </c>
       <c r="D844" s="3">
-        <f t="shared" si="15"/>
+        <f>100%-F844</f>
         <v>0.38</v>
       </c>
       <c r="E844" s="4">
@@ -38590,7 +38590,7 @@
         <v>344</v>
       </c>
       <c r="D845" s="3">
-        <f t="shared" si="15"/>
+        <f>100%-F845</f>
         <v>0</v>
       </c>
       <c r="E845" s="4">
@@ -38632,7 +38632,7 @@
         <v>178</v>
       </c>
       <c r="D846" s="3">
-        <f t="shared" si="15"/>
+        <f>100%-F846</f>
         <v>0.38</v>
       </c>
       <c r="E846" s="4">
@@ -38674,7 +38674,7 @@
         <v>279</v>
       </c>
       <c r="D847" s="3">
-        <f t="shared" si="15"/>
+        <f>100%-F847</f>
         <v>0.30000000000000004</v>
       </c>
       <c r="E847" s="4">
@@ -38716,7 +38716,7 @@
         <v>201</v>
       </c>
       <c r="D848" s="3">
-        <f t="shared" si="15"/>
+        <f>100%-F848</f>
         <v>0.30000000000000004</v>
       </c>
       <c r="E848" s="4">
@@ -38758,7 +38758,7 @@
         <v>620</v>
       </c>
       <c r="D849" s="3">
-        <f t="shared" si="15"/>
+        <f>100%-F849</f>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="E849" s="4">
@@ -38800,7 +38800,7 @@
         <v>285</v>
       </c>
       <c r="D850" s="3">
-        <f t="shared" si="15"/>
+        <f>100%-F850</f>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E850" s="4">
@@ -38842,7 +38842,7 @@
         <v>115</v>
       </c>
       <c r="D851" s="3">
-        <f t="shared" si="15"/>
+        <f>100%-F851</f>
         <v>0.44999999999999996</v>
       </c>
       <c r="E851" s="4">
@@ -38884,7 +38884,7 @@
         <v>885</v>
       </c>
       <c r="D852" s="3">
-        <f t="shared" si="15"/>
+        <f>100%-F852</f>
         <v>0.18000000000000005</v>
       </c>
       <c r="E852" s="4">
@@ -38926,7 +38926,7 @@
         <v>431</v>
       </c>
       <c r="D853" s="3">
-        <f t="shared" si="15"/>
+        <f>100%-F853</f>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="E853" s="4">
@@ -38968,7 +38968,7 @@
         <v>339</v>
       </c>
       <c r="D854" s="3">
-        <f t="shared" si="15"/>
+        <f>100%-F854</f>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E854" s="4">
@@ -39010,7 +39010,7 @@
         <v>176</v>
       </c>
       <c r="D855" s="3">
-        <f t="shared" si="15"/>
+        <f>100%-F855</f>
         <v>0.44999999999999996</v>
       </c>
       <c r="E855" s="4">
@@ -39052,7 +39052,7 @@
         <v>226</v>
       </c>
       <c r="D856" s="3">
-        <f t="shared" si="15"/>
+        <f>100%-F856</f>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E856" s="4">
@@ -39094,7 +39094,7 @@
         <v>390</v>
       </c>
       <c r="D857" s="3">
-        <f t="shared" si="15"/>
+        <f>100%-F857</f>
         <v>0.22999999999999998</v>
       </c>
       <c r="E857" s="4">
@@ -39136,7 +39136,7 @@
         <v>122</v>
       </c>
       <c r="D858" s="3">
-        <f t="shared" si="15"/>
+        <f>100%-F858</f>
         <v>0.30000000000000004</v>
       </c>
       <c r="E858" s="4">
@@ -39178,7 +39178,7 @@
         <v>469</v>
       </c>
       <c r="D859" s="3">
-        <f t="shared" si="15"/>
+        <f>100%-F859</f>
         <v>0.22999999999999998</v>
       </c>
       <c r="E859" s="4">
@@ -39220,7 +39220,7 @@
         <v>5371</v>
       </c>
       <c r="D860" s="3">
-        <f t="shared" si="15"/>
+        <f>100%-F860</f>
         <v>0</v>
       </c>
       <c r="E860" s="4">
@@ -39262,7 +39262,7 @@
         <v>479</v>
       </c>
       <c r="D861" s="3">
-        <f t="shared" si="15"/>
+        <f>100%-F861</f>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="E861" s="4">
@@ -39304,7 +39304,7 @@
         <v>258</v>
       </c>
       <c r="D862" s="3">
-        <f t="shared" si="15"/>
+        <f>100%-F862</f>
         <v>0.30000000000000004</v>
       </c>
       <c r="E862" s="4">
@@ -39346,7 +39346,7 @@
         <v>814</v>
       </c>
       <c r="D863" s="3">
-        <f t="shared" si="15"/>
+        <f>100%-F863</f>
         <v>0</v>
       </c>
       <c r="E863" s="4">
@@ -39388,7 +39388,7 @@
         <v>597</v>
       </c>
       <c r="D864" s="3">
-        <f t="shared" si="15"/>
+        <f>100%-F864</f>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="E864" s="4">
@@ -39430,7 +39430,7 @@
         <v>190</v>
       </c>
       <c r="D865" s="3">
-        <f t="shared" si="15"/>
+        <f>100%-F865</f>
         <v>0.21999999999999997</v>
       </c>
       <c r="E865" s="4">
@@ -39472,7 +39472,7 @@
         <v>262</v>
       </c>
       <c r="D866" s="3">
-        <f t="shared" si="15"/>
+        <f>100%-F866</f>
         <v>0.38</v>
       </c>
       <c r="E866" s="4">
@@ -39514,7 +39514,7 @@
         <v>398</v>
       </c>
       <c r="D867" s="3">
-        <f t="shared" si="15"/>
+        <f>100%-F867</f>
         <v>0.38</v>
       </c>
       <c r="E867" s="4">
@@ -39556,7 +39556,7 @@
         <v>657</v>
       </c>
       <c r="D868" s="3">
-        <f t="shared" si="15"/>
+        <f>100%-F868</f>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="E868" s="4">
@@ -39598,7 +39598,7 @@
         <v>450</v>
       </c>
       <c r="D869" s="3">
-        <f t="shared" si="15"/>
+        <f>100%-F869</f>
         <v>0.15000000000000002</v>
       </c>
       <c r="E869" s="4">
@@ -39640,7 +39640,7 @@
         <v>127</v>
       </c>
       <c r="D870" s="3">
-        <f t="shared" si="15"/>
+        <f>100%-F870</f>
         <v>0.57000000000000006</v>
       </c>
       <c r="E870" s="4">
@@ -39682,7 +39682,7 @@
         <v>953</v>
       </c>
       <c r="D871" s="3">
-        <f t="shared" si="15"/>
+        <f>100%-F871</f>
         <v>0.15000000000000002</v>
       </c>
       <c r="E871" s="4">
@@ -39724,7 +39724,7 @@
         <v>296</v>
       </c>
       <c r="D872" s="3">
-        <f t="shared" si="15"/>
+        <f>100%-F872</f>
         <v>0.5</v>
       </c>
       <c r="E872" s="4">
@@ -39766,7 +39766,7 @@
         <v>367</v>
       </c>
       <c r="D873" s="3">
-        <f t="shared" si="15"/>
+        <f>100%-F873</f>
         <v>0.22999999999999998</v>
       </c>
       <c r="E873" s="4">
@@ -39808,7 +39808,7 @@
         <v>521</v>
       </c>
       <c r="D874" s="3">
-        <f t="shared" si="15"/>
+        <f>100%-F874</f>
         <v>0.30000000000000004</v>
       </c>
       <c r="E874" s="4">
@@ -39850,7 +39850,7 @@
         <v>463</v>
       </c>
       <c r="D875" s="3">
-        <f t="shared" si="15"/>
+        <f>100%-F875</f>
         <v>0.38</v>
       </c>
       <c r="E875" s="4">
@@ -39892,7 +39892,7 @@
         <v>296</v>
       </c>
       <c r="D876" s="3">
-        <f t="shared" si="15"/>
+        <f>100%-F876</f>
         <v>0.15000000000000002</v>
       </c>
       <c r="E876" s="4">
@@ -39934,7 +39934,7 @@
         <v>540</v>
       </c>
       <c r="D877" s="3">
-        <f t="shared" si="15"/>
+        <f>100%-F877</f>
         <v>0</v>
       </c>
       <c r="E877" s="4">

--- a/content/xls/DB_01.01.2026_NP.xlsx
+++ b/content/xls/DB_01.01.2026_NP.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Python\InfPanel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Python\InfPanel\content\xls\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F3157E9-B3A1-4FBD-A1CF-CD361A72361F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE667DBE-1106-4830-9D36-B1EDF92D4EC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-111" yWindow="-111" windowWidth="31729" windowHeight="17342" xr2:uid="{CD9FBE00-C105-441E-AC9D-D16C82556AEE}"/>
   </bookViews>
@@ -2628,12 +2628,6 @@
     <t>Уровень финансовой доступности</t>
   </si>
   <si>
-    <t>Уровень потребности в развитии дистанционного банковского обслуживания с учетом альтернативной инфраструктуры (Уровень потребности в ДБО)</t>
-  </si>
-  <si>
-    <t>Изменение уровня потребности в ДБО с учетом альтернативной инфраструктуры</t>
-  </si>
-  <si>
     <t>Изменение уровня финансовой доступности к предыдущей отчетной дате, п.п.</t>
   </si>
   <si>
@@ -2650,6 +2644,12 @@
   </si>
   <si>
     <t>Количество банкоматов</t>
+  </si>
+  <si>
+    <t>Уровень потребности в развитии дистанционного банковского обслуживания с учетом альтернативной инфраструктуры</t>
+  </si>
+  <si>
+    <t>Изменение уровня потребности в развитии дистанционного банковского обслуживания с учетом альтернативной инфраструктуры, п.п.</t>
   </si>
 </sst>
 </file>
@@ -3090,7 +3090,7 @@
     <col min="2" max="2" width="37.44140625" customWidth="1"/>
     <col min="3" max="3" width="16.109375" customWidth="1"/>
     <col min="4" max="4" width="21.44140625" customWidth="1"/>
-    <col min="5" max="5" width="16.5546875" customWidth="1"/>
+    <col min="5" max="5" width="24.44140625" customWidth="1"/>
     <col min="6" max="8" width="14.33203125" customWidth="1"/>
     <col min="9" max="9" width="22.6640625" customWidth="1"/>
     <col min="10" max="10" width="14.6640625" customWidth="1"/>
@@ -3099,7 +3099,7 @@
     <col min="13" max="13" width="12.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" s="1" customFormat="1" ht="147.69999999999999" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:13" s="1" customFormat="1" ht="124.35" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="12" t="s">
         <v>861</v>
       </c>
@@ -3110,34 +3110,34 @@
         <v>0</v>
       </c>
       <c r="D1" s="12" t="s">
-        <v>864</v>
+        <v>870</v>
       </c>
       <c r="E1" s="12" t="s">
-        <v>865</v>
+        <v>871</v>
       </c>
       <c r="F1" s="12" t="s">
         <v>863</v>
       </c>
       <c r="G1" s="12" t="s">
+        <v>864</v>
+      </c>
+      <c r="H1" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="I1" s="12" t="s">
+        <v>865</v>
+      </c>
+      <c r="J1" s="12" t="s">
         <v>866</v>
       </c>
-      <c r="H1" s="12" t="s">
-        <v>1</v>
-      </c>
-      <c r="I1" s="12" t="s">
+      <c r="K1" s="12" t="s">
         <v>867</v>
       </c>
-      <c r="J1" s="12" t="s">
+      <c r="L1" s="12" t="s">
         <v>868</v>
       </c>
-      <c r="K1" s="12" t="s">
+      <c r="M1" s="12" t="s">
         <v>869</v>
-      </c>
-      <c r="L1" s="12" t="s">
-        <v>870</v>
-      </c>
-      <c r="M1" s="12" t="s">
-        <v>871</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.3">
@@ -3151,7 +3151,7 @@
         <v>846</v>
       </c>
       <c r="D2" s="3">
-        <f>100%-F2</f>
+        <f t="shared" ref="D2:D65" si="0">100%-F2</f>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E2" s="4">
@@ -3193,7 +3193,7 @@
         <v>100</v>
       </c>
       <c r="D3" s="3">
-        <f>100%-F3</f>
+        <f t="shared" si="0"/>
         <v>0.30000000000000004</v>
       </c>
       <c r="E3" s="4">
@@ -3235,7 +3235,7 @@
         <v>497</v>
       </c>
       <c r="D4" s="3">
-        <f>100%-F4</f>
+        <f t="shared" si="0"/>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="E4" s="4">
@@ -3277,7 +3277,7 @@
         <v>160</v>
       </c>
       <c r="D5" s="3">
-        <f>100%-F5</f>
+        <f t="shared" si="0"/>
         <v>0.18000000000000005</v>
       </c>
       <c r="E5" s="4">
@@ -3319,7 +3319,7 @@
         <v>591</v>
       </c>
       <c r="D6" s="3">
-        <f>100%-F6</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="E6" s="4">
@@ -3361,7 +3361,7 @@
         <v>346</v>
       </c>
       <c r="D7" s="3">
-        <f>100%-F7</f>
+        <f t="shared" si="0"/>
         <v>0.30000000000000004</v>
       </c>
       <c r="E7" s="4">
@@ -3403,7 +3403,7 @@
         <v>295</v>
       </c>
       <c r="D8" s="3">
-        <f>100%-F8</f>
+        <f t="shared" si="0"/>
         <v>0.44999999999999996</v>
       </c>
       <c r="E8" s="4">
@@ -3445,7 +3445,7 @@
         <v>791</v>
       </c>
       <c r="D9" s="3">
-        <f>100%-F9</f>
+        <f t="shared" si="0"/>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="E9" s="4">
@@ -3487,7 +3487,7 @@
         <v>419</v>
       </c>
       <c r="D10" s="3">
-        <f>100%-F10</f>
+        <f t="shared" si="0"/>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E10" s="4">
@@ -3529,7 +3529,7 @@
         <v>213</v>
       </c>
       <c r="D11" s="3">
-        <f>100%-F11</f>
+        <f t="shared" si="0"/>
         <v>0.37</v>
       </c>
       <c r="E11" s="4">
@@ -3571,7 +3571,7 @@
         <v>146</v>
       </c>
       <c r="D12" s="3">
-        <f>100%-F12</f>
+        <f t="shared" si="0"/>
         <v>0.44999999999999996</v>
       </c>
       <c r="E12" s="4">
@@ -3613,7 +3613,7 @@
         <v>477</v>
       </c>
       <c r="D13" s="3">
-        <f>100%-F13</f>
+        <f t="shared" si="0"/>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="E13" s="4">
@@ -3655,7 +3655,7 @@
         <v>116</v>
       </c>
       <c r="D14" s="3">
-        <f>100%-F14</f>
+        <f t="shared" si="0"/>
         <v>0.37</v>
       </c>
       <c r="E14" s="4">
@@ -3697,7 +3697,7 @@
         <v>576</v>
       </c>
       <c r="D15" s="3">
-        <f>100%-F15</f>
+        <f t="shared" si="0"/>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E15" s="4">
@@ -3739,7 +3739,7 @@
         <v>553</v>
       </c>
       <c r="D16" s="3">
-        <f>100%-F16</f>
+        <f t="shared" si="0"/>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E16" s="4">
@@ -3781,7 +3781,7 @@
         <v>182</v>
       </c>
       <c r="D17" s="3">
-        <f>100%-F17</f>
+        <f t="shared" si="0"/>
         <v>0.30000000000000004</v>
       </c>
       <c r="E17" s="4">
@@ -3823,7 +3823,7 @@
         <v>101</v>
       </c>
       <c r="D18" s="3">
-        <f>100%-F18</f>
+        <f t="shared" si="0"/>
         <v>0.30000000000000004</v>
       </c>
       <c r="E18" s="4">
@@ -3865,7 +3865,7 @@
         <v>345</v>
       </c>
       <c r="D19" s="3">
-        <f>100%-F19</f>
+        <f t="shared" si="0"/>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E19" s="4">
@@ -3907,7 +3907,7 @@
         <v>270</v>
       </c>
       <c r="D20" s="3">
-        <f>100%-F20</f>
+        <f t="shared" si="0"/>
         <v>0.22999999999999998</v>
       </c>
       <c r="E20" s="4">
@@ -3949,7 +3949,7 @@
         <v>143</v>
       </c>
       <c r="D21" s="3">
-        <f>100%-F21</f>
+        <f t="shared" si="0"/>
         <v>0.30000000000000004</v>
       </c>
       <c r="E21" s="4">
@@ -3991,7 +3991,7 @@
         <v>141</v>
       </c>
       <c r="D22" s="3">
-        <f>100%-F22</f>
+        <f t="shared" si="0"/>
         <v>0.30000000000000004</v>
       </c>
       <c r="E22" s="4">
@@ -4033,7 +4033,7 @@
         <v>142</v>
       </c>
       <c r="D23" s="3">
-        <f>100%-F23</f>
+        <f t="shared" si="0"/>
         <v>0.22999999999999998</v>
       </c>
       <c r="E23" s="4">
@@ -4075,7 +4075,7 @@
         <v>5482</v>
       </c>
       <c r="D24" s="3">
-        <f>100%-F24</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="E24" s="4">
@@ -4117,7 +4117,7 @@
         <v>323</v>
       </c>
       <c r="D25" s="3">
-        <f>100%-F25</f>
+        <f t="shared" si="0"/>
         <v>0.30000000000000004</v>
       </c>
       <c r="E25" s="4">
@@ -4159,7 +4159,7 @@
         <v>109</v>
       </c>
       <c r="D26" s="3">
-        <f>100%-F26</f>
+        <f t="shared" si="0"/>
         <v>0.37</v>
       </c>
       <c r="E26" s="4">
@@ -4201,7 +4201,7 @@
         <v>484</v>
       </c>
       <c r="D27" s="3">
-        <f>100%-F27</f>
+        <f t="shared" si="0"/>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E27" s="4">
@@ -4243,7 +4243,7 @@
         <v>123</v>
       </c>
       <c r="D28" s="3">
-        <f>100%-F28</f>
+        <f t="shared" si="0"/>
         <v>0.30000000000000004</v>
       </c>
       <c r="E28" s="4">
@@ -4285,7 +4285,7 @@
         <v>474</v>
       </c>
       <c r="D29" s="3">
-        <f>100%-F29</f>
+        <f t="shared" si="0"/>
         <v>0.22999999999999998</v>
       </c>
       <c r="E29" s="4">
@@ -4327,7 +4327,7 @@
         <v>124</v>
       </c>
       <c r="D30" s="3">
-        <f>100%-F30</f>
+        <f t="shared" si="0"/>
         <v>0.22999999999999998</v>
       </c>
       <c r="E30" s="4">
@@ -4369,7 +4369,7 @@
         <v>482</v>
       </c>
       <c r="D31" s="3">
-        <f>100%-F31</f>
+        <f t="shared" si="0"/>
         <v>0.15000000000000002</v>
       </c>
       <c r="E31" s="4">
@@ -4411,7 +4411,7 @@
         <v>499</v>
       </c>
       <c r="D32" s="3">
-        <f>100%-F32</f>
+        <f t="shared" si="0"/>
         <v>0.18000000000000005</v>
       </c>
       <c r="E32" s="4">
@@ -4453,7 +4453,7 @@
         <v>144</v>
       </c>
       <c r="D33" s="3">
-        <f>100%-F33</f>
+        <f t="shared" si="0"/>
         <v>0.38</v>
       </c>
       <c r="E33" s="4">
@@ -4495,7 +4495,7 @@
         <v>419</v>
       </c>
       <c r="D34" s="3">
-        <f>100%-F34</f>
+        <f t="shared" si="0"/>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="E34" s="4">
@@ -4537,7 +4537,7 @@
         <v>676</v>
       </c>
       <c r="D35" s="3">
-        <f>100%-F35</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="E35" s="4">
@@ -4579,7 +4579,7 @@
         <v>152</v>
       </c>
       <c r="D36" s="3">
-        <f>100%-F36</f>
+        <f t="shared" si="0"/>
         <v>0.38</v>
       </c>
       <c r="E36" s="4">
@@ -4621,7 +4621,7 @@
         <v>108</v>
       </c>
       <c r="D37" s="3">
-        <f>100%-F37</f>
+        <f t="shared" si="0"/>
         <v>0.8</v>
       </c>
       <c r="E37" s="4">
@@ -4663,7 +4663,7 @@
         <v>633</v>
       </c>
       <c r="D38" s="3">
-        <f>100%-F38</f>
+        <f t="shared" si="0"/>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="E38" s="4">
@@ -4705,7 +4705,7 @@
         <v>213</v>
       </c>
       <c r="D39" s="3">
-        <f>100%-F39</f>
+        <f t="shared" si="0"/>
         <v>0.38</v>
       </c>
       <c r="E39" s="4">
@@ -4747,7 +4747,7 @@
         <v>524</v>
       </c>
       <c r="D40" s="3">
-        <f>100%-F40</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="E40" s="4">
@@ -4789,7 +4789,7 @@
         <v>103</v>
       </c>
       <c r="D41" s="3">
-        <f>100%-F41</f>
+        <f t="shared" si="0"/>
         <v>0.44999999999999996</v>
       </c>
       <c r="E41" s="4">
@@ -4831,7 +4831,7 @@
         <v>196</v>
       </c>
       <c r="D42" s="3">
-        <f>100%-F42</f>
+        <f t="shared" si="0"/>
         <v>0.44999999999999996</v>
       </c>
       <c r="E42" s="4">
@@ -4873,7 +4873,7 @@
         <v>211</v>
       </c>
       <c r="D43" s="3">
-        <f>100%-F43</f>
+        <f t="shared" si="0"/>
         <v>0.44999999999999996</v>
       </c>
       <c r="E43" s="4">
@@ -4915,7 +4915,7 @@
         <v>367</v>
       </c>
       <c r="D44" s="3">
-        <f>100%-F44</f>
+        <f t="shared" si="0"/>
         <v>0.38</v>
       </c>
       <c r="E44" s="4">
@@ -4957,7 +4957,7 @@
         <v>822</v>
       </c>
       <c r="D45" s="3">
-        <f>100%-F45</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="E45" s="4">
@@ -4999,7 +4999,7 @@
         <v>271</v>
       </c>
       <c r="D46" s="3">
-        <f>100%-F46</f>
+        <f t="shared" si="0"/>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E46" s="4">
@@ -5041,7 +5041,7 @@
         <v>116</v>
       </c>
       <c r="D47" s="3">
-        <f>100%-F47</f>
+        <f t="shared" si="0"/>
         <v>0.22999999999999998</v>
       </c>
       <c r="E47" s="4">
@@ -5083,7 +5083,7 @@
         <v>480</v>
       </c>
       <c r="D48" s="3">
-        <f>100%-F48</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="E48" s="4">
@@ -5125,7 +5125,7 @@
         <v>176</v>
       </c>
       <c r="D49" s="3">
-        <f>100%-F49</f>
+        <f t="shared" si="0"/>
         <v>0.44999999999999996</v>
       </c>
       <c r="E49" s="4">
@@ -5167,7 +5167,7 @@
         <v>351</v>
       </c>
       <c r="D50" s="3">
-        <f>100%-F50</f>
+        <f t="shared" si="0"/>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E50" s="4">
@@ -5209,7 +5209,7 @@
         <v>106</v>
       </c>
       <c r="D51" s="3">
-        <f>100%-F51</f>
+        <f t="shared" si="0"/>
         <v>0.65</v>
       </c>
       <c r="E51" s="4">
@@ -5251,7 +5251,7 @@
         <v>294</v>
       </c>
       <c r="D52" s="3">
-        <f>100%-F52</f>
+        <f t="shared" si="0"/>
         <v>0.44999999999999996</v>
       </c>
       <c r="E52" s="4">
@@ -5293,7 +5293,7 @@
         <v>272</v>
       </c>
       <c r="D53" s="3">
-        <f>100%-F53</f>
+        <f t="shared" si="0"/>
         <v>0.22999999999999998</v>
       </c>
       <c r="E53" s="4">
@@ -5335,7 +5335,7 @@
         <v>413</v>
       </c>
       <c r="D54" s="3">
-        <f>100%-F54</f>
+        <f t="shared" si="0"/>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="E54" s="4">
@@ -5377,7 +5377,7 @@
         <v>166</v>
       </c>
       <c r="D55" s="3">
-        <f>100%-F55</f>
+        <f t="shared" si="0"/>
         <v>0.38</v>
       </c>
       <c r="E55" s="4">
@@ -5419,7 +5419,7 @@
         <v>150</v>
       </c>
       <c r="D56" s="3">
-        <f>100%-F56</f>
+        <f t="shared" si="0"/>
         <v>0.44999999999999996</v>
       </c>
       <c r="E56" s="4">
@@ -5461,7 +5461,7 @@
         <v>563</v>
       </c>
       <c r="D57" s="3">
-        <f>100%-F57</f>
+        <f t="shared" si="0"/>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E57" s="4">
@@ -5503,7 +5503,7 @@
         <v>314</v>
       </c>
       <c r="D58" s="3">
-        <f>100%-F58</f>
+        <f t="shared" si="0"/>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E58" s="4">
@@ -5545,7 +5545,7 @@
         <v>355</v>
       </c>
       <c r="D59" s="3">
-        <f>100%-F59</f>
+        <f t="shared" si="0"/>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="E59" s="4">
@@ -5587,7 +5587,7 @@
         <v>267</v>
       </c>
       <c r="D60" s="3">
-        <f>100%-F60</f>
+        <f t="shared" si="0"/>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E60" s="4">
@@ -5629,7 +5629,7 @@
         <v>611</v>
       </c>
       <c r="D61" s="3">
-        <f>100%-F61</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="E61" s="4">
@@ -5671,7 +5671,7 @@
         <v>178</v>
       </c>
       <c r="D62" s="3">
-        <f>100%-F62</f>
+        <f t="shared" si="0"/>
         <v>0.44999999999999996</v>
       </c>
       <c r="E62" s="4">
@@ -5713,7 +5713,7 @@
         <v>233</v>
       </c>
       <c r="D63" s="3">
-        <f>100%-F63</f>
+        <f t="shared" si="0"/>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E63" s="4">
@@ -5755,7 +5755,7 @@
         <v>712</v>
       </c>
       <c r="D64" s="3">
-        <f>100%-F64</f>
+        <f t="shared" si="0"/>
         <v>0.32999999999999996</v>
       </c>
       <c r="E64" s="4">
@@ -5797,7 +5797,7 @@
         <v>695</v>
       </c>
       <c r="D65" s="3">
-        <f>100%-F65</f>
+        <f t="shared" si="0"/>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E65" s="4">
@@ -5839,7 +5839,7 @@
         <v>434</v>
       </c>
       <c r="D66" s="3">
-        <f>100%-F66</f>
+        <f t="shared" ref="D66:D129" si="1">100%-F66</f>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E66" s="4">
@@ -5881,7 +5881,7 @@
         <v>371</v>
       </c>
       <c r="D67" s="3">
-        <f>100%-F67</f>
+        <f t="shared" si="1"/>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E67" s="4">
@@ -5923,7 +5923,7 @@
         <v>365</v>
       </c>
       <c r="D68" s="3">
-        <f>100%-F68</f>
+        <f t="shared" si="1"/>
         <v>0.15000000000000002</v>
       </c>
       <c r="E68" s="4">
@@ -5965,7 +5965,7 @@
         <v>221</v>
       </c>
       <c r="D69" s="3">
-        <f>100%-F69</f>
+        <f t="shared" si="1"/>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E69" s="4">
@@ -6007,7 +6007,7 @@
         <v>122</v>
       </c>
       <c r="D70" s="3">
-        <f>100%-F70</f>
+        <f t="shared" si="1"/>
         <v>0.37</v>
       </c>
       <c r="E70" s="4">
@@ -6049,7 +6049,7 @@
         <v>387</v>
       </c>
       <c r="D71" s="3">
-        <f>100%-F71</f>
+        <f t="shared" si="1"/>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E71" s="4">
@@ -6091,7 +6091,7 @@
         <v>232</v>
       </c>
       <c r="D72" s="3">
-        <f>100%-F72</f>
+        <f t="shared" si="1"/>
         <v>0.15000000000000002</v>
       </c>
       <c r="E72" s="4">
@@ -6133,7 +6133,7 @@
         <v>279</v>
       </c>
       <c r="D73" s="3">
-        <f>100%-F73</f>
+        <f t="shared" si="1"/>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E73" s="4">
@@ -6175,7 +6175,7 @@
         <v>157</v>
       </c>
       <c r="D74" s="3">
-        <f>100%-F74</f>
+        <f t="shared" si="1"/>
         <v>0.30000000000000004</v>
       </c>
       <c r="E74" s="4">
@@ -6217,7 +6217,7 @@
         <v>291</v>
       </c>
       <c r="D75" s="3">
-        <f>100%-F75</f>
+        <f t="shared" si="1"/>
         <v>0.38</v>
       </c>
       <c r="E75" s="4">
@@ -6259,7 +6259,7 @@
         <v>524</v>
       </c>
       <c r="D76" s="3">
-        <f>100%-F76</f>
+        <f t="shared" si="1"/>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E76" s="4">
@@ -6301,7 +6301,7 @@
         <v>218</v>
       </c>
       <c r="D77" s="3">
-        <f>100%-F77</f>
+        <f t="shared" si="1"/>
         <v>0.30000000000000004</v>
       </c>
       <c r="E77" s="4">
@@ -6343,7 +6343,7 @@
         <v>706</v>
       </c>
       <c r="D78" s="3">
-        <f>100%-F78</f>
+        <f t="shared" si="1"/>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E78" s="4">
@@ -6385,7 +6385,7 @@
         <v>230</v>
       </c>
       <c r="D79" s="3">
-        <f>100%-F79</f>
+        <f t="shared" si="1"/>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E79" s="4">
@@ -6427,7 +6427,7 @@
         <v>344</v>
       </c>
       <c r="D80" s="3">
-        <f>100%-F80</f>
+        <f t="shared" si="1"/>
         <v>0.18000000000000005</v>
       </c>
       <c r="E80" s="4">
@@ -6469,7 +6469,7 @@
         <v>179</v>
       </c>
       <c r="D81" s="3">
-        <f>100%-F81</f>
+        <f t="shared" si="1"/>
         <v>0.30000000000000004</v>
       </c>
       <c r="E81" s="4">
@@ -6511,7 +6511,7 @@
         <v>565</v>
       </c>
       <c r="D82" s="3">
-        <f>100%-F82</f>
+        <f t="shared" si="1"/>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="E82" s="4">
@@ -6553,7 +6553,7 @@
         <v>230</v>
       </c>
       <c r="D83" s="3">
-        <f>100%-F83</f>
+        <f t="shared" si="1"/>
         <v>0.25</v>
       </c>
       <c r="E83" s="4">
@@ -6595,7 +6595,7 @@
         <v>495</v>
       </c>
       <c r="D84" s="3">
-        <f>100%-F84</f>
+        <f t="shared" si="1"/>
         <v>0.18000000000000005</v>
       </c>
       <c r="E84" s="4">
@@ -6637,7 +6637,7 @@
         <v>465</v>
       </c>
       <c r="D85" s="3">
-        <f>100%-F85</f>
+        <f t="shared" si="1"/>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E85" s="4">
@@ -6679,7 +6679,7 @@
         <v>409</v>
       </c>
       <c r="D86" s="3">
-        <f>100%-F86</f>
+        <f t="shared" si="1"/>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E86" s="4">
@@ -6721,7 +6721,7 @@
         <v>217</v>
       </c>
       <c r="D87" s="3">
-        <f>100%-F87</f>
+        <f t="shared" si="1"/>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="E87" s="4">
@@ -6763,7 +6763,7 @@
         <v>122</v>
       </c>
       <c r="D88" s="3">
-        <f>100%-F88</f>
+        <f t="shared" si="1"/>
         <v>0.17000000000000004</v>
       </c>
       <c r="E88" s="4">
@@ -6805,7 +6805,7 @@
         <v>466</v>
       </c>
       <c r="D89" s="3">
-        <f>100%-F89</f>
+        <f t="shared" si="1"/>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="E89" s="4">
@@ -6847,7 +6847,7 @@
         <v>202</v>
       </c>
       <c r="D90" s="3">
-        <f>100%-F90</f>
+        <f t="shared" si="1"/>
         <v>0.32999999999999996</v>
       </c>
       <c r="E90" s="4">
@@ -6889,7 +6889,7 @@
         <v>278</v>
       </c>
       <c r="D91" s="3">
-        <f>100%-F91</f>
+        <f t="shared" si="1"/>
         <v>0.15000000000000002</v>
       </c>
       <c r="E91" s="4">
@@ -6931,7 +6931,7 @@
         <v>207</v>
       </c>
       <c r="D92" s="3">
-        <f>100%-F92</f>
+        <f t="shared" si="1"/>
         <v>0.22999999999999998</v>
       </c>
       <c r="E92" s="4">
@@ -6973,7 +6973,7 @@
         <v>125</v>
       </c>
       <c r="D93" s="3">
-        <f>100%-F93</f>
+        <f t="shared" si="1"/>
         <v>0.30000000000000004</v>
       </c>
       <c r="E93" s="4">
@@ -7015,7 +7015,7 @@
         <v>904</v>
       </c>
       <c r="D94" s="3">
-        <f>100%-F94</f>
+        <f t="shared" si="1"/>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="E94" s="4">
@@ -7057,7 +7057,7 @@
         <v>548</v>
       </c>
       <c r="D95" s="3">
-        <f>100%-F95</f>
+        <f t="shared" si="1"/>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E95" s="4">
@@ -7099,7 +7099,7 @@
         <v>265</v>
       </c>
       <c r="D96" s="3">
-        <f>100%-F96</f>
+        <f t="shared" si="1"/>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E96" s="4">
@@ -7141,7 +7141,7 @@
         <v>457</v>
       </c>
       <c r="D97" s="3">
-        <f>100%-F97</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="E97" s="4">
@@ -7183,7 +7183,7 @@
         <v>177</v>
       </c>
       <c r="D98" s="3">
-        <f>100%-F98</f>
+        <f t="shared" si="1"/>
         <v>0.22999999999999998</v>
       </c>
       <c r="E98" s="4">
@@ -7225,7 +7225,7 @@
         <v>447</v>
       </c>
       <c r="D99" s="3">
-        <f>100%-F99</f>
+        <f t="shared" si="1"/>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E99" s="4">
@@ -7267,7 +7267,7 @@
         <v>347</v>
       </c>
       <c r="D100" s="3">
-        <f>100%-F100</f>
+        <f t="shared" si="1"/>
         <v>0.32999999999999996</v>
       </c>
       <c r="E100" s="4">
@@ -7309,7 +7309,7 @@
         <v>194</v>
       </c>
       <c r="D101" s="3">
-        <f>100%-F101</f>
+        <f t="shared" si="1"/>
         <v>0.22999999999999998</v>
       </c>
       <c r="E101" s="4">
@@ -7351,7 +7351,7 @@
         <v>189</v>
       </c>
       <c r="D102" s="3">
-        <f>100%-F102</f>
+        <f t="shared" si="1"/>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E102" s="4">
@@ -7393,7 +7393,7 @@
         <v>970</v>
       </c>
       <c r="D103" s="3">
-        <f>100%-F103</f>
+        <f t="shared" si="1"/>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="E103" s="4">
@@ -7435,7 +7435,7 @@
         <v>243</v>
       </c>
       <c r="D104" s="3">
-        <f>100%-F104</f>
+        <f t="shared" si="1"/>
         <v>0.17000000000000004</v>
       </c>
       <c r="E104" s="4">
@@ -7477,7 +7477,7 @@
         <v>478</v>
       </c>
       <c r="D105" s="3">
-        <f>100%-F105</f>
+        <f t="shared" si="1"/>
         <v>0.38</v>
       </c>
       <c r="E105" s="4">
@@ -7519,7 +7519,7 @@
         <v>134</v>
       </c>
       <c r="D106" s="3">
-        <f>100%-F106</f>
+        <f t="shared" si="1"/>
         <v>0.30000000000000004</v>
       </c>
       <c r="E106" s="4">
@@ -7561,7 +7561,7 @@
         <v>160</v>
       </c>
       <c r="D107" s="3">
-        <f>100%-F107</f>
+        <f t="shared" si="1"/>
         <v>0.38</v>
       </c>
       <c r="E107" s="4">
@@ -7603,7 +7603,7 @@
         <v>248</v>
       </c>
       <c r="D108" s="3">
-        <f>100%-F108</f>
+        <f t="shared" si="1"/>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E108" s="4">
@@ -7645,7 +7645,7 @@
         <v>360</v>
       </c>
       <c r="D109" s="3">
-        <f>100%-F109</f>
+        <f t="shared" si="1"/>
         <v>0.38</v>
       </c>
       <c r="E109" s="4">
@@ -7687,7 +7687,7 @@
         <v>147</v>
       </c>
       <c r="D110" s="3">
-        <f>100%-F110</f>
+        <f t="shared" si="1"/>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="E110" s="4">
@@ -7729,7 +7729,7 @@
         <v>655</v>
       </c>
       <c r="D111" s="3">
-        <f>100%-F111</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="E111" s="4">
@@ -7771,7 +7771,7 @@
         <v>6090</v>
       </c>
       <c r="D112" s="3">
-        <f>100%-F112</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="E112" s="4">
@@ -7813,7 +7813,7 @@
         <v>461</v>
       </c>
       <c r="D113" s="3">
-        <f>100%-F113</f>
+        <f t="shared" si="1"/>
         <v>0.15000000000000002</v>
       </c>
       <c r="E113" s="4">
@@ -7855,7 +7855,7 @@
         <v>113</v>
       </c>
       <c r="D114" s="3">
-        <f>100%-F114</f>
+        <f t="shared" si="1"/>
         <v>0.18999999999999995</v>
       </c>
       <c r="E114" s="4">
@@ -7897,7 +7897,7 @@
         <v>830</v>
       </c>
       <c r="D115" s="3">
-        <f>100%-F115</f>
+        <f t="shared" si="1"/>
         <v>0.15000000000000002</v>
       </c>
       <c r="E115" s="4">
@@ -7939,7 +7939,7 @@
         <v>514</v>
       </c>
       <c r="D116" s="3">
-        <f>100%-F116</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="E116" s="4">
@@ -7981,7 +7981,7 @@
         <v>606</v>
       </c>
       <c r="D117" s="3">
-        <f>100%-F117</f>
+        <f t="shared" si="1"/>
         <v>0.15000000000000002</v>
       </c>
       <c r="E117" s="4">
@@ -8023,7 +8023,7 @@
         <v>554</v>
       </c>
       <c r="D118" s="3">
-        <f>100%-F118</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="E118" s="4">
@@ -8065,7 +8065,7 @@
         <v>142</v>
       </c>
       <c r="D119" s="3">
-        <f>100%-F119</f>
+        <f t="shared" si="1"/>
         <v>0.5</v>
       </c>
       <c r="E119" s="4">
@@ -8107,7 +8107,7 @@
         <v>227</v>
       </c>
       <c r="D120" s="3">
-        <f>100%-F120</f>
+        <f t="shared" si="1"/>
         <v>0.15000000000000002</v>
       </c>
       <c r="E120" s="4">
@@ -8149,7 +8149,7 @@
         <v>797</v>
       </c>
       <c r="D121" s="3">
-        <f>100%-F121</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="E121" s="4">
@@ -8191,7 +8191,7 @@
         <v>395</v>
       </c>
       <c r="D122" s="3">
-        <f>100%-F122</f>
+        <f t="shared" si="1"/>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="E122" s="4">
@@ -8233,7 +8233,7 @@
         <v>656</v>
       </c>
       <c r="D123" s="3">
-        <f>100%-F123</f>
+        <f t="shared" si="1"/>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="E123" s="4">
@@ -8275,7 +8275,7 @@
         <v>143</v>
       </c>
       <c r="D124" s="3">
-        <f>100%-F124</f>
+        <f t="shared" si="1"/>
         <v>0.35</v>
       </c>
       <c r="E124" s="4">
@@ -8317,7 +8317,7 @@
         <v>162</v>
       </c>
       <c r="D125" s="3">
-        <f>100%-F125</f>
+        <f t="shared" si="1"/>
         <v>0.15000000000000002</v>
       </c>
       <c r="E125" s="4">
@@ -8359,7 +8359,7 @@
         <v>6155</v>
       </c>
       <c r="D126" s="3">
-        <f>100%-F126</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="E126" s="4">
@@ -8401,7 +8401,7 @@
         <v>309</v>
       </c>
       <c r="D127" s="3">
-        <f>100%-F127</f>
+        <f t="shared" si="1"/>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="E127" s="4">
@@ -8443,7 +8443,7 @@
         <v>510</v>
       </c>
       <c r="D128" s="3">
-        <f>100%-F128</f>
+        <f t="shared" si="1"/>
         <v>0.15000000000000002</v>
       </c>
       <c r="E128" s="4">
@@ -8485,7 +8485,7 @@
         <v>671</v>
       </c>
       <c r="D129" s="3">
-        <f>100%-F129</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="E129" s="4">
@@ -8527,7 +8527,7 @@
         <v>113</v>
       </c>
       <c r="D130" s="3">
-        <f>100%-F130</f>
+        <f t="shared" ref="D130:D193" si="2">100%-F130</f>
         <v>0.30000000000000004</v>
       </c>
       <c r="E130" s="4">
@@ -8569,7 +8569,7 @@
         <v>682</v>
       </c>
       <c r="D131" s="3">
-        <f>100%-F131</f>
+        <f t="shared" si="2"/>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E131" s="4">
@@ -8611,7 +8611,7 @@
         <v>239</v>
       </c>
       <c r="D132" s="3">
-        <f>100%-F132</f>
+        <f t="shared" si="2"/>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E132" s="4">
@@ -8653,7 +8653,7 @@
         <v>562</v>
       </c>
       <c r="D133" s="3">
-        <f>100%-F133</f>
+        <f t="shared" si="2"/>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E133" s="4">
@@ -8695,7 +8695,7 @@
         <v>107</v>
       </c>
       <c r="D134" s="3">
-        <f>100%-F134</f>
+        <f t="shared" si="2"/>
         <v>0.15000000000000002</v>
       </c>
       <c r="E134" s="4">
@@ -8737,7 +8737,7 @@
         <v>253</v>
       </c>
       <c r="D135" s="3">
-        <f>100%-F135</f>
+        <f t="shared" si="2"/>
         <v>0.22999999999999998</v>
       </c>
       <c r="E135" s="4">
@@ -8779,7 +8779,7 @@
         <v>107</v>
       </c>
       <c r="D136" s="3">
-        <f>100%-F136</f>
+        <f t="shared" si="2"/>
         <v>0.44999999999999996</v>
       </c>
       <c r="E136" s="4">
@@ -8821,7 +8821,7 @@
         <v>277</v>
       </c>
       <c r="D137" s="3">
-        <f>100%-F137</f>
+        <f t="shared" si="2"/>
         <v>0.38</v>
       </c>
       <c r="E137" s="4">
@@ -8863,7 +8863,7 @@
         <v>375</v>
       </c>
       <c r="D138" s="3">
-        <f>100%-F138</f>
+        <f t="shared" si="2"/>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="E138" s="4">
@@ -8905,7 +8905,7 @@
         <v>131</v>
       </c>
       <c r="D139" s="3">
-        <f>100%-F139</f>
+        <f t="shared" si="2"/>
         <v>0.15000000000000002</v>
       </c>
       <c r="E139" s="4">
@@ -8947,7 +8947,7 @@
         <v>632</v>
       </c>
       <c r="D140" s="3">
-        <f>100%-F140</f>
+        <f t="shared" si="2"/>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E140" s="4">
@@ -8989,7 +8989,7 @@
         <v>615</v>
       </c>
       <c r="D141" s="3">
-        <f>100%-F141</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="E141" s="4">
@@ -9031,7 +9031,7 @@
         <v>4961</v>
       </c>
       <c r="D142" s="3">
-        <f>100%-F142</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="E142" s="4">
@@ -9073,7 +9073,7 @@
         <v>501</v>
       </c>
       <c r="D143" s="3">
-        <f>100%-F143</f>
+        <f t="shared" si="2"/>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E143" s="4">
@@ -9115,7 +9115,7 @@
         <v>584</v>
       </c>
       <c r="D144" s="3">
-        <f>100%-F144</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="E144" s="4">
@@ -9157,7 +9157,7 @@
         <v>663</v>
       </c>
       <c r="D145" s="3">
-        <f>100%-F145</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="E145" s="4">
@@ -9199,7 +9199,7 @@
         <v>303</v>
       </c>
       <c r="D146" s="3">
-        <f>100%-F146</f>
+        <f t="shared" si="2"/>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="E146" s="4">
@@ -9241,7 +9241,7 @@
         <v>170</v>
       </c>
       <c r="D147" s="3">
-        <f>100%-F147</f>
+        <f t="shared" si="2"/>
         <v>0.30000000000000004</v>
       </c>
       <c r="E147" s="4">
@@ -9283,7 +9283,7 @@
         <v>130</v>
       </c>
       <c r="D148" s="3">
-        <f>100%-F148</f>
+        <f t="shared" si="2"/>
         <v>0.22999999999999998</v>
       </c>
       <c r="E148" s="4">
@@ -9325,7 +9325,7 @@
         <v>619</v>
       </c>
       <c r="D149" s="3">
-        <f>100%-F149</f>
+        <f t="shared" si="2"/>
         <v>0.22999999999999998</v>
       </c>
       <c r="E149" s="4">
@@ -9367,7 +9367,7 @@
         <v>1049</v>
       </c>
       <c r="D150" s="3">
-        <f>100%-F150</f>
+        <f t="shared" si="2"/>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E150" s="4">
@@ -9409,7 +9409,7 @@
         <v>677</v>
       </c>
       <c r="D151" s="3">
-        <f>100%-F151</f>
+        <f t="shared" si="2"/>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E151" s="4">
@@ -9451,7 +9451,7 @@
         <v>169</v>
       </c>
       <c r="D152" s="3">
-        <f>100%-F152</f>
+        <f t="shared" si="2"/>
         <v>0.30000000000000004</v>
       </c>
       <c r="E152" s="4">
@@ -9493,7 +9493,7 @@
         <v>516</v>
       </c>
       <c r="D153" s="3">
-        <f>100%-F153</f>
+        <f t="shared" si="2"/>
         <v>0.22999999999999998</v>
       </c>
       <c r="E153" s="4">
@@ -9535,7 +9535,7 @@
         <v>406</v>
       </c>
       <c r="D154" s="3">
-        <f>100%-F154</f>
+        <f t="shared" si="2"/>
         <v>0.22999999999999998</v>
       </c>
       <c r="E154" s="4">
@@ -9577,7 +9577,7 @@
         <v>382</v>
       </c>
       <c r="D155" s="3">
-        <f>100%-F155</f>
+        <f t="shared" si="2"/>
         <v>0.22999999999999998</v>
       </c>
       <c r="E155" s="4">
@@ -9619,7 +9619,7 @@
         <v>2043.0000000000002</v>
       </c>
       <c r="D156" s="3">
-        <f>100%-F156</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="E156" s="4">
@@ -9661,7 +9661,7 @@
         <v>223</v>
       </c>
       <c r="D157" s="3">
-        <f>100%-F157</f>
+        <f t="shared" si="2"/>
         <v>0.38</v>
       </c>
       <c r="E157" s="4">
@@ -9703,7 +9703,7 @@
         <v>424</v>
       </c>
       <c r="D158" s="3">
-        <f>100%-F158</f>
+        <f t="shared" si="2"/>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E158" s="4">
@@ -9745,7 +9745,7 @@
         <v>315</v>
       </c>
       <c r="D159" s="3">
-        <f>100%-F159</f>
+        <f t="shared" si="2"/>
         <v>0.22999999999999998</v>
       </c>
       <c r="E159" s="4">
@@ -9787,7 +9787,7 @@
         <v>150</v>
       </c>
       <c r="D160" s="3">
-        <f>100%-F160</f>
+        <f t="shared" si="2"/>
         <v>0.37</v>
       </c>
       <c r="E160" s="4">
@@ -9829,7 +9829,7 @@
         <v>1341</v>
       </c>
       <c r="D161" s="3">
-        <f>100%-F161</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="E161" s="4">
@@ -9871,7 +9871,7 @@
         <v>266</v>
       </c>
       <c r="D162" s="3">
-        <f>100%-F162</f>
+        <f t="shared" si="2"/>
         <v>0.30000000000000004</v>
       </c>
       <c r="E162" s="4">
@@ -9913,7 +9913,7 @@
         <v>364</v>
       </c>
       <c r="D163" s="3">
-        <f>100%-F163</f>
+        <f t="shared" si="2"/>
         <v>0.22999999999999998</v>
       </c>
       <c r="E163" s="4">
@@ -9955,7 +9955,7 @@
         <v>176</v>
       </c>
       <c r="D164" s="3">
-        <f>100%-F164</f>
+        <f t="shared" si="2"/>
         <v>0.37</v>
       </c>
       <c r="E164" s="4">
@@ -9997,7 +9997,7 @@
         <v>1774</v>
       </c>
       <c r="D165" s="3">
-        <f>100%-F165</f>
+        <f t="shared" si="2"/>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E165" s="4">
@@ -10039,7 +10039,7 @@
         <v>115</v>
       </c>
       <c r="D166" s="3">
-        <f>100%-F166</f>
+        <f t="shared" si="2"/>
         <v>0.37</v>
       </c>
       <c r="E166" s="4">
@@ -10081,7 +10081,7 @@
         <v>162</v>
       </c>
       <c r="D167" s="3">
-        <f>100%-F167</f>
+        <f t="shared" si="2"/>
         <v>0.37</v>
       </c>
       <c r="E167" s="4">
@@ -10123,7 +10123,7 @@
         <v>215</v>
       </c>
       <c r="D168" s="3">
-        <f>100%-F168</f>
+        <f t="shared" si="2"/>
         <v>0.22999999999999998</v>
       </c>
       <c r="E168" s="4">
@@ -10165,7 +10165,7 @@
         <v>715</v>
       </c>
       <c r="D169" s="3">
-        <f>100%-F169</f>
+        <f t="shared" si="2"/>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E169" s="4">
@@ -10207,7 +10207,7 @@
         <v>249</v>
       </c>
       <c r="D170" s="3">
-        <f>100%-F170</f>
+        <f t="shared" si="2"/>
         <v>0.28000000000000003</v>
       </c>
       <c r="E170" s="4">
@@ -10249,7 +10249,7 @@
         <v>610</v>
       </c>
       <c r="D171" s="3">
-        <f>100%-F171</f>
+        <f t="shared" si="2"/>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E171" s="4">
@@ -10291,7 +10291,7 @@
         <v>507</v>
       </c>
       <c r="D172" s="3">
-        <f>100%-F172</f>
+        <f t="shared" si="2"/>
         <v>0.15000000000000002</v>
       </c>
       <c r="E172" s="4">
@@ -10333,7 +10333,7 @@
         <v>3356</v>
       </c>
       <c r="D173" s="3">
-        <f>100%-F173</f>
+        <f t="shared" si="2"/>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E173" s="4">
@@ -10375,7 +10375,7 @@
         <v>1772</v>
       </c>
       <c r="D174" s="3">
-        <f>100%-F174</f>
+        <f t="shared" si="2"/>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E174" s="4">
@@ -10417,7 +10417,7 @@
         <v>150</v>
       </c>
       <c r="D175" s="3">
-        <f>100%-F175</f>
+        <f t="shared" si="2"/>
         <v>0.8</v>
       </c>
       <c r="E175" s="4">
@@ -10459,7 +10459,7 @@
         <v>249</v>
       </c>
       <c r="D176" s="3">
-        <f>100%-F176</f>
+        <f t="shared" si="2"/>
         <v>0.38</v>
       </c>
       <c r="E176" s="4">
@@ -10501,7 +10501,7 @@
         <v>489</v>
       </c>
       <c r="D177" s="3">
-        <f>100%-F177</f>
+        <f t="shared" si="2"/>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E177" s="4">
@@ -10543,7 +10543,7 @@
         <v>955</v>
       </c>
       <c r="D178" s="3">
-        <f>100%-F178</f>
+        <f t="shared" si="2"/>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E178" s="4">
@@ -10585,7 +10585,7 @@
         <v>663</v>
       </c>
       <c r="D179" s="3">
-        <f>100%-F179</f>
+        <f t="shared" si="2"/>
         <v>0.22999999999999998</v>
       </c>
       <c r="E179" s="4">
@@ -10627,7 +10627,7 @@
         <v>821</v>
       </c>
       <c r="D180" s="3">
-        <f>100%-F180</f>
+        <f t="shared" si="2"/>
         <v>0.22999999999999998</v>
       </c>
       <c r="E180" s="4">
@@ -10669,7 +10669,7 @@
         <v>1561</v>
       </c>
       <c r="D181" s="3">
-        <f>100%-F181</f>
+        <f t="shared" si="2"/>
         <v>0.15000000000000002</v>
       </c>
       <c r="E181" s="4">
@@ -10711,7 +10711,7 @@
         <v>107</v>
       </c>
       <c r="D182" s="3">
-        <f>100%-F182</f>
+        <f t="shared" si="2"/>
         <v>0.44999999999999996</v>
       </c>
       <c r="E182" s="4">
@@ -10753,7 +10753,7 @@
         <v>147</v>
       </c>
       <c r="D183" s="3">
-        <f>100%-F183</f>
+        <f t="shared" si="2"/>
         <v>0.38</v>
       </c>
       <c r="E183" s="4">
@@ -10795,7 +10795,7 @@
         <v>197</v>
       </c>
       <c r="D184" s="3">
-        <f>100%-F184</f>
+        <f t="shared" si="2"/>
         <v>0.44999999999999996</v>
       </c>
       <c r="E184" s="4">
@@ -10837,7 +10837,7 @@
         <v>1173</v>
       </c>
       <c r="D185" s="3">
-        <f>100%-F185</f>
+        <f t="shared" si="2"/>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E185" s="4">
@@ -10879,7 +10879,7 @@
         <v>2657</v>
       </c>
       <c r="D186" s="3">
-        <f>100%-F186</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="E186" s="4">
@@ -10921,7 +10921,7 @@
         <v>323</v>
       </c>
       <c r="D187" s="3">
-        <f>100%-F187</f>
+        <f t="shared" si="2"/>
         <v>0.15000000000000002</v>
       </c>
       <c r="E187" s="4">
@@ -10963,7 +10963,7 @@
         <v>676</v>
       </c>
       <c r="D188" s="3">
-        <f>100%-F188</f>
+        <f t="shared" si="2"/>
         <v>0.22999999999999998</v>
       </c>
       <c r="E188" s="4">
@@ -11005,7 +11005,7 @@
         <v>4695</v>
       </c>
       <c r="D189" s="3">
-        <f>100%-F189</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="E189" s="4">
@@ -11047,7 +11047,7 @@
         <v>623</v>
       </c>
       <c r="D190" s="3">
-        <f>100%-F190</f>
+        <f t="shared" si="2"/>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E190" s="4">
@@ -11089,7 +11089,7 @@
         <v>754</v>
       </c>
       <c r="D191" s="3">
-        <f>100%-F191</f>
+        <f t="shared" si="2"/>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="E191" s="4">
@@ -11131,7 +11131,7 @@
         <v>503</v>
       </c>
       <c r="D192" s="3">
-        <f>100%-F192</f>
+        <f t="shared" si="2"/>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="E192" s="4">
@@ -11173,7 +11173,7 @@
         <v>188</v>
       </c>
       <c r="D193" s="3">
-        <f>100%-F193</f>
+        <f t="shared" si="2"/>
         <v>0.44999999999999996</v>
       </c>
       <c r="E193" s="4">
@@ -11215,7 +11215,7 @@
         <v>149</v>
       </c>
       <c r="D194" s="3">
-        <f>100%-F194</f>
+        <f t="shared" ref="D194:D257" si="3">100%-F194</f>
         <v>0.44999999999999996</v>
       </c>
       <c r="E194" s="4">
@@ -11257,7 +11257,7 @@
         <v>571</v>
       </c>
       <c r="D195" s="3">
-        <f>100%-F195</f>
+        <f t="shared" si="3"/>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E195" s="4">
@@ -11299,7 +11299,7 @@
         <v>989</v>
       </c>
       <c r="D196" s="3">
-        <f>100%-F196</f>
+        <f t="shared" si="3"/>
         <v>0.15000000000000002</v>
       </c>
       <c r="E196" s="4">
@@ -11341,7 +11341,7 @@
         <v>214</v>
       </c>
       <c r="D197" s="3">
-        <f>100%-F197</f>
+        <f t="shared" si="3"/>
         <v>0.36</v>
       </c>
       <c r="E197" s="4">
@@ -11383,7 +11383,7 @@
         <v>147</v>
       </c>
       <c r="D198" s="3">
-        <f>100%-F198</f>
+        <f t="shared" si="3"/>
         <v>0.26</v>
       </c>
       <c r="E198" s="4">
@@ -11425,7 +11425,7 @@
         <v>227</v>
       </c>
       <c r="D199" s="3">
-        <f>100%-F199</f>
+        <f t="shared" si="3"/>
         <v>0.30000000000000004</v>
       </c>
       <c r="E199" s="4">
@@ -11467,7 +11467,7 @@
         <v>957</v>
       </c>
       <c r="D200" s="3">
-        <f>100%-F200</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="E200" s="4">
@@ -11509,7 +11509,7 @@
         <v>1130</v>
       </c>
       <c r="D201" s="3">
-        <f>100%-F201</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="E201" s="4">
@@ -11551,7 +11551,7 @@
         <v>17779</v>
       </c>
       <c r="D202" s="3">
-        <f>100%-F202</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="E202" s="4">
@@ -11593,7 +11593,7 @@
         <v>409</v>
       </c>
       <c r="D203" s="3">
-        <f>100%-F203</f>
+        <f t="shared" si="3"/>
         <v>0.30000000000000004</v>
       </c>
       <c r="E203" s="4">
@@ -11635,7 +11635,7 @@
         <v>109</v>
       </c>
       <c r="D204" s="3">
-        <f>100%-F204</f>
+        <f t="shared" si="3"/>
         <v>0.37</v>
       </c>
       <c r="E204" s="4">
@@ -11677,7 +11677,7 @@
         <v>523</v>
       </c>
       <c r="D205" s="3">
-        <f>100%-F205</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="E205" s="4">
@@ -11719,7 +11719,7 @@
         <v>648</v>
       </c>
       <c r="D206" s="3">
-        <f>100%-F206</f>
+        <f t="shared" si="3"/>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="E206" s="4">
@@ -11761,7 +11761,7 @@
         <v>903</v>
       </c>
       <c r="D207" s="3">
-        <f>100%-F207</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="E207" s="4">
@@ -11803,7 +11803,7 @@
         <v>630</v>
       </c>
       <c r="D208" s="3">
-        <f>100%-F208</f>
+        <f t="shared" si="3"/>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="E208" s="4">
@@ -11845,7 +11845,7 @@
         <v>801</v>
       </c>
       <c r="D209" s="3">
-        <f>100%-F209</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="E209" s="4">
@@ -11887,7 +11887,7 @@
         <v>401</v>
       </c>
       <c r="D210" s="3">
-        <f>100%-F210</f>
+        <f t="shared" si="3"/>
         <v>0.22999999999999998</v>
       </c>
       <c r="E210" s="4">
@@ -11929,7 +11929,7 @@
         <v>246</v>
       </c>
       <c r="D211" s="3">
-        <f>100%-F211</f>
+        <f t="shared" si="3"/>
         <v>0.31999999999999995</v>
       </c>
       <c r="E211" s="4">
@@ -11971,7 +11971,7 @@
         <v>374</v>
       </c>
       <c r="D212" s="3">
-        <f>100%-F212</f>
+        <f t="shared" si="3"/>
         <v>0.30000000000000004</v>
       </c>
       <c r="E212" s="4">
@@ -12013,7 +12013,7 @@
         <v>621</v>
       </c>
       <c r="D213" s="3">
-        <f>100%-F213</f>
+        <f t="shared" si="3"/>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="E213" s="4">
@@ -12055,7 +12055,7 @@
         <v>204</v>
       </c>
       <c r="D214" s="3">
-        <f>100%-F214</f>
+        <f t="shared" si="3"/>
         <v>0.31999999999999995</v>
       </c>
       <c r="E214" s="4">
@@ -12097,7 +12097,7 @@
         <v>614</v>
       </c>
       <c r="D215" s="3">
-        <f>100%-F215</f>
+        <f t="shared" si="3"/>
         <v>0.22999999999999998</v>
       </c>
       <c r="E215" s="4">
@@ -12139,7 +12139,7 @@
         <v>814</v>
       </c>
       <c r="D216" s="3">
-        <f>100%-F216</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="E216" s="4">
@@ -12181,7 +12181,7 @@
         <v>205</v>
       </c>
       <c r="D217" s="3">
-        <f>100%-F217</f>
+        <f t="shared" si="3"/>
         <v>0.30000000000000004</v>
       </c>
       <c r="E217" s="4">
@@ -12223,7 +12223,7 @@
         <v>119</v>
       </c>
       <c r="D218" s="3">
-        <f>100%-F218</f>
+        <f t="shared" si="3"/>
         <v>0.20999999999999996</v>
       </c>
       <c r="E218" s="4">
@@ -12265,7 +12265,7 @@
         <v>122</v>
       </c>
       <c r="D219" s="3">
-        <f>100%-F219</f>
+        <f t="shared" si="3"/>
         <v>0.30000000000000004</v>
       </c>
       <c r="E219" s="4">
@@ -12307,7 +12307,7 @@
         <v>477</v>
       </c>
       <c r="D220" s="3">
-        <f>100%-F220</f>
+        <f t="shared" si="3"/>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E220" s="4">
@@ -12349,7 +12349,7 @@
         <v>503</v>
       </c>
       <c r="D221" s="3">
-        <f>100%-F221</f>
+        <f t="shared" si="3"/>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="E221" s="4">
@@ -12391,7 +12391,7 @@
         <v>125</v>
       </c>
       <c r="D222" s="3">
-        <f>100%-F222</f>
+        <f t="shared" si="3"/>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E222" s="4">
@@ -12433,7 +12433,7 @@
         <v>262</v>
       </c>
       <c r="D223" s="3">
-        <f>100%-F223</f>
+        <f t="shared" si="3"/>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E223" s="4">
@@ -12475,7 +12475,7 @@
         <v>184</v>
       </c>
       <c r="D224" s="3">
-        <f>100%-F224</f>
+        <f t="shared" si="3"/>
         <v>0.37</v>
       </c>
       <c r="E224" s="4">
@@ -12517,7 +12517,7 @@
         <v>439</v>
       </c>
       <c r="D225" s="3">
-        <f>100%-F225</f>
+        <f t="shared" si="3"/>
         <v>0.30000000000000004</v>
       </c>
       <c r="E225" s="4">
@@ -12559,7 +12559,7 @@
         <v>173</v>
       </c>
       <c r="D226" s="3">
-        <f>100%-F226</f>
+        <f t="shared" si="3"/>
         <v>0.22999999999999998</v>
       </c>
       <c r="E226" s="4">
@@ -12601,7 +12601,7 @@
         <v>528</v>
       </c>
       <c r="D227" s="3">
-        <f>100%-F227</f>
+        <f t="shared" si="3"/>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="E227" s="4">
@@ -12643,7 +12643,7 @@
         <v>189</v>
       </c>
       <c r="D228" s="3">
-        <f>100%-F228</f>
+        <f t="shared" si="3"/>
         <v>0.22999999999999998</v>
       </c>
       <c r="E228" s="4">
@@ -12685,7 +12685,7 @@
         <v>494</v>
       </c>
       <c r="D229" s="3">
-        <f>100%-F229</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="E229" s="4">
@@ -12727,7 +12727,7 @@
         <v>112</v>
       </c>
       <c r="D230" s="3">
-        <f>100%-F230</f>
+        <f t="shared" si="3"/>
         <v>0.44999999999999996</v>
       </c>
       <c r="E230" s="4">
@@ -12769,7 +12769,7 @@
         <v>700</v>
       </c>
       <c r="D231" s="3">
-        <f>100%-F231</f>
+        <f t="shared" si="3"/>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="E231" s="4">
@@ -12811,7 +12811,7 @@
         <v>630</v>
       </c>
       <c r="D232" s="3">
-        <f>100%-F232</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="E232" s="4">
@@ -12853,7 +12853,7 @@
         <v>274</v>
       </c>
       <c r="D233" s="3">
-        <f>100%-F233</f>
+        <f t="shared" si="3"/>
         <v>0.22999999999999998</v>
       </c>
       <c r="E233" s="4">
@@ -12895,7 +12895,7 @@
         <v>102</v>
       </c>
       <c r="D234" s="3">
-        <f>100%-F234</f>
+        <f t="shared" si="3"/>
         <v>0.65</v>
       </c>
       <c r="E234" s="4">
@@ -12937,7 +12937,7 @@
         <v>390</v>
       </c>
       <c r="D235" s="3">
-        <f>100%-F235</f>
+        <f t="shared" si="3"/>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E235" s="4">
@@ -12979,7 +12979,7 @@
         <v>238</v>
       </c>
       <c r="D236" s="3">
-        <f>100%-F236</f>
+        <f t="shared" si="3"/>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E236" s="4">
@@ -13021,7 +13021,7 @@
         <v>314</v>
       </c>
       <c r="D237" s="3">
-        <f>100%-F237</f>
+        <f t="shared" si="3"/>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="E237" s="4">
@@ -13063,7 +13063,7 @@
         <v>218</v>
       </c>
       <c r="D238" s="3">
-        <f>100%-F238</f>
+        <f t="shared" si="3"/>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E238" s="4">
@@ -13105,7 +13105,7 @@
         <v>232</v>
       </c>
       <c r="D239" s="3">
-        <f>100%-F239</f>
+        <f t="shared" si="3"/>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E239" s="4">
@@ -13147,7 +13147,7 @@
         <v>111</v>
       </c>
       <c r="D240" s="3">
-        <f>100%-F240</f>
+        <f t="shared" si="3"/>
         <v>0.38</v>
       </c>
       <c r="E240" s="4">
@@ -13189,7 +13189,7 @@
         <v>104</v>
       </c>
       <c r="D241" s="3">
-        <f>100%-F241</f>
+        <f t="shared" si="3"/>
         <v>0.38</v>
       </c>
       <c r="E241" s="4">
@@ -13231,7 +13231,7 @@
         <v>852</v>
       </c>
       <c r="D242" s="3">
-        <f>100%-F242</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="E242" s="4">
@@ -13273,7 +13273,7 @@
         <v>152</v>
       </c>
       <c r="D243" s="3">
-        <f>100%-F243</f>
+        <f t="shared" si="3"/>
         <v>0.22999999999999998</v>
       </c>
       <c r="E243" s="4">
@@ -13315,7 +13315,7 @@
         <v>679</v>
       </c>
       <c r="D244" s="3">
-        <f>100%-F244</f>
+        <f t="shared" si="3"/>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="E244" s="4">
@@ -13357,7 +13357,7 @@
         <v>145</v>
       </c>
       <c r="D245" s="3">
-        <f>100%-F245</f>
+        <f t="shared" si="3"/>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E245" s="4">
@@ -13399,7 +13399,7 @@
         <v>278</v>
       </c>
       <c r="D246" s="3">
-        <f>100%-F246</f>
+        <f t="shared" si="3"/>
         <v>0.32999999999999996</v>
       </c>
       <c r="E246" s="4">
@@ -13441,7 +13441,7 @@
         <v>224</v>
       </c>
       <c r="D247" s="3">
-        <f>100%-F247</f>
+        <f t="shared" si="3"/>
         <v>0.22999999999999998</v>
       </c>
       <c r="E247" s="4">
@@ -13483,7 +13483,7 @@
         <v>115</v>
       </c>
       <c r="D248" s="3">
-        <f>100%-F248</f>
+        <f t="shared" si="3"/>
         <v>0.22999999999999998</v>
       </c>
       <c r="E248" s="4">
@@ -13525,7 +13525,7 @@
         <v>992</v>
       </c>
       <c r="D249" s="3">
-        <f>100%-F249</f>
+        <f t="shared" si="3"/>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="E249" s="4">
@@ -13567,7 +13567,7 @@
         <v>189</v>
       </c>
       <c r="D250" s="3">
-        <f>100%-F250</f>
+        <f t="shared" si="3"/>
         <v>0.38</v>
       </c>
       <c r="E250" s="4">
@@ -13609,7 +13609,7 @@
         <v>217</v>
       </c>
       <c r="D251" s="3">
-        <f>100%-F251</f>
+        <f t="shared" si="3"/>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="E251" s="4">
@@ -13651,7 +13651,7 @@
         <v>231</v>
       </c>
       <c r="D252" s="3">
-        <f>100%-F252</f>
+        <f t="shared" si="3"/>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="E252" s="4">
@@ -13693,7 +13693,7 @@
         <v>259</v>
       </c>
       <c r="D253" s="3">
-        <f>100%-F253</f>
+        <f t="shared" si="3"/>
         <v>0.22999999999999998</v>
       </c>
       <c r="E253" s="4">
@@ -13735,7 +13735,7 @@
         <v>891</v>
       </c>
       <c r="D254" s="3">
-        <f>100%-F254</f>
+        <f t="shared" si="3"/>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="E254" s="4">
@@ -13777,7 +13777,7 @@
         <v>152</v>
       </c>
       <c r="D255" s="3">
-        <f>100%-F255</f>
+        <f t="shared" si="3"/>
         <v>0.37</v>
       </c>
       <c r="E255" s="4">
@@ -13819,7 +13819,7 @@
         <v>403</v>
       </c>
       <c r="D256" s="3">
-        <f>100%-F256</f>
+        <f t="shared" si="3"/>
         <v>0.22999999999999998</v>
       </c>
       <c r="E256" s="4">
@@ -13861,7 +13861,7 @@
         <v>2082</v>
       </c>
       <c r="D257" s="3">
-        <f>100%-F257</f>
+        <f t="shared" si="3"/>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="E257" s="4">
@@ -13903,7 +13903,7 @@
         <v>232</v>
       </c>
       <c r="D258" s="3">
-        <f>100%-F258</f>
+        <f t="shared" ref="D258:D321" si="4">100%-F258</f>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E258" s="4">
@@ -13945,7 +13945,7 @@
         <v>430</v>
       </c>
       <c r="D259" s="3">
-        <f>100%-F259</f>
+        <f t="shared" si="4"/>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E259" s="4">
@@ -13987,7 +13987,7 @@
         <v>128</v>
       </c>
       <c r="D260" s="3">
-        <f>100%-F260</f>
+        <f t="shared" si="4"/>
         <v>0.17000000000000004</v>
       </c>
       <c r="E260" s="4">
@@ -14029,7 +14029,7 @@
         <v>112</v>
       </c>
       <c r="D261" s="3">
-        <f>100%-F261</f>
+        <f t="shared" si="4"/>
         <v>0.37</v>
       </c>
       <c r="E261" s="4">
@@ -14071,7 +14071,7 @@
         <v>498</v>
       </c>
       <c r="D262" s="3">
-        <f>100%-F262</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="E262" s="4">
@@ -14113,7 +14113,7 @@
         <v>512</v>
       </c>
       <c r="D263" s="3">
-        <f>100%-F263</f>
+        <f t="shared" si="4"/>
         <v>0.22999999999999998</v>
       </c>
       <c r="E263" s="4">
@@ -14155,7 +14155,7 @@
         <v>1228</v>
       </c>
       <c r="D264" s="3">
-        <f>100%-F264</f>
+        <f t="shared" si="4"/>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="E264" s="4">
@@ -14197,7 +14197,7 @@
         <v>255</v>
       </c>
       <c r="D265" s="3">
-        <f>100%-F265</f>
+        <f t="shared" si="4"/>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E265" s="4">
@@ -14239,7 +14239,7 @@
         <v>102</v>
       </c>
       <c r="D266" s="3">
-        <f>100%-F266</f>
+        <f t="shared" si="4"/>
         <v>0.15000000000000002</v>
       </c>
       <c r="E266" s="4">
@@ -14281,7 +14281,7 @@
         <v>487</v>
       </c>
       <c r="D267" s="3">
-        <f>100%-F267</f>
+        <f t="shared" si="4"/>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E267" s="4">
@@ -14323,7 +14323,7 @@
         <v>226</v>
       </c>
       <c r="D268" s="3">
-        <f>100%-F268</f>
+        <f t="shared" si="4"/>
         <v>0.32999999999999996</v>
       </c>
       <c r="E268" s="4">
@@ -14365,7 +14365,7 @@
         <v>682</v>
       </c>
       <c r="D269" s="3">
-        <f>100%-F269</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="E269" s="4">
@@ -14407,7 +14407,7 @@
         <v>111</v>
       </c>
       <c r="D270" s="3">
-        <f>100%-F270</f>
+        <f t="shared" si="4"/>
         <v>0.31999999999999995</v>
       </c>
       <c r="E270" s="4">
@@ -14449,7 +14449,7 @@
         <v>543</v>
       </c>
       <c r="D271" s="3">
-        <f>100%-F271</f>
+        <f t="shared" si="4"/>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="E271" s="4">
@@ -14491,7 +14491,7 @@
         <v>1048</v>
       </c>
       <c r="D272" s="3">
-        <f>100%-F272</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="E272" s="4">
@@ -14533,7 +14533,7 @@
         <v>210</v>
       </c>
       <c r="D273" s="3">
-        <f>100%-F273</f>
+        <f t="shared" si="4"/>
         <v>0.22999999999999998</v>
       </c>
       <c r="E273" s="4">
@@ -14575,7 +14575,7 @@
         <v>297</v>
       </c>
       <c r="D274" s="3">
-        <f>100%-F274</f>
+        <f t="shared" si="4"/>
         <v>0.22999999999999998</v>
       </c>
       <c r="E274" s="4">
@@ -14617,7 +14617,7 @@
         <v>730</v>
       </c>
       <c r="D275" s="3">
-        <f>100%-F275</f>
+        <f t="shared" si="4"/>
         <v>0.22999999999999998</v>
       </c>
       <c r="E275" s="4">
@@ -14659,7 +14659,7 @@
         <v>12585</v>
       </c>
       <c r="D276" s="3">
-        <f>100%-F276</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="E276" s="4">
@@ -14701,7 +14701,7 @@
         <v>165</v>
       </c>
       <c r="D277" s="3">
-        <f>100%-F277</f>
+        <f t="shared" si="4"/>
         <v>0.22999999999999998</v>
       </c>
       <c r="E277" s="4">
@@ -14743,7 +14743,7 @@
         <v>208</v>
       </c>
       <c r="D278" s="3">
-        <f>100%-F278</f>
+        <f t="shared" si="4"/>
         <v>0.30000000000000004</v>
       </c>
       <c r="E278" s="4">
@@ -14785,7 +14785,7 @@
         <v>805</v>
       </c>
       <c r="D279" s="3">
-        <f>100%-F279</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="E279" s="4">
@@ -14827,7 +14827,7 @@
         <v>629</v>
       </c>
       <c r="D280" s="3">
-        <f>100%-F280</f>
+        <f t="shared" si="4"/>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="E280" s="4">
@@ -14869,7 +14869,7 @@
         <v>812</v>
       </c>
       <c r="D281" s="3">
-        <f>100%-F281</f>
+        <f t="shared" si="4"/>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E281" s="4">
@@ -14911,7 +14911,7 @@
         <v>210</v>
       </c>
       <c r="D282" s="3">
-        <f>100%-F282</f>
+        <f t="shared" si="4"/>
         <v>0.22999999999999998</v>
       </c>
       <c r="E282" s="4">
@@ -14953,7 +14953,7 @@
         <v>208</v>
       </c>
       <c r="D283" s="3">
-        <f>100%-F283</f>
+        <f t="shared" si="4"/>
         <v>0.30000000000000004</v>
       </c>
       <c r="E283" s="4">
@@ -14995,7 +14995,7 @@
         <v>146</v>
       </c>
       <c r="D284" s="3">
-        <f>100%-F284</f>
+        <f t="shared" si="4"/>
         <v>0.37</v>
       </c>
       <c r="E284" s="4">
@@ -15037,7 +15037,7 @@
         <v>761</v>
       </c>
       <c r="D285" s="3">
-        <f>100%-F285</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="E285" s="5">
@@ -15079,7 +15079,7 @@
         <v>584</v>
       </c>
       <c r="D286" s="3">
-        <f>100%-F286</f>
+        <f t="shared" si="4"/>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E286" s="4">
@@ -15121,7 +15121,7 @@
         <v>118</v>
       </c>
       <c r="D287" s="3">
-        <f>100%-F287</f>
+        <f t="shared" si="4"/>
         <v>0.30000000000000004</v>
       </c>
       <c r="E287" s="4">
@@ -15163,7 +15163,7 @@
         <v>596</v>
       </c>
       <c r="D288" s="3">
-        <f>100%-F288</f>
+        <f t="shared" si="4"/>
         <v>0.30000000000000004</v>
       </c>
       <c r="E288" s="4">
@@ -15205,7 +15205,7 @@
         <v>302</v>
       </c>
       <c r="D289" s="3">
-        <f>100%-F289</f>
+        <f t="shared" si="4"/>
         <v>0.22999999999999998</v>
       </c>
       <c r="E289" s="4">
@@ -15247,7 +15247,7 @@
         <v>204</v>
       </c>
       <c r="D290" s="3">
-        <f>100%-F290</f>
+        <f t="shared" si="4"/>
         <v>0.30000000000000004</v>
       </c>
       <c r="E290" s="4">
@@ -15289,7 +15289,7 @@
         <v>337</v>
       </c>
       <c r="D291" s="3">
-        <f>100%-F291</f>
+        <f t="shared" si="4"/>
         <v>0.15000000000000002</v>
       </c>
       <c r="E291" s="4">
@@ -15331,7 +15331,7 @@
         <v>474</v>
       </c>
       <c r="D292" s="3">
-        <f>100%-F292</f>
+        <f t="shared" si="4"/>
         <v>0.13</v>
       </c>
       <c r="E292" s="4">
@@ -15373,7 +15373,7 @@
         <v>584</v>
       </c>
       <c r="D293" s="3">
-        <f>100%-F293</f>
+        <f t="shared" si="4"/>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E293" s="4">
@@ -15415,7 +15415,7 @@
         <v>254</v>
       </c>
       <c r="D294" s="3">
-        <f>100%-F294</f>
+        <f t="shared" si="4"/>
         <v>0.22999999999999998</v>
       </c>
       <c r="E294" s="4">
@@ -15457,7 +15457,7 @@
         <v>230</v>
       </c>
       <c r="D295" s="3">
-        <f>100%-F295</f>
+        <f t="shared" si="4"/>
         <v>0.30000000000000004</v>
       </c>
       <c r="E295" s="4">
@@ -15499,7 +15499,7 @@
         <v>358</v>
       </c>
       <c r="D296" s="3">
-        <f>100%-F296</f>
+        <f t="shared" si="4"/>
         <v>0.28000000000000003</v>
       </c>
       <c r="E296" s="4">
@@ -15542,7 +15542,7 @@
         <v>5961</v>
       </c>
       <c r="D297" s="3">
-        <f>100%-F297</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="E297" s="4">
@@ -15584,7 +15584,7 @@
         <v>125</v>
       </c>
       <c r="D298" s="3">
-        <f>100%-F298</f>
+        <f t="shared" si="4"/>
         <v>0.37</v>
       </c>
       <c r="E298" s="4">
@@ -15626,7 +15626,7 @@
         <v>1189</v>
       </c>
       <c r="D299" s="3">
-        <f>100%-F299</f>
+        <f t="shared" si="4"/>
         <v>0.25</v>
       </c>
       <c r="E299" s="4">
@@ -15668,7 +15668,7 @@
         <v>120</v>
       </c>
       <c r="D300" s="3">
-        <f>100%-F300</f>
+        <f t="shared" si="4"/>
         <v>0.44999999999999996</v>
       </c>
       <c r="E300" s="4">
@@ -15710,7 +15710,7 @@
         <v>560</v>
       </c>
       <c r="D301" s="3">
-        <f>100%-F301</f>
+        <f t="shared" si="4"/>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E301" s="4">
@@ -15753,7 +15753,7 @@
         <v>1210</v>
       </c>
       <c r="D302" s="3">
-        <f>100%-F302</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="E302" s="4">
@@ -15795,7 +15795,7 @@
         <v>101</v>
       </c>
       <c r="D303" s="3">
-        <f>100%-F303</f>
+        <f t="shared" si="4"/>
         <v>0.44999999999999996</v>
       </c>
       <c r="E303" s="4">
@@ -15837,7 +15837,7 @@
         <v>1082</v>
       </c>
       <c r="D304" s="3">
-        <f>100%-F304</f>
+        <f t="shared" si="4"/>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E304" s="4">
@@ -15880,7 +15880,7 @@
         <v>246</v>
       </c>
       <c r="D305" s="3">
-        <f>100%-F305</f>
+        <f t="shared" si="4"/>
         <v>0.22999999999999998</v>
       </c>
       <c r="E305" s="4">
@@ -15923,7 +15923,7 @@
         <v>557</v>
       </c>
       <c r="D306" s="3">
-        <f>100%-F306</f>
+        <f t="shared" si="4"/>
         <v>0.32999999999999996</v>
       </c>
       <c r="E306" s="4">
@@ -15965,7 +15965,7 @@
         <v>177</v>
       </c>
       <c r="D307" s="3">
-        <f>100%-F307</f>
+        <f t="shared" si="4"/>
         <v>0.72</v>
       </c>
       <c r="E307" s="4">
@@ -16007,7 +16007,7 @@
         <v>1276</v>
       </c>
       <c r="D308" s="3">
-        <f>100%-F308</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="E308" s="4">
@@ -16049,7 +16049,7 @@
         <v>397</v>
       </c>
       <c r="D309" s="3">
-        <f>100%-F309</f>
+        <f t="shared" si="4"/>
         <v>0.22999999999999998</v>
       </c>
       <c r="E309" s="4">
@@ -16091,7 +16091,7 @@
         <v>285</v>
       </c>
       <c r="D310" s="3">
-        <f>100%-F310</f>
+        <f t="shared" si="4"/>
         <v>0.37</v>
       </c>
       <c r="E310" s="4">
@@ -16133,7 +16133,7 @@
         <v>952</v>
       </c>
       <c r="D311" s="3">
-        <f>100%-F311</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="E311" s="4">
@@ -16175,7 +16175,7 @@
         <v>5078</v>
       </c>
       <c r="D312" s="3">
-        <f>100%-F312</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="E312" s="4">
@@ -16217,7 +16217,7 @@
         <v>17053</v>
       </c>
       <c r="D313" s="3">
-        <f>100%-F313</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="E313" s="5">
@@ -16259,7 +16259,7 @@
         <v>373</v>
       </c>
       <c r="D314" s="3">
-        <f>100%-F314</f>
+        <f t="shared" si="4"/>
         <v>0.30000000000000004</v>
       </c>
       <c r="E314" s="4">
@@ -16301,7 +16301,7 @@
         <v>859</v>
       </c>
       <c r="D315" s="3">
-        <f>100%-F315</f>
+        <f t="shared" si="4"/>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E315" s="4">
@@ -16343,7 +16343,7 @@
         <v>365</v>
       </c>
       <c r="D316" s="3">
-        <f>100%-F316</f>
+        <f t="shared" si="4"/>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E316" s="4">
@@ -16385,7 +16385,7 @@
         <v>496</v>
       </c>
       <c r="D317" s="3">
-        <f>100%-F317</f>
+        <f t="shared" si="4"/>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E317" s="4">
@@ -16427,7 +16427,7 @@
         <v>1631</v>
       </c>
       <c r="D318" s="3">
-        <f>100%-F318</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="E318" s="4">
@@ -16469,7 +16469,7 @@
         <v>955</v>
       </c>
       <c r="D319" s="3">
-        <f>100%-F319</f>
+        <f t="shared" si="4"/>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E319" s="4">
@@ -16511,7 +16511,7 @@
         <v>923</v>
       </c>
       <c r="D320" s="3">
-        <f>100%-F320</f>
+        <f t="shared" si="4"/>
         <v>0.22999999999999998</v>
       </c>
       <c r="E320" s="4">
@@ -16553,7 +16553,7 @@
         <v>3670</v>
       </c>
       <c r="D321" s="3">
-        <f>100%-F321</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="E321" s="4">
@@ -16595,7 +16595,7 @@
         <v>222</v>
       </c>
       <c r="D322" s="3">
-        <f>100%-F322</f>
+        <f t="shared" ref="D322:D385" si="5">100%-F322</f>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E322" s="4">
@@ -16637,7 +16637,7 @@
         <v>890</v>
       </c>
       <c r="D323" s="3">
-        <f>100%-F323</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="E323" s="4">
@@ -16679,7 +16679,7 @@
         <v>265</v>
       </c>
       <c r="D324" s="3">
-        <f>100%-F324</f>
+        <f t="shared" si="5"/>
         <v>0.25</v>
       </c>
       <c r="E324" s="4">
@@ -16721,7 +16721,7 @@
         <v>875</v>
       </c>
       <c r="D325" s="3">
-        <f>100%-F325</f>
+        <f t="shared" si="5"/>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="E325" s="4">
@@ -16763,7 +16763,7 @@
         <v>446</v>
       </c>
       <c r="D326" s="3">
-        <f>100%-F326</f>
+        <f t="shared" si="5"/>
         <v>0.38</v>
       </c>
       <c r="E326" s="4">
@@ -16806,7 +16806,7 @@
         <v>111</v>
       </c>
       <c r="D327" s="3">
-        <f>100%-F327</f>
+        <f t="shared" si="5"/>
         <v>0.37</v>
       </c>
       <c r="E327" s="4">
@@ -16848,7 +16848,7 @@
         <v>585</v>
       </c>
       <c r="D328" s="3">
-        <f>100%-F328</f>
+        <f t="shared" si="5"/>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="E328" s="4">
@@ -16890,7 +16890,7 @@
         <v>801</v>
       </c>
       <c r="D329" s="3">
-        <f>100%-F329</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="E329" s="4">
@@ -16932,7 +16932,7 @@
         <v>191</v>
       </c>
       <c r="D330" s="3">
-        <f>100%-F330</f>
+        <f t="shared" si="5"/>
         <v>0.30000000000000004</v>
       </c>
       <c r="E330" s="4">
@@ -16975,7 +16975,7 @@
         <v>2820</v>
       </c>
       <c r="D331" s="3">
-        <f>100%-F331</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="E331" s="4">
@@ -17017,7 +17017,7 @@
         <v>805</v>
       </c>
       <c r="D332" s="3">
-        <f>100%-F332</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="E332" s="4">
@@ -17059,7 +17059,7 @@
         <v>147</v>
       </c>
       <c r="D333" s="3">
-        <f>100%-F333</f>
+        <f t="shared" si="5"/>
         <v>0.8</v>
       </c>
       <c r="E333" s="4">
@@ -17101,7 +17101,7 @@
         <v>227</v>
       </c>
       <c r="D334" s="3">
-        <f>100%-F334</f>
+        <f t="shared" si="5"/>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E334" s="4">
@@ -17144,7 +17144,7 @@
         <v>580</v>
       </c>
       <c r="D335" s="3">
-        <f>100%-F335</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="E335" s="4">
@@ -17186,7 +17186,7 @@
         <v>924</v>
       </c>
       <c r="D336" s="3">
-        <f>100%-F336</f>
+        <f t="shared" si="5"/>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E336" s="4">
@@ -17229,7 +17229,7 @@
         <v>492</v>
       </c>
       <c r="D337" s="3">
-        <f>100%-F337</f>
+        <f t="shared" si="5"/>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E337" s="4">
@@ -17271,7 +17271,7 @@
         <v>880</v>
       </c>
       <c r="D338" s="3">
-        <f>100%-F338</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="E338" s="4">
@@ -17313,7 +17313,7 @@
         <v>272</v>
       </c>
       <c r="D339" s="3">
-        <f>100%-F339</f>
+        <f t="shared" si="5"/>
         <v>0.30000000000000004</v>
       </c>
       <c r="E339" s="4">
@@ -17355,7 +17355,7 @@
         <v>915</v>
       </c>
       <c r="D340" s="3">
-        <f>100%-F340</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="E340" s="4">
@@ -17397,7 +17397,7 @@
         <v>413</v>
       </c>
       <c r="D341" s="3">
-        <f>100%-F341</f>
+        <f t="shared" si="5"/>
         <v>0.30000000000000004</v>
       </c>
       <c r="E341" s="4">
@@ -17440,7 +17440,7 @@
         <v>683</v>
       </c>
       <c r="D342" s="3">
-        <f>100%-F342</f>
+        <f t="shared" si="5"/>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="E342" s="4">
@@ -17482,7 +17482,7 @@
         <v>767</v>
       </c>
       <c r="D343" s="3">
-        <f>100%-F343</f>
+        <f t="shared" si="5"/>
         <v>0.38</v>
       </c>
       <c r="E343" s="4">
@@ -17524,7 +17524,7 @@
         <v>323</v>
       </c>
       <c r="D344" s="3">
-        <f>100%-F344</f>
+        <f t="shared" si="5"/>
         <v>0.22999999999999998</v>
       </c>
       <c r="E344" s="4">
@@ -17566,7 +17566,7 @@
         <v>942</v>
       </c>
       <c r="D345" s="3">
-        <f>100%-F345</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="E345" s="4">
@@ -17608,7 +17608,7 @@
         <v>297</v>
       </c>
       <c r="D346" s="3">
-        <f>100%-F346</f>
+        <f t="shared" si="5"/>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E346" s="4">
@@ -17651,7 +17651,7 @@
         <v>461</v>
       </c>
       <c r="D347" s="3">
-        <f>100%-F347</f>
+        <f t="shared" si="5"/>
         <v>0.22999999999999998</v>
       </c>
       <c r="E347" s="4">
@@ -17693,7 +17693,7 @@
         <v>588</v>
       </c>
       <c r="D348" s="3">
-        <f>100%-F348</f>
+        <f t="shared" si="5"/>
         <v>0.22999999999999998</v>
       </c>
       <c r="E348" s="4">
@@ -17736,7 +17736,7 @@
         <v>370</v>
       </c>
       <c r="D349" s="3">
-        <f>100%-F349</f>
+        <f t="shared" si="5"/>
         <v>0.30000000000000004</v>
       </c>
       <c r="E349" s="4">
@@ -17779,7 +17779,7 @@
         <v>510</v>
       </c>
       <c r="D350" s="3">
-        <f>100%-F350</f>
+        <f t="shared" si="5"/>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="E350" s="4">
@@ -17821,7 +17821,7 @@
         <v>220</v>
       </c>
       <c r="D351" s="3">
-        <f>100%-F351</f>
+        <f t="shared" si="5"/>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E351" s="4">
@@ -17863,7 +17863,7 @@
         <v>627</v>
       </c>
       <c r="D352" s="3">
-        <f>100%-F352</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="E352" s="4">
@@ -17905,7 +17905,7 @@
         <v>276</v>
       </c>
       <c r="D353" s="3">
-        <f>100%-F353</f>
+        <f t="shared" si="5"/>
         <v>0.30000000000000004</v>
       </c>
       <c r="E353" s="4">
@@ -17947,7 +17947,7 @@
         <v>1483</v>
       </c>
       <c r="D354" s="3">
-        <f>100%-F354</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="E354" s="4">
@@ -17989,7 +17989,7 @@
         <v>504</v>
       </c>
       <c r="D355" s="3">
-        <f>100%-F355</f>
+        <f t="shared" si="5"/>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E355" s="4">
@@ -18032,7 +18032,7 @@
         <v>8955</v>
       </c>
       <c r="D356" s="3">
-        <f>100%-F356</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="E356" s="4">
@@ -18074,7 +18074,7 @@
         <v>360</v>
       </c>
       <c r="D357" s="3">
-        <f>100%-F357</f>
+        <f t="shared" si="5"/>
         <v>0.30000000000000004</v>
       </c>
       <c r="E357" s="4">
@@ -18116,7 +18116,7 @@
         <v>105</v>
       </c>
       <c r="D358" s="3">
-        <f>100%-F358</f>
+        <f t="shared" si="5"/>
         <v>0.73</v>
       </c>
       <c r="E358" s="4">
@@ -18158,7 +18158,7 @@
         <v>1012</v>
       </c>
       <c r="D359" s="3">
-        <f>100%-F359</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="E359" s="5">
@@ -18200,7 +18200,7 @@
         <v>139</v>
       </c>
       <c r="D360" s="3">
-        <f>100%-F360</f>
+        <f t="shared" si="5"/>
         <v>0.8</v>
       </c>
       <c r="E360" s="6">
@@ -18243,7 +18243,7 @@
         <v>776</v>
       </c>
       <c r="D361" s="3">
-        <f>100%-F361</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="E361" s="6">
@@ -18285,7 +18285,7 @@
         <v>217</v>
       </c>
       <c r="D362" s="3">
-        <f>100%-F362</f>
+        <f t="shared" si="5"/>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E362" s="6">
@@ -18327,7 +18327,7 @@
         <v>215</v>
       </c>
       <c r="D363" s="3">
-        <f>100%-F363</f>
+        <f t="shared" si="5"/>
         <v>0.32999999999999996</v>
       </c>
       <c r="E363" s="6">
@@ -18369,7 +18369,7 @@
         <v>274</v>
       </c>
       <c r="D364" s="3">
-        <f>100%-F364</f>
+        <f t="shared" si="5"/>
         <v>0.22999999999999998</v>
       </c>
       <c r="E364" s="6">
@@ -18411,7 +18411,7 @@
         <v>146</v>
       </c>
       <c r="D365" s="3">
-        <f>100%-F365</f>
+        <f t="shared" si="5"/>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E365" s="6">
@@ -18453,7 +18453,7 @@
         <v>1711</v>
       </c>
       <c r="D366" s="3">
-        <f>100%-F366</f>
+        <f t="shared" si="5"/>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E366" s="6">
@@ -18495,7 +18495,7 @@
         <v>357</v>
       </c>
       <c r="D367" s="3">
-        <f>100%-F367</f>
+        <f t="shared" si="5"/>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="E367" s="6">
@@ -18537,7 +18537,7 @@
         <v>122</v>
       </c>
       <c r="D368" s="3">
-        <f>100%-F368</f>
+        <f t="shared" si="5"/>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E368" s="6">
@@ -18579,7 +18579,7 @@
         <v>199</v>
       </c>
       <c r="D369" s="3">
-        <f>100%-F369</f>
+        <f t="shared" si="5"/>
         <v>0.30000000000000004</v>
       </c>
       <c r="E369" s="6">
@@ -18621,7 +18621,7 @@
         <v>162</v>
       </c>
       <c r="D370" s="3">
-        <f>100%-F370</f>
+        <f t="shared" si="5"/>
         <v>0.15000000000000002</v>
       </c>
       <c r="E370" s="6">
@@ -18663,7 +18663,7 @@
         <v>138</v>
       </c>
       <c r="D371" s="3">
-        <f>100%-F371</f>
+        <f t="shared" si="5"/>
         <v>0.8</v>
       </c>
       <c r="E371" s="6">
@@ -18705,7 +18705,7 @@
         <v>387</v>
       </c>
       <c r="D372" s="3">
-        <f>100%-F372</f>
+        <f t="shared" si="5"/>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="E372" s="4">
@@ -18748,7 +18748,7 @@
         <v>365</v>
       </c>
       <c r="D373" s="3">
-        <f>100%-F373</f>
+        <f t="shared" si="5"/>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="E373" s="4">
@@ -18790,7 +18790,7 @@
         <v>244</v>
       </c>
       <c r="D374" s="3">
-        <f>100%-F374</f>
+        <f t="shared" si="5"/>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E374" s="4">
@@ -18832,7 +18832,7 @@
         <v>514</v>
       </c>
       <c r="D375" s="3">
-        <f>100%-F375</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="E375" s="4">
@@ -18874,7 +18874,7 @@
         <v>421</v>
       </c>
       <c r="D376" s="3">
-        <f>100%-F376</f>
+        <f t="shared" si="5"/>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="E376" s="4">
@@ -18916,7 +18916,7 @@
         <v>520</v>
       </c>
       <c r="D377" s="3">
-        <f>100%-F377</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="E377" s="4">
@@ -18958,7 +18958,7 @@
         <v>164</v>
       </c>
       <c r="D378" s="3">
-        <f>100%-F378</f>
+        <f t="shared" si="5"/>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E378" s="4">
@@ -19001,7 +19001,7 @@
         <v>290</v>
       </c>
       <c r="D379" s="3">
-        <f>100%-F379</f>
+        <f t="shared" si="5"/>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E379" s="4">
@@ -19043,7 +19043,7 @@
         <v>252</v>
       </c>
       <c r="D380" s="3">
-        <f>100%-F380</f>
+        <f t="shared" si="5"/>
         <v>0.38</v>
       </c>
       <c r="E380" s="4">
@@ -19086,7 +19086,7 @@
         <v>451</v>
       </c>
       <c r="D381" s="3">
-        <f>100%-F381</f>
+        <f t="shared" si="5"/>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="E381" s="4">
@@ -19128,7 +19128,7 @@
         <v>207</v>
       </c>
       <c r="D382" s="3">
-        <f>100%-F382</f>
+        <f t="shared" si="5"/>
         <v>0.17000000000000004</v>
       </c>
       <c r="E382" s="4">
@@ -19170,7 +19170,7 @@
         <v>1457</v>
       </c>
       <c r="D383" s="3">
-        <f>100%-F383</f>
+        <f t="shared" si="5"/>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E383" s="4">
@@ -19212,7 +19212,7 @@
         <v>174</v>
       </c>
       <c r="D384" s="3">
-        <f>100%-F384</f>
+        <f t="shared" si="5"/>
         <v>0.44999999999999996</v>
       </c>
       <c r="E384" s="4">
@@ -19254,7 +19254,7 @@
         <v>571</v>
       </c>
       <c r="D385" s="3">
-        <f>100%-F385</f>
+        <f t="shared" si="5"/>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E385" s="4">
@@ -19296,7 +19296,7 @@
         <v>253</v>
       </c>
       <c r="D386" s="3">
-        <f>100%-F386</f>
+        <f t="shared" ref="D386:D449" si="6">100%-F386</f>
         <v>0.38</v>
       </c>
       <c r="E386" s="4">
@@ -19338,7 +19338,7 @@
         <v>147</v>
       </c>
       <c r="D387" s="3">
-        <f>100%-F387</f>
+        <f t="shared" si="6"/>
         <v>0.19999999999999996</v>
       </c>
       <c r="E387" s="4">
@@ -19380,7 +19380,7 @@
         <v>306</v>
       </c>
       <c r="D388" s="3">
-        <f>100%-F388</f>
+        <f t="shared" si="6"/>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E388" s="4">
@@ -19422,7 +19422,7 @@
         <v>575</v>
       </c>
       <c r="D389" s="3">
-        <f>100%-F389</f>
+        <f t="shared" si="6"/>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="E389" s="4">
@@ -19464,7 +19464,7 @@
         <v>235</v>
       </c>
       <c r="D390" s="3">
-        <f>100%-F390</f>
+        <f t="shared" si="6"/>
         <v>0.25</v>
       </c>
       <c r="E390" s="4">
@@ -19506,7 +19506,7 @@
         <v>631</v>
       </c>
       <c r="D391" s="3">
-        <f>100%-F391</f>
+        <f t="shared" si="6"/>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="E391" s="4">
@@ -19548,7 +19548,7 @@
         <v>431</v>
       </c>
       <c r="D392" s="3">
-        <f>100%-F392</f>
+        <f t="shared" si="6"/>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="E392" s="4">
@@ -19590,7 +19590,7 @@
         <v>526</v>
       </c>
       <c r="D393" s="3">
-        <f>100%-F393</f>
+        <f t="shared" si="6"/>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="E393" s="4">
@@ -19632,7 +19632,7 @@
         <v>201</v>
       </c>
       <c r="D394" s="3">
-        <f>100%-F394</f>
+        <f t="shared" si="6"/>
         <v>0.38</v>
       </c>
       <c r="E394" s="4">
@@ -19674,7 +19674,7 @@
         <v>354</v>
       </c>
       <c r="D395" s="3">
-        <f>100%-F395</f>
+        <f t="shared" si="6"/>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="E395" s="4">
@@ -19716,7 +19716,7 @@
         <v>270</v>
       </c>
       <c r="D396" s="3">
-        <f>100%-F396</f>
+        <f t="shared" si="6"/>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E396" s="4">
@@ -19758,7 +19758,7 @@
         <v>571</v>
       </c>
       <c r="D397" s="3">
-        <f>100%-F397</f>
+        <f t="shared" si="6"/>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="E397" s="4">
@@ -19800,7 +19800,7 @@
         <v>106</v>
       </c>
       <c r="D398" s="3">
-        <f>100%-F398</f>
+        <f t="shared" si="6"/>
         <v>0.37</v>
       </c>
       <c r="E398" s="4">
@@ -19842,7 +19842,7 @@
         <v>372</v>
       </c>
       <c r="D399" s="3">
-        <f>100%-F399</f>
+        <f t="shared" si="6"/>
         <v>0.12</v>
       </c>
       <c r="E399" s="4">
@@ -19884,7 +19884,7 @@
         <v>182</v>
       </c>
       <c r="D400" s="3">
-        <f>100%-F400</f>
+        <f t="shared" si="6"/>
         <v>0.30000000000000004</v>
       </c>
       <c r="E400" s="4">
@@ -19926,7 +19926,7 @@
         <v>501</v>
       </c>
       <c r="D401" s="3">
-        <f>100%-F401</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="E401" s="4">
@@ -19968,7 +19968,7 @@
         <v>486</v>
       </c>
       <c r="D402" s="3">
-        <f>100%-F402</f>
+        <f t="shared" si="6"/>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="E402" s="4">
@@ -20010,7 +20010,7 @@
         <v>517</v>
       </c>
       <c r="D403" s="3">
-        <f>100%-F403</f>
+        <f t="shared" si="6"/>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E403" s="4">
@@ -20052,7 +20052,7 @@
         <v>252</v>
       </c>
       <c r="D404" s="3">
-        <f>100%-F404</f>
+        <f t="shared" si="6"/>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="E404" s="4">
@@ -20094,7 +20094,7 @@
         <v>310</v>
       </c>
       <c r="D405" s="3">
-        <f>100%-F405</f>
+        <f t="shared" si="6"/>
         <v>0.15000000000000002</v>
       </c>
       <c r="E405" s="4">
@@ -20136,7 +20136,7 @@
         <v>339</v>
       </c>
       <c r="D406" s="3">
-        <f>100%-F406</f>
+        <f t="shared" si="6"/>
         <v>0.17000000000000004</v>
       </c>
       <c r="E406" s="4">
@@ -20178,7 +20178,7 @@
         <v>178</v>
       </c>
       <c r="D407" s="3">
-        <f>100%-F407</f>
+        <f t="shared" si="6"/>
         <v>0.38</v>
       </c>
       <c r="E407" s="4">
@@ -20220,7 +20220,7 @@
         <v>173</v>
       </c>
       <c r="D408" s="3">
-        <f>100%-F408</f>
+        <f t="shared" si="6"/>
         <v>0.12</v>
       </c>
       <c r="E408" s="4">
@@ -20262,7 +20262,7 @@
         <v>515</v>
       </c>
       <c r="D409" s="3">
-        <f>100%-F409</f>
+        <f t="shared" si="6"/>
         <v>0.15000000000000002</v>
       </c>
       <c r="E409" s="4">
@@ -20304,7 +20304,7 @@
         <v>169</v>
       </c>
       <c r="D410" s="3">
-        <f>100%-F410</f>
+        <f t="shared" si="6"/>
         <v>0.4</v>
       </c>
       <c r="E410" s="4">
@@ -20346,7 +20346,7 @@
         <v>401</v>
       </c>
       <c r="D411" s="3">
-        <f>100%-F411</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="E411" s="4">
@@ -20388,7 +20388,7 @@
         <v>267</v>
       </c>
       <c r="D412" s="3">
-        <f>100%-F412</f>
+        <f t="shared" si="6"/>
         <v>0.12</v>
       </c>
       <c r="E412" s="4">
@@ -20430,7 +20430,7 @@
         <v>153</v>
       </c>
       <c r="D413" s="3">
-        <f>100%-F413</f>
+        <f t="shared" si="6"/>
         <v>0.17000000000000004</v>
       </c>
       <c r="E413" s="4">
@@ -20472,7 +20472,7 @@
         <v>125</v>
       </c>
       <c r="D414" s="3">
-        <f>100%-F414</f>
+        <f t="shared" si="6"/>
         <v>0.17000000000000004</v>
       </c>
       <c r="E414" s="4">
@@ -20514,7 +20514,7 @@
         <v>295</v>
       </c>
       <c r="D415" s="3">
-        <f>100%-F415</f>
+        <f t="shared" si="6"/>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="E415" s="4">
@@ -20556,7 +20556,7 @@
         <v>224</v>
       </c>
       <c r="D416" s="3">
-        <f>100%-F416</f>
+        <f t="shared" si="6"/>
         <v>0.12</v>
       </c>
       <c r="E416" s="4">
@@ -20598,7 +20598,7 @@
         <v>152</v>
       </c>
       <c r="D417" s="3">
-        <f>100%-F417</f>
+        <f t="shared" si="6"/>
         <v>0.44999999999999996</v>
       </c>
       <c r="E417" s="4">
@@ -20640,7 +20640,7 @@
         <v>193</v>
       </c>
       <c r="D418" s="3">
-        <f>100%-F418</f>
+        <f t="shared" si="6"/>
         <v>0.12</v>
       </c>
       <c r="E418" s="4">
@@ -20682,7 +20682,7 @@
         <v>4974</v>
       </c>
       <c r="D419" s="3">
-        <f>100%-F419</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="E419" s="4">
@@ -20724,7 +20724,7 @@
         <v>194</v>
       </c>
       <c r="D420" s="3">
-        <f>100%-F420</f>
+        <f t="shared" si="6"/>
         <v>0.4</v>
       </c>
       <c r="E420" s="4">
@@ -20766,7 +20766,7 @@
         <v>103</v>
       </c>
       <c r="D421" s="3">
-        <f>100%-F421</f>
+        <f t="shared" si="6"/>
         <v>0.17000000000000004</v>
       </c>
       <c r="E421" s="4">
@@ -20808,7 +20808,7 @@
         <v>210</v>
       </c>
       <c r="D422" s="3">
-        <f>100%-F422</f>
+        <f t="shared" si="6"/>
         <v>0.17000000000000004</v>
       </c>
       <c r="E422" s="4">
@@ -20850,7 +20850,7 @@
         <v>204</v>
       </c>
       <c r="D423" s="3">
-        <f>100%-F423</f>
+        <f t="shared" si="6"/>
         <v>0.15000000000000002</v>
       </c>
       <c r="E423" s="4">
@@ -20892,7 +20892,7 @@
         <v>220</v>
       </c>
       <c r="D424" s="3">
-        <f>100%-F424</f>
+        <f t="shared" si="6"/>
         <v>0.12</v>
       </c>
       <c r="E424" s="4">
@@ -20934,7 +20934,7 @@
         <v>252</v>
       </c>
       <c r="D425" s="3">
-        <f>100%-F425</f>
+        <f t="shared" si="6"/>
         <v>0.4</v>
       </c>
       <c r="E425" s="4">
@@ -20976,7 +20976,7 @@
         <v>140</v>
       </c>
       <c r="D426" s="3">
-        <f>100%-F426</f>
+        <f t="shared" si="6"/>
         <v>0.44999999999999996</v>
       </c>
       <c r="E426" s="4">
@@ -21018,7 +21018,7 @@
         <v>104</v>
       </c>
       <c r="D427" s="3">
-        <f>100%-F427</f>
+        <f t="shared" si="6"/>
         <v>0.44999999999999996</v>
       </c>
       <c r="E427" s="4">
@@ -21060,7 +21060,7 @@
         <v>262</v>
       </c>
       <c r="D428" s="3">
-        <f>100%-F428</f>
+        <f t="shared" si="6"/>
         <v>0.38</v>
       </c>
       <c r="E428" s="4">
@@ -21102,7 +21102,7 @@
         <v>120</v>
       </c>
       <c r="D429" s="3">
-        <f>100%-F429</f>
+        <f t="shared" si="6"/>
         <v>0.31999999999999995</v>
       </c>
       <c r="E429" s="4">
@@ -21144,7 +21144,7 @@
         <v>363</v>
       </c>
       <c r="D430" s="3">
-        <f>100%-F430</f>
+        <f t="shared" si="6"/>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="E430" s="4">
@@ -21186,7 +21186,7 @@
         <v>107</v>
       </c>
       <c r="D431" s="3">
-        <f>100%-F431</f>
+        <f t="shared" si="6"/>
         <v>0.8</v>
       </c>
       <c r="E431" s="4">
@@ -21228,7 +21228,7 @@
         <v>519</v>
       </c>
       <c r="D432" s="3">
-        <f>100%-F432</f>
+        <f t="shared" si="6"/>
         <v>0.18000000000000005</v>
       </c>
       <c r="E432" s="4">
@@ -21270,7 +21270,7 @@
         <v>194</v>
       </c>
       <c r="D433" s="3">
-        <f>100%-F433</f>
+        <f t="shared" si="6"/>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E433" s="4">
@@ -21312,7 +21312,7 @@
         <v>334</v>
       </c>
       <c r="D434" s="3">
-        <f>100%-F434</f>
+        <f t="shared" si="6"/>
         <v>0.18000000000000005</v>
       </c>
       <c r="E434" s="4">
@@ -21354,7 +21354,7 @@
         <v>144</v>
       </c>
       <c r="D435" s="3">
-        <f>100%-F435</f>
+        <f t="shared" si="6"/>
         <v>0.15000000000000002</v>
       </c>
       <c r="E435" s="4">
@@ -21396,7 +21396,7 @@
         <v>131</v>
       </c>
       <c r="D436" s="3">
-        <f>100%-F436</f>
+        <f t="shared" si="6"/>
         <v>0.30000000000000004</v>
       </c>
       <c r="E436" s="4">
@@ -21438,7 +21438,7 @@
         <v>138</v>
       </c>
       <c r="D437" s="3">
-        <f>100%-F437</f>
+        <f t="shared" si="6"/>
         <v>0.22999999999999998</v>
       </c>
       <c r="E437" s="4">
@@ -21480,7 +21480,7 @@
         <v>406</v>
       </c>
       <c r="D438" s="3">
-        <f>100%-F438</f>
+        <f t="shared" si="6"/>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E438" s="4">
@@ -21523,7 +21523,7 @@
         <v>481</v>
       </c>
       <c r="D439" s="3">
-        <f>100%-F439</f>
+        <f t="shared" si="6"/>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E439" s="4">
@@ -21565,7 +21565,7 @@
         <v>459</v>
       </c>
       <c r="D440" s="3">
-        <f>100%-F440</f>
+        <f t="shared" si="6"/>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E440" s="4">
@@ -21607,7 +21607,7 @@
         <v>126</v>
       </c>
       <c r="D441" s="3">
-        <f>100%-F441</f>
+        <f t="shared" si="6"/>
         <v>0.37</v>
       </c>
       <c r="E441" s="4">
@@ -21649,7 +21649,7 @@
         <v>1793</v>
       </c>
       <c r="D442" s="3">
-        <f>100%-F442</f>
+        <f t="shared" si="6"/>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E442" s="4">
@@ -21691,7 +21691,7 @@
         <v>490</v>
       </c>
       <c r="D443" s="3">
-        <f>100%-F443</f>
+        <f t="shared" si="6"/>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E443" s="4">
@@ -21733,7 +21733,7 @@
         <v>156</v>
       </c>
       <c r="D444" s="3">
-        <f>100%-F444</f>
+        <f t="shared" si="6"/>
         <v>0.37</v>
       </c>
       <c r="E444" s="4">
@@ -21775,7 +21775,7 @@
         <v>129</v>
       </c>
       <c r="D445" s="3">
-        <f>100%-F445</f>
+        <f t="shared" si="6"/>
         <v>0.37</v>
       </c>
       <c r="E445" s="4">
@@ -21817,7 +21817,7 @@
         <v>757</v>
       </c>
       <c r="D446" s="3">
-        <f>100%-F446</f>
+        <f t="shared" si="6"/>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E446" s="4">
@@ -21860,11 +21860,11 @@
         <v>579</v>
       </c>
       <c r="D447" s="3">
-        <f>100%-F447</f>
+        <f t="shared" si="6"/>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E447" s="4">
-        <f t="shared" ref="E447:E448" si="0">I447*2%</f>
+        <f t="shared" ref="E447:E448" si="7">I447*2%</f>
         <v>0.02</v>
       </c>
       <c r="F447" s="4">
@@ -21903,11 +21903,11 @@
         <v>623</v>
       </c>
       <c r="D448" s="3">
-        <f>100%-F448</f>
+        <f t="shared" si="6"/>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E448" s="4">
-        <f t="shared" si="0"/>
+        <f t="shared" si="7"/>
         <v>0.02</v>
       </c>
       <c r="F448" s="4">
@@ -21946,7 +21946,7 @@
         <v>163</v>
       </c>
       <c r="D449" s="3">
-        <f>100%-F449</f>
+        <f t="shared" si="6"/>
         <v>0.17000000000000004</v>
       </c>
       <c r="E449" s="4">
@@ -21988,7 +21988,7 @@
         <v>166</v>
       </c>
       <c r="D450" s="3">
-        <f>100%-F450</f>
+        <f t="shared" ref="D450:D513" si="8">100%-F450</f>
         <v>0.22999999999999998</v>
       </c>
       <c r="E450" s="4">
@@ -22030,7 +22030,7 @@
         <v>654</v>
       </c>
       <c r="D451" s="3">
-        <f>100%-F451</f>
+        <f t="shared" si="8"/>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="E451" s="4">
@@ -22072,7 +22072,7 @@
         <v>510</v>
       </c>
       <c r="D452" s="3">
-        <f>100%-F452</f>
+        <f t="shared" si="8"/>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E452" s="4">
@@ -22114,7 +22114,7 @@
         <v>525</v>
       </c>
       <c r="D453" s="3">
-        <f>100%-F453</f>
+        <f t="shared" si="8"/>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E453" s="4">
@@ -22156,7 +22156,7 @@
         <v>539</v>
       </c>
       <c r="D454" s="3">
-        <f>100%-F454</f>
+        <f t="shared" si="8"/>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E454" s="4">
@@ -22199,7 +22199,7 @@
         <v>410</v>
       </c>
       <c r="D455" s="3">
-        <f>100%-F455</f>
+        <f t="shared" si="8"/>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E455" s="4">
@@ -22241,7 +22241,7 @@
         <v>13147</v>
       </c>
       <c r="D456" s="3">
-        <f>100%-F456</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="E456" s="4">
@@ -22283,7 +22283,7 @@
         <v>338</v>
       </c>
       <c r="D457" s="3">
-        <f>100%-F457</f>
+        <f t="shared" si="8"/>
         <v>0.25</v>
       </c>
       <c r="E457" s="4">
@@ -22325,7 +22325,7 @@
         <v>786</v>
       </c>
       <c r="D458" s="3">
-        <f>100%-F458</f>
+        <f t="shared" si="8"/>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E458" s="4">
@@ -22367,7 +22367,7 @@
         <v>120</v>
       </c>
       <c r="D459" s="3">
-        <f>100%-F459</f>
+        <f t="shared" si="8"/>
         <v>0.31999999999999995</v>
       </c>
       <c r="E459" s="4">
@@ -22409,7 +22409,7 @@
         <v>103</v>
       </c>
       <c r="D460" s="3">
-        <f>100%-F460</f>
+        <f t="shared" si="8"/>
         <v>0.30000000000000004</v>
       </c>
       <c r="E460" s="4">
@@ -22451,7 +22451,7 @@
         <v>2406</v>
       </c>
       <c r="D461" s="3">
-        <f>100%-F461</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="E461" s="4">
@@ -22493,7 +22493,7 @@
         <v>217</v>
       </c>
       <c r="D462" s="3">
-        <f>100%-F462</f>
+        <f t="shared" si="8"/>
         <v>0.30000000000000004</v>
       </c>
       <c r="E462" s="4">
@@ -22535,7 +22535,7 @@
         <v>715</v>
       </c>
       <c r="D463" s="3">
-        <f>100%-F463</f>
+        <f t="shared" si="8"/>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E463" s="4">
@@ -22577,7 +22577,7 @@
         <v>213</v>
       </c>
       <c r="D464" s="3">
-        <f>100%-F464</f>
+        <f t="shared" si="8"/>
         <v>0.18999999999999995</v>
       </c>
       <c r="E464" s="4">
@@ -22619,7 +22619,7 @@
         <v>497</v>
       </c>
       <c r="D465" s="3">
-        <f>100%-F465</f>
+        <f t="shared" si="8"/>
         <v>0.22999999999999998</v>
       </c>
       <c r="E465" s="4">
@@ -22661,7 +22661,7 @@
         <v>408</v>
       </c>
       <c r="D466" s="3">
-        <f>100%-F466</f>
+        <f t="shared" si="8"/>
         <v>0.22999999999999998</v>
       </c>
       <c r="E466" s="4">
@@ -22703,7 +22703,7 @@
         <v>5696</v>
       </c>
       <c r="D467" s="3">
-        <f>100%-F467</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="E467" s="4">
@@ -22745,7 +22745,7 @@
         <v>222</v>
       </c>
       <c r="D468" s="3">
-        <f>100%-F468</f>
+        <f t="shared" si="8"/>
         <v>0.25</v>
       </c>
       <c r="E468" s="4">
@@ -22787,7 +22787,7 @@
         <v>175</v>
       </c>
       <c r="D469" s="3">
-        <f>100%-F469</f>
+        <f t="shared" si="8"/>
         <v>0.22999999999999998</v>
       </c>
       <c r="E469" s="4">
@@ -22829,7 +22829,7 @@
         <v>776</v>
       </c>
       <c r="D470" s="3">
-        <f>100%-F470</f>
+        <f t="shared" si="8"/>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E470" s="4">
@@ -22871,7 +22871,7 @@
         <v>418</v>
       </c>
       <c r="D471" s="3">
-        <f>100%-F471</f>
+        <f t="shared" si="8"/>
         <v>0.22999999999999998</v>
       </c>
       <c r="E471" s="4">
@@ -22913,7 +22913,7 @@
         <v>201</v>
       </c>
       <c r="D472" s="3">
-        <f>100%-F472</f>
+        <f t="shared" si="8"/>
         <v>0.10999999999999999</v>
       </c>
       <c r="E472" s="4">
@@ -22955,7 +22955,7 @@
         <v>773</v>
       </c>
       <c r="D473" s="3">
-        <f>100%-F473</f>
+        <f t="shared" si="8"/>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E473" s="4">
@@ -22997,7 +22997,7 @@
         <v>175</v>
       </c>
       <c r="D474" s="3">
-        <f>100%-F474</f>
+        <f t="shared" si="8"/>
         <v>0.25</v>
       </c>
       <c r="E474" s="4">
@@ -23039,7 +23039,7 @@
         <v>135</v>
       </c>
       <c r="D475" s="3">
-        <f>100%-F475</f>
+        <f t="shared" si="8"/>
         <v>0.4</v>
       </c>
       <c r="E475" s="4">
@@ -23081,7 +23081,7 @@
         <v>352</v>
       </c>
       <c r="D476" s="3">
-        <f>100%-F476</f>
+        <f t="shared" si="8"/>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E476" s="4">
@@ -23123,7 +23123,7 @@
         <v>405</v>
       </c>
       <c r="D477" s="3">
-        <f>100%-F477</f>
+        <f t="shared" si="8"/>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E477" s="4">
@@ -23165,7 +23165,7 @@
         <v>986</v>
       </c>
       <c r="D478" s="3">
-        <f>100%-F478</f>
+        <f t="shared" si="8"/>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E478" s="4">
@@ -23207,7 +23207,7 @@
         <v>454</v>
       </c>
       <c r="D479" s="3">
-        <f>100%-F479</f>
+        <f t="shared" si="8"/>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E479" s="4">
@@ -23249,7 +23249,7 @@
         <v>133</v>
       </c>
       <c r="D480" s="3">
-        <f>100%-F480</f>
+        <f t="shared" si="8"/>
         <v>0.65</v>
       </c>
       <c r="E480" s="4">
@@ -23291,7 +23291,7 @@
         <v>857</v>
       </c>
       <c r="D481" s="3">
-        <f>100%-F481</f>
+        <f t="shared" si="8"/>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="E481" s="4">
@@ -23333,7 +23333,7 @@
         <v>238</v>
       </c>
       <c r="D482" s="3">
-        <f>100%-F482</f>
+        <f t="shared" si="8"/>
         <v>0.30000000000000004</v>
       </c>
       <c r="E482" s="4">
@@ -23375,7 +23375,7 @@
         <v>307</v>
       </c>
       <c r="D483" s="3">
-        <f>100%-F483</f>
+        <f t="shared" si="8"/>
         <v>0.22999999999999998</v>
       </c>
       <c r="E483" s="4">
@@ -23417,7 +23417,7 @@
         <v>7448</v>
       </c>
       <c r="D484" s="3">
-        <f>100%-F484</f>
+        <f t="shared" si="8"/>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E484" s="4">
@@ -23459,7 +23459,7 @@
         <v>159</v>
       </c>
       <c r="D485" s="3">
-        <f>100%-F485</f>
+        <f t="shared" si="8"/>
         <v>0.28000000000000003</v>
       </c>
       <c r="E485" s="4">
@@ -23501,7 +23501,7 @@
         <v>453</v>
       </c>
       <c r="D486" s="3">
-        <f>100%-F486</f>
+        <f t="shared" si="8"/>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E486" s="4">
@@ -23543,7 +23543,7 @@
         <v>437</v>
       </c>
       <c r="D487" s="3">
-        <f>100%-F487</f>
+        <f t="shared" si="8"/>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E487" s="4">
@@ -23585,7 +23585,7 @@
         <v>4178</v>
       </c>
       <c r="D488" s="3">
-        <f>100%-F488</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="E488" s="4">
@@ -23627,7 +23627,7 @@
         <v>9691</v>
       </c>
       <c r="D489" s="3">
-        <f>100%-F489</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="E489" s="4">
@@ -23669,7 +23669,7 @@
         <v>355</v>
       </c>
       <c r="D490" s="3">
-        <f>100%-F490</f>
+        <f t="shared" si="8"/>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E490" s="4">
@@ -23711,7 +23711,7 @@
         <v>504</v>
       </c>
       <c r="D491" s="3">
-        <f>100%-F491</f>
+        <f t="shared" si="8"/>
         <v>0.25</v>
       </c>
       <c r="E491" s="4">
@@ -23753,7 +23753,7 @@
         <v>273</v>
       </c>
       <c r="D492" s="3">
-        <f>100%-F492</f>
+        <f t="shared" si="8"/>
         <v>0.30000000000000004</v>
       </c>
       <c r="E492" s="4">
@@ -23795,7 +23795,7 @@
         <v>666</v>
       </c>
       <c r="D493" s="3">
-        <f>100%-F493</f>
+        <f t="shared" si="8"/>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E493" s="4">
@@ -23837,7 +23837,7 @@
         <v>3482</v>
       </c>
       <c r="D494" s="3">
-        <f>100%-F494</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="E494" s="4">
@@ -23879,7 +23879,7 @@
         <v>2213</v>
       </c>
       <c r="D495" s="3">
-        <f>100%-F495</f>
+        <f t="shared" si="8"/>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E495" s="4">
@@ -23921,7 +23921,7 @@
         <v>233</v>
       </c>
       <c r="D496" s="3">
-        <f>100%-F496</f>
+        <f t="shared" si="8"/>
         <v>0.30000000000000004</v>
       </c>
       <c r="E496" s="4">
@@ -23963,7 +23963,7 @@
         <v>312</v>
       </c>
       <c r="D497" s="3">
-        <f>100%-F497</f>
+        <f t="shared" si="8"/>
         <v>0.30000000000000004</v>
       </c>
       <c r="E497" s="4">
@@ -24005,7 +24005,7 @@
         <v>687</v>
       </c>
       <c r="D498" s="3">
-        <f>100%-F498</f>
+        <f t="shared" si="8"/>
         <v>0.15000000000000002</v>
       </c>
       <c r="E498" s="4">
@@ -24047,7 +24047,7 @@
         <v>9242</v>
       </c>
       <c r="D499" s="3">
-        <f>100%-F499</f>
+        <f t="shared" si="8"/>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E499" s="4">
@@ -24089,7 +24089,7 @@
         <v>862</v>
       </c>
       <c r="D500" s="3">
-        <f>100%-F500</f>
+        <f t="shared" si="8"/>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="E500" s="4">
@@ -24131,7 +24131,7 @@
         <v>439</v>
       </c>
       <c r="D501" s="3">
-        <f>100%-F501</f>
+        <f t="shared" si="8"/>
         <v>0.37</v>
       </c>
       <c r="E501" s="4">
@@ -24173,7 +24173,7 @@
         <v>4599</v>
       </c>
       <c r="D502" s="3">
-        <f>100%-F502</f>
+        <f t="shared" si="8"/>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E502" s="4">
@@ -24215,7 +24215,7 @@
         <v>586</v>
       </c>
       <c r="D503" s="3">
-        <f>100%-F503</f>
+        <f t="shared" si="8"/>
         <v>0.25</v>
       </c>
       <c r="E503" s="4">
@@ -24257,7 +24257,7 @@
         <v>354</v>
       </c>
       <c r="D504" s="3">
-        <f>100%-F504</f>
+        <f t="shared" si="8"/>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E504" s="4">
@@ -24299,7 +24299,7 @@
         <v>3589</v>
       </c>
       <c r="D505" s="3">
-        <f>100%-F505</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="E505" s="4">
@@ -24341,7 +24341,7 @@
         <v>653</v>
       </c>
       <c r="D506" s="3">
-        <f>100%-F506</f>
+        <f t="shared" si="8"/>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E506" s="4">
@@ -24383,7 +24383,7 @@
         <v>4220</v>
       </c>
       <c r="D507" s="3">
-        <f>100%-F507</f>
+        <f t="shared" si="8"/>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="E507" s="4">
@@ -24425,7 +24425,7 @@
         <v>270</v>
       </c>
       <c r="D508" s="3">
-        <f>100%-F508</f>
+        <f t="shared" si="8"/>
         <v>0.19999999999999996</v>
       </c>
       <c r="E508" s="4">
@@ -24467,7 +24467,7 @@
         <v>1516</v>
       </c>
       <c r="D509" s="3">
-        <f>100%-F509</f>
+        <f t="shared" si="8"/>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E509" s="4">
@@ -24509,7 +24509,7 @@
         <v>1000.9999999999999</v>
       </c>
       <c r="D510" s="3">
-        <f>100%-F510</f>
+        <f t="shared" si="8"/>
         <v>0.15000000000000002</v>
       </c>
       <c r="E510" s="4">
@@ -24551,7 +24551,7 @@
         <v>6949</v>
       </c>
       <c r="D511" s="3">
-        <f>100%-F511</f>
+        <f t="shared" si="8"/>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E511" s="4">
@@ -24593,7 +24593,7 @@
         <v>2625</v>
       </c>
       <c r="D512" s="3">
-        <f>100%-F512</f>
+        <f t="shared" si="8"/>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E512" s="4">
@@ -24635,7 +24635,7 @@
         <v>3346</v>
       </c>
       <c r="D513" s="3">
-        <f>100%-F513</f>
+        <f t="shared" si="8"/>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="E513" s="4">
@@ -24677,7 +24677,7 @@
         <v>1242</v>
       </c>
       <c r="D514" s="3">
-        <f>100%-F514</f>
+        <f t="shared" ref="D514:D577" si="9">100%-F514</f>
         <v>0.30000000000000004</v>
       </c>
       <c r="E514" s="4">
@@ -24719,7 +24719,7 @@
         <v>3480</v>
       </c>
       <c r="D515" s="3">
-        <f>100%-F515</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="E515" s="4">
@@ -24761,7 +24761,7 @@
         <v>1684</v>
       </c>
       <c r="D516" s="3">
-        <f>100%-F516</f>
+        <f t="shared" si="9"/>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E516" s="4">
@@ -24803,7 +24803,7 @@
         <v>6232</v>
       </c>
       <c r="D517" s="3">
-        <f>100%-F517</f>
+        <f t="shared" si="9"/>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E517" s="4">
@@ -24845,7 +24845,7 @@
         <v>2191</v>
       </c>
       <c r="D518" s="3">
-        <f>100%-F518</f>
+        <f t="shared" si="9"/>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E518" s="4">
@@ -24887,7 +24887,7 @@
         <v>1282</v>
       </c>
       <c r="D519" s="3">
-        <f>100%-F519</f>
+        <f t="shared" si="9"/>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E519" s="4">
@@ -24929,7 +24929,7 @@
         <v>177</v>
       </c>
       <c r="D520" s="3">
-        <f>100%-F520</f>
+        <f t="shared" si="9"/>
         <v>0.26</v>
       </c>
       <c r="E520" s="4">
@@ -24971,7 +24971,7 @@
         <v>5656</v>
       </c>
       <c r="D521" s="3">
-        <f>100%-F521</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="E521" s="4">
@@ -25013,7 +25013,7 @@
         <v>339</v>
       </c>
       <c r="D522" s="3">
-        <f>100%-F522</f>
+        <f t="shared" si="9"/>
         <v>0.30000000000000004</v>
       </c>
       <c r="E522" s="4">
@@ -25055,7 +25055,7 @@
         <v>1246</v>
       </c>
       <c r="D523" s="3">
-        <f>100%-F523</f>
+        <f t="shared" si="9"/>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="E523" s="4">
@@ -25097,7 +25097,7 @@
         <v>2000</v>
       </c>
       <c r="D524" s="3">
-        <f>100%-F524</f>
+        <f t="shared" si="9"/>
         <v>6.0000000000000053E-2</v>
       </c>
       <c r="E524" s="4">
@@ -25139,7 +25139,7 @@
         <v>276</v>
       </c>
       <c r="D525" s="3">
-        <f>100%-F525</f>
+        <f t="shared" si="9"/>
         <v>0.44999999999999996</v>
       </c>
       <c r="E525" s="4">
@@ -25181,7 +25181,7 @@
         <v>1126</v>
       </c>
       <c r="D526" s="3">
-        <f>100%-F526</f>
+        <f t="shared" si="9"/>
         <v>0.28000000000000003</v>
       </c>
       <c r="E526" s="4">
@@ -25223,7 +25223,7 @@
         <v>3690</v>
       </c>
       <c r="D527" s="3">
-        <f>100%-F527</f>
+        <f t="shared" si="9"/>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E527" s="4">
@@ -25265,7 +25265,7 @@
         <v>11874</v>
       </c>
       <c r="D528" s="3">
-        <f>100%-F528</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="E528" s="4">
@@ -25307,7 +25307,7 @@
         <v>6545</v>
       </c>
       <c r="D529" s="3">
-        <f>100%-F529</f>
+        <f t="shared" si="9"/>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E529" s="4">
@@ -25349,7 +25349,7 @@
         <v>284</v>
       </c>
       <c r="D530" s="3">
-        <f>100%-F530</f>
+        <f t="shared" si="9"/>
         <v>0.30000000000000004</v>
       </c>
       <c r="E530" s="4">
@@ -25391,7 +25391,7 @@
         <v>1989</v>
       </c>
       <c r="D531" s="3">
-        <f>100%-F531</f>
+        <f t="shared" si="9"/>
         <v>8.9999999999999969E-2</v>
       </c>
       <c r="E531" s="4">
@@ -25433,7 +25433,7 @@
         <v>2454</v>
       </c>
       <c r="D532" s="3">
-        <f>100%-F532</f>
+        <f t="shared" si="9"/>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E532" s="4">
@@ -25475,7 +25475,7 @@
         <v>206</v>
       </c>
       <c r="D533" s="3">
-        <f>100%-F533</f>
+        <f t="shared" si="9"/>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E533" s="4">
@@ -25517,7 +25517,7 @@
         <v>679</v>
       </c>
       <c r="D534" s="3">
-        <f>100%-F534</f>
+        <f t="shared" si="9"/>
         <v>0.26</v>
       </c>
       <c r="E534" s="4">
@@ -25559,7 +25559,7 @@
         <v>339</v>
       </c>
       <c r="D535" s="3">
-        <f>100%-F535</f>
+        <f t="shared" si="9"/>
         <v>0.37</v>
       </c>
       <c r="E535" s="4">
@@ -25601,7 +25601,7 @@
         <v>8324</v>
       </c>
       <c r="D536" s="3">
-        <f>100%-F536</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="E536" s="4">
@@ -25643,7 +25643,7 @@
         <v>614</v>
       </c>
       <c r="D537" s="3">
-        <f>100%-F537</f>
+        <f t="shared" si="9"/>
         <v>0.30000000000000004</v>
       </c>
       <c r="E537" s="4">
@@ -25685,7 +25685,7 @@
         <v>174</v>
       </c>
       <c r="D538" s="3">
-        <f>100%-F538</f>
+        <f t="shared" si="9"/>
         <v>0.37</v>
       </c>
       <c r="E538" s="4">
@@ -25727,7 +25727,7 @@
         <v>2402</v>
       </c>
       <c r="D539" s="3">
-        <f>100%-F539</f>
+        <f t="shared" si="9"/>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="E539" s="4">
@@ -25769,7 +25769,7 @@
         <v>400</v>
       </c>
       <c r="D540" s="3">
-        <f>100%-F540</f>
+        <f t="shared" si="9"/>
         <v>0.30000000000000004</v>
       </c>
       <c r="E540" s="4">
@@ -25811,7 +25811,7 @@
         <v>384</v>
       </c>
       <c r="D541" s="3">
-        <f>100%-F541</f>
+        <f t="shared" si="9"/>
         <v>0.22999999999999998</v>
       </c>
       <c r="E541" s="4">
@@ -25853,7 +25853,7 @@
         <v>153</v>
       </c>
       <c r="D542" s="3">
-        <f>100%-F542</f>
+        <f t="shared" si="9"/>
         <v>0.30000000000000004</v>
       </c>
       <c r="E542" s="4">
@@ -25895,7 +25895,7 @@
         <v>1541</v>
       </c>
       <c r="D543" s="3">
-        <f>100%-F543</f>
+        <f t="shared" si="9"/>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E543" s="4">
@@ -25937,7 +25937,7 @@
         <v>1456</v>
       </c>
       <c r="D544" s="3">
-        <f>100%-F544</f>
+        <f t="shared" si="9"/>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="E544" s="4">
@@ -25979,7 +25979,7 @@
         <v>627</v>
       </c>
       <c r="D545" s="3">
-        <f>100%-F545</f>
+        <f t="shared" si="9"/>
         <v>0.22999999999999998</v>
       </c>
       <c r="E545" s="4">
@@ -26021,7 +26021,7 @@
         <v>864</v>
       </c>
       <c r="D546" s="3">
-        <f>100%-F546</f>
+        <f t="shared" si="9"/>
         <v>0.22999999999999998</v>
       </c>
       <c r="E546" s="4">
@@ -26063,7 +26063,7 @@
         <v>999</v>
       </c>
       <c r="D547" s="3">
-        <f>100%-F547</f>
+        <f t="shared" si="9"/>
         <v>0.15000000000000002</v>
       </c>
       <c r="E547" s="4">
@@ -26105,7 +26105,7 @@
         <v>1422</v>
       </c>
       <c r="D548" s="3">
-        <f>100%-F548</f>
+        <f t="shared" si="9"/>
         <v>0.22999999999999998</v>
       </c>
       <c r="E548" s="4">
@@ -26147,7 +26147,7 @@
         <v>2518</v>
       </c>
       <c r="D549" s="3">
-        <f>100%-F549</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="E549" s="4">
@@ -26189,7 +26189,7 @@
         <v>5547</v>
       </c>
       <c r="D550" s="3">
-        <f>100%-F550</f>
+        <f t="shared" si="9"/>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E550" s="4">
@@ -26231,7 +26231,7 @@
         <v>29086</v>
       </c>
       <c r="D551" s="3">
-        <f>100%-F551</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="E551" s="4">
@@ -26273,7 +26273,7 @@
         <v>453</v>
       </c>
       <c r="D552" s="3">
-        <f>100%-F552</f>
+        <f t="shared" si="9"/>
         <v>0.31999999999999995</v>
       </c>
       <c r="E552" s="4">
@@ -26315,7 +26315,7 @@
         <v>571</v>
       </c>
       <c r="D553" s="3">
-        <f>100%-F553</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="E553" s="4">
@@ -26357,7 +26357,7 @@
         <v>631</v>
       </c>
       <c r="D554" s="3">
-        <f>100%-F554</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="E554" s="4">
@@ -26399,7 +26399,7 @@
         <v>107</v>
       </c>
       <c r="D555" s="3">
-        <f>100%-F555</f>
+        <f t="shared" si="9"/>
         <v>0.37</v>
       </c>
       <c r="E555" s="4">
@@ -26441,7 +26441,7 @@
         <v>127</v>
       </c>
       <c r="D556" s="3">
-        <f>100%-F556</f>
+        <f t="shared" si="9"/>
         <v>0.30000000000000004</v>
       </c>
       <c r="E556" s="4">
@@ -26483,7 +26483,7 @@
         <v>244</v>
       </c>
       <c r="D557" s="3">
-        <f>100%-F557</f>
+        <f t="shared" si="9"/>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E557" s="4">
@@ -26525,7 +26525,7 @@
         <v>385</v>
       </c>
       <c r="D558" s="3">
-        <f>100%-F558</f>
+        <f t="shared" si="9"/>
         <v>0.22999999999999998</v>
       </c>
       <c r="E558" s="4">
@@ -26567,7 +26567,7 @@
         <v>735</v>
       </c>
       <c r="D559" s="3">
-        <f>100%-F559</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="E559" s="4">
@@ -26609,7 +26609,7 @@
         <v>126</v>
       </c>
       <c r="D560" s="3">
-        <f>100%-F560</f>
+        <f t="shared" si="9"/>
         <v>0.15000000000000002</v>
       </c>
       <c r="E560" s="4">
@@ -26651,7 +26651,7 @@
         <v>168</v>
       </c>
       <c r="D561" s="3">
-        <f>100%-F561</f>
+        <f t="shared" si="9"/>
         <v>0.30000000000000004</v>
       </c>
       <c r="E561" s="4">
@@ -26693,7 +26693,7 @@
         <v>638</v>
       </c>
       <c r="D562" s="3">
-        <f>100%-F562</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="E562" s="4">
@@ -26735,7 +26735,7 @@
         <v>637</v>
       </c>
       <c r="D563" s="3">
-        <f>100%-F563</f>
+        <f t="shared" si="9"/>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="E563" s="4">
@@ -26777,7 +26777,7 @@
         <v>1266</v>
       </c>
       <c r="D564" s="3">
-        <f>100%-F564</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="E564" s="4">
@@ -26819,7 +26819,7 @@
         <v>1372</v>
       </c>
       <c r="D565" s="3">
-        <f>100%-F565</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="E565" s="4">
@@ -26861,7 +26861,7 @@
         <v>1033</v>
       </c>
       <c r="D566" s="3">
-        <f>100%-F566</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="E566" s="4">
@@ -26903,7 +26903,7 @@
         <v>954</v>
       </c>
       <c r="D567" s="3">
-        <f>100%-F567</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="E567" s="4">
@@ -26945,7 +26945,7 @@
         <v>243</v>
       </c>
       <c r="D568" s="3">
-        <f>100%-F568</f>
+        <f t="shared" si="9"/>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E568" s="4">
@@ -26987,7 +26987,7 @@
         <v>104</v>
       </c>
       <c r="D569" s="3">
-        <f>100%-F569</f>
+        <f t="shared" si="9"/>
         <v>0.36</v>
       </c>
       <c r="E569" s="4">
@@ -27029,7 +27029,7 @@
         <v>978</v>
       </c>
       <c r="D570" s="3">
-        <f>100%-F570</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="E570" s="4">
@@ -27071,7 +27071,7 @@
         <v>1431</v>
       </c>
       <c r="D571" s="3">
-        <f>100%-F571</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="E571" s="4">
@@ -27113,7 +27113,7 @@
         <v>140</v>
       </c>
       <c r="D572" s="3">
-        <f>100%-F572</f>
+        <f t="shared" si="9"/>
         <v>0.30000000000000004</v>
       </c>
       <c r="E572" s="4">
@@ -27155,7 +27155,7 @@
         <v>639</v>
       </c>
       <c r="D573" s="3">
-        <f>100%-F573</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="E573" s="4">
@@ -27197,7 +27197,7 @@
         <v>1550</v>
       </c>
       <c r="D574" s="3">
-        <f>100%-F574</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="E574" s="4">
@@ -27239,7 +27239,7 @@
         <v>115</v>
       </c>
       <c r="D575" s="3">
-        <f>100%-F575</f>
+        <f t="shared" si="9"/>
         <v>0.38</v>
       </c>
       <c r="E575" s="4">
@@ -27281,7 +27281,7 @@
         <v>506</v>
       </c>
       <c r="D576" s="3">
-        <f>100%-F576</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="E576" s="4">
@@ -27323,7 +27323,7 @@
         <v>217</v>
       </c>
       <c r="D577" s="3">
-        <f>100%-F577</f>
+        <f t="shared" si="9"/>
         <v>0.37</v>
       </c>
       <c r="E577" s="4">
@@ -27365,7 +27365,7 @@
         <v>340</v>
       </c>
       <c r="D578" s="3">
-        <f>100%-F578</f>
+        <f t="shared" ref="D578:D641" si="10">100%-F578</f>
         <v>0.20999999999999996</v>
       </c>
       <c r="E578" s="4">
@@ -27407,7 +27407,7 @@
         <v>2940</v>
       </c>
       <c r="D579" s="3">
-        <f>100%-F579</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="E579" s="4">
@@ -27449,7 +27449,7 @@
         <v>661</v>
       </c>
       <c r="D580" s="3">
-        <f>100%-F580</f>
+        <f t="shared" si="10"/>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="E580" s="4">
@@ -27491,7 +27491,7 @@
         <v>217</v>
       </c>
       <c r="D581" s="3">
-        <f>100%-F581</f>
+        <f t="shared" si="10"/>
         <v>0.30000000000000004</v>
       </c>
       <c r="E581" s="4">
@@ -27533,7 +27533,7 @@
         <v>581</v>
       </c>
       <c r="D582" s="3">
-        <f>100%-F582</f>
+        <f t="shared" si="10"/>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="E582" s="4">
@@ -27575,7 +27575,7 @@
         <v>1278</v>
       </c>
       <c r="D583" s="3">
-        <f>100%-F583</f>
+        <f t="shared" si="10"/>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E583" s="4">
@@ -27617,7 +27617,7 @@
         <v>2691</v>
       </c>
       <c r="D584" s="3">
-        <f>100%-F584</f>
+        <f t="shared" si="10"/>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E584" s="4">
@@ -27659,7 +27659,7 @@
         <v>9455</v>
       </c>
       <c r="D585" s="3">
-        <f>100%-F585</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="E585" s="4">
@@ -27701,7 +27701,7 @@
         <v>20862</v>
       </c>
       <c r="D586" s="9">
-        <f>100%-F586</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="E586" s="10">
@@ -27744,7 +27744,7 @@
         <v>190</v>
       </c>
       <c r="D587" s="3">
-        <f>100%-F587</f>
+        <f t="shared" si="10"/>
         <v>0.17000000000000004</v>
       </c>
       <c r="E587" s="4">
@@ -27786,7 +27786,7 @@
         <v>209</v>
       </c>
       <c r="D588" s="3">
-        <f>100%-F588</f>
+        <f t="shared" si="10"/>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E588" s="4">
@@ -27828,7 +27828,7 @@
         <v>216</v>
       </c>
       <c r="D589" s="3">
-        <f>100%-F589</f>
+        <f t="shared" si="10"/>
         <v>0.22999999999999998</v>
       </c>
       <c r="E589" s="4">
@@ -27870,7 +27870,7 @@
         <v>143</v>
       </c>
       <c r="D590" s="3">
-        <f>100%-F590</f>
+        <f t="shared" si="10"/>
         <v>0.15000000000000002</v>
       </c>
       <c r="E590" s="4">
@@ -27912,7 +27912,7 @@
         <v>4700</v>
       </c>
       <c r="D591" s="3">
-        <f>100%-F591</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="E591" s="4">
@@ -27954,7 +27954,7 @@
         <v>165</v>
       </c>
       <c r="D592" s="3">
-        <f>100%-F592</f>
+        <f t="shared" si="10"/>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E592" s="4">
@@ -27996,7 +27996,7 @@
         <v>146</v>
       </c>
       <c r="D593" s="3">
-        <f>100%-F593</f>
+        <f t="shared" si="10"/>
         <v>0.17000000000000004</v>
       </c>
       <c r="E593" s="4">
@@ -28038,7 +28038,7 @@
         <v>249</v>
       </c>
       <c r="D594" s="3">
-        <f>100%-F594</f>
+        <f t="shared" si="10"/>
         <v>0.25</v>
       </c>
       <c r="E594" s="4">
@@ -28080,7 +28080,7 @@
         <v>128</v>
       </c>
       <c r="D595" s="3">
-        <f>100%-F595</f>
+        <f t="shared" si="10"/>
         <v>0.65</v>
       </c>
       <c r="E595" s="4">
@@ -28122,7 +28122,7 @@
         <v>236</v>
       </c>
       <c r="D596" s="3">
-        <f>100%-F596</f>
+        <f t="shared" si="10"/>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="E596" s="4">
@@ -28164,7 +28164,7 @@
         <v>380</v>
       </c>
       <c r="D597" s="3">
-        <f>100%-F597</f>
+        <f t="shared" si="10"/>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="E597" s="4">
@@ -28206,7 +28206,7 @@
         <v>269</v>
       </c>
       <c r="D598" s="3">
-        <f>100%-F598</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="E598" s="4">
@@ -28248,7 +28248,7 @@
         <v>227</v>
       </c>
       <c r="D599" s="3">
-        <f>100%-F599</f>
+        <f t="shared" si="10"/>
         <v>0.32999999999999996</v>
       </c>
       <c r="E599" s="4">
@@ -28290,7 +28290,7 @@
         <v>175</v>
       </c>
       <c r="D600" s="3">
-        <f>100%-F600</f>
+        <f t="shared" si="10"/>
         <v>0.30000000000000004</v>
       </c>
       <c r="E600" s="4">
@@ -28332,7 +28332,7 @@
         <v>364</v>
       </c>
       <c r="D601" s="3">
-        <f>100%-F601</f>
+        <f t="shared" si="10"/>
         <v>0.15000000000000002</v>
       </c>
       <c r="E601" s="4">
@@ -28374,7 +28374,7 @@
         <v>1341</v>
       </c>
       <c r="D602" s="3">
-        <f>100%-F602</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="E602" s="4">
@@ -28416,7 +28416,7 @@
         <v>197</v>
       </c>
       <c r="D603" s="3">
-        <f>100%-F603</f>
+        <f t="shared" si="10"/>
         <v>0.37</v>
       </c>
       <c r="E603" s="4">
@@ -28458,7 +28458,7 @@
         <v>722</v>
       </c>
       <c r="D604" s="3">
-        <f>100%-F604</f>
+        <f t="shared" si="10"/>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E604" s="4">
@@ -28500,7 +28500,7 @@
         <v>244</v>
       </c>
       <c r="D605" s="3">
-        <f>100%-F605</f>
+        <f t="shared" si="10"/>
         <v>0.30000000000000004</v>
       </c>
       <c r="E605" s="4">
@@ -28542,7 +28542,7 @@
         <v>965</v>
       </c>
       <c r="D606" s="3">
-        <f>100%-F606</f>
+        <f t="shared" si="10"/>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="E606" s="4">
@@ -28584,7 +28584,7 @@
         <v>913</v>
       </c>
       <c r="D607" s="3">
-        <f>100%-F607</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="E607" s="4">
@@ -28626,7 +28626,7 @@
         <v>310</v>
       </c>
       <c r="D608" s="3">
-        <f>100%-F608</f>
+        <f t="shared" si="10"/>
         <v>0.22999999999999998</v>
       </c>
       <c r="E608" s="4">
@@ -28668,7 +28668,7 @@
         <v>622</v>
       </c>
       <c r="D609" s="3">
-        <f>100%-F609</f>
+        <f t="shared" si="10"/>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E609" s="4">
@@ -28710,7 +28710,7 @@
         <v>369</v>
       </c>
       <c r="D610" s="3">
-        <f>100%-F610</f>
+        <f t="shared" si="10"/>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E610" s="4">
@@ -28752,7 +28752,7 @@
         <v>152</v>
       </c>
       <c r="D611" s="3">
-        <f>100%-F611</f>
+        <f t="shared" si="10"/>
         <v>0.38</v>
       </c>
       <c r="E611" s="4">
@@ -28794,7 +28794,7 @@
         <v>539</v>
       </c>
       <c r="D612" s="3">
-        <f>100%-F612</f>
+        <f t="shared" si="10"/>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E612" s="4">
@@ -28836,7 +28836,7 @@
         <v>413</v>
       </c>
       <c r="D613" s="3">
-        <f>100%-F613</f>
+        <f t="shared" si="10"/>
         <v>0.30000000000000004</v>
       </c>
       <c r="E613" s="4">
@@ -28878,7 +28878,7 @@
         <v>875</v>
       </c>
       <c r="D614" s="3">
-        <f>100%-F614</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="E614" s="4">
@@ -28920,7 +28920,7 @@
         <v>120</v>
       </c>
       <c r="D615" s="3">
-        <f>100%-F615</f>
+        <f t="shared" si="10"/>
         <v>0.44999999999999996</v>
       </c>
       <c r="E615" s="4">
@@ -28962,7 +28962,7 @@
         <v>243</v>
       </c>
       <c r="D616" s="3">
-        <f>100%-F616</f>
+        <f t="shared" si="10"/>
         <v>0.38</v>
       </c>
       <c r="E616" s="4">
@@ -29004,7 +29004,7 @@
         <v>647</v>
       </c>
       <c r="D617" s="3">
-        <f>100%-F617</f>
+        <f t="shared" si="10"/>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E617" s="4">
@@ -29046,7 +29046,7 @@
         <v>1213</v>
       </c>
       <c r="D618" s="3">
-        <f>100%-F618</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="E618" s="4">
@@ -29088,7 +29088,7 @@
         <v>782</v>
       </c>
       <c r="D619" s="3">
-        <f>100%-F619</f>
+        <f t="shared" si="10"/>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="E619" s="4">
@@ -29130,7 +29130,7 @@
         <v>246</v>
       </c>
       <c r="D620" s="3">
-        <f>100%-F620</f>
+        <f t="shared" si="10"/>
         <v>0.22999999999999998</v>
       </c>
       <c r="E620" s="4">
@@ -29172,7 +29172,7 @@
         <v>958</v>
       </c>
       <c r="D621" s="3">
-        <f>100%-F621</f>
+        <f t="shared" si="10"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="E621" s="4">
@@ -29214,7 +29214,7 @@
         <v>179</v>
       </c>
       <c r="D622" s="3">
-        <f>100%-F622</f>
+        <f t="shared" si="10"/>
         <v>0.37</v>
       </c>
       <c r="E622" s="4">
@@ -29256,7 +29256,7 @@
         <v>1769</v>
       </c>
       <c r="D623" s="3">
-        <f>100%-F623</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="E623" s="4">
@@ -29298,7 +29298,7 @@
         <v>178</v>
       </c>
       <c r="D624" s="3">
-        <f>100%-F624</f>
+        <f t="shared" si="10"/>
         <v>0.37</v>
       </c>
       <c r="E624" s="4">
@@ -29340,7 +29340,7 @@
         <v>1114</v>
       </c>
       <c r="D625" s="3">
-        <f>100%-F625</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="E625" s="4">
@@ -29382,7 +29382,7 @@
         <v>193</v>
       </c>
       <c r="D626" s="3">
-        <f>100%-F626</f>
+        <f t="shared" si="10"/>
         <v>0.30000000000000004</v>
       </c>
       <c r="E626" s="4">
@@ -29424,7 +29424,7 @@
         <v>15482</v>
       </c>
       <c r="D627" s="3">
-        <f>100%-F627</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="E627" s="4">
@@ -29466,7 +29466,7 @@
         <v>170</v>
       </c>
       <c r="D628" s="3">
-        <f>100%-F628</f>
+        <f t="shared" si="10"/>
         <v>0.72</v>
       </c>
       <c r="E628" s="4">
@@ -29508,7 +29508,7 @@
         <v>295</v>
       </c>
       <c r="D629" s="3">
-        <f>100%-F629</f>
+        <f t="shared" si="10"/>
         <v>0.38</v>
       </c>
       <c r="E629" s="4">
@@ -29550,7 +29550,7 @@
         <v>547</v>
       </c>
       <c r="D630" s="3">
-        <f>100%-F630</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="E630" s="4">
@@ -29592,7 +29592,7 @@
         <v>168</v>
       </c>
       <c r="D631" s="3">
-        <f>100%-F631</f>
+        <f t="shared" si="10"/>
         <v>0.38</v>
       </c>
       <c r="E631" s="4">
@@ -29634,7 +29634,7 @@
         <v>154</v>
       </c>
       <c r="D632" s="3">
-        <f>100%-F632</f>
+        <f t="shared" si="10"/>
         <v>0.73</v>
       </c>
       <c r="E632" s="4">
@@ -29676,7 +29676,7 @@
         <v>828</v>
       </c>
       <c r="D633" s="3">
-        <f>100%-F633</f>
+        <f t="shared" si="10"/>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="E633" s="4">
@@ -29718,7 +29718,7 @@
         <v>117</v>
       </c>
       <c r="D634" s="3">
-        <f>100%-F634</f>
+        <f t="shared" si="10"/>
         <v>0.44999999999999996</v>
       </c>
       <c r="E634" s="4">
@@ -29760,7 +29760,7 @@
         <v>278</v>
       </c>
       <c r="D635" s="3">
-        <f>100%-F635</f>
+        <f t="shared" si="10"/>
         <v>0.22999999999999998</v>
       </c>
       <c r="E635" s="4">
@@ -29802,7 +29802,7 @@
         <v>129</v>
       </c>
       <c r="D636" s="3">
-        <f>100%-F636</f>
+        <f t="shared" si="10"/>
         <v>0.37</v>
       </c>
       <c r="E636" s="4">
@@ -29845,7 +29845,7 @@
         <v>270</v>
       </c>
       <c r="D637" s="3">
-        <f>100%-F637</f>
+        <f t="shared" si="10"/>
         <v>0.22999999999999998</v>
       </c>
       <c r="E637" s="4">
@@ -29887,7 +29887,7 @@
         <v>197</v>
       </c>
       <c r="D638" s="3">
-        <f>100%-F638</f>
+        <f t="shared" si="10"/>
         <v>0.38</v>
       </c>
       <c r="E638" s="4">
@@ -29929,7 +29929,7 @@
         <v>105</v>
       </c>
       <c r="D639" s="3">
-        <f>100%-F639</f>
+        <f t="shared" si="10"/>
         <v>0.65</v>
       </c>
       <c r="E639" s="4">
@@ -29971,7 +29971,7 @@
         <v>243</v>
       </c>
       <c r="D640" s="3">
-        <f>100%-F640</f>
+        <f t="shared" si="10"/>
         <v>0.30000000000000004</v>
       </c>
       <c r="E640" s="4">
@@ -30014,7 +30014,7 @@
         <v>617</v>
       </c>
       <c r="D641" s="3">
-        <f>100%-F641</f>
+        <f t="shared" si="10"/>
         <v>0.22999999999999998</v>
       </c>
       <c r="E641" s="4">
@@ -30056,7 +30056,7 @@
         <v>780</v>
       </c>
       <c r="D642" s="3">
-        <f>100%-F642</f>
+        <f t="shared" ref="D642:D705" si="11">100%-F642</f>
         <v>0</v>
       </c>
       <c r="E642" s="4">
@@ -30098,7 +30098,7 @@
         <v>656</v>
       </c>
       <c r="D643" s="3">
-        <f>100%-F643</f>
+        <f t="shared" si="11"/>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="E643" s="4">
@@ -30140,7 +30140,7 @@
         <v>162</v>
       </c>
       <c r="D644" s="3">
-        <f>100%-F644</f>
+        <f t="shared" si="11"/>
         <v>0.38</v>
       </c>
       <c r="E644" s="4">
@@ -30182,7 +30182,7 @@
         <v>380</v>
       </c>
       <c r="D645" s="3">
-        <f>100%-F645</f>
+        <f t="shared" si="11"/>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E645" s="4">
@@ -30225,7 +30225,7 @@
         <v>536</v>
       </c>
       <c r="D646" s="3">
-        <f>100%-F646</f>
+        <f t="shared" si="11"/>
         <v>0.38</v>
       </c>
       <c r="E646" s="4">
@@ -30268,7 +30268,7 @@
         <v>419</v>
       </c>
       <c r="D647" s="3">
-        <f>100%-F647</f>
+        <f t="shared" si="11"/>
         <v>0.38</v>
       </c>
       <c r="E647" s="4">
@@ -30311,7 +30311,7 @@
         <v>102</v>
       </c>
       <c r="D648" s="3">
-        <f>100%-F648</f>
+        <f t="shared" si="11"/>
         <v>0.65</v>
       </c>
       <c r="E648" s="4">
@@ -30353,7 +30353,7 @@
         <v>127</v>
       </c>
       <c r="D649" s="3">
-        <f>100%-F649</f>
+        <f t="shared" si="11"/>
         <v>0.44999999999999996</v>
       </c>
       <c r="E649" s="4">
@@ -30395,7 +30395,7 @@
         <v>440</v>
       </c>
       <c r="D650" s="3">
-        <f>100%-F650</f>
+        <f t="shared" si="11"/>
         <v>0.38</v>
       </c>
       <c r="E650" s="4">
@@ -30438,11 +30438,11 @@
         <v>260</v>
       </c>
       <c r="D651" s="3">
-        <f>100%-F651</f>
+        <f t="shared" si="11"/>
         <v>0.38</v>
       </c>
       <c r="E651" s="4">
-        <f t="shared" ref="E651:E652" si="1">I651*4%</f>
+        <f t="shared" ref="E651:E652" si="12">I651*4%</f>
         <v>0.04</v>
       </c>
       <c r="F651" s="4">
@@ -30481,11 +30481,11 @@
         <v>455</v>
       </c>
       <c r="D652" s="3">
-        <f>100%-F652</f>
+        <f t="shared" si="11"/>
         <v>0.38</v>
       </c>
       <c r="E652" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="12"/>
         <v>0.04</v>
       </c>
       <c r="F652" s="4">
@@ -30524,7 +30524,7 @@
         <v>352</v>
       </c>
       <c r="D653" s="3">
-        <f>100%-F653</f>
+        <f t="shared" si="11"/>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E653" s="4">
@@ -30567,7 +30567,7 @@
         <v>133</v>
       </c>
       <c r="D654" s="3">
-        <f>100%-F654</f>
+        <f t="shared" si="11"/>
         <v>0.73</v>
       </c>
       <c r="E654" s="4">
@@ -30609,7 +30609,7 @@
         <v>387</v>
       </c>
       <c r="D655" s="3">
-        <f>100%-F655</f>
+        <f t="shared" si="11"/>
         <v>0.22999999999999998</v>
       </c>
       <c r="E655" s="4">
@@ -30651,7 +30651,7 @@
         <v>682</v>
       </c>
       <c r="D656" s="3">
-        <f>100%-F656</f>
+        <f t="shared" si="11"/>
         <v>0.18000000000000005</v>
       </c>
       <c r="E656" s="4">
@@ -30693,7 +30693,7 @@
         <v>546</v>
       </c>
       <c r="D657" s="3">
-        <f>100%-F657</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="E657" s="4">
@@ -30735,7 +30735,7 @@
         <v>447</v>
       </c>
       <c r="D658" s="3">
-        <f>100%-F658</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="E658" s="4">
@@ -30777,7 +30777,7 @@
         <v>403</v>
       </c>
       <c r="D659" s="3">
-        <f>100%-F659</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="E659" s="4">
@@ -30819,7 +30819,7 @@
         <v>132</v>
       </c>
       <c r="D660" s="3">
-        <f>100%-F660</f>
+        <f t="shared" si="11"/>
         <v>0.8</v>
       </c>
       <c r="E660" s="4">
@@ -30861,7 +30861,7 @@
         <v>802</v>
       </c>
       <c r="D661" s="3">
-        <f>100%-F661</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="E661" s="4">
@@ -30903,7 +30903,7 @@
         <v>177</v>
       </c>
       <c r="D662" s="3">
-        <f>100%-F662</f>
+        <f t="shared" si="11"/>
         <v>0.44999999999999996</v>
       </c>
       <c r="E662" s="4">
@@ -30946,7 +30946,7 @@
         <v>1387</v>
       </c>
       <c r="D663" s="3">
-        <f>100%-F663</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="E663" s="4">
@@ -30988,7 +30988,7 @@
         <v>515</v>
       </c>
       <c r="D664" s="3">
-        <f>100%-F664</f>
+        <f t="shared" si="11"/>
         <v>0.25</v>
       </c>
       <c r="E664" s="4">
@@ -31030,7 +31030,7 @@
         <v>450</v>
       </c>
       <c r="D665" s="3">
-        <f>100%-F665</f>
+        <f t="shared" si="11"/>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="E665" s="4">
@@ -31072,7 +31072,7 @@
         <v>633</v>
       </c>
       <c r="D666" s="3">
-        <f>100%-F666</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="E666" s="4">
@@ -31114,7 +31114,7 @@
         <v>178</v>
       </c>
       <c r="D667" s="3">
-        <f>100%-F667</f>
+        <f t="shared" si="11"/>
         <v>0.22999999999999998</v>
       </c>
       <c r="E667" s="4">
@@ -31156,7 +31156,7 @@
         <v>162</v>
       </c>
       <c r="D668" s="3">
-        <f>100%-F668</f>
+        <f t="shared" si="11"/>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E668" s="4">
@@ -31198,7 +31198,7 @@
         <v>594</v>
       </c>
       <c r="D669" s="3">
-        <f>100%-F669</f>
+        <f t="shared" si="11"/>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E669" s="4">
@@ -31240,7 +31240,7 @@
         <v>549</v>
       </c>
       <c r="D670" s="3">
-        <f>100%-F670</f>
+        <f t="shared" si="11"/>
         <v>0.38</v>
       </c>
       <c r="E670" s="4">
@@ -31282,7 +31282,7 @@
         <v>1116</v>
       </c>
       <c r="D671" s="3">
-        <f>100%-F671</f>
+        <f t="shared" si="11"/>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E671" s="4">
@@ -31324,7 +31324,7 @@
         <v>294</v>
       </c>
       <c r="D672" s="3">
-        <f>100%-F672</f>
+        <f t="shared" si="11"/>
         <v>0.30000000000000004</v>
       </c>
       <c r="E672" s="4">
@@ -31366,7 +31366,7 @@
         <v>987</v>
       </c>
       <c r="D673" s="3">
-        <f>100%-F673</f>
+        <f t="shared" si="11"/>
         <v>0.30000000000000004</v>
       </c>
       <c r="E673" s="4">
@@ -31408,7 +31408,7 @@
         <v>137</v>
       </c>
       <c r="D674" s="3">
-        <f>100%-F674</f>
+        <f t="shared" si="11"/>
         <v>0.30000000000000004</v>
       </c>
       <c r="E674" s="4">
@@ -31450,7 +31450,7 @@
         <v>256</v>
       </c>
       <c r="D675" s="3">
-        <f>100%-F675</f>
+        <f t="shared" si="11"/>
         <v>0.26</v>
       </c>
       <c r="E675" s="4">
@@ -31492,7 +31492,7 @@
         <v>371</v>
       </c>
       <c r="D676" s="3">
-        <f>100%-F676</f>
+        <f t="shared" si="11"/>
         <v>0.25</v>
       </c>
       <c r="E676" s="4">
@@ -31534,7 +31534,7 @@
         <v>543</v>
       </c>
       <c r="D677" s="3">
-        <f>100%-F677</f>
+        <f t="shared" si="11"/>
         <v>0.28000000000000003</v>
       </c>
       <c r="E677" s="4">
@@ -31576,7 +31576,7 @@
         <v>546</v>
       </c>
       <c r="D678" s="3">
-        <f>100%-F678</f>
+        <f t="shared" si="11"/>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E678" s="4">
@@ -31618,7 +31618,7 @@
         <v>416</v>
       </c>
       <c r="D679" s="3">
-        <f>100%-F679</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="E679" s="4">
@@ -31660,7 +31660,7 @@
         <v>886</v>
       </c>
       <c r="D680" s="3">
-        <f>100%-F680</f>
+        <f t="shared" si="11"/>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E680" s="4">
@@ -31702,7 +31702,7 @@
         <v>388</v>
       </c>
       <c r="D681" s="3">
-        <f>100%-F681</f>
+        <f t="shared" si="11"/>
         <v>0.18000000000000005</v>
       </c>
       <c r="E681" s="4">
@@ -31744,7 +31744,7 @@
         <v>574</v>
       </c>
       <c r="D682" s="3">
-        <f>100%-F682</f>
+        <f t="shared" si="11"/>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E682" s="4">
@@ -31786,7 +31786,7 @@
         <v>102</v>
       </c>
       <c r="D683" s="3">
-        <f>100%-F683</f>
+        <f t="shared" si="11"/>
         <v>0.22999999999999998</v>
       </c>
       <c r="E683" s="4">
@@ -31828,7 +31828,7 @@
         <v>131</v>
       </c>
       <c r="D684" s="3">
-        <f>100%-F684</f>
+        <f t="shared" si="11"/>
         <v>0.30000000000000004</v>
       </c>
       <c r="E684" s="4">
@@ -31870,7 +31870,7 @@
         <v>183</v>
       </c>
       <c r="D685" s="3">
-        <f>100%-F685</f>
+        <f t="shared" si="11"/>
         <v>0.38</v>
       </c>
       <c r="E685" s="4">
@@ -31912,7 +31912,7 @@
         <v>458</v>
       </c>
       <c r="D686" s="3">
-        <f>100%-F686</f>
+        <f t="shared" si="11"/>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E686" s="4">
@@ -31954,7 +31954,7 @@
         <v>429</v>
       </c>
       <c r="D687" s="3">
-        <f>100%-F687</f>
+        <f t="shared" si="11"/>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="E687" s="4">
@@ -31996,7 +31996,7 @@
         <v>248</v>
       </c>
       <c r="D688" s="3">
-        <f>100%-F688</f>
+        <f t="shared" si="11"/>
         <v>0.38</v>
       </c>
       <c r="E688" s="4">
@@ -32038,7 +32038,7 @@
         <v>678</v>
       </c>
       <c r="D689" s="3">
-        <f>100%-F689</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="E689" s="4">
@@ -32080,7 +32080,7 @@
         <v>846</v>
       </c>
       <c r="D690" s="3">
-        <f>100%-F690</f>
+        <f t="shared" si="11"/>
         <v>0.32999999999999996</v>
       </c>
       <c r="E690" s="4">
@@ -32122,7 +32122,7 @@
         <v>189</v>
       </c>
       <c r="D691" s="3">
-        <f>100%-F691</f>
+        <f t="shared" si="11"/>
         <v>0.38</v>
       </c>
       <c r="E691" s="4">
@@ -32164,7 +32164,7 @@
         <v>130</v>
       </c>
       <c r="D692" s="3">
-        <f>100%-F692</f>
+        <f t="shared" si="11"/>
         <v>0.71</v>
       </c>
       <c r="E692" s="4">
@@ -32206,7 +32206,7 @@
         <v>105</v>
       </c>
       <c r="D693" s="3">
-        <f>100%-F693</f>
+        <f t="shared" si="11"/>
         <v>0.38</v>
       </c>
       <c r="E693" s="4">
@@ -32248,7 +32248,7 @@
         <v>249</v>
       </c>
       <c r="D694" s="3">
-        <f>100%-F694</f>
+        <f t="shared" si="11"/>
         <v>0.30000000000000004</v>
       </c>
       <c r="E694" s="4">
@@ -32290,7 +32290,7 @@
         <v>993</v>
       </c>
       <c r="D695" s="3">
-        <f>100%-F695</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="E695" s="4">
@@ -32332,7 +32332,7 @@
         <v>584</v>
       </c>
       <c r="D696" s="3">
-        <f>100%-F696</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="E696" s="4">
@@ -32374,7 +32374,7 @@
         <v>142</v>
       </c>
       <c r="D697" s="3">
-        <f>100%-F697</f>
+        <f t="shared" si="11"/>
         <v>0.20999999999999996</v>
       </c>
       <c r="E697" s="4">
@@ -32416,7 +32416,7 @@
         <v>114</v>
       </c>
       <c r="D698" s="3">
-        <f>100%-F698</f>
+        <f t="shared" si="11"/>
         <v>0.22999999999999998</v>
       </c>
       <c r="E698" s="4">
@@ -32458,7 +32458,7 @@
         <v>118</v>
       </c>
       <c r="D699" s="3">
-        <f>100%-F699</f>
+        <f t="shared" si="11"/>
         <v>0.37</v>
       </c>
       <c r="E699" s="4">
@@ -32500,7 +32500,7 @@
         <v>386</v>
       </c>
       <c r="D700" s="3">
-        <f>100%-F700</f>
+        <f t="shared" si="11"/>
         <v>0.18000000000000005</v>
       </c>
       <c r="E700" s="4">
@@ -32542,7 +32542,7 @@
         <v>188</v>
       </c>
       <c r="D701" s="3">
-        <f>100%-F701</f>
+        <f t="shared" si="11"/>
         <v>0.38</v>
       </c>
       <c r="E701" s="4">
@@ -32584,7 +32584,7 @@
         <v>153</v>
       </c>
       <c r="D702" s="3">
-        <f>100%-F702</f>
+        <f t="shared" si="11"/>
         <v>0.38</v>
       </c>
       <c r="E702" s="4">
@@ -32626,7 +32626,7 @@
         <v>109</v>
       </c>
       <c r="D703" s="3">
-        <f>100%-F703</f>
+        <f t="shared" si="11"/>
         <v>0.30000000000000004</v>
       </c>
       <c r="E703" s="4">
@@ -32668,7 +32668,7 @@
         <v>600</v>
       </c>
       <c r="D704" s="3">
-        <f>100%-F704</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="E704" s="4">
@@ -32710,7 +32710,7 @@
         <v>218</v>
       </c>
       <c r="D705" s="3">
-        <f>100%-F705</f>
+        <f t="shared" si="11"/>
         <v>0.22999999999999998</v>
       </c>
       <c r="E705" s="4">
@@ -32752,7 +32752,7 @@
         <v>109</v>
       </c>
       <c r="D706" s="3">
-        <f>100%-F706</f>
+        <f t="shared" ref="D706:D769" si="13">100%-F706</f>
         <v>0.44999999999999996</v>
       </c>
       <c r="E706" s="4">
@@ -32794,7 +32794,7 @@
         <v>649</v>
       </c>
       <c r="D707" s="3">
-        <f>100%-F707</f>
+        <f t="shared" si="13"/>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E707" s="4">
@@ -32836,7 +32836,7 @@
         <v>418</v>
       </c>
       <c r="D708" s="3">
-        <f>100%-F708</f>
+        <f t="shared" si="13"/>
         <v>0.18000000000000005</v>
       </c>
       <c r="E708" s="4">
@@ -32878,7 +32878,7 @@
         <v>228</v>
       </c>
       <c r="D709" s="3">
-        <f>100%-F709</f>
+        <f t="shared" si="13"/>
         <v>0.30000000000000004</v>
       </c>
       <c r="E709" s="4">
@@ -32920,7 +32920,7 @@
         <v>326</v>
       </c>
       <c r="D710" s="3">
-        <f>100%-F710</f>
+        <f t="shared" si="13"/>
         <v>0.30000000000000004</v>
       </c>
       <c r="E710" s="4">
@@ -32962,7 +32962,7 @@
         <v>593</v>
       </c>
       <c r="D711" s="3">
-        <f>100%-F711</f>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="E711" s="4">
@@ -33004,7 +33004,7 @@
         <v>130</v>
       </c>
       <c r="D712" s="3">
-        <f>100%-F712</f>
+        <f t="shared" si="13"/>
         <v>0.45999999999999996</v>
       </c>
       <c r="E712" s="4">
@@ -33046,7 +33046,7 @@
         <v>608</v>
       </c>
       <c r="D713" s="3">
-        <f>100%-F713</f>
+        <f t="shared" si="13"/>
         <v>0.30000000000000004</v>
       </c>
       <c r="E713" s="4">
@@ -33088,7 +33088,7 @@
         <v>145</v>
       </c>
       <c r="D714" s="3">
-        <f>100%-F714</f>
+        <f t="shared" si="13"/>
         <v>0.65</v>
       </c>
       <c r="E714" s="4">
@@ -33130,7 +33130,7 @@
         <v>113</v>
       </c>
       <c r="D715" s="3">
-        <f>100%-F715</f>
+        <f t="shared" si="13"/>
         <v>0.5</v>
       </c>
       <c r="E715" s="4">
@@ -33172,7 +33172,7 @@
         <v>130</v>
       </c>
       <c r="D716" s="3">
-        <f>100%-F716</f>
+        <f t="shared" si="13"/>
         <v>0.26</v>
       </c>
       <c r="E716" s="4">
@@ -33214,7 +33214,7 @@
         <v>886</v>
       </c>
       <c r="D717" s="3">
-        <f>100%-F717</f>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="E717" s="4">
@@ -33256,7 +33256,7 @@
         <v>681</v>
       </c>
       <c r="D718" s="3">
-        <f>100%-F718</f>
+        <f t="shared" si="13"/>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E718" s="4">
@@ -33298,7 +33298,7 @@
         <v>169</v>
       </c>
       <c r="D719" s="3">
-        <f>100%-F719</f>
+        <f t="shared" si="13"/>
         <v>0.22999999999999998</v>
       </c>
       <c r="E719" s="4">
@@ -33340,7 +33340,7 @@
         <v>110</v>
       </c>
       <c r="D720" s="3">
-        <f>100%-F720</f>
+        <f t="shared" si="13"/>
         <v>0.28000000000000003</v>
       </c>
       <c r="E720" s="4">
@@ -33382,7 +33382,7 @@
         <v>8967</v>
       </c>
       <c r="D721" s="3">
-        <f>100%-F721</f>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="E721" s="4">
@@ -33424,7 +33424,7 @@
         <v>216</v>
       </c>
       <c r="D722" s="3">
-        <f>100%-F722</f>
+        <f t="shared" si="13"/>
         <v>0.32999999999999996</v>
       </c>
       <c r="E722" s="4">
@@ -33466,7 +33466,7 @@
         <v>5047</v>
       </c>
       <c r="D723" s="3">
-        <f>100%-F723</f>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="E723" s="4">
@@ -33508,7 +33508,7 @@
         <v>157</v>
       </c>
       <c r="D724" s="3">
-        <f>100%-F724</f>
+        <f t="shared" si="13"/>
         <v>0.25</v>
       </c>
       <c r="E724" s="4">
@@ -33550,7 +33550,7 @@
         <v>147</v>
       </c>
       <c r="D725" s="3">
-        <f>100%-F725</f>
+        <f t="shared" si="13"/>
         <v>0.30000000000000004</v>
       </c>
       <c r="E725" s="4">
@@ -33592,7 +33592,7 @@
         <v>1524</v>
       </c>
       <c r="D726" s="3">
-        <f>100%-F726</f>
+        <f t="shared" si="13"/>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="E726" s="4">
@@ -33634,7 +33634,7 @@
         <v>138</v>
       </c>
       <c r="D727" s="3">
-        <f>100%-F727</f>
+        <f t="shared" si="13"/>
         <v>0.32999999999999996</v>
       </c>
       <c r="E727" s="4">
@@ -33676,7 +33676,7 @@
         <v>285</v>
       </c>
       <c r="D728" s="3">
-        <f>100%-F728</f>
+        <f t="shared" si="13"/>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E728" s="4">
@@ -33718,7 +33718,7 @@
         <v>281</v>
       </c>
       <c r="D729" s="3">
-        <f>100%-F729</f>
+        <f t="shared" si="13"/>
         <v>0.21999999999999997</v>
       </c>
       <c r="E729" s="4">
@@ -33760,7 +33760,7 @@
         <v>648</v>
       </c>
       <c r="D730" s="3">
-        <f>100%-F730</f>
+        <f t="shared" si="13"/>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="E730" s="4">
@@ -33802,7 +33802,7 @@
         <v>232</v>
       </c>
       <c r="D731" s="3">
-        <f>100%-F731</f>
+        <f t="shared" si="13"/>
         <v>0.15000000000000002</v>
       </c>
       <c r="E731" s="4">
@@ -33844,7 +33844,7 @@
         <v>221</v>
       </c>
       <c r="D732" s="3">
-        <f>100%-F732</f>
+        <f t="shared" si="13"/>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E732" s="4">
@@ -33886,7 +33886,7 @@
         <v>942</v>
       </c>
       <c r="D733" s="3">
-        <f>100%-F733</f>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="E733" s="4">
@@ -33928,7 +33928,7 @@
         <v>174</v>
       </c>
       <c r="D734" s="3">
-        <f>100%-F734</f>
+        <f t="shared" si="13"/>
         <v>0.15000000000000002</v>
       </c>
       <c r="E734" s="4">
@@ -33970,7 +33970,7 @@
         <v>213</v>
       </c>
       <c r="D735" s="3">
-        <f>100%-F735</f>
+        <f t="shared" si="13"/>
         <v>0.15000000000000002</v>
       </c>
       <c r="E735" s="4">
@@ -34012,7 +34012,7 @@
         <v>239</v>
       </c>
       <c r="D736" s="3">
-        <f>100%-F736</f>
+        <f t="shared" si="13"/>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="E736" s="4">
@@ -34054,7 +34054,7 @@
         <v>252</v>
       </c>
       <c r="D737" s="3">
-        <f>100%-F737</f>
+        <f t="shared" si="13"/>
         <v>0.17000000000000004</v>
       </c>
       <c r="E737" s="4">
@@ -34096,7 +34096,7 @@
         <v>415</v>
       </c>
       <c r="D738" s="3">
-        <f>100%-F738</f>
+        <f t="shared" si="13"/>
         <v>0.38</v>
       </c>
       <c r="E738" s="4">
@@ -34138,7 +34138,7 @@
         <v>601</v>
       </c>
       <c r="D739" s="3">
-        <f>100%-F739</f>
+        <f t="shared" si="13"/>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="E739" s="4">
@@ -34180,7 +34180,7 @@
         <v>118</v>
       </c>
       <c r="D740" s="3">
-        <f>100%-F740</f>
+        <f t="shared" si="13"/>
         <v>0.5</v>
       </c>
       <c r="E740" s="4">
@@ -34222,7 +34222,7 @@
         <v>635</v>
       </c>
       <c r="D741" s="3">
-        <f>100%-F741</f>
+        <f t="shared" si="13"/>
         <v>0.15000000000000002</v>
       </c>
       <c r="E741" s="4">
@@ -34264,7 +34264,7 @@
         <v>356</v>
       </c>
       <c r="D742" s="3">
-        <f>100%-F742</f>
+        <f t="shared" si="13"/>
         <v>0.22999999999999998</v>
       </c>
       <c r="E742" s="4">
@@ -34306,7 +34306,7 @@
         <v>4054.0000000000005</v>
       </c>
       <c r="D743" s="3">
-        <f>100%-F743</f>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="E743" s="4">
@@ -34348,7 +34348,7 @@
         <v>187</v>
       </c>
       <c r="D744" s="3">
-        <f>100%-F744</f>
+        <f t="shared" si="13"/>
         <v>0.53</v>
       </c>
       <c r="E744" s="4">
@@ -34390,7 +34390,7 @@
         <v>300</v>
       </c>
       <c r="D745" s="3">
-        <f>100%-F745</f>
+        <f t="shared" si="13"/>
         <v>0.43000000000000005</v>
       </c>
       <c r="E745" s="4">
@@ -34432,7 +34432,7 @@
         <v>317</v>
       </c>
       <c r="D746" s="3">
-        <f>100%-F746</f>
+        <f t="shared" si="13"/>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="E746" s="4">
@@ -34474,7 +34474,7 @@
         <v>191</v>
       </c>
       <c r="D747" s="3">
-        <f>100%-F747</f>
+        <f t="shared" si="13"/>
         <v>0.15000000000000002</v>
       </c>
       <c r="E747" s="4">
@@ -34516,7 +34516,7 @@
         <v>291</v>
       </c>
       <c r="D748" s="3">
-        <f>100%-F748</f>
+        <f t="shared" si="13"/>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="E748" s="4">
@@ -34558,7 +34558,7 @@
         <v>172</v>
       </c>
       <c r="D749" s="3">
-        <f>100%-F749</f>
+        <f t="shared" si="13"/>
         <v>0.65</v>
       </c>
       <c r="E749" s="4">
@@ -34600,7 +34600,7 @@
         <v>399</v>
       </c>
       <c r="D750" s="3">
-        <f>100%-F750</f>
+        <f t="shared" si="13"/>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="E750" s="4">
@@ -34642,7 +34642,7 @@
         <v>398</v>
       </c>
       <c r="D751" s="3">
-        <f>100%-F751</f>
+        <f t="shared" si="13"/>
         <v>0.28000000000000003</v>
       </c>
       <c r="E751" s="4">
@@ -34684,7 +34684,7 @@
         <v>139</v>
       </c>
       <c r="D752" s="3">
-        <f>100%-F752</f>
+        <f t="shared" si="13"/>
         <v>0.5</v>
       </c>
       <c r="E752" s="4">
@@ -34726,7 +34726,7 @@
         <v>305</v>
       </c>
       <c r="D753" s="3">
-        <f>100%-F753</f>
+        <f t="shared" si="13"/>
         <v>0.38</v>
       </c>
       <c r="E753" s="4">
@@ -34768,7 +34768,7 @@
         <v>575</v>
       </c>
       <c r="D754" s="3">
-        <f>100%-F754</f>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="E754" s="4">
@@ -34810,7 +34810,7 @@
         <v>763</v>
       </c>
       <c r="D755" s="3">
-        <f>100%-F755</f>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="E755" s="4">
@@ -34852,7 +34852,7 @@
         <v>120</v>
       </c>
       <c r="D756" s="3">
-        <f>100%-F756</f>
+        <f t="shared" si="13"/>
         <v>0.17000000000000004</v>
       </c>
       <c r="E756" s="4">
@@ -34894,7 +34894,7 @@
         <v>205</v>
       </c>
       <c r="D757" s="3">
-        <f>100%-F757</f>
+        <f t="shared" si="13"/>
         <v>0.22999999999999998</v>
       </c>
       <c r="E757" s="4">
@@ -34936,7 +34936,7 @@
         <v>338</v>
       </c>
       <c r="D758" s="3">
-        <f>100%-F758</f>
+        <f t="shared" si="13"/>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E758" s="4">
@@ -34978,7 +34978,7 @@
         <v>360</v>
       </c>
       <c r="D759" s="3">
-        <f>100%-F759</f>
+        <f t="shared" si="13"/>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="E759" s="4">
@@ -35020,7 +35020,7 @@
         <v>329</v>
       </c>
       <c r="D760" s="3">
-        <f>100%-F760</f>
+        <f t="shared" si="13"/>
         <v>0.30000000000000004</v>
       </c>
       <c r="E760" s="4">
@@ -35062,7 +35062,7 @@
         <v>265</v>
       </c>
       <c r="D761" s="3">
-        <f>100%-F761</f>
+        <f t="shared" si="13"/>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E761" s="4">
@@ -35104,7 +35104,7 @@
         <v>491</v>
       </c>
       <c r="D762" s="3">
-        <f>100%-F762</f>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="E762" s="4">
@@ -35146,7 +35146,7 @@
         <v>102</v>
       </c>
       <c r="D763" s="3">
-        <f>100%-F763</f>
+        <f t="shared" si="13"/>
         <v>0.37</v>
       </c>
       <c r="E763" s="4">
@@ -35188,7 +35188,7 @@
         <v>252</v>
       </c>
       <c r="D764" s="3">
-        <f>100%-F764</f>
+        <f t="shared" si="13"/>
         <v>0.30000000000000004</v>
       </c>
       <c r="E764" s="4">
@@ -35230,7 +35230,7 @@
         <v>124</v>
       </c>
       <c r="D765" s="3">
-        <f>100%-F765</f>
+        <f t="shared" si="13"/>
         <v>0.44999999999999996</v>
       </c>
       <c r="E765" s="4">
@@ -35272,7 +35272,7 @@
         <v>328</v>
       </c>
       <c r="D766" s="3">
-        <f>100%-F766</f>
+        <f t="shared" si="13"/>
         <v>0.30000000000000004</v>
       </c>
       <c r="E766" s="4">
@@ -35314,7 +35314,7 @@
         <v>644</v>
       </c>
       <c r="D767" s="3">
-        <f>100%-F767</f>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="E767" s="4">
@@ -35356,7 +35356,7 @@
         <v>336</v>
       </c>
       <c r="D768" s="3">
-        <f>100%-F768</f>
+        <f t="shared" si="13"/>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E768" s="4">
@@ -35398,7 +35398,7 @@
         <v>158</v>
       </c>
       <c r="D769" s="3">
-        <f>100%-F769</f>
+        <f t="shared" si="13"/>
         <v>0.30000000000000004</v>
       </c>
       <c r="E769" s="4">
@@ -35440,7 +35440,7 @@
         <v>171</v>
       </c>
       <c r="D770" s="3">
-        <f>100%-F770</f>
+        <f t="shared" ref="D770:D833" si="14">100%-F770</f>
         <v>0.15000000000000002</v>
       </c>
       <c r="E770" s="4">
@@ -35482,7 +35482,7 @@
         <v>358</v>
       </c>
       <c r="D771" s="3">
-        <f>100%-F771</f>
+        <f t="shared" si="14"/>
         <v>0.12</v>
       </c>
       <c r="E771" s="4">
@@ -35524,7 +35524,7 @@
         <v>322</v>
       </c>
       <c r="D772" s="3">
-        <f>100%-F772</f>
+        <f t="shared" si="14"/>
         <v>0.22999999999999998</v>
       </c>
       <c r="E772" s="4">
@@ -35566,7 +35566,7 @@
         <v>146</v>
       </c>
       <c r="D773" s="3">
-        <f>100%-F773</f>
+        <f t="shared" si="14"/>
         <v>0.30000000000000004</v>
       </c>
       <c r="E773" s="4">
@@ -35608,7 +35608,7 @@
         <v>1372</v>
       </c>
       <c r="D774" s="3">
-        <f>100%-F774</f>
+        <f t="shared" si="14"/>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="E774" s="4">
@@ -35650,7 +35650,7 @@
         <v>360</v>
       </c>
       <c r="D775" s="3">
-        <f>100%-F775</f>
+        <f t="shared" si="14"/>
         <v>0.15000000000000002</v>
       </c>
       <c r="E775" s="4">
@@ -35692,7 +35692,7 @@
         <v>158</v>
       </c>
       <c r="D776" s="3">
-        <f>100%-F776</f>
+        <f t="shared" si="14"/>
         <v>0.18999999999999995</v>
       </c>
       <c r="E776" s="4">
@@ -35734,7 +35734,7 @@
         <v>518</v>
       </c>
       <c r="D777" s="3">
-        <f>100%-F777</f>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="E777" s="4">
@@ -35776,7 +35776,7 @@
         <v>279</v>
       </c>
       <c r="D778" s="3">
-        <f>100%-F778</f>
+        <f t="shared" si="14"/>
         <v>0.28000000000000003</v>
       </c>
       <c r="E778" s="4">
@@ -35818,7 +35818,7 @@
         <v>345</v>
       </c>
       <c r="D779" s="3">
-        <f>100%-F779</f>
+        <f t="shared" si="14"/>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="E779" s="4">
@@ -35860,7 +35860,7 @@
         <v>105</v>
       </c>
       <c r="D780" s="3">
-        <f>100%-F780</f>
+        <f t="shared" si="14"/>
         <v>0.44999999999999996</v>
       </c>
       <c r="E780" s="4">
@@ -35902,7 +35902,7 @@
         <v>297</v>
       </c>
       <c r="D781" s="3">
-        <f>100%-F781</f>
+        <f t="shared" si="14"/>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E781" s="4">
@@ -35944,7 +35944,7 @@
         <v>342</v>
       </c>
       <c r="D782" s="3">
-        <f>100%-F782</f>
+        <f t="shared" si="14"/>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E782" s="4">
@@ -35986,7 +35986,7 @@
         <v>153</v>
       </c>
       <c r="D783" s="3">
-        <f>100%-F783</f>
+        <f t="shared" si="14"/>
         <v>0.22999999999999998</v>
       </c>
       <c r="E783" s="4">
@@ -36028,7 +36028,7 @@
         <v>216</v>
       </c>
       <c r="D784" s="3">
-        <f>100%-F784</f>
+        <f t="shared" si="14"/>
         <v>0.22999999999999998</v>
       </c>
       <c r="E784" s="4">
@@ -36070,7 +36070,7 @@
         <v>147</v>
       </c>
       <c r="D785" s="3">
-        <f>100%-F785</f>
+        <f t="shared" si="14"/>
         <v>0.30000000000000004</v>
       </c>
       <c r="E785" s="4">
@@ -36112,7 +36112,7 @@
         <v>471</v>
       </c>
       <c r="D786" s="3">
-        <f>100%-F786</f>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="E786" s="4">
@@ -36154,7 +36154,7 @@
         <v>107</v>
       </c>
       <c r="D787" s="3">
-        <f>100%-F787</f>
+        <f t="shared" si="14"/>
         <v>0.30000000000000004</v>
       </c>
       <c r="E787" s="4">
@@ -36196,7 +36196,7 @@
         <v>164</v>
       </c>
       <c r="D788" s="3">
-        <f>100%-F788</f>
+        <f t="shared" si="14"/>
         <v>0.38</v>
       </c>
       <c r="E788" s="4">
@@ -36238,7 +36238,7 @@
         <v>467</v>
       </c>
       <c r="D789" s="3">
-        <f>100%-F789</f>
+        <f t="shared" si="14"/>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="E789" s="4">
@@ -36280,7 +36280,7 @@
         <v>198</v>
       </c>
       <c r="D790" s="3">
-        <f>100%-F790</f>
+        <f t="shared" si="14"/>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E790" s="4">
@@ -36322,7 +36322,7 @@
         <v>220</v>
       </c>
       <c r="D791" s="3">
-        <f>100%-F791</f>
+        <f t="shared" si="14"/>
         <v>0.30000000000000004</v>
       </c>
       <c r="E791" s="4">
@@ -36364,7 +36364,7 @@
         <v>131</v>
       </c>
       <c r="D792" s="3">
-        <f>100%-F792</f>
+        <f t="shared" si="14"/>
         <v>0.15000000000000002</v>
       </c>
       <c r="E792" s="4">
@@ -36406,7 +36406,7 @@
         <v>708</v>
       </c>
       <c r="D793" s="3">
-        <f>100%-F793</f>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="E793" s="4">
@@ -36448,7 +36448,7 @@
         <v>117</v>
       </c>
       <c r="D794" s="3">
-        <f>100%-F794</f>
+        <f t="shared" si="14"/>
         <v>0.30000000000000004</v>
       </c>
       <c r="E794" s="4">
@@ -36490,7 +36490,7 @@
         <v>406</v>
       </c>
       <c r="D795" s="3">
-        <f>100%-F795</f>
+        <f t="shared" si="14"/>
         <v>0.30000000000000004</v>
       </c>
       <c r="E795" s="4">
@@ -36532,7 +36532,7 @@
         <v>8000</v>
       </c>
       <c r="D796" s="3">
-        <f>100%-F796</f>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="E796" s="4">
@@ -36574,7 +36574,7 @@
         <v>205</v>
       </c>
       <c r="D797" s="3">
-        <f>100%-F797</f>
+        <f t="shared" si="14"/>
         <v>0.30000000000000004</v>
       </c>
       <c r="E797" s="4">
@@ -36616,7 +36616,7 @@
         <v>1010</v>
       </c>
       <c r="D798" s="3">
-        <f>100%-F798</f>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="E798" s="4">
@@ -36658,7 +36658,7 @@
         <v>607</v>
       </c>
       <c r="D799" s="3">
-        <f>100%-F799</f>
+        <f t="shared" si="14"/>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="E799" s="4">
@@ -36700,7 +36700,7 @@
         <v>212</v>
       </c>
       <c r="D800" s="3">
-        <f>100%-F800</f>
+        <f t="shared" si="14"/>
         <v>0.30000000000000004</v>
       </c>
       <c r="E800" s="4">
@@ -36742,7 +36742,7 @@
         <v>292</v>
       </c>
       <c r="D801" s="3">
-        <f>100%-F801</f>
+        <f t="shared" si="14"/>
         <v>0.22999999999999998</v>
       </c>
       <c r="E801" s="4">
@@ -36784,7 +36784,7 @@
         <v>688</v>
       </c>
       <c r="D802" s="3">
-        <f>100%-F802</f>
+        <f t="shared" si="14"/>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E802" s="4">
@@ -36826,7 +36826,7 @@
         <v>140</v>
       </c>
       <c r="D803" s="3">
-        <f>100%-F803</f>
+        <f t="shared" si="14"/>
         <v>0.72</v>
       </c>
       <c r="E803" s="4">
@@ -36868,7 +36868,7 @@
         <v>127</v>
       </c>
       <c r="D804" s="3">
-        <f>100%-F804</f>
+        <f t="shared" si="14"/>
         <v>0.37</v>
       </c>
       <c r="E804" s="4">
@@ -36910,7 +36910,7 @@
         <v>277</v>
       </c>
       <c r="D805" s="3">
-        <f>100%-F805</f>
+        <f t="shared" si="14"/>
         <v>0.30000000000000004</v>
       </c>
       <c r="E805" s="4">
@@ -36952,7 +36952,7 @@
         <v>862</v>
       </c>
       <c r="D806" s="3">
-        <f>100%-F806</f>
+        <f t="shared" si="14"/>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E806" s="4">
@@ -36994,7 +36994,7 @@
         <v>1402</v>
       </c>
       <c r="D807" s="3">
-        <f>100%-F807</f>
+        <f t="shared" si="14"/>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E807" s="4">
@@ -37036,7 +37036,7 @@
         <v>720</v>
       </c>
       <c r="D808" s="3">
-        <f>100%-F808</f>
+        <f t="shared" si="14"/>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E808" s="4">
@@ -37078,7 +37078,7 @@
         <v>608</v>
       </c>
       <c r="D809" s="3">
-        <f>100%-F809</f>
+        <f t="shared" si="14"/>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E809" s="4">
@@ -37120,7 +37120,7 @@
         <v>241</v>
       </c>
       <c r="D810" s="3">
-        <f>100%-F810</f>
+        <f t="shared" si="14"/>
         <v>0.58000000000000007</v>
       </c>
       <c r="E810" s="4">
@@ -37162,7 +37162,7 @@
         <v>186</v>
       </c>
       <c r="D811" s="3">
-        <f>100%-F811</f>
+        <f t="shared" si="14"/>
         <v>0.30000000000000004</v>
       </c>
       <c r="E811" s="4">
@@ -37204,7 +37204,7 @@
         <v>202</v>
       </c>
       <c r="D812" s="3">
-        <f>100%-F812</f>
+        <f t="shared" si="14"/>
         <v>0.30000000000000004</v>
       </c>
       <c r="E812" s="4">
@@ -37246,7 +37246,7 @@
         <v>1116</v>
       </c>
       <c r="D813" s="3">
-        <f>100%-F813</f>
+        <f t="shared" si="14"/>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E813" s="4">
@@ -37288,7 +37288,7 @@
         <v>215</v>
       </c>
       <c r="D814" s="3">
-        <f>100%-F814</f>
+        <f t="shared" si="14"/>
         <v>0.37</v>
       </c>
       <c r="E814" s="4">
@@ -37330,7 +37330,7 @@
         <v>599</v>
       </c>
       <c r="D815" s="3">
-        <f>100%-F815</f>
+        <f t="shared" si="14"/>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E815" s="4">
@@ -37372,7 +37372,7 @@
         <v>1008.9999999999999</v>
       </c>
       <c r="D816" s="3">
-        <f>100%-F816</f>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="E816" s="4">
@@ -37414,7 +37414,7 @@
         <v>172</v>
       </c>
       <c r="D817" s="3">
-        <f>100%-F817</f>
+        <f t="shared" si="14"/>
         <v>0.30000000000000004</v>
       </c>
       <c r="E817" s="4">
@@ -37456,7 +37456,7 @@
         <v>138</v>
       </c>
       <c r="D818" s="3">
-        <f>100%-F818</f>
+        <f t="shared" si="14"/>
         <v>0.30000000000000004</v>
       </c>
       <c r="E818" s="4">
@@ -37498,7 +37498,7 @@
         <v>561</v>
       </c>
       <c r="D819" s="3">
-        <f>100%-F819</f>
+        <f t="shared" si="14"/>
         <v>0.18000000000000005</v>
       </c>
       <c r="E819" s="4">
@@ -37540,7 +37540,7 @@
         <v>144</v>
       </c>
       <c r="D820" s="3">
-        <f>100%-F820</f>
+        <f t="shared" si="14"/>
         <v>0.30000000000000004</v>
       </c>
       <c r="E820" s="4">
@@ -37582,7 +37582,7 @@
         <v>1180</v>
       </c>
       <c r="D821" s="3">
-        <f>100%-F821</f>
+        <f t="shared" si="14"/>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E821" s="4">
@@ -37624,7 +37624,7 @@
         <v>417</v>
       </c>
       <c r="D822" s="3">
-        <f>100%-F822</f>
+        <f t="shared" si="14"/>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E822" s="4">
@@ -37666,7 +37666,7 @@
         <v>127</v>
       </c>
       <c r="D823" s="3">
-        <f>100%-F823</f>
+        <f t="shared" si="14"/>
         <v>0.22999999999999998</v>
       </c>
       <c r="E823" s="4">
@@ -37708,7 +37708,7 @@
         <v>144</v>
       </c>
       <c r="D824" s="3">
-        <f>100%-F824</f>
+        <f t="shared" si="14"/>
         <v>0.30000000000000004</v>
       </c>
       <c r="E824" s="4">
@@ -37750,7 +37750,7 @@
         <v>1109</v>
       </c>
       <c r="D825" s="3">
-        <f>100%-F825</f>
+        <f t="shared" si="14"/>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E825" s="4">
@@ -37792,7 +37792,7 @@
         <v>1495</v>
       </c>
       <c r="D826" s="3">
-        <f>100%-F826</f>
+        <f t="shared" si="14"/>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E826" s="4">
@@ -37834,7 +37834,7 @@
         <v>701</v>
       </c>
       <c r="D827" s="3">
-        <f>100%-F827</f>
+        <f t="shared" si="14"/>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E827" s="4">
@@ -37876,7 +37876,7 @@
         <v>332</v>
       </c>
       <c r="D828" s="3">
-        <f>100%-F828</f>
+        <f t="shared" si="14"/>
         <v>0.30000000000000004</v>
       </c>
       <c r="E828" s="4">
@@ -37918,7 +37918,7 @@
         <v>352</v>
       </c>
       <c r="D829" s="3">
-        <f>100%-F829</f>
+        <f t="shared" si="14"/>
         <v>0.30000000000000004</v>
       </c>
       <c r="E829" s="4">
@@ -37960,7 +37960,7 @@
         <v>174</v>
       </c>
       <c r="D830" s="3">
-        <f>100%-F830</f>
+        <f t="shared" si="14"/>
         <v>0.65</v>
       </c>
       <c r="E830" s="4">
@@ -38002,7 +38002,7 @@
         <v>2041</v>
       </c>
       <c r="D831" s="3">
-        <f>100%-F831</f>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="E831" s="4">
@@ -38044,7 +38044,7 @@
         <v>371</v>
       </c>
       <c r="D832" s="3">
-        <f>100%-F832</f>
+        <f t="shared" si="14"/>
         <v>0.15000000000000002</v>
       </c>
       <c r="E832" s="4">
@@ -38086,7 +38086,7 @@
         <v>101</v>
       </c>
       <c r="D833" s="3">
-        <f>100%-F833</f>
+        <f t="shared" si="14"/>
         <v>0.37</v>
       </c>
       <c r="E833" s="4">
@@ -38128,7 +38128,7 @@
         <v>4657</v>
       </c>
       <c r="D834" s="3">
-        <f>100%-F834</f>
+        <f t="shared" ref="D834:D877" si="15">100%-F834</f>
         <v>0</v>
       </c>
       <c r="E834" s="4">
@@ -38170,7 +38170,7 @@
         <v>4163</v>
       </c>
       <c r="D835" s="3">
-        <f>100%-F835</f>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="E835" s="4">
@@ -38212,7 +38212,7 @@
         <v>554</v>
       </c>
       <c r="D836" s="3">
-        <f>100%-F836</f>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="E836" s="4">
@@ -38254,7 +38254,7 @@
         <v>301</v>
       </c>
       <c r="D837" s="3">
-        <f>100%-F837</f>
+        <f t="shared" si="15"/>
         <v>0.32999999999999996</v>
       </c>
       <c r="E837" s="4">
@@ -38296,7 +38296,7 @@
         <v>136</v>
       </c>
       <c r="D838" s="3">
-        <f>100%-F838</f>
+        <f t="shared" si="15"/>
         <v>0.30000000000000004</v>
       </c>
       <c r="E838" s="4">
@@ -38338,7 +38338,7 @@
         <v>144</v>
       </c>
       <c r="D839" s="3">
-        <f>100%-F839</f>
+        <f t="shared" si="15"/>
         <v>0.72</v>
       </c>
       <c r="E839" s="4">
@@ -38380,7 +38380,7 @@
         <v>1056</v>
       </c>
       <c r="D840" s="3">
-        <f>100%-F840</f>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="E840" s="4">
@@ -38422,7 +38422,7 @@
         <v>412</v>
       </c>
       <c r="D841" s="3">
-        <f>100%-F841</f>
+        <f t="shared" si="15"/>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="E841" s="4">
@@ -38464,7 +38464,7 @@
         <v>301</v>
       </c>
       <c r="D842" s="3">
-        <f>100%-F842</f>
+        <f t="shared" si="15"/>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="E842" s="4">
@@ -38506,7 +38506,7 @@
         <v>372</v>
       </c>
       <c r="D843" s="3">
-        <f>100%-F843</f>
+        <f t="shared" si="15"/>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="E843" s="4">
@@ -38548,7 +38548,7 @@
         <v>109</v>
       </c>
       <c r="D844" s="3">
-        <f>100%-F844</f>
+        <f t="shared" si="15"/>
         <v>0.38</v>
       </c>
       <c r="E844" s="4">
@@ -38590,7 +38590,7 @@
         <v>344</v>
       </c>
       <c r="D845" s="3">
-        <f>100%-F845</f>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="E845" s="4">
@@ -38632,7 +38632,7 @@
         <v>178</v>
       </c>
       <c r="D846" s="3">
-        <f>100%-F846</f>
+        <f t="shared" si="15"/>
         <v>0.38</v>
       </c>
       <c r="E846" s="4">
@@ -38674,7 +38674,7 @@
         <v>279</v>
       </c>
       <c r="D847" s="3">
-        <f>100%-F847</f>
+        <f t="shared" si="15"/>
         <v>0.30000000000000004</v>
       </c>
       <c r="E847" s="4">
@@ -38716,7 +38716,7 @@
         <v>201</v>
       </c>
       <c r="D848" s="3">
-        <f>100%-F848</f>
+        <f t="shared" si="15"/>
         <v>0.30000000000000004</v>
       </c>
       <c r="E848" s="4">
@@ -38758,7 +38758,7 @@
         <v>620</v>
       </c>
       <c r="D849" s="3">
-        <f>100%-F849</f>
+        <f t="shared" si="15"/>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="E849" s="4">
@@ -38800,7 +38800,7 @@
         <v>285</v>
       </c>
       <c r="D850" s="3">
-        <f>100%-F850</f>
+        <f t="shared" si="15"/>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E850" s="4">
@@ -38842,7 +38842,7 @@
         <v>115</v>
       </c>
       <c r="D851" s="3">
-        <f>100%-F851</f>
+        <f t="shared" si="15"/>
         <v>0.44999999999999996</v>
       </c>
       <c r="E851" s="4">
@@ -38884,7 +38884,7 @@
         <v>885</v>
       </c>
       <c r="D852" s="3">
-        <f>100%-F852</f>
+        <f t="shared" si="15"/>
         <v>0.18000000000000005</v>
       </c>
       <c r="E852" s="4">
@@ -38926,7 +38926,7 @@
         <v>431</v>
       </c>
       <c r="D853" s="3">
-        <f>100%-F853</f>
+        <f t="shared" si="15"/>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="E853" s="4">
@@ -38968,7 +38968,7 @@
         <v>339</v>
       </c>
       <c r="D854" s="3">
-        <f>100%-F854</f>
+        <f t="shared" si="15"/>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E854" s="4">
@@ -39010,7 +39010,7 @@
         <v>176</v>
       </c>
       <c r="D855" s="3">
-        <f>100%-F855</f>
+        <f t="shared" si="15"/>
         <v>0.44999999999999996</v>
       </c>
       <c r="E855" s="4">
@@ -39052,7 +39052,7 @@
         <v>226</v>
       </c>
       <c r="D856" s="3">
-        <f>100%-F856</f>
+        <f t="shared" si="15"/>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="E856" s="4">
@@ -39094,7 +39094,7 @@
         <v>390</v>
       </c>
       <c r="D857" s="3">
-        <f>100%-F857</f>
+        <f t="shared" si="15"/>
         <v>0.22999999999999998</v>
       </c>
       <c r="E857" s="4">
@@ -39136,7 +39136,7 @@
         <v>122</v>
       </c>
       <c r="D858" s="3">
-        <f>100%-F858</f>
+        <f t="shared" si="15"/>
         <v>0.30000000000000004</v>
       </c>
       <c r="E858" s="4">
@@ -39178,7 +39178,7 @@
         <v>469</v>
       </c>
       <c r="D859" s="3">
-        <f>100%-F859</f>
+        <f t="shared" si="15"/>
         <v>0.22999999999999998</v>
       </c>
       <c r="E859" s="4">
@@ -39220,7 +39220,7 @@
         <v>5371</v>
       </c>
       <c r="D860" s="3">
-        <f>100%-F860</f>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="E860" s="4">
@@ -39262,7 +39262,7 @@
         <v>479</v>
       </c>
       <c r="D861" s="3">
-        <f>100%-F861</f>
+        <f t="shared" si="15"/>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="E861" s="4">
@@ -39304,7 +39304,7 @@
         <v>258</v>
       </c>
       <c r="D862" s="3">
-        <f>100%-F862</f>
+        <f t="shared" si="15"/>
         <v>0.30000000000000004</v>
       </c>
       <c r="E862" s="4">
@@ -39346,7 +39346,7 @@
         <v>814</v>
       </c>
       <c r="D863" s="3">
-        <f>100%-F863</f>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="E863" s="4">
@@ -39388,7 +39388,7 @@
         <v>597</v>
       </c>
       <c r="D864" s="3">
-        <f>100%-F864</f>
+        <f t="shared" si="15"/>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="E864" s="4">
@@ -39430,7 +39430,7 @@
         <v>190</v>
       </c>
       <c r="D865" s="3">
-        <f>100%-F865</f>
+        <f t="shared" si="15"/>
         <v>0.21999999999999997</v>
       </c>
       <c r="E865" s="4">
@@ -39472,7 +39472,7 @@
         <v>262</v>
       </c>
       <c r="D866" s="3">
-        <f>100%-F866</f>
+        <f t="shared" si="15"/>
         <v>0.38</v>
       </c>
       <c r="E866" s="4">
@@ -39514,7 +39514,7 @@
         <v>398</v>
       </c>
       <c r="D867" s="3">
-        <f>100%-F867</f>
+        <f t="shared" si="15"/>
         <v>0.38</v>
       </c>
       <c r="E867" s="4">
@@ -39556,7 +39556,7 @@
         <v>657</v>
       </c>
       <c r="D868" s="3">
-        <f>100%-F868</f>
+        <f t="shared" si="15"/>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="E868" s="4">
@@ -39598,7 +39598,7 @@
         <v>450</v>
       </c>
       <c r="D869" s="3">
-        <f>100%-F869</f>
+        <f t="shared" si="15"/>
         <v>0.15000000000000002</v>
       </c>
       <c r="E869" s="4">
@@ -39640,7 +39640,7 @@
         <v>127</v>
       </c>
       <c r="D870" s="3">
-        <f>100%-F870</f>
+        <f t="shared" si="15"/>
         <v>0.57000000000000006</v>
       </c>
       <c r="E870" s="4">
@@ -39682,7 +39682,7 @@
         <v>953</v>
       </c>
       <c r="D871" s="3">
-        <f>100%-F871</f>
+        <f t="shared" si="15"/>
         <v>0.15000000000000002</v>
       </c>
       <c r="E871" s="4">
@@ -39724,7 +39724,7 @@
         <v>296</v>
       </c>
       <c r="D872" s="3">
-        <f>100%-F872</f>
+        <f t="shared" si="15"/>
         <v>0.5</v>
       </c>
       <c r="E872" s="4">
@@ -39766,7 +39766,7 @@
         <v>367</v>
       </c>
       <c r="D873" s="3">
-        <f>100%-F873</f>
+        <f t="shared" si="15"/>
         <v>0.22999999999999998</v>
       </c>
       <c r="E873" s="4">
@@ -39808,7 +39808,7 @@
         <v>521</v>
       </c>
       <c r="D874" s="3">
-        <f>100%-F874</f>
+        <f t="shared" si="15"/>
         <v>0.30000000000000004</v>
       </c>
       <c r="E874" s="4">
@@ -39850,7 +39850,7 @@
         <v>463</v>
       </c>
       <c r="D875" s="3">
-        <f>100%-F875</f>
+        <f t="shared" si="15"/>
         <v>0.38</v>
       </c>
       <c r="E875" s="4">
@@ -39892,7 +39892,7 @@
         <v>296</v>
       </c>
       <c r="D876" s="3">
-        <f>100%-F876</f>
+        <f t="shared" si="15"/>
         <v>0.15000000000000002</v>
       </c>
       <c r="E876" s="4">
@@ -39934,7 +39934,7 @@
         <v>540</v>
       </c>
       <c r="D877" s="3">
-        <f>100%-F877</f>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="E877" s="4">

--- a/content/xls/DB_01.01.2026_NP.xlsx
+++ b/content/xls/DB_01.01.2026_NP.xlsx
@@ -8,13 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Python\InfPanel\content\xls\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B49BFD0-B566-4A75-90C8-C6D260E5D728}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{598C416F-5B01-438D-8633-F50B8066FA6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4012" yWindow="4012" windowWidth="23631" windowHeight="8566" xr2:uid="{CD9FBE00-C105-441E-AC9D-D16C82556AEE}"/>
+    <workbookView xWindow="-111" yWindow="-111" windowWidth="31729" windowHeight="17342" xr2:uid="{CD9FBE00-C105-441E-AC9D-D16C82556AEE}"/>
   </bookViews>
   <sheets>
     <sheet name="sheet01" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">sheet01!$E$1:$E$878</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -2622,31 +2625,31 @@
     <t>Количество банкоматов</t>
   </si>
   <si>
-    <t>Венгеровский муниципальный округ</t>
-  </si>
-  <si>
-    <t>Доволенский муниципальный округ</t>
-  </si>
-  <si>
-    <t>Северный муниципальный округ</t>
-  </si>
-  <si>
-    <t>Сузунский муниципальный округ</t>
-  </si>
-  <si>
-    <t>Убинский муниципальный округ</t>
-  </si>
-  <si>
     <t>п Крещенский</t>
   </si>
   <si>
-    <t>Чановский муниципальный округ</t>
-  </si>
-  <si>
     <t>Уровень потребности в развитии дистанционного банковского обслуживания с учетом альтернативной инфраструктуры</t>
   </si>
   <si>
     <t>Изменение уровня потребности в развитии дистанционного банковского обслуживания за счет альтернативной инфраструктуры, п.п.</t>
+  </si>
+  <si>
+    <t>Венгеровский муниципальный район</t>
+  </si>
+  <si>
+    <t>Доволенский муниципальный район</t>
+  </si>
+  <si>
+    <t>Северный муниципальный район</t>
+  </si>
+  <si>
+    <t>Сузунский муниципальный район</t>
+  </si>
+  <si>
+    <t>Убинский муниципальный район</t>
+  </si>
+  <si>
+    <t>Чановский муниципальный район</t>
   </si>
 </sst>
 </file>
@@ -2659,12 +2662,20 @@
     <numFmt numFmtId="165" formatCode="_-\ #,##0.0_-;\-\ #,##0.0_-;_-\ &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="166" formatCode="_-\ #,##0.00_-;\-\ #,##0.00_-;_-\ &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -2739,10 +2750,10 @@
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -2753,8 +2764,8 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -2774,8 +2785,10 @@
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -3129,7 +3142,7 @@
     <col min="13" max="13" width="12.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" s="1" customFormat="1" ht="162.5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:13" s="1" customFormat="1" ht="132.94999999999999" x14ac:dyDescent="0.3">
       <c r="A1" s="7" t="s">
         <v>853</v>
       </c>
@@ -3140,10 +3153,10 @@
         <v>0</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>869</v>
+        <v>863</v>
       </c>
       <c r="E1" s="7" t="s">
-        <v>870</v>
+        <v>864</v>
       </c>
       <c r="F1" s="7" t="s">
         <v>855</v>
@@ -4196,7 +4209,7 @@
       </c>
     </row>
     <row r="27" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A27" s="14" t="s">
+      <c r="A27" s="15" t="s">
         <v>2</v>
       </c>
       <c r="B27" t="s">
@@ -6657,7 +6670,7 @@
     </row>
     <row r="87" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A87" s="13" t="s">
-        <v>862</v>
+        <v>865</v>
       </c>
       <c r="B87" t="s">
         <v>108</v>
@@ -6698,7 +6711,7 @@
     </row>
     <row r="88" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A88" s="13" t="s">
-        <v>862</v>
+        <v>865</v>
       </c>
       <c r="B88" t="s">
         <v>112</v>
@@ -6739,7 +6752,7 @@
     </row>
     <row r="89" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A89" s="13" t="s">
-        <v>862</v>
+        <v>865</v>
       </c>
       <c r="B89" t="s">
         <v>110</v>
@@ -6780,7 +6793,7 @@
     </row>
     <row r="90" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A90" s="13" t="s">
-        <v>862</v>
+        <v>865</v>
       </c>
       <c r="B90" t="s">
         <v>93</v>
@@ -6821,7 +6834,7 @@
     </row>
     <row r="91" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A91" s="13" t="s">
-        <v>862</v>
+        <v>865</v>
       </c>
       <c r="B91" t="s">
         <v>103</v>
@@ -6862,7 +6875,7 @@
     </row>
     <row r="92" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A92" s="13" t="s">
-        <v>862</v>
+        <v>865</v>
       </c>
       <c r="B92" t="s">
         <v>96</v>
@@ -6903,7 +6916,7 @@
     </row>
     <row r="93" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A93" s="13" t="s">
-        <v>862</v>
+        <v>865</v>
       </c>
       <c r="B93" t="s">
         <v>109</v>
@@ -6944,7 +6957,7 @@
     </row>
     <row r="94" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A94" s="13" t="s">
-        <v>862</v>
+        <v>865</v>
       </c>
       <c r="B94" t="s">
         <v>101</v>
@@ -6985,7 +6998,7 @@
     </row>
     <row r="95" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A95" s="13" t="s">
-        <v>862</v>
+        <v>865</v>
       </c>
       <c r="B95" t="s">
         <v>95</v>
@@ -7026,7 +7039,7 @@
     </row>
     <row r="96" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A96" s="13" t="s">
-        <v>862</v>
+        <v>865</v>
       </c>
       <c r="B96" t="s">
         <v>104</v>
@@ -7067,7 +7080,7 @@
     </row>
     <row r="97" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A97" s="13" t="s">
-        <v>862</v>
+        <v>865</v>
       </c>
       <c r="B97" t="s">
         <v>107</v>
@@ -7108,7 +7121,7 @@
     </row>
     <row r="98" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A98" s="13" t="s">
-        <v>862</v>
+        <v>865</v>
       </c>
       <c r="B98" t="s">
         <v>91</v>
@@ -7149,7 +7162,7 @@
     </row>
     <row r="99" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A99" s="13" t="s">
-        <v>862</v>
+        <v>865</v>
       </c>
       <c r="B99" t="s">
         <v>94</v>
@@ -7190,7 +7203,7 @@
     </row>
     <row r="100" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A100" s="13" t="s">
-        <v>862</v>
+        <v>865</v>
       </c>
       <c r="B100" t="s">
         <v>99</v>
@@ -7231,7 +7244,7 @@
     </row>
     <row r="101" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A101" s="13" t="s">
-        <v>862</v>
+        <v>865</v>
       </c>
       <c r="B101" t="s">
         <v>98</v>
@@ -7272,7 +7285,7 @@
     </row>
     <row r="102" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A102" s="13" t="s">
-        <v>862</v>
+        <v>865</v>
       </c>
       <c r="B102" t="s">
         <v>102</v>
@@ -7313,7 +7326,7 @@
     </row>
     <row r="103" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A103" s="13" t="s">
-        <v>862</v>
+        <v>865</v>
       </c>
       <c r="B103" t="s">
         <v>105</v>
@@ -7354,7 +7367,7 @@
     </row>
     <row r="104" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A104" s="13" t="s">
-        <v>862</v>
+        <v>865</v>
       </c>
       <c r="B104" t="s">
         <v>111</v>
@@ -7395,7 +7408,7 @@
     </row>
     <row r="105" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A105" s="13" t="s">
-        <v>862</v>
+        <v>865</v>
       </c>
       <c r="B105" t="s">
         <v>113</v>
@@ -7436,7 +7449,7 @@
     </row>
     <row r="106" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A106" s="13" t="s">
-        <v>862</v>
+        <v>865</v>
       </c>
       <c r="B106" t="s">
         <v>97</v>
@@ -7477,7 +7490,7 @@
     </row>
     <row r="107" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A107" s="13" t="s">
-        <v>862</v>
+        <v>865</v>
       </c>
       <c r="B107" t="s">
         <v>106</v>
@@ -7518,7 +7531,7 @@
     </row>
     <row r="108" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A108" s="13" t="s">
-        <v>862</v>
+        <v>865</v>
       </c>
       <c r="B108" t="s">
         <v>92</v>
@@ -7559,7 +7572,7 @@
     </row>
     <row r="109" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A109" s="13" t="s">
-        <v>862</v>
+        <v>865</v>
       </c>
       <c r="B109" t="s">
         <v>90</v>
@@ -7600,7 +7613,7 @@
     </row>
     <row r="110" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A110" s="13" t="s">
-        <v>862</v>
+        <v>865</v>
       </c>
       <c r="B110" t="s">
         <v>100</v>
@@ -7641,7 +7654,7 @@
     </row>
     <row r="111" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A111" s="13" t="s">
-        <v>862</v>
+        <v>865</v>
       </c>
       <c r="B111" t="s">
         <v>114</v>
@@ -7682,7 +7695,7 @@
     </row>
     <row r="112" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A112" s="14" t="s">
-        <v>862</v>
+        <v>865</v>
       </c>
       <c r="B112" t="s">
         <v>17</v>
@@ -7723,7 +7736,7 @@
     </row>
     <row r="113" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A113" s="13" t="s">
-        <v>863</v>
+        <v>866</v>
       </c>
       <c r="B113" t="s">
         <v>121</v>
@@ -7764,7 +7777,7 @@
     </row>
     <row r="114" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A114" s="13" t="s">
-        <v>863</v>
+        <v>866</v>
       </c>
       <c r="B114" t="s">
         <v>126</v>
@@ -7805,7 +7818,7 @@
     </row>
     <row r="115" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A115" s="13" t="s">
-        <v>863</v>
+        <v>866</v>
       </c>
       <c r="B115" t="s">
         <v>122</v>
@@ -7846,7 +7859,7 @@
     </row>
     <row r="116" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A116" s="13" t="s">
-        <v>863</v>
+        <v>866</v>
       </c>
       <c r="B116" t="s">
         <v>127</v>
@@ -7887,7 +7900,7 @@
     </row>
     <row r="117" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A117" s="13" t="s">
-        <v>863</v>
+        <v>866</v>
       </c>
       <c r="B117" t="s">
         <v>116</v>
@@ -7928,7 +7941,7 @@
     </row>
     <row r="118" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A118" s="13" t="s">
-        <v>863</v>
+        <v>866</v>
       </c>
       <c r="B118" t="s">
         <v>115</v>
@@ -7969,7 +7982,7 @@
     </row>
     <row r="119" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A119" s="13" t="s">
-        <v>863</v>
+        <v>866</v>
       </c>
       <c r="B119" t="s">
         <v>117</v>
@@ -8010,7 +8023,7 @@
     </row>
     <row r="120" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A120" s="13" t="s">
-        <v>863</v>
+        <v>866</v>
       </c>
       <c r="B120" t="s">
         <v>119</v>
@@ -8051,7 +8064,7 @@
     </row>
     <row r="121" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A121" s="13" t="s">
-        <v>863</v>
+        <v>866</v>
       </c>
       <c r="B121" t="s">
         <v>130</v>
@@ -8092,7 +8105,7 @@
     </row>
     <row r="122" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A122" s="13" t="s">
-        <v>863</v>
+        <v>866</v>
       </c>
       <c r="B122" t="s">
         <v>124</v>
@@ -8133,7 +8146,7 @@
     </row>
     <row r="123" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A123" s="13" t="s">
-        <v>863</v>
+        <v>866</v>
       </c>
       <c r="B123" t="s">
         <v>129</v>
@@ -8174,7 +8187,7 @@
     </row>
     <row r="124" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A124" s="13" t="s">
-        <v>863</v>
+        <v>866</v>
       </c>
       <c r="B124" t="s">
         <v>125</v>
@@ -8215,7 +8228,7 @@
     </row>
     <row r="125" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A125" s="13" t="s">
-        <v>863</v>
+        <v>866</v>
       </c>
       <c r="B125" t="s">
         <v>118</v>
@@ -8256,7 +8269,7 @@
     </row>
     <row r="126" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A126" s="13" t="s">
-        <v>863</v>
+        <v>866</v>
       </c>
       <c r="B126" t="s">
         <v>123</v>
@@ -8297,7 +8310,7 @@
     </row>
     <row r="127" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A127" s="13" t="s">
-        <v>863</v>
+        <v>866</v>
       </c>
       <c r="B127" t="s">
         <v>120</v>
@@ -8338,7 +8351,7 @@
     </row>
     <row r="128" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A128" s="14" t="s">
-        <v>863</v>
+        <v>866</v>
       </c>
       <c r="B128" t="s">
         <v>128</v>
@@ -14992,7 +15005,7 @@
         <v>0.25</v>
       </c>
       <c r="E290" s="12">
-        <v>3</v>
+        <v>-3</v>
       </c>
       <c r="F290" s="3">
         <v>0.72</v>
@@ -15197,7 +15210,7 @@
         <v>0.2</v>
       </c>
       <c r="E295" s="12">
-        <v>3</v>
+        <v>-3</v>
       </c>
       <c r="F295" s="3">
         <v>0.77</v>
@@ -15361,7 +15374,7 @@
         <v>0.08</v>
       </c>
       <c r="E299" s="12">
-        <v>2</v>
+        <v>-2</v>
       </c>
       <c r="F299" s="3">
         <v>0.9</v>
@@ -15443,7 +15456,7 @@
         <v>0.08</v>
       </c>
       <c r="E301" s="12">
-        <v>2</v>
+        <v>-2</v>
       </c>
       <c r="F301" s="3">
         <v>0.9</v>
@@ -16550,7 +16563,7 @@
         <v>0.34</v>
       </c>
       <c r="E328" s="12">
-        <v>4</v>
+        <v>-4</v>
       </c>
       <c r="F328" s="3">
         <v>0.62</v>
@@ -16632,7 +16645,7 @@
         <v>0.27</v>
       </c>
       <c r="E330" s="12">
-        <v>3</v>
+        <v>-3</v>
       </c>
       <c r="F330" s="3">
         <v>0.7</v>
@@ -16673,7 +16686,7 @@
         <v>0.27</v>
       </c>
       <c r="E331" s="12">
-        <v>3</v>
+        <v>-3</v>
       </c>
       <c r="F331" s="3">
         <v>0.7</v>
@@ -16796,7 +16809,7 @@
         <v>0.27</v>
       </c>
       <c r="E334" s="12">
-        <v>3</v>
+        <v>-3</v>
       </c>
       <c r="F334" s="3">
         <v>0.7</v>
@@ -16919,7 +16932,7 @@
         <v>0.18</v>
       </c>
       <c r="E337" s="12">
-        <v>3</v>
+        <v>-3</v>
       </c>
       <c r="F337" s="3">
         <v>0.79</v>
@@ -17001,7 +17014,7 @@
         <v>0.08</v>
       </c>
       <c r="E339" s="12">
-        <v>2</v>
+        <v>-2</v>
       </c>
       <c r="F339" s="3">
         <v>0.9</v>
@@ -17083,7 +17096,7 @@
         <v>0.08</v>
       </c>
       <c r="E341" s="12">
-        <v>2</v>
+        <v>-2</v>
       </c>
       <c r="F341" s="3">
         <v>0.9</v>
@@ -17124,7 +17137,7 @@
         <v>0.08</v>
       </c>
       <c r="E342" s="12">
-        <v>2</v>
+        <v>-2</v>
       </c>
       <c r="F342" s="3">
         <v>0.9</v>
@@ -17247,7 +17260,7 @@
         <v>0.08</v>
       </c>
       <c r="E345" s="12">
-        <v>2</v>
+        <v>-2</v>
       </c>
       <c r="F345" s="3">
         <v>0.9</v>
@@ -17780,7 +17793,7 @@
         <v>0.34</v>
       </c>
       <c r="E358" s="12">
-        <v>6</v>
+        <v>-6</v>
       </c>
       <c r="F358" s="3">
         <v>0.60000000000000009</v>
@@ -17862,7 +17875,7 @@
         <v>0.34</v>
       </c>
       <c r="E360" s="12">
-        <v>4</v>
+        <v>-4</v>
       </c>
       <c r="F360" s="3">
         <v>0.62</v>
@@ -18313,7 +18326,7 @@
         <v>0.08</v>
       </c>
       <c r="E371" s="12">
-        <v>2</v>
+        <v>-2</v>
       </c>
       <c r="F371" s="3">
         <v>0.9</v>
@@ -21388,7 +21401,7 @@
         <v>0.08</v>
       </c>
       <c r="E446" s="12">
-        <v>2</v>
+        <v>-2</v>
       </c>
       <c r="F446" s="3">
         <v>0.9</v>
@@ -21470,7 +21483,7 @@
         <v>0.08</v>
       </c>
       <c r="E448" s="12">
-        <v>2</v>
+        <v>-2</v>
       </c>
       <c r="F448" s="3">
         <v>0.9</v>
@@ -21511,7 +21524,7 @@
         <v>0.08</v>
       </c>
       <c r="E449" s="12">
-        <v>2</v>
+        <v>-2</v>
       </c>
       <c r="F449" s="3">
         <v>0.9</v>
@@ -21716,7 +21729,7 @@
         <v>0.03</v>
       </c>
       <c r="E454" s="12">
-        <v>2</v>
+        <v>-2</v>
       </c>
       <c r="F454" s="3">
         <v>0.95</v>
@@ -21757,7 +21770,7 @@
         <v>0.03</v>
       </c>
       <c r="E455" s="12">
-        <v>2</v>
+        <v>-2</v>
       </c>
       <c r="F455" s="3">
         <v>0.95000000000000007</v>
@@ -27116,7 +27129,7 @@
     </row>
     <row r="586" spans="1:16" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A586" s="13" t="s">
-        <v>864</v>
+        <v>867</v>
       </c>
       <c r="B586" t="s">
         <v>595</v>
@@ -27158,7 +27171,7 @@
     </row>
     <row r="587" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A587" s="13" t="s">
-        <v>864</v>
+        <v>867</v>
       </c>
       <c r="B587" t="s">
         <v>591</v>
@@ -27199,7 +27212,7 @@
     </row>
     <row r="588" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A588" s="13" t="s">
-        <v>864</v>
+        <v>867</v>
       </c>
       <c r="B588" t="s">
         <v>270</v>
@@ -27240,7 +27253,7 @@
     </row>
     <row r="589" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A589" s="13" t="s">
-        <v>864</v>
+        <v>867</v>
       </c>
       <c r="B589" t="s">
         <v>586</v>
@@ -27281,7 +27294,7 @@
     </row>
     <row r="590" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A590" s="13" t="s">
-        <v>864</v>
+        <v>867</v>
       </c>
       <c r="B590" t="s">
         <v>590</v>
@@ -27322,7 +27335,7 @@
     </row>
     <row r="591" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A591" s="13" t="s">
-        <v>864</v>
+        <v>867</v>
       </c>
       <c r="B591" t="s">
         <v>584</v>
@@ -27363,7 +27376,7 @@
     </row>
     <row r="592" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A592" s="13" t="s">
-        <v>864</v>
+        <v>867</v>
       </c>
       <c r="B592" t="s">
         <v>587</v>
@@ -27404,7 +27417,7 @@
     </row>
     <row r="593" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A593" s="13" t="s">
-        <v>864</v>
+        <v>867</v>
       </c>
       <c r="B593" t="s">
         <v>585</v>
@@ -27445,7 +27458,7 @@
     </row>
     <row r="594" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A594" s="13" t="s">
-        <v>864</v>
+        <v>867</v>
       </c>
       <c r="B594" t="s">
         <v>589</v>
@@ -27486,7 +27499,7 @@
     </row>
     <row r="595" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A595" s="13" t="s">
-        <v>864</v>
+        <v>867</v>
       </c>
       <c r="B595" t="s">
         <v>592</v>
@@ -27527,7 +27540,7 @@
     </row>
     <row r="596" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A596" s="13" t="s">
-        <v>864</v>
+        <v>867</v>
       </c>
       <c r="B596" t="s">
         <v>593</v>
@@ -27568,7 +27581,7 @@
     </row>
     <row r="597" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A597" s="13" t="s">
-        <v>864</v>
+        <v>867</v>
       </c>
       <c r="B597" t="s">
         <v>594</v>
@@ -27609,7 +27622,7 @@
     </row>
     <row r="598" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A598" s="14" t="s">
-        <v>864</v>
+        <v>867</v>
       </c>
       <c r="B598" t="s">
         <v>588</v>
@@ -27650,7 +27663,7 @@
     </row>
     <row r="599" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A599" s="13" t="s">
-        <v>865</v>
+        <v>868</v>
       </c>
       <c r="B599" t="s">
         <v>611</v>
@@ -27691,7 +27704,7 @@
     </row>
     <row r="600" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A600" s="13" t="s">
-        <v>865</v>
+        <v>868</v>
       </c>
       <c r="B600" t="s">
         <v>612</v>
@@ -27732,7 +27745,7 @@
     </row>
     <row r="601" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A601" s="13" t="s">
-        <v>865</v>
+        <v>868</v>
       </c>
       <c r="B601" t="s">
         <v>599</v>
@@ -27773,7 +27786,7 @@
     </row>
     <row r="602" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A602" s="13" t="s">
-        <v>865</v>
+        <v>868</v>
       </c>
       <c r="B602" t="s">
         <v>618</v>
@@ -27814,7 +27827,7 @@
     </row>
     <row r="603" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A603" s="13" t="s">
-        <v>865</v>
+        <v>868</v>
       </c>
       <c r="B603" t="s">
         <v>620</v>
@@ -27855,7 +27868,7 @@
     </row>
     <row r="604" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A604" s="13" t="s">
-        <v>865</v>
+        <v>868</v>
       </c>
       <c r="B604" t="s">
         <v>609</v>
@@ -27896,7 +27909,7 @@
     </row>
     <row r="605" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A605" s="13" t="s">
-        <v>865</v>
+        <v>868</v>
       </c>
       <c r="B605" t="s">
         <v>622</v>
@@ -27937,7 +27950,7 @@
     </row>
     <row r="606" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A606" s="13" t="s">
-        <v>865</v>
+        <v>868</v>
       </c>
       <c r="B606" t="s">
         <v>596</v>
@@ -27978,7 +27991,7 @@
     </row>
     <row r="607" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A607" s="13" t="s">
-        <v>865</v>
+        <v>868</v>
       </c>
       <c r="B607" t="s">
         <v>616</v>
@@ -28019,7 +28032,7 @@
     </row>
     <row r="608" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A608" s="13" t="s">
-        <v>865</v>
+        <v>868</v>
       </c>
       <c r="B608" t="s">
         <v>604</v>
@@ -28060,7 +28073,7 @@
     </row>
     <row r="609" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A609" s="13" t="s">
-        <v>865</v>
+        <v>868</v>
       </c>
       <c r="B609" t="s">
         <v>607</v>
@@ -28101,7 +28114,7 @@
     </row>
     <row r="610" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A610" s="13" t="s">
-        <v>865</v>
+        <v>868</v>
       </c>
       <c r="B610" t="s">
         <v>601</v>
@@ -28142,7 +28155,7 @@
     </row>
     <row r="611" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A611" s="13" t="s">
-        <v>865</v>
+        <v>868</v>
       </c>
       <c r="B611" t="s">
         <v>613</v>
@@ -28183,7 +28196,7 @@
     </row>
     <row r="612" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A612" s="13" t="s">
-        <v>865</v>
+        <v>868</v>
       </c>
       <c r="B612" t="s">
         <v>606</v>
@@ -28224,7 +28237,7 @@
     </row>
     <row r="613" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A613" s="13" t="s">
-        <v>865</v>
+        <v>868</v>
       </c>
       <c r="B613" t="s">
         <v>605</v>
@@ -28265,7 +28278,7 @@
     </row>
     <row r="614" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A614" s="13" t="s">
-        <v>865</v>
+        <v>868</v>
       </c>
       <c r="B614" t="s">
         <v>608</v>
@@ -28306,7 +28319,7 @@
     </row>
     <row r="615" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A615" s="13" t="s">
-        <v>865</v>
+        <v>868</v>
       </c>
       <c r="B615" t="s">
         <v>597</v>
@@ -28347,7 +28360,7 @@
     </row>
     <row r="616" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A616" s="13" t="s">
-        <v>865</v>
+        <v>868</v>
       </c>
       <c r="B616" t="s">
         <v>615</v>
@@ -28388,7 +28401,7 @@
     </row>
     <row r="617" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A617" s="13" t="s">
-        <v>865</v>
+        <v>868</v>
       </c>
       <c r="B617" t="s">
         <v>600</v>
@@ -28429,7 +28442,7 @@
     </row>
     <row r="618" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A618" s="13" t="s">
-        <v>865</v>
+        <v>868</v>
       </c>
       <c r="B618" t="s">
         <v>617</v>
@@ -28470,7 +28483,7 @@
     </row>
     <row r="619" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A619" s="13" t="s">
-        <v>865</v>
+        <v>868</v>
       </c>
       <c r="B619" t="s">
         <v>602</v>
@@ -28511,7 +28524,7 @@
     </row>
     <row r="620" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A620" s="13" t="s">
-        <v>865</v>
+        <v>868</v>
       </c>
       <c r="B620" t="s">
         <v>623</v>
@@ -28552,7 +28565,7 @@
     </row>
     <row r="621" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A621" s="13" t="s">
-        <v>865</v>
+        <v>868</v>
       </c>
       <c r="B621" t="s">
         <v>619</v>
@@ -28593,7 +28606,7 @@
     </row>
     <row r="622" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A622" s="13" t="s">
-        <v>865</v>
+        <v>868</v>
       </c>
       <c r="B622" t="s">
         <v>610</v>
@@ -28634,7 +28647,7 @@
     </row>
     <row r="623" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A623" s="13" t="s">
-        <v>865</v>
+        <v>868</v>
       </c>
       <c r="B623" t="s">
         <v>614</v>
@@ -28675,7 +28688,7 @@
     </row>
     <row r="624" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A624" s="13" t="s">
-        <v>865</v>
+        <v>868</v>
       </c>
       <c r="B624" t="s">
         <v>621</v>
@@ -28716,7 +28729,7 @@
     </row>
     <row r="625" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A625" s="13" t="s">
-        <v>865</v>
+        <v>868</v>
       </c>
       <c r="B625" t="s">
         <v>603</v>
@@ -28757,7 +28770,7 @@
     </row>
     <row r="626" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A626" s="14" t="s">
-        <v>865</v>
+        <v>868</v>
       </c>
       <c r="B626" t="s">
         <v>598</v>
@@ -29015,7 +29028,7 @@
         <v>0.41</v>
       </c>
       <c r="E632" s="12">
-        <v>4</v>
+        <v>-4</v>
       </c>
       <c r="F632" s="3">
         <v>0.55000000000000004</v>
@@ -29138,7 +29151,7 @@
         <v>0.34</v>
       </c>
       <c r="E635" s="12">
-        <v>4</v>
+        <v>-4</v>
       </c>
       <c r="F635" s="3">
         <v>0.62</v>
@@ -29261,7 +29274,7 @@
         <v>0.34</v>
       </c>
       <c r="E638" s="12">
-        <v>4</v>
+        <v>-4</v>
       </c>
       <c r="F638" s="3">
         <v>0.62</v>
@@ -29302,7 +29315,7 @@
         <v>0.34</v>
       </c>
       <c r="E639" s="12">
-        <v>4</v>
+        <v>-4</v>
       </c>
       <c r="F639" s="3">
         <v>0.62</v>
@@ -29384,7 +29397,7 @@
         <v>0.34</v>
       </c>
       <c r="E641" s="12">
-        <v>4</v>
+        <v>-4</v>
       </c>
       <c r="F641" s="3">
         <v>0.62</v>
@@ -29425,7 +29438,7 @@
         <v>0.33</v>
       </c>
       <c r="E642" s="12">
-        <v>4</v>
+        <v>-4</v>
       </c>
       <c r="F642" s="3">
         <v>0.63</v>
@@ -29466,7 +29479,7 @@
         <v>0.28999999999999998</v>
       </c>
       <c r="E643" s="12">
-        <v>4</v>
+        <v>-4</v>
       </c>
       <c r="F643" s="3">
         <v>0.67</v>
@@ -29589,7 +29602,7 @@
         <v>0.27</v>
       </c>
       <c r="E646" s="12">
-        <v>3</v>
+        <v>-3</v>
       </c>
       <c r="F646" s="3">
         <v>0.7</v>
@@ -29835,7 +29848,7 @@
         <v>0.08</v>
       </c>
       <c r="E652" s="12">
-        <v>2</v>
+        <v>-2</v>
       </c>
       <c r="F652" s="3">
         <v>0.9</v>
@@ -29876,7 +29889,7 @@
         <v>0.08</v>
       </c>
       <c r="E653" s="12">
-        <v>2</v>
+        <v>-2</v>
       </c>
       <c r="F653" s="3">
         <v>0.9</v>
@@ -32652,10 +32665,10 @@
     </row>
     <row r="721" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A721" s="13" t="s">
-        <v>866</v>
+        <v>869</v>
       </c>
       <c r="B721" t="s">
-        <v>867</v>
+        <v>862</v>
       </c>
       <c r="C721" s="9">
         <v>232</v>
@@ -32693,7 +32706,7 @@
     </row>
     <row r="722" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A722" s="13" t="s">
-        <v>866</v>
+        <v>869</v>
       </c>
       <c r="B722" t="s">
         <v>716</v>
@@ -32734,7 +32747,7 @@
     </row>
     <row r="723" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A723" s="13" t="s">
-        <v>866</v>
+        <v>869</v>
       </c>
       <c r="B723" t="s">
         <v>724</v>
@@ -32775,7 +32788,7 @@
     </row>
     <row r="724" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A724" s="13" t="s">
-        <v>866</v>
+        <v>869</v>
       </c>
       <c r="B724" t="s">
         <v>718</v>
@@ -32816,7 +32829,7 @@
     </row>
     <row r="725" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A725" s="13" t="s">
-        <v>866</v>
+        <v>869</v>
       </c>
       <c r="B725" t="s">
         <v>713</v>
@@ -32857,7 +32870,7 @@
     </row>
     <row r="726" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A726" s="13" t="s">
-        <v>866</v>
+        <v>869</v>
       </c>
       <c r="B726" t="s">
         <v>715</v>
@@ -32898,7 +32911,7 @@
     </row>
     <row r="727" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A727" s="13" t="s">
-        <v>866</v>
+        <v>869</v>
       </c>
       <c r="B727" t="s">
         <v>727</v>
@@ -32939,7 +32952,7 @@
     </row>
     <row r="728" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A728" s="13" t="s">
-        <v>866</v>
+        <v>869</v>
       </c>
       <c r="B728" t="s">
         <v>720</v>
@@ -32980,7 +32993,7 @@
     </row>
     <row r="729" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A729" s="13" t="s">
-        <v>866</v>
+        <v>869</v>
       </c>
       <c r="B729" t="s">
         <v>725</v>
@@ -33021,7 +33034,7 @@
     </row>
     <row r="730" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A730" s="13" t="s">
-        <v>866</v>
+        <v>869</v>
       </c>
       <c r="B730" t="s">
         <v>719</v>
@@ -33062,7 +33075,7 @@
     </row>
     <row r="731" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A731" s="13" t="s">
-        <v>866</v>
+        <v>869</v>
       </c>
       <c r="B731" t="s">
         <v>722</v>
@@ -33103,7 +33116,7 @@
     </row>
     <row r="732" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A732" s="13" t="s">
-        <v>866</v>
+        <v>869</v>
       </c>
       <c r="B732" t="s">
         <v>721</v>
@@ -33144,7 +33157,7 @@
     </row>
     <row r="733" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A733" s="13" t="s">
-        <v>866</v>
+        <v>869</v>
       </c>
       <c r="B733" t="s">
         <v>726</v>
@@ -33185,7 +33198,7 @@
     </row>
     <row r="734" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A734" s="13" t="s">
-        <v>866</v>
+        <v>869</v>
       </c>
       <c r="B734" t="s">
         <v>717</v>
@@ -33226,7 +33239,7 @@
     </row>
     <row r="735" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A735" s="13" t="s">
-        <v>866</v>
+        <v>869</v>
       </c>
       <c r="B735" t="s">
         <v>723</v>
@@ -33267,7 +33280,7 @@
     </row>
     <row r="736" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A736" s="14" t="s">
-        <v>866</v>
+        <v>869</v>
       </c>
       <c r="B736" t="s">
         <v>714</v>
@@ -34045,8 +34058,8 @@
       </c>
     </row>
     <row r="755" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A755" s="13" t="s">
-        <v>868</v>
+      <c r="A755" s="16" t="s">
+        <v>870</v>
       </c>
       <c r="B755" t="s">
         <v>772</v>
@@ -34086,8 +34099,8 @@
       </c>
     </row>
     <row r="756" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A756" s="13" t="s">
-        <v>868</v>
+      <c r="A756" s="16" t="s">
+        <v>870</v>
       </c>
       <c r="B756" t="s">
         <v>767</v>
@@ -34127,8 +34140,8 @@
       </c>
     </row>
     <row r="757" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A757" s="13" t="s">
-        <v>868</v>
+      <c r="A757" s="16" t="s">
+        <v>870</v>
       </c>
       <c r="B757" t="s">
         <v>753</v>
@@ -34168,8 +34181,8 @@
       </c>
     </row>
     <row r="758" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A758" s="13" t="s">
-        <v>868</v>
+      <c r="A758" s="16" t="s">
+        <v>870</v>
       </c>
       <c r="B758" t="s">
         <v>774</v>
@@ -34209,8 +34222,8 @@
       </c>
     </row>
     <row r="759" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A759" s="13" t="s">
-        <v>868</v>
+      <c r="A759" s="16" t="s">
+        <v>870</v>
       </c>
       <c r="B759" t="s">
         <v>751</v>
@@ -34250,8 +34263,8 @@
       </c>
     </row>
     <row r="760" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A760" s="13" t="s">
-        <v>868</v>
+      <c r="A760" s="16" t="s">
+        <v>870</v>
       </c>
       <c r="B760" t="s">
         <v>760</v>
@@ -34291,8 +34304,8 @@
       </c>
     </row>
     <row r="761" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A761" s="13" t="s">
-        <v>868</v>
+      <c r="A761" s="16" t="s">
+        <v>870</v>
       </c>
       <c r="B761" t="s">
         <v>756</v>
@@ -34332,8 +34345,8 @@
       </c>
     </row>
     <row r="762" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A762" s="13" t="s">
-        <v>868</v>
+      <c r="A762" s="16" t="s">
+        <v>870</v>
       </c>
       <c r="B762" t="s">
         <v>777</v>
@@ -34373,8 +34386,8 @@
       </c>
     </row>
     <row r="763" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A763" s="13" t="s">
-        <v>868</v>
+      <c r="A763" s="16" t="s">
+        <v>870</v>
       </c>
       <c r="B763" t="s">
         <v>748</v>
@@ -34414,8 +34427,8 @@
       </c>
     </row>
     <row r="764" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A764" s="13" t="s">
-        <v>868</v>
+      <c r="A764" s="16" t="s">
+        <v>870</v>
       </c>
       <c r="B764" t="s">
         <v>754</v>
@@ -34455,8 +34468,8 @@
       </c>
     </row>
     <row r="765" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A765" s="13" t="s">
-        <v>868</v>
+      <c r="A765" s="16" t="s">
+        <v>870</v>
       </c>
       <c r="B765" t="s">
         <v>765</v>
@@ -34496,8 +34509,8 @@
       </c>
     </row>
     <row r="766" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A766" s="13" t="s">
-        <v>868</v>
+      <c r="A766" s="16" t="s">
+        <v>870</v>
       </c>
       <c r="B766" t="s">
         <v>121</v>
@@ -34537,8 +34550,8 @@
       </c>
     </row>
     <row r="767" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A767" s="13" t="s">
-        <v>868</v>
+      <c r="A767" s="16" t="s">
+        <v>870</v>
       </c>
       <c r="B767" t="s">
         <v>779</v>
@@ -34578,8 +34591,8 @@
       </c>
     </row>
     <row r="768" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A768" s="13" t="s">
-        <v>868</v>
+      <c r="A768" s="16" t="s">
+        <v>870</v>
       </c>
       <c r="B768" t="s">
         <v>757</v>
@@ -34619,8 +34632,8 @@
       </c>
     </row>
     <row r="769" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A769" s="13" t="s">
-        <v>868</v>
+      <c r="A769" s="16" t="s">
+        <v>870</v>
       </c>
       <c r="B769" t="s">
         <v>733</v>
@@ -34660,8 +34673,8 @@
       </c>
     </row>
     <row r="770" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A770" s="13" t="s">
-        <v>868</v>
+      <c r="A770" s="16" t="s">
+        <v>870</v>
       </c>
       <c r="B770" t="s">
         <v>759</v>
@@ -34701,8 +34714,8 @@
       </c>
     </row>
     <row r="771" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A771" s="13" t="s">
-        <v>868</v>
+      <c r="A771" s="16" t="s">
+        <v>870</v>
       </c>
       <c r="B771" t="s">
         <v>771</v>
@@ -34742,8 +34755,8 @@
       </c>
     </row>
     <row r="772" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A772" s="13" t="s">
-        <v>868</v>
+      <c r="A772" s="16" t="s">
+        <v>870</v>
       </c>
       <c r="B772" t="s">
         <v>745</v>
@@ -34783,8 +34796,8 @@
       </c>
     </row>
     <row r="773" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A773" s="13" t="s">
-        <v>868</v>
+      <c r="A773" s="16" t="s">
+        <v>870</v>
       </c>
       <c r="B773" t="s">
         <v>770</v>
@@ -34824,8 +34837,8 @@
       </c>
     </row>
     <row r="774" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A774" s="13" t="s">
-        <v>868</v>
+      <c r="A774" s="16" t="s">
+        <v>870</v>
       </c>
       <c r="B774" t="s">
         <v>763</v>
@@ -34865,8 +34878,8 @@
       </c>
     </row>
     <row r="775" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A775" s="13" t="s">
-        <v>868</v>
+      <c r="A775" s="16" t="s">
+        <v>870</v>
       </c>
       <c r="B775" t="s">
         <v>744</v>
@@ -34906,8 +34919,8 @@
       </c>
     </row>
     <row r="776" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A776" s="13" t="s">
-        <v>868</v>
+      <c r="A776" s="16" t="s">
+        <v>870</v>
       </c>
       <c r="B776" t="s">
         <v>752</v>
@@ -34947,8 +34960,8 @@
       </c>
     </row>
     <row r="777" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A777" s="13" t="s">
-        <v>868</v>
+      <c r="A777" s="16" t="s">
+        <v>870</v>
       </c>
       <c r="B777" t="s">
         <v>768</v>
@@ -34988,8 +35001,8 @@
       </c>
     </row>
     <row r="778" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A778" s="13" t="s">
-        <v>868</v>
+      <c r="A778" s="16" t="s">
+        <v>870</v>
       </c>
       <c r="B778" t="s">
         <v>780</v>
@@ -35029,8 +35042,8 @@
       </c>
     </row>
     <row r="779" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A779" s="13" t="s">
-        <v>868</v>
+      <c r="A779" s="16" t="s">
+        <v>870</v>
       </c>
       <c r="B779" t="s">
         <v>776</v>
@@ -35070,8 +35083,8 @@
       </c>
     </row>
     <row r="780" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A780" s="13" t="s">
-        <v>868</v>
+      <c r="A780" s="16" t="s">
+        <v>870</v>
       </c>
       <c r="B780" t="s">
         <v>762</v>
@@ -35111,8 +35124,8 @@
       </c>
     </row>
     <row r="781" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A781" s="13" t="s">
-        <v>868</v>
+      <c r="A781" s="16" t="s">
+        <v>870</v>
       </c>
       <c r="B781" t="s">
         <v>749</v>
@@ -35152,8 +35165,8 @@
       </c>
     </row>
     <row r="782" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A782" s="13" t="s">
-        <v>868</v>
+      <c r="A782" s="16" t="s">
+        <v>870</v>
       </c>
       <c r="B782" t="s">
         <v>126</v>
@@ -35193,8 +35206,8 @@
       </c>
     </row>
     <row r="783" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A783" s="13" t="s">
-        <v>868</v>
+      <c r="A783" s="16" t="s">
+        <v>870</v>
       </c>
       <c r="B783" t="s">
         <v>761</v>
@@ -35234,8 +35247,8 @@
       </c>
     </row>
     <row r="784" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A784" s="13" t="s">
-        <v>868</v>
+      <c r="A784" s="16" t="s">
+        <v>870</v>
       </c>
       <c r="B784" t="s">
         <v>769</v>
@@ -35275,8 +35288,8 @@
       </c>
     </row>
     <row r="785" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A785" s="13" t="s">
-        <v>868</v>
+      <c r="A785" s="16" t="s">
+        <v>870</v>
       </c>
       <c r="B785" t="s">
         <v>746</v>
@@ -35316,8 +35329,8 @@
       </c>
     </row>
     <row r="786" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A786" s="13" t="s">
-        <v>868</v>
+      <c r="A786" s="16" t="s">
+        <v>870</v>
       </c>
       <c r="B786" t="s">
         <v>758</v>
@@ -35357,8 +35370,8 @@
       </c>
     </row>
     <row r="787" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A787" s="13" t="s">
-        <v>868</v>
+      <c r="A787" s="16" t="s">
+        <v>870</v>
       </c>
       <c r="B787" t="s">
         <v>766</v>
@@ -35398,8 +35411,8 @@
       </c>
     </row>
     <row r="788" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A788" s="13" t="s">
-        <v>868</v>
+      <c r="A788" s="16" t="s">
+        <v>870</v>
       </c>
       <c r="B788" t="s">
         <v>775</v>
@@ -35439,8 +35452,8 @@
       </c>
     </row>
     <row r="789" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A789" s="13" t="s">
-        <v>868</v>
+      <c r="A789" s="16" t="s">
+        <v>870</v>
       </c>
       <c r="B789" t="s">
         <v>747</v>
@@ -35480,8 +35493,8 @@
       </c>
     </row>
     <row r="790" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A790" s="13" t="s">
-        <v>868</v>
+      <c r="A790" s="16" t="s">
+        <v>870</v>
       </c>
       <c r="B790" t="s">
         <v>764</v>
@@ -35521,8 +35534,8 @@
       </c>
     </row>
     <row r="791" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A791" s="13" t="s">
-        <v>868</v>
+      <c r="A791" s="16" t="s">
+        <v>870</v>
       </c>
       <c r="B791" t="s">
         <v>773</v>
@@ -35562,8 +35575,8 @@
       </c>
     </row>
     <row r="792" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A792" s="13" t="s">
-        <v>868</v>
+      <c r="A792" s="16" t="s">
+        <v>870</v>
       </c>
       <c r="B792" t="s">
         <v>778</v>
@@ -35603,8 +35616,8 @@
       </c>
     </row>
     <row r="793" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A793" s="13" t="s">
-        <v>868</v>
+      <c r="A793" s="16" t="s">
+        <v>870</v>
       </c>
       <c r="B793" t="s">
         <v>755</v>
@@ -35644,8 +35657,8 @@
       </c>
     </row>
     <row r="794" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A794" s="13" t="s">
-        <v>868</v>
+      <c r="A794" s="16" t="s">
+        <v>870</v>
       </c>
       <c r="B794" t="s">
         <v>750</v>
@@ -35685,8 +35698,8 @@
       </c>
     </row>
     <row r="795" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A795" s="14" t="s">
-        <v>868</v>
+      <c r="A795" s="16" t="s">
+        <v>870</v>
       </c>
       <c r="B795" t="s">
         <v>781</v>

--- a/content/xls/DB_01.01.2026_NP.xlsx
+++ b/content/xls/DB_01.01.2026_NP.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Python\InfPanel\content\xls\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{598C416F-5B01-438D-8633-F50B8066FA6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91BE0CC8-BEBC-4BD5-A1F7-7597ED2CE4EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-111" yWindow="-111" windowWidth="31729" windowHeight="17342" xr2:uid="{CD9FBE00-C105-441E-AC9D-D16C82556AEE}"/>
   </bookViews>
@@ -2610,9 +2610,6 @@
     <t>Изменение уровня финансовой доступности к предыдущей отчетной дате, п.п.</t>
   </si>
   <si>
-    <t>Количество Финансовых помощников</t>
-  </si>
-  <si>
     <t>Количество торговых точек с сервисом "Выдача наличных на кассе"</t>
   </si>
   <si>
@@ -2650,6 +2647,9 @@
   </si>
   <si>
     <t>Чановский муниципальный район</t>
+  </si>
+  <si>
+    <t>Количество финансовых помощников</t>
   </si>
 </sst>
 </file>
@@ -3153,10 +3153,10 @@
         <v>0</v>
       </c>
       <c r="D1" s="7" t="s">
+        <v>862</v>
+      </c>
+      <c r="E1" s="7" t="s">
         <v>863</v>
-      </c>
-      <c r="E1" s="7" t="s">
-        <v>864</v>
       </c>
       <c r="F1" s="7" t="s">
         <v>855</v>
@@ -3168,19 +3168,19 @@
         <v>1</v>
       </c>
       <c r="I1" s="7" t="s">
+        <v>870</v>
+      </c>
+      <c r="J1" s="7" t="s">
         <v>857</v>
       </c>
-      <c r="J1" s="7" t="s">
+      <c r="K1" s="7" t="s">
         <v>858</v>
       </c>
-      <c r="K1" s="7" t="s">
+      <c r="L1" s="7" t="s">
         <v>859</v>
       </c>
-      <c r="L1" s="7" t="s">
+      <c r="M1" s="7" t="s">
         <v>860</v>
-      </c>
-      <c r="M1" s="7" t="s">
-        <v>861</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.3">
@@ -6670,7 +6670,7 @@
     </row>
     <row r="87" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A87" s="13" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="B87" t="s">
         <v>108</v>
@@ -6711,7 +6711,7 @@
     </row>
     <row r="88" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A88" s="13" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="B88" t="s">
         <v>112</v>
@@ -6752,7 +6752,7 @@
     </row>
     <row r="89" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A89" s="13" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="B89" t="s">
         <v>110</v>
@@ -6793,7 +6793,7 @@
     </row>
     <row r="90" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A90" s="13" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="B90" t="s">
         <v>93</v>
@@ -6834,7 +6834,7 @@
     </row>
     <row r="91" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A91" s="13" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="B91" t="s">
         <v>103</v>
@@ -6875,7 +6875,7 @@
     </row>
     <row r="92" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A92" s="13" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="B92" t="s">
         <v>96</v>
@@ -6916,7 +6916,7 @@
     </row>
     <row r="93" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A93" s="13" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="B93" t="s">
         <v>109</v>
@@ -6957,7 +6957,7 @@
     </row>
     <row r="94" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A94" s="13" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="B94" t="s">
         <v>101</v>
@@ -6998,7 +6998,7 @@
     </row>
     <row r="95" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A95" s="13" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="B95" t="s">
         <v>95</v>
@@ -7039,7 +7039,7 @@
     </row>
     <row r="96" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A96" s="13" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="B96" t="s">
         <v>104</v>
@@ -7080,7 +7080,7 @@
     </row>
     <row r="97" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A97" s="13" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="B97" t="s">
         <v>107</v>
@@ -7121,7 +7121,7 @@
     </row>
     <row r="98" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A98" s="13" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="B98" t="s">
         <v>91</v>
@@ -7162,7 +7162,7 @@
     </row>
     <row r="99" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A99" s="13" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="B99" t="s">
         <v>94</v>
@@ -7203,7 +7203,7 @@
     </row>
     <row r="100" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A100" s="13" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="B100" t="s">
         <v>99</v>
@@ -7244,7 +7244,7 @@
     </row>
     <row r="101" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A101" s="13" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="B101" t="s">
         <v>98</v>
@@ -7285,7 +7285,7 @@
     </row>
     <row r="102" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A102" s="13" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="B102" t="s">
         <v>102</v>
@@ -7326,7 +7326,7 @@
     </row>
     <row r="103" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A103" s="13" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="B103" t="s">
         <v>105</v>
@@ -7367,7 +7367,7 @@
     </row>
     <row r="104" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A104" s="13" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="B104" t="s">
         <v>111</v>
@@ -7408,7 +7408,7 @@
     </row>
     <row r="105" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A105" s="13" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="B105" t="s">
         <v>113</v>
@@ -7449,7 +7449,7 @@
     </row>
     <row r="106" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A106" s="13" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="B106" t="s">
         <v>97</v>
@@ -7490,7 +7490,7 @@
     </row>
     <row r="107" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A107" s="13" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="B107" t="s">
         <v>106</v>
@@ -7531,7 +7531,7 @@
     </row>
     <row r="108" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A108" s="13" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="B108" t="s">
         <v>92</v>
@@ -7572,7 +7572,7 @@
     </row>
     <row r="109" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A109" s="13" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="B109" t="s">
         <v>90</v>
@@ -7613,7 +7613,7 @@
     </row>
     <row r="110" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A110" s="13" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="B110" t="s">
         <v>100</v>
@@ -7654,7 +7654,7 @@
     </row>
     <row r="111" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A111" s="13" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="B111" t="s">
         <v>114</v>
@@ -7695,7 +7695,7 @@
     </row>
     <row r="112" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A112" s="14" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="B112" t="s">
         <v>17</v>
@@ -7736,7 +7736,7 @@
     </row>
     <row r="113" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A113" s="13" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="B113" t="s">
         <v>121</v>
@@ -7777,7 +7777,7 @@
     </row>
     <row r="114" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A114" s="13" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="B114" t="s">
         <v>126</v>
@@ -7818,7 +7818,7 @@
     </row>
     <row r="115" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A115" s="13" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="B115" t="s">
         <v>122</v>
@@ -7859,7 +7859,7 @@
     </row>
     <row r="116" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A116" s="13" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="B116" t="s">
         <v>127</v>
@@ -7900,7 +7900,7 @@
     </row>
     <row r="117" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A117" s="13" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="B117" t="s">
         <v>116</v>
@@ -7941,7 +7941,7 @@
     </row>
     <row r="118" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A118" s="13" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="B118" t="s">
         <v>115</v>
@@ -7982,7 +7982,7 @@
     </row>
     <row r="119" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A119" s="13" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="B119" t="s">
         <v>117</v>
@@ -8023,7 +8023,7 @@
     </row>
     <row r="120" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A120" s="13" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="B120" t="s">
         <v>119</v>
@@ -8064,7 +8064,7 @@
     </row>
     <row r="121" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A121" s="13" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="B121" t="s">
         <v>130</v>
@@ -8105,7 +8105,7 @@
     </row>
     <row r="122" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A122" s="13" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="B122" t="s">
         <v>124</v>
@@ -8146,7 +8146,7 @@
     </row>
     <row r="123" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A123" s="13" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="B123" t="s">
         <v>129</v>
@@ -8187,7 +8187,7 @@
     </row>
     <row r="124" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A124" s="13" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="B124" t="s">
         <v>125</v>
@@ -8228,7 +8228,7 @@
     </row>
     <row r="125" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A125" s="13" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="B125" t="s">
         <v>118</v>
@@ -8269,7 +8269,7 @@
     </row>
     <row r="126" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A126" s="13" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="B126" t="s">
         <v>123</v>
@@ -8310,7 +8310,7 @@
     </row>
     <row r="127" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A127" s="13" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="B127" t="s">
         <v>120</v>
@@ -8351,7 +8351,7 @@
     </row>
     <row r="128" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A128" s="14" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="B128" t="s">
         <v>128</v>
@@ -27129,7 +27129,7 @@
     </row>
     <row r="586" spans="1:16" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A586" s="13" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
       <c r="B586" t="s">
         <v>595</v>
@@ -27171,7 +27171,7 @@
     </row>
     <row r="587" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A587" s="13" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
       <c r="B587" t="s">
         <v>591</v>
@@ -27212,7 +27212,7 @@
     </row>
     <row r="588" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A588" s="13" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
       <c r="B588" t="s">
         <v>270</v>
@@ -27253,7 +27253,7 @@
     </row>
     <row r="589" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A589" s="13" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
       <c r="B589" t="s">
         <v>586</v>
@@ -27294,7 +27294,7 @@
     </row>
     <row r="590" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A590" s="13" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
       <c r="B590" t="s">
         <v>590</v>
@@ -27335,7 +27335,7 @@
     </row>
     <row r="591" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A591" s="13" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
       <c r="B591" t="s">
         <v>584</v>
@@ -27376,7 +27376,7 @@
     </row>
     <row r="592" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A592" s="13" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
       <c r="B592" t="s">
         <v>587</v>
@@ -27417,7 +27417,7 @@
     </row>
     <row r="593" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A593" s="13" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
       <c r="B593" t="s">
         <v>585</v>
@@ -27458,7 +27458,7 @@
     </row>
     <row r="594" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A594" s="13" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
       <c r="B594" t="s">
         <v>589</v>
@@ -27499,7 +27499,7 @@
     </row>
     <row r="595" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A595" s="13" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
       <c r="B595" t="s">
         <v>592</v>
@@ -27540,7 +27540,7 @@
     </row>
     <row r="596" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A596" s="13" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
       <c r="B596" t="s">
         <v>593</v>
@@ -27581,7 +27581,7 @@
     </row>
     <row r="597" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A597" s="13" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
       <c r="B597" t="s">
         <v>594</v>
@@ -27622,7 +27622,7 @@
     </row>
     <row r="598" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A598" s="14" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
       <c r="B598" t="s">
         <v>588</v>
@@ -27663,7 +27663,7 @@
     </row>
     <row r="599" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A599" s="13" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="B599" t="s">
         <v>611</v>
@@ -27704,7 +27704,7 @@
     </row>
     <row r="600" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A600" s="13" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="B600" t="s">
         <v>612</v>
@@ -27745,7 +27745,7 @@
     </row>
     <row r="601" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A601" s="13" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="B601" t="s">
         <v>599</v>
@@ -27786,7 +27786,7 @@
     </row>
     <row r="602" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A602" s="13" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="B602" t="s">
         <v>618</v>
@@ -27827,7 +27827,7 @@
     </row>
     <row r="603" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A603" s="13" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="B603" t="s">
         <v>620</v>
@@ -27868,7 +27868,7 @@
     </row>
     <row r="604" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A604" s="13" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="B604" t="s">
         <v>609</v>
@@ -27909,7 +27909,7 @@
     </row>
     <row r="605" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A605" s="13" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="B605" t="s">
         <v>622</v>
@@ -27950,7 +27950,7 @@
     </row>
     <row r="606" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A606" s="13" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="B606" t="s">
         <v>596</v>
@@ -27991,7 +27991,7 @@
     </row>
     <row r="607" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A607" s="13" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="B607" t="s">
         <v>616</v>
@@ -28032,7 +28032,7 @@
     </row>
     <row r="608" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A608" s="13" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="B608" t="s">
         <v>604</v>
@@ -28073,7 +28073,7 @@
     </row>
     <row r="609" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A609" s="13" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="B609" t="s">
         <v>607</v>
@@ -28114,7 +28114,7 @@
     </row>
     <row r="610" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A610" s="13" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="B610" t="s">
         <v>601</v>
@@ -28155,7 +28155,7 @@
     </row>
     <row r="611" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A611" s="13" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="B611" t="s">
         <v>613</v>
@@ -28196,7 +28196,7 @@
     </row>
     <row r="612" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A612" s="13" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="B612" t="s">
         <v>606</v>
@@ -28237,7 +28237,7 @@
     </row>
     <row r="613" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A613" s="13" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="B613" t="s">
         <v>605</v>
@@ -28278,7 +28278,7 @@
     </row>
     <row r="614" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A614" s="13" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="B614" t="s">
         <v>608</v>
@@ -28319,7 +28319,7 @@
     </row>
     <row r="615" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A615" s="13" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="B615" t="s">
         <v>597</v>
@@ -28360,7 +28360,7 @@
     </row>
     <row r="616" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A616" s="13" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="B616" t="s">
         <v>615</v>
@@ -28401,7 +28401,7 @@
     </row>
     <row r="617" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A617" s="13" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="B617" t="s">
         <v>600</v>
@@ -28442,7 +28442,7 @@
     </row>
     <row r="618" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A618" s="13" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="B618" t="s">
         <v>617</v>
@@ -28483,7 +28483,7 @@
     </row>
     <row r="619" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A619" s="13" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="B619" t="s">
         <v>602</v>
@@ -28524,7 +28524,7 @@
     </row>
     <row r="620" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A620" s="13" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="B620" t="s">
         <v>623</v>
@@ -28565,7 +28565,7 @@
     </row>
     <row r="621" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A621" s="13" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="B621" t="s">
         <v>619</v>
@@ -28606,7 +28606,7 @@
     </row>
     <row r="622" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A622" s="13" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="B622" t="s">
         <v>610</v>
@@ -28647,7 +28647,7 @@
     </row>
     <row r="623" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A623" s="13" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="B623" t="s">
         <v>614</v>
@@ -28688,7 +28688,7 @@
     </row>
     <row r="624" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A624" s="13" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="B624" t="s">
         <v>621</v>
@@ -28729,7 +28729,7 @@
     </row>
     <row r="625" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A625" s="13" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="B625" t="s">
         <v>603</v>
@@ -28770,7 +28770,7 @@
     </row>
     <row r="626" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A626" s="14" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="B626" t="s">
         <v>598</v>
@@ -32665,10 +32665,10 @@
     </row>
     <row r="721" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A721" s="13" t="s">
-        <v>869</v>
+        <v>868</v>
       </c>
       <c r="B721" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="C721" s="9">
         <v>232</v>
@@ -32706,7 +32706,7 @@
     </row>
     <row r="722" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A722" s="13" t="s">
-        <v>869</v>
+        <v>868</v>
       </c>
       <c r="B722" t="s">
         <v>716</v>
@@ -32747,7 +32747,7 @@
     </row>
     <row r="723" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A723" s="13" t="s">
-        <v>869</v>
+        <v>868</v>
       </c>
       <c r="B723" t="s">
         <v>724</v>
@@ -32788,7 +32788,7 @@
     </row>
     <row r="724" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A724" s="13" t="s">
-        <v>869</v>
+        <v>868</v>
       </c>
       <c r="B724" t="s">
         <v>718</v>
@@ -32829,7 +32829,7 @@
     </row>
     <row r="725" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A725" s="13" t="s">
-        <v>869</v>
+        <v>868</v>
       </c>
       <c r="B725" t="s">
         <v>713</v>
@@ -32870,7 +32870,7 @@
     </row>
     <row r="726" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A726" s="13" t="s">
-        <v>869</v>
+        <v>868</v>
       </c>
       <c r="B726" t="s">
         <v>715</v>
@@ -32911,7 +32911,7 @@
     </row>
     <row r="727" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A727" s="13" t="s">
-        <v>869</v>
+        <v>868</v>
       </c>
       <c r="B727" t="s">
         <v>727</v>
@@ -32952,7 +32952,7 @@
     </row>
     <row r="728" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A728" s="13" t="s">
-        <v>869</v>
+        <v>868</v>
       </c>
       <c r="B728" t="s">
         <v>720</v>
@@ -32993,7 +32993,7 @@
     </row>
     <row r="729" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A729" s="13" t="s">
-        <v>869</v>
+        <v>868</v>
       </c>
       <c r="B729" t="s">
         <v>725</v>
@@ -33034,7 +33034,7 @@
     </row>
     <row r="730" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A730" s="13" t="s">
-        <v>869</v>
+        <v>868</v>
       </c>
       <c r="B730" t="s">
         <v>719</v>
@@ -33075,7 +33075,7 @@
     </row>
     <row r="731" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A731" s="13" t="s">
-        <v>869</v>
+        <v>868</v>
       </c>
       <c r="B731" t="s">
         <v>722</v>
@@ -33116,7 +33116,7 @@
     </row>
     <row r="732" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A732" s="13" t="s">
-        <v>869</v>
+        <v>868</v>
       </c>
       <c r="B732" t="s">
         <v>721</v>
@@ -33157,7 +33157,7 @@
     </row>
     <row r="733" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A733" s="13" t="s">
-        <v>869</v>
+        <v>868</v>
       </c>
       <c r="B733" t="s">
         <v>726</v>
@@ -33198,7 +33198,7 @@
     </row>
     <row r="734" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A734" s="13" t="s">
-        <v>869</v>
+        <v>868</v>
       </c>
       <c r="B734" t="s">
         <v>717</v>
@@ -33239,7 +33239,7 @@
     </row>
     <row r="735" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A735" s="13" t="s">
-        <v>869</v>
+        <v>868</v>
       </c>
       <c r="B735" t="s">
         <v>723</v>
@@ -33280,7 +33280,7 @@
     </row>
     <row r="736" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A736" s="14" t="s">
-        <v>869</v>
+        <v>868</v>
       </c>
       <c r="B736" t="s">
         <v>714</v>
@@ -34059,7 +34059,7 @@
     </row>
     <row r="755" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A755" s="16" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
       <c r="B755" t="s">
         <v>772</v>
@@ -34100,7 +34100,7 @@
     </row>
     <row r="756" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A756" s="16" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
       <c r="B756" t="s">
         <v>767</v>
@@ -34141,7 +34141,7 @@
     </row>
     <row r="757" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A757" s="16" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
       <c r="B757" t="s">
         <v>753</v>
@@ -34182,7 +34182,7 @@
     </row>
     <row r="758" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A758" s="16" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
       <c r="B758" t="s">
         <v>774</v>
@@ -34223,7 +34223,7 @@
     </row>
     <row r="759" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A759" s="16" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
       <c r="B759" t="s">
         <v>751</v>
@@ -34264,7 +34264,7 @@
     </row>
     <row r="760" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A760" s="16" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
       <c r="B760" t="s">
         <v>760</v>
@@ -34305,7 +34305,7 @@
     </row>
     <row r="761" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A761" s="16" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
       <c r="B761" t="s">
         <v>756</v>
@@ -34346,7 +34346,7 @@
     </row>
     <row r="762" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A762" s="16" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
       <c r="B762" t="s">
         <v>777</v>
@@ -34387,7 +34387,7 @@
     </row>
     <row r="763" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A763" s="16" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
       <c r="B763" t="s">
         <v>748</v>
@@ -34428,7 +34428,7 @@
     </row>
     <row r="764" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A764" s="16" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
       <c r="B764" t="s">
         <v>754</v>
@@ -34469,7 +34469,7 @@
     </row>
     <row r="765" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A765" s="16" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
       <c r="B765" t="s">
         <v>765</v>
@@ -34510,7 +34510,7 @@
     </row>
     <row r="766" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A766" s="16" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
       <c r="B766" t="s">
         <v>121</v>
@@ -34551,7 +34551,7 @@
     </row>
     <row r="767" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A767" s="16" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
       <c r="B767" t="s">
         <v>779</v>
@@ -34592,7 +34592,7 @@
     </row>
     <row r="768" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A768" s="16" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
       <c r="B768" t="s">
         <v>757</v>
@@ -34633,7 +34633,7 @@
     </row>
     <row r="769" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A769" s="16" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
       <c r="B769" t="s">
         <v>733</v>
@@ -34674,7 +34674,7 @@
     </row>
     <row r="770" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A770" s="16" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
       <c r="B770" t="s">
         <v>759</v>
@@ -34715,7 +34715,7 @@
     </row>
     <row r="771" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A771" s="16" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
       <c r="B771" t="s">
         <v>771</v>
@@ -34756,7 +34756,7 @@
     </row>
     <row r="772" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A772" s="16" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
       <c r="B772" t="s">
         <v>745</v>
@@ -34797,7 +34797,7 @@
     </row>
     <row r="773" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A773" s="16" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
       <c r="B773" t="s">
         <v>770</v>
@@ -34838,7 +34838,7 @@
     </row>
     <row r="774" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A774" s="16" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
       <c r="B774" t="s">
         <v>763</v>
@@ -34879,7 +34879,7 @@
     </row>
     <row r="775" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A775" s="16" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
       <c r="B775" t="s">
         <v>744</v>
@@ -34920,7 +34920,7 @@
     </row>
     <row r="776" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A776" s="16" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
       <c r="B776" t="s">
         <v>752</v>
@@ -34961,7 +34961,7 @@
     </row>
     <row r="777" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A777" s="16" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
       <c r="B777" t="s">
         <v>768</v>
@@ -35002,7 +35002,7 @@
     </row>
     <row r="778" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A778" s="16" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
       <c r="B778" t="s">
         <v>780</v>
@@ -35043,7 +35043,7 @@
     </row>
     <row r="779" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A779" s="16" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
       <c r="B779" t="s">
         <v>776</v>
@@ -35084,7 +35084,7 @@
     </row>
     <row r="780" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A780" s="16" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
       <c r="B780" t="s">
         <v>762</v>
@@ -35125,7 +35125,7 @@
     </row>
     <row r="781" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A781" s="16" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
       <c r="B781" t="s">
         <v>749</v>
@@ -35166,7 +35166,7 @@
     </row>
     <row r="782" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A782" s="16" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
       <c r="B782" t="s">
         <v>126</v>
@@ -35207,7 +35207,7 @@
     </row>
     <row r="783" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A783" s="16" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
       <c r="B783" t="s">
         <v>761</v>
@@ -35248,7 +35248,7 @@
     </row>
     <row r="784" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A784" s="16" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
       <c r="B784" t="s">
         <v>769</v>
@@ -35289,7 +35289,7 @@
     </row>
     <row r="785" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A785" s="16" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
       <c r="B785" t="s">
         <v>746</v>
@@ -35330,7 +35330,7 @@
     </row>
     <row r="786" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A786" s="16" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
       <c r="B786" t="s">
         <v>758</v>
@@ -35371,7 +35371,7 @@
     </row>
     <row r="787" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A787" s="16" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
       <c r="B787" t="s">
         <v>766</v>
@@ -35412,7 +35412,7 @@
     </row>
     <row r="788" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A788" s="16" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
       <c r="B788" t="s">
         <v>775</v>
@@ -35453,7 +35453,7 @@
     </row>
     <row r="789" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A789" s="16" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
       <c r="B789" t="s">
         <v>747</v>
@@ -35494,7 +35494,7 @@
     </row>
     <row r="790" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A790" s="16" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
       <c r="B790" t="s">
         <v>764</v>
@@ -35535,7 +35535,7 @@
     </row>
     <row r="791" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A791" s="16" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
       <c r="B791" t="s">
         <v>773</v>
@@ -35576,7 +35576,7 @@
     </row>
     <row r="792" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A792" s="16" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
       <c r="B792" t="s">
         <v>778</v>
@@ -35617,7 +35617,7 @@
     </row>
     <row r="793" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A793" s="16" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
       <c r="B793" t="s">
         <v>755</v>
@@ -35658,7 +35658,7 @@
     </row>
     <row r="794" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A794" s="16" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
       <c r="B794" t="s">
         <v>750</v>
@@ -35699,7 +35699,7 @@
     </row>
     <row r="795" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A795" s="16" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
       <c r="B795" t="s">
         <v>781</v>

--- a/content/xls/DB_01.01.2026_NP.xlsx
+++ b/content/xls/DB_01.01.2026_NP.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Python\InfPanel\content\xls\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91BE0CC8-BEBC-4BD5-A1F7-7597ED2CE4EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7728C1B2-BC18-4A48-9232-83D618F7C938}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-111" yWindow="-111" windowWidth="31729" windowHeight="17342" xr2:uid="{CD9FBE00-C105-441E-AC9D-D16C82556AEE}"/>
   </bookViews>
@@ -2631,25 +2631,25 @@
     <t>Изменение уровня потребности в развитии дистанционного банковского обслуживания за счет альтернативной инфраструктуры, п.п.</t>
   </si>
   <si>
-    <t>Венгеровский муниципальный район</t>
-  </si>
-  <si>
-    <t>Доволенский муниципальный район</t>
-  </si>
-  <si>
-    <t>Северный муниципальный район</t>
-  </si>
-  <si>
-    <t>Сузунский муниципальный район</t>
-  </si>
-  <si>
-    <t>Убинский муниципальный район</t>
-  </si>
-  <si>
-    <t>Чановский муниципальный район</t>
-  </si>
-  <si>
     <t>Количество финансовых помощников</t>
+  </si>
+  <si>
+    <t>Венгеровский муниципальный округ</t>
+  </si>
+  <si>
+    <t>Доволенский муниципальный округ</t>
+  </si>
+  <si>
+    <t>Северный муниципальный округ</t>
+  </si>
+  <si>
+    <t>Сузунский муниципальный округ</t>
+  </si>
+  <si>
+    <t>Убинский муниципальный округ</t>
+  </si>
+  <si>
+    <t>Чановский муниципальный округ</t>
   </si>
 </sst>
 </file>
@@ -2662,12 +2662,20 @@
     <numFmt numFmtId="165" formatCode="_-\ #,##0.0_-;\-\ #,##0.0_-;_-\ &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="166" formatCode="_-\ #,##0.00_-;\-\ #,##0.00_-;_-\ &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -2750,10 +2758,10 @@
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -2764,8 +2772,8 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -2785,9 +2793,10 @@
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="3">
@@ -3168,7 +3177,7 @@
         <v>1</v>
       </c>
       <c r="I1" s="7" t="s">
-        <v>870</v>
+        <v>864</v>
       </c>
       <c r="J1" s="7" t="s">
         <v>857</v>
@@ -6669,8 +6678,8 @@
       </c>
     </row>
     <row r="87" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A87" s="13" t="s">
-        <v>864</v>
+      <c r="A87" s="17" t="s">
+        <v>865</v>
       </c>
       <c r="B87" t="s">
         <v>108</v>
@@ -6711,7 +6720,7 @@
     </row>
     <row r="88" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A88" s="13" t="s">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="B88" t="s">
         <v>112</v>
@@ -6752,7 +6761,7 @@
     </row>
     <row r="89" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A89" s="13" t="s">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="B89" t="s">
         <v>110</v>
@@ -6793,7 +6802,7 @@
     </row>
     <row r="90" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A90" s="13" t="s">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="B90" t="s">
         <v>93</v>
@@ -6834,7 +6843,7 @@
     </row>
     <row r="91" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A91" s="13" t="s">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="B91" t="s">
         <v>103</v>
@@ -6875,7 +6884,7 @@
     </row>
     <row r="92" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A92" s="13" t="s">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="B92" t="s">
         <v>96</v>
@@ -6916,7 +6925,7 @@
     </row>
     <row r="93" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A93" s="13" t="s">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="B93" t="s">
         <v>109</v>
@@ -6957,7 +6966,7 @@
     </row>
     <row r="94" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A94" s="13" t="s">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="B94" t="s">
         <v>101</v>
@@ -6998,7 +7007,7 @@
     </row>
     <row r="95" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A95" s="13" t="s">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="B95" t="s">
         <v>95</v>
@@ -7039,7 +7048,7 @@
     </row>
     <row r="96" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A96" s="13" t="s">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="B96" t="s">
         <v>104</v>
@@ -7080,7 +7089,7 @@
     </row>
     <row r="97" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A97" s="13" t="s">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="B97" t="s">
         <v>107</v>
@@ -7121,7 +7130,7 @@
     </row>
     <row r="98" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A98" s="13" t="s">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="B98" t="s">
         <v>91</v>
@@ -7162,7 +7171,7 @@
     </row>
     <row r="99" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A99" s="13" t="s">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="B99" t="s">
         <v>94</v>
@@ -7203,7 +7212,7 @@
     </row>
     <row r="100" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A100" s="13" t="s">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="B100" t="s">
         <v>99</v>
@@ -7244,7 +7253,7 @@
     </row>
     <row r="101" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A101" s="13" t="s">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="B101" t="s">
         <v>98</v>
@@ -7285,7 +7294,7 @@
     </row>
     <row r="102" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A102" s="13" t="s">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="B102" t="s">
         <v>102</v>
@@ -7326,7 +7335,7 @@
     </row>
     <row r="103" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A103" s="13" t="s">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="B103" t="s">
         <v>105</v>
@@ -7367,7 +7376,7 @@
     </row>
     <row r="104" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A104" s="13" t="s">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="B104" t="s">
         <v>111</v>
@@ -7408,7 +7417,7 @@
     </row>
     <row r="105" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A105" s="13" t="s">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="B105" t="s">
         <v>113</v>
@@ -7449,7 +7458,7 @@
     </row>
     <row r="106" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A106" s="13" t="s">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="B106" t="s">
         <v>97</v>
@@ -7490,7 +7499,7 @@
     </row>
     <row r="107" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A107" s="13" t="s">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="B107" t="s">
         <v>106</v>
@@ -7531,7 +7540,7 @@
     </row>
     <row r="108" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A108" s="13" t="s">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="B108" t="s">
         <v>92</v>
@@ -7572,7 +7581,7 @@
     </row>
     <row r="109" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A109" s="13" t="s">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="B109" t="s">
         <v>90</v>
@@ -7613,7 +7622,7 @@
     </row>
     <row r="110" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A110" s="13" t="s">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="B110" t="s">
         <v>100</v>
@@ -7654,7 +7663,7 @@
     </row>
     <row r="111" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A111" s="13" t="s">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="B111" t="s">
         <v>114</v>
@@ -7695,7 +7704,7 @@
     </row>
     <row r="112" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A112" s="14" t="s">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="B112" t="s">
         <v>17</v>
@@ -7736,7 +7745,7 @@
     </row>
     <row r="113" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A113" s="13" t="s">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="B113" t="s">
         <v>121</v>
@@ -7777,7 +7786,7 @@
     </row>
     <row r="114" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A114" s="13" t="s">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="B114" t="s">
         <v>126</v>
@@ -7818,7 +7827,7 @@
     </row>
     <row r="115" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A115" s="13" t="s">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="B115" t="s">
         <v>122</v>
@@ -7859,7 +7868,7 @@
     </row>
     <row r="116" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A116" s="13" t="s">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="B116" t="s">
         <v>127</v>
@@ -7900,7 +7909,7 @@
     </row>
     <row r="117" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A117" s="13" t="s">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="B117" t="s">
         <v>116</v>
@@ -7941,7 +7950,7 @@
     </row>
     <row r="118" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A118" s="13" t="s">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="B118" t="s">
         <v>115</v>
@@ -7982,7 +7991,7 @@
     </row>
     <row r="119" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A119" s="13" t="s">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="B119" t="s">
         <v>117</v>
@@ -8023,7 +8032,7 @@
     </row>
     <row r="120" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A120" s="13" t="s">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="B120" t="s">
         <v>119</v>
@@ -8064,7 +8073,7 @@
     </row>
     <row r="121" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A121" s="13" t="s">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="B121" t="s">
         <v>130</v>
@@ -8105,7 +8114,7 @@
     </row>
     <row r="122" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A122" s="13" t="s">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="B122" t="s">
         <v>124</v>
@@ -8146,7 +8155,7 @@
     </row>
     <row r="123" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A123" s="13" t="s">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="B123" t="s">
         <v>129</v>
@@ -8187,7 +8196,7 @@
     </row>
     <row r="124" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A124" s="13" t="s">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="B124" t="s">
         <v>125</v>
@@ -8228,7 +8237,7 @@
     </row>
     <row r="125" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A125" s="13" t="s">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="B125" t="s">
         <v>118</v>
@@ -8269,7 +8278,7 @@
     </row>
     <row r="126" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A126" s="13" t="s">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="B126" t="s">
         <v>123</v>
@@ -8310,7 +8319,7 @@
     </row>
     <row r="127" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A127" s="13" t="s">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="B127" t="s">
         <v>120</v>
@@ -8351,7 +8360,7 @@
     </row>
     <row r="128" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A128" s="14" t="s">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="B128" t="s">
         <v>128</v>
@@ -27129,7 +27138,7 @@
     </row>
     <row r="586" spans="1:16" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A586" s="13" t="s">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="B586" t="s">
         <v>595</v>
@@ -27171,7 +27180,7 @@
     </row>
     <row r="587" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A587" s="13" t="s">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="B587" t="s">
         <v>591</v>
@@ -27212,7 +27221,7 @@
     </row>
     <row r="588" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A588" s="13" t="s">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="B588" t="s">
         <v>270</v>
@@ -27253,7 +27262,7 @@
     </row>
     <row r="589" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A589" s="13" t="s">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="B589" t="s">
         <v>586</v>
@@ -27294,7 +27303,7 @@
     </row>
     <row r="590" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A590" s="13" t="s">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="B590" t="s">
         <v>590</v>
@@ -27335,7 +27344,7 @@
     </row>
     <row r="591" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A591" s="13" t="s">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="B591" t="s">
         <v>584</v>
@@ -27376,7 +27385,7 @@
     </row>
     <row r="592" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A592" s="13" t="s">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="B592" t="s">
         <v>587</v>
@@ -27417,7 +27426,7 @@
     </row>
     <row r="593" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A593" s="13" t="s">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="B593" t="s">
         <v>585</v>
@@ -27458,7 +27467,7 @@
     </row>
     <row r="594" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A594" s="13" t="s">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="B594" t="s">
         <v>589</v>
@@ -27499,7 +27508,7 @@
     </row>
     <row r="595" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A595" s="13" t="s">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="B595" t="s">
         <v>592</v>
@@ -27540,7 +27549,7 @@
     </row>
     <row r="596" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A596" s="13" t="s">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="B596" t="s">
         <v>593</v>
@@ -27581,7 +27590,7 @@
     </row>
     <row r="597" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A597" s="13" t="s">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="B597" t="s">
         <v>594</v>
@@ -27622,7 +27631,7 @@
     </row>
     <row r="598" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A598" s="14" t="s">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="B598" t="s">
         <v>588</v>
@@ -27663,7 +27672,7 @@
     </row>
     <row r="599" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A599" s="13" t="s">
-        <v>867</v>
+        <v>868</v>
       </c>
       <c r="B599" t="s">
         <v>611</v>
@@ -27704,7 +27713,7 @@
     </row>
     <row r="600" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A600" s="13" t="s">
-        <v>867</v>
+        <v>868</v>
       </c>
       <c r="B600" t="s">
         <v>612</v>
@@ -27745,7 +27754,7 @@
     </row>
     <row r="601" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A601" s="13" t="s">
-        <v>867</v>
+        <v>868</v>
       </c>
       <c r="B601" t="s">
         <v>599</v>
@@ -27786,7 +27795,7 @@
     </row>
     <row r="602" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A602" s="13" t="s">
-        <v>867</v>
+        <v>868</v>
       </c>
       <c r="B602" t="s">
         <v>618</v>
@@ -27827,7 +27836,7 @@
     </row>
     <row r="603" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A603" s="13" t="s">
-        <v>867</v>
+        <v>868</v>
       </c>
       <c r="B603" t="s">
         <v>620</v>
@@ -27868,7 +27877,7 @@
     </row>
     <row r="604" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A604" s="13" t="s">
-        <v>867</v>
+        <v>868</v>
       </c>
       <c r="B604" t="s">
         <v>609</v>
@@ -27909,7 +27918,7 @@
     </row>
     <row r="605" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A605" s="13" t="s">
-        <v>867</v>
+        <v>868</v>
       </c>
       <c r="B605" t="s">
         <v>622</v>
@@ -27950,7 +27959,7 @@
     </row>
     <row r="606" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A606" s="13" t="s">
-        <v>867</v>
+        <v>868</v>
       </c>
       <c r="B606" t="s">
         <v>596</v>
@@ -27991,7 +28000,7 @@
     </row>
     <row r="607" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A607" s="13" t="s">
-        <v>867</v>
+        <v>868</v>
       </c>
       <c r="B607" t="s">
         <v>616</v>
@@ -28032,7 +28041,7 @@
     </row>
     <row r="608" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A608" s="13" t="s">
-        <v>867</v>
+        <v>868</v>
       </c>
       <c r="B608" t="s">
         <v>604</v>
@@ -28073,7 +28082,7 @@
     </row>
     <row r="609" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A609" s="13" t="s">
-        <v>867</v>
+        <v>868</v>
       </c>
       <c r="B609" t="s">
         <v>607</v>
@@ -28114,7 +28123,7 @@
     </row>
     <row r="610" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A610" s="13" t="s">
-        <v>867</v>
+        <v>868</v>
       </c>
       <c r="B610" t="s">
         <v>601</v>
@@ -28155,7 +28164,7 @@
     </row>
     <row r="611" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A611" s="13" t="s">
-        <v>867</v>
+        <v>868</v>
       </c>
       <c r="B611" t="s">
         <v>613</v>
@@ -28196,7 +28205,7 @@
     </row>
     <row r="612" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A612" s="13" t="s">
-        <v>867</v>
+        <v>868</v>
       </c>
       <c r="B612" t="s">
         <v>606</v>
@@ -28237,7 +28246,7 @@
     </row>
     <row r="613" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A613" s="13" t="s">
-        <v>867</v>
+        <v>868</v>
       </c>
       <c r="B613" t="s">
         <v>605</v>
@@ -28278,7 +28287,7 @@
     </row>
     <row r="614" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A614" s="13" t="s">
-        <v>867</v>
+        <v>868</v>
       </c>
       <c r="B614" t="s">
         <v>608</v>
@@ -28319,7 +28328,7 @@
     </row>
     <row r="615" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A615" s="13" t="s">
-        <v>867</v>
+        <v>868</v>
       </c>
       <c r="B615" t="s">
         <v>597</v>
@@ -28360,7 +28369,7 @@
     </row>
     <row r="616" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A616" s="13" t="s">
-        <v>867</v>
+        <v>868</v>
       </c>
       <c r="B616" t="s">
         <v>615</v>
@@ -28401,7 +28410,7 @@
     </row>
     <row r="617" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A617" s="13" t="s">
-        <v>867</v>
+        <v>868</v>
       </c>
       <c r="B617" t="s">
         <v>600</v>
@@ -28442,7 +28451,7 @@
     </row>
     <row r="618" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A618" s="13" t="s">
-        <v>867</v>
+        <v>868</v>
       </c>
       <c r="B618" t="s">
         <v>617</v>
@@ -28483,7 +28492,7 @@
     </row>
     <row r="619" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A619" s="13" t="s">
-        <v>867</v>
+        <v>868</v>
       </c>
       <c r="B619" t="s">
         <v>602</v>
@@ -28524,7 +28533,7 @@
     </row>
     <row r="620" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A620" s="13" t="s">
-        <v>867</v>
+        <v>868</v>
       </c>
       <c r="B620" t="s">
         <v>623</v>
@@ -28565,7 +28574,7 @@
     </row>
     <row r="621" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A621" s="13" t="s">
-        <v>867</v>
+        <v>868</v>
       </c>
       <c r="B621" t="s">
         <v>619</v>
@@ -28606,7 +28615,7 @@
     </row>
     <row r="622" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A622" s="13" t="s">
-        <v>867</v>
+        <v>868</v>
       </c>
       <c r="B622" t="s">
         <v>610</v>
@@ -28647,7 +28656,7 @@
     </row>
     <row r="623" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A623" s="13" t="s">
-        <v>867</v>
+        <v>868</v>
       </c>
       <c r="B623" t="s">
         <v>614</v>
@@ -28688,7 +28697,7 @@
     </row>
     <row r="624" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A624" s="13" t="s">
-        <v>867</v>
+        <v>868</v>
       </c>
       <c r="B624" t="s">
         <v>621</v>
@@ -28729,7 +28738,7 @@
     </row>
     <row r="625" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A625" s="13" t="s">
-        <v>867</v>
+        <v>868</v>
       </c>
       <c r="B625" t="s">
         <v>603</v>
@@ -28770,7 +28779,7 @@
     </row>
     <row r="626" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A626" s="14" t="s">
-        <v>867</v>
+        <v>868</v>
       </c>
       <c r="B626" t="s">
         <v>598</v>
@@ -32665,7 +32674,7 @@
     </row>
     <row r="721" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A721" s="13" t="s">
-        <v>868</v>
+        <v>869</v>
       </c>
       <c r="B721" t="s">
         <v>861</v>
@@ -32706,7 +32715,7 @@
     </row>
     <row r="722" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A722" s="13" t="s">
-        <v>868</v>
+        <v>869</v>
       </c>
       <c r="B722" t="s">
         <v>716</v>
@@ -32747,7 +32756,7 @@
     </row>
     <row r="723" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A723" s="13" t="s">
-        <v>868</v>
+        <v>869</v>
       </c>
       <c r="B723" t="s">
         <v>724</v>
@@ -32788,7 +32797,7 @@
     </row>
     <row r="724" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A724" s="13" t="s">
-        <v>868</v>
+        <v>869</v>
       </c>
       <c r="B724" t="s">
         <v>718</v>
@@ -32829,7 +32838,7 @@
     </row>
     <row r="725" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A725" s="13" t="s">
-        <v>868</v>
+        <v>869</v>
       </c>
       <c r="B725" t="s">
         <v>713</v>
@@ -32870,7 +32879,7 @@
     </row>
     <row r="726" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A726" s="13" t="s">
-        <v>868</v>
+        <v>869</v>
       </c>
       <c r="B726" t="s">
         <v>715</v>
@@ -32911,7 +32920,7 @@
     </row>
     <row r="727" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A727" s="13" t="s">
-        <v>868</v>
+        <v>869</v>
       </c>
       <c r="B727" t="s">
         <v>727</v>
@@ -32952,7 +32961,7 @@
     </row>
     <row r="728" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A728" s="13" t="s">
-        <v>868</v>
+        <v>869</v>
       </c>
       <c r="B728" t="s">
         <v>720</v>
@@ -32993,7 +33002,7 @@
     </row>
     <row r="729" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A729" s="13" t="s">
-        <v>868</v>
+        <v>869</v>
       </c>
       <c r="B729" t="s">
         <v>725</v>
@@ -33034,7 +33043,7 @@
     </row>
     <row r="730" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A730" s="13" t="s">
-        <v>868</v>
+        <v>869</v>
       </c>
       <c r="B730" t="s">
         <v>719</v>
@@ -33075,7 +33084,7 @@
     </row>
     <row r="731" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A731" s="13" t="s">
-        <v>868</v>
+        <v>869</v>
       </c>
       <c r="B731" t="s">
         <v>722</v>
@@ -33116,7 +33125,7 @@
     </row>
     <row r="732" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A732" s="13" t="s">
-        <v>868</v>
+        <v>869</v>
       </c>
       <c r="B732" t="s">
         <v>721</v>
@@ -33157,7 +33166,7 @@
     </row>
     <row r="733" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A733" s="13" t="s">
-        <v>868</v>
+        <v>869</v>
       </c>
       <c r="B733" t="s">
         <v>726</v>
@@ -33198,7 +33207,7 @@
     </row>
     <row r="734" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A734" s="13" t="s">
-        <v>868</v>
+        <v>869</v>
       </c>
       <c r="B734" t="s">
         <v>717</v>
@@ -33239,7 +33248,7 @@
     </row>
     <row r="735" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A735" s="13" t="s">
-        <v>868</v>
+        <v>869</v>
       </c>
       <c r="B735" t="s">
         <v>723</v>
@@ -33280,7 +33289,7 @@
     </row>
     <row r="736" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A736" s="14" t="s">
-        <v>868</v>
+        <v>869</v>
       </c>
       <c r="B736" t="s">
         <v>714</v>
@@ -34059,7 +34068,7 @@
     </row>
     <row r="755" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A755" s="16" t="s">
-        <v>869</v>
+        <v>870</v>
       </c>
       <c r="B755" t="s">
         <v>772</v>
@@ -34100,7 +34109,7 @@
     </row>
     <row r="756" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A756" s="16" t="s">
-        <v>869</v>
+        <v>870</v>
       </c>
       <c r="B756" t="s">
         <v>767</v>
@@ -34141,7 +34150,7 @@
     </row>
     <row r="757" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A757" s="16" t="s">
-        <v>869</v>
+        <v>870</v>
       </c>
       <c r="B757" t="s">
         <v>753</v>
@@ -34182,7 +34191,7 @@
     </row>
     <row r="758" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A758" s="16" t="s">
-        <v>869</v>
+        <v>870</v>
       </c>
       <c r="B758" t="s">
         <v>774</v>
@@ -34223,7 +34232,7 @@
     </row>
     <row r="759" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A759" s="16" t="s">
-        <v>869</v>
+        <v>870</v>
       </c>
       <c r="B759" t="s">
         <v>751</v>
@@ -34264,7 +34273,7 @@
     </row>
     <row r="760" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A760" s="16" t="s">
-        <v>869</v>
+        <v>870</v>
       </c>
       <c r="B760" t="s">
         <v>760</v>
@@ -34305,7 +34314,7 @@
     </row>
     <row r="761" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A761" s="16" t="s">
-        <v>869</v>
+        <v>870</v>
       </c>
       <c r="B761" t="s">
         <v>756</v>
@@ -34346,7 +34355,7 @@
     </row>
     <row r="762" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A762" s="16" t="s">
-        <v>869</v>
+        <v>870</v>
       </c>
       <c r="B762" t="s">
         <v>777</v>
@@ -34387,7 +34396,7 @@
     </row>
     <row r="763" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A763" s="16" t="s">
-        <v>869</v>
+        <v>870</v>
       </c>
       <c r="B763" t="s">
         <v>748</v>
@@ -34428,7 +34437,7 @@
     </row>
     <row r="764" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A764" s="16" t="s">
-        <v>869</v>
+        <v>870</v>
       </c>
       <c r="B764" t="s">
         <v>754</v>
@@ -34469,7 +34478,7 @@
     </row>
     <row r="765" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A765" s="16" t="s">
-        <v>869</v>
+        <v>870</v>
       </c>
       <c r="B765" t="s">
         <v>765</v>
@@ -34510,7 +34519,7 @@
     </row>
     <row r="766" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A766" s="16" t="s">
-        <v>869</v>
+        <v>870</v>
       </c>
       <c r="B766" t="s">
         <v>121</v>
@@ -34551,7 +34560,7 @@
     </row>
     <row r="767" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A767" s="16" t="s">
-        <v>869</v>
+        <v>870</v>
       </c>
       <c r="B767" t="s">
         <v>779</v>
@@ -34592,7 +34601,7 @@
     </row>
     <row r="768" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A768" s="16" t="s">
-        <v>869</v>
+        <v>870</v>
       </c>
       <c r="B768" t="s">
         <v>757</v>
@@ -34633,7 +34642,7 @@
     </row>
     <row r="769" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A769" s="16" t="s">
-        <v>869</v>
+        <v>870</v>
       </c>
       <c r="B769" t="s">
         <v>733</v>
@@ -34674,7 +34683,7 @@
     </row>
     <row r="770" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A770" s="16" t="s">
-        <v>869</v>
+        <v>870</v>
       </c>
       <c r="B770" t="s">
         <v>759</v>
@@ -34715,7 +34724,7 @@
     </row>
     <row r="771" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A771" s="16" t="s">
-        <v>869</v>
+        <v>870</v>
       </c>
       <c r="B771" t="s">
         <v>771</v>
@@ -34756,7 +34765,7 @@
     </row>
     <row r="772" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A772" s="16" t="s">
-        <v>869</v>
+        <v>870</v>
       </c>
       <c r="B772" t="s">
         <v>745</v>
@@ -34797,7 +34806,7 @@
     </row>
     <row r="773" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A773" s="16" t="s">
-        <v>869</v>
+        <v>870</v>
       </c>
       <c r="B773" t="s">
         <v>770</v>
@@ -34838,7 +34847,7 @@
     </row>
     <row r="774" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A774" s="16" t="s">
-        <v>869</v>
+        <v>870</v>
       </c>
       <c r="B774" t="s">
         <v>763</v>
@@ -34879,7 +34888,7 @@
     </row>
     <row r="775" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A775" s="16" t="s">
-        <v>869</v>
+        <v>870</v>
       </c>
       <c r="B775" t="s">
         <v>744</v>
@@ -34920,7 +34929,7 @@
     </row>
     <row r="776" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A776" s="16" t="s">
-        <v>869</v>
+        <v>870</v>
       </c>
       <c r="B776" t="s">
         <v>752</v>
@@ -34961,7 +34970,7 @@
     </row>
     <row r="777" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A777" s="16" t="s">
-        <v>869</v>
+        <v>870</v>
       </c>
       <c r="B777" t="s">
         <v>768</v>
@@ -35002,7 +35011,7 @@
     </row>
     <row r="778" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A778" s="16" t="s">
-        <v>869</v>
+        <v>870</v>
       </c>
       <c r="B778" t="s">
         <v>780</v>
@@ -35043,7 +35052,7 @@
     </row>
     <row r="779" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A779" s="16" t="s">
-        <v>869</v>
+        <v>870</v>
       </c>
       <c r="B779" t="s">
         <v>776</v>
@@ -35084,7 +35093,7 @@
     </row>
     <row r="780" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A780" s="16" t="s">
-        <v>869</v>
+        <v>870</v>
       </c>
       <c r="B780" t="s">
         <v>762</v>
@@ -35125,7 +35134,7 @@
     </row>
     <row r="781" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A781" s="16" t="s">
-        <v>869</v>
+        <v>870</v>
       </c>
       <c r="B781" t="s">
         <v>749</v>
@@ -35166,7 +35175,7 @@
     </row>
     <row r="782" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A782" s="16" t="s">
-        <v>869</v>
+        <v>870</v>
       </c>
       <c r="B782" t="s">
         <v>126</v>
@@ -35207,7 +35216,7 @@
     </row>
     <row r="783" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A783" s="16" t="s">
-        <v>869</v>
+        <v>870</v>
       </c>
       <c r="B783" t="s">
         <v>761</v>
@@ -35248,7 +35257,7 @@
     </row>
     <row r="784" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A784" s="16" t="s">
-        <v>869</v>
+        <v>870</v>
       </c>
       <c r="B784" t="s">
         <v>769</v>
@@ -35289,7 +35298,7 @@
     </row>
     <row r="785" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A785" s="16" t="s">
-        <v>869</v>
+        <v>870</v>
       </c>
       <c r="B785" t="s">
         <v>746</v>
@@ -35330,7 +35339,7 @@
     </row>
     <row r="786" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A786" s="16" t="s">
-        <v>869</v>
+        <v>870</v>
       </c>
       <c r="B786" t="s">
         <v>758</v>
@@ -35371,7 +35380,7 @@
     </row>
     <row r="787" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A787" s="16" t="s">
-        <v>869</v>
+        <v>870</v>
       </c>
       <c r="B787" t="s">
         <v>766</v>
@@ -35412,7 +35421,7 @@
     </row>
     <row r="788" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A788" s="16" t="s">
-        <v>869</v>
+        <v>870</v>
       </c>
       <c r="B788" t="s">
         <v>775</v>
@@ -35453,7 +35462,7 @@
     </row>
     <row r="789" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A789" s="16" t="s">
-        <v>869</v>
+        <v>870</v>
       </c>
       <c r="B789" t="s">
         <v>747</v>
@@ -35494,7 +35503,7 @@
     </row>
     <row r="790" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A790" s="16" t="s">
-        <v>869</v>
+        <v>870</v>
       </c>
       <c r="B790" t="s">
         <v>764</v>
@@ -35535,7 +35544,7 @@
     </row>
     <row r="791" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A791" s="16" t="s">
-        <v>869</v>
+        <v>870</v>
       </c>
       <c r="B791" t="s">
         <v>773</v>
@@ -35576,7 +35585,7 @@
     </row>
     <row r="792" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A792" s="16" t="s">
-        <v>869</v>
+        <v>870</v>
       </c>
       <c r="B792" t="s">
         <v>778</v>
@@ -35617,7 +35626,7 @@
     </row>
     <row r="793" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A793" s="16" t="s">
-        <v>869</v>
+        <v>870</v>
       </c>
       <c r="B793" t="s">
         <v>755</v>
@@ -35658,7 +35667,7 @@
     </row>
     <row r="794" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A794" s="16" t="s">
-        <v>869</v>
+        <v>870</v>
       </c>
       <c r="B794" t="s">
         <v>750</v>
@@ -35699,7 +35708,7 @@
     </row>
     <row r="795" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A795" s="16" t="s">
-        <v>869</v>
+        <v>870</v>
       </c>
       <c r="B795" t="s">
         <v>781</v>
